--- a/R Markdown/resultados/regionalizacao_acoes_2022.xlsx
+++ b/R Markdown/resultados/regionalizacao_acoes_2022.xlsx
@@ -1,21 +1,1267 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_BF4BBDDF8F79A8D366075C52F37BD2723AC9DF5B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DE54850-DE22-4EBB-8437-F2D0797F1F65}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="411">
+  <si>
+    <t>descricao_proj_ativ</t>
+  </si>
+  <si>
+    <t>ano</t>
+  </si>
+  <si>
+    <t>valor_total</t>
+  </si>
+  <si>
+    <t>valor_regionalizado</t>
+  </si>
+  <si>
+    <t>perc_regionalizado</t>
+  </si>
+  <si>
+    <t>n_subpref</t>
+  </si>
+  <si>
+    <t>Aposentadorias e Pensões</t>
+  </si>
+  <si>
+    <t>Administração da Unidade</t>
+  </si>
+  <si>
+    <t>Compensações Tarifárias do Sistema de Ônibus</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Rede Parceira - Centro de Educação Infantil (CEI)</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação em Atenção Hospitalar e de Urgência e Emergência</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação em Atenção Básica, Especialidades e de Serviços Auxiliares de Diagnóstico e Terapia</t>
+  </si>
+  <si>
+    <t>Obrigações e Contribuições Patronais RPPS Educação</t>
+  </si>
+  <si>
+    <t>Aporte do IRRF para cobertura do deficit atuarial do RPPS</t>
+  </si>
+  <si>
+    <t>Condenações Judiciais - Créditos de Natureza Alimentar</t>
+  </si>
+  <si>
+    <t>Concessão dos Serviços Divisíveis de Limpeza Urbana em Regime Público</t>
+  </si>
+  <si>
+    <t>Intervenções no Sistema de Drenagem</t>
+  </si>
+  <si>
+    <t>Serviços de Engenharia de Tráfego</t>
+  </si>
+  <si>
+    <t>Sistema Municipal de Regulação, Controle, Avaliação e Auditoria do SUS</t>
+  </si>
+  <si>
+    <t>Recomposição de Depósitos Judiciais</t>
+  </si>
+  <si>
+    <t>Obrigações e Contribuições Patronais</t>
+  </si>
+  <si>
+    <t>Alimentação Escolar</t>
+  </si>
+  <si>
+    <t>Contribuição Formação Patrimônio Servidor Público - PASEP</t>
+  </si>
+  <si>
+    <t>Intervenção, Urbanização e Melhoria de Bairros - Plano de Obras das Subprefeituras</t>
+  </si>
+  <si>
+    <t>Obrigações e Contribuições Patronais RPPS Saúde</t>
+  </si>
+  <si>
+    <t>Condenações Judiciais - Outras Espécies</t>
+  </si>
+  <si>
+    <t>Execução do Programa de Mananciais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação em Atenção Básica, Especialidades e Vigilância da Assistência Farmacêutica</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Sistemas de Informação e Comunicação</t>
+  </si>
+  <si>
+    <t>Construção de Unidades Habitacionais</t>
+  </si>
+  <si>
+    <t>Contraprestação de Parceria Público-Privada (PPP) - Iluminação Pública</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População em Situação de Rua</t>
+  </si>
+  <si>
+    <t>Aquisição de Materiais, Equipamentos e Serviços de Informação e Comunicação</t>
+  </si>
+  <si>
+    <t>Pavimentação e Recapeamento de Vias</t>
+  </si>
+  <si>
+    <t>Intervenções no Sistema Viário</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Sistema Municipal de Transporte Coletivo</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para Crianças e Adolescentes</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Ensino Fundamental (EMEF)</t>
+  </si>
+  <si>
+    <t>Manutenção de Sistemas de Drenagem</t>
+  </si>
+  <si>
+    <t>Promoção de Campanhas e Eventos de Interesse do Município</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Centros Educacionais Unificados (CEU)</t>
+  </si>
+  <si>
+    <t>Fornecimento de Uniformes e Material Escolar-Educação Infantil</t>
+  </si>
+  <si>
+    <t>Serviço da Dívida Pública Interna - Refinanciamento</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Centros Educacionais Unificados (CEU)</t>
+  </si>
+  <si>
+    <t>Administração de Material  Médico Hospitalar e Ambulatorial em Atenção Básica, Especialidades e Vigilância</t>
+  </si>
+  <si>
+    <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Educação Infantil</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Áreas Verdes e Vegetação Arbórea</t>
+  </si>
+  <si>
+    <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Ensino Fundamental</t>
+  </si>
+  <si>
+    <t>Serviços de Limpeza Urbana - Varrição e Lavagem de Áreas Públicas</t>
+  </si>
+  <si>
+    <t>Fornecimento de Uniformes e Material Escolar-Ensino Fundamental</t>
+  </si>
+  <si>
+    <t>Recuperação e Reforço de Obras de Arte Especiais - OAE</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Proteção Social Especial a Crianças, Adolescentes e Jovens em Risco Social</t>
+  </si>
+  <si>
+    <t>Administração de Material Médico Hospitalar em Atenção Hospitalar, de Urgência e Emergência</t>
+  </si>
+  <si>
+    <t>Transporte Escolar - Educação Infantil</t>
+  </si>
+  <si>
+    <t>Serviço da Dívida Pública Interna</t>
+  </si>
+  <si>
+    <t>Publicidade Institucional</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Terminais de Ônibus</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Escolas Municipais de Educação Infantil (EMEI)</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Parques Urbanos e Lineares</t>
+  </si>
+  <si>
+    <t>Ações e Materiais de Apoio Didático-Pedagógico Educacional</t>
+  </si>
+  <si>
+    <t>Programa Nacional de Alimentação Escolar - PNAE/ FNDE</t>
+  </si>
+  <si>
+    <t>Sistema de Remuneração Variável</t>
+  </si>
+  <si>
+    <t>Transporte Escolar - Ensino Fundamental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avança Saúde SP - Ampliação, Reforma e Requalificação de Equipamentos de Saúde_x000D__x000D_
+</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação no Serviço de Guias e Sarjetas (Vias e Logradouros)</t>
+  </si>
+  <si>
+    <t>Transporte de Pessoas com Deficiência ou Mobilidade Reduzida - ATENDE</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Centros de Educação Infantil (CEI)</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Controle e Fiscalização de Tráfego</t>
+  </si>
+  <si>
+    <t>Condenações Judiciais - Créditos de Pequeno Valor</t>
+  </si>
+  <si>
+    <t>Obras e Serviços nas Áreas de Riscos Geológicos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Intergeracionais de Convivência e Fortalecimento de Vínculos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Esportivos</t>
+  </si>
+  <si>
+    <t>Encargos pela Manutenção do Fundo de Depósitos Judiciais nas quais o Município é Parte</t>
+  </si>
+  <si>
+    <t>Projetos e Ações de Apoio Habitacional</t>
+  </si>
+  <si>
+    <t>Precatórios Pagos com Rendimentos dos Depósitos do Regime Especial</t>
+  </si>
+  <si>
+    <t>Leve-Leite</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Corredores de Ônibus</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Sinalização do Sistema Viário</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Vigilância em Saúde</t>
+  </si>
+  <si>
+    <t>Operação Tapa Buraco</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Central de Atendimento Telefônico - 156</t>
+  </si>
+  <si>
+    <t>Programação de Atividades Culturais</t>
+  </si>
+  <si>
+    <t>Manutenção de Vias e Áreas Públicas</t>
+  </si>
+  <si>
+    <t>Ações de Difusão Cultural do Theatro Municipal - Grupos Artísticos, Técnicos e Administrativos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Serviço de Atendimento Médico de Urgência (SAMU)</t>
+  </si>
+  <si>
+    <t>Remuneração dos Profissionais do Magistério - Ensino Fundamental</t>
+  </si>
+  <si>
+    <t>Ações de Apoio à Educação Especial</t>
+  </si>
+  <si>
+    <t>Programa de Incentivo Fiscal Relacionado à Arena Corinthians</t>
+  </si>
+  <si>
+    <t>Servidores Comissionados em Outras Entidades</t>
+  </si>
+  <si>
+    <t>Serviço de Moradia Transitória</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Proteção Social Básica às Famílias</t>
+  </si>
+  <si>
+    <t>Urbanização de Favelas</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos Esportivos</t>
+  </si>
+  <si>
+    <t>Incentivo à Prática de Esportes</t>
+  </si>
+  <si>
+    <t>Realização de Eventos de Esporte, Lazer e Recreação</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Atenção Hospitalar da Assistência Farmacêutica</t>
+  </si>
+  <si>
+    <t>Remuneração dos Profissionais do Magistério - Centro de Educação Infantil (CEI)</t>
+  </si>
+  <si>
+    <t>Capacitação, Formação e Aperfeiçoamento dos Trabalhadores</t>
+  </si>
+  <si>
+    <t>Ações Integradas de Segurança Pública - Operação Delegada - Convênio SSP SO</t>
+  </si>
+  <si>
+    <t>Remuneração dos Profissionais do Magistério - Escola Municipal de Educação Infantil (EMEI)</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação Semafórica</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à Pessoa com Deficiência</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População Idosa</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos da Assistência Social</t>
+  </si>
+  <si>
+    <t>Administração da Carteira Imobiliária</t>
+  </si>
+  <si>
+    <t>Construção de Centros de Educação Infantil - CEI</t>
+  </si>
+  <si>
+    <t>Ações Permanentes de Promoção dos Direitos da Criança e do Adolescente</t>
+  </si>
+  <si>
+    <t>Serviço da Dívida Pública Externa</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Posto do Corpo de Bombeiros</t>
+  </si>
+  <si>
+    <t>Realização de Eventos Culturais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Guarda Civil Metropolitana</t>
+  </si>
+  <si>
+    <t>Administração dos Conselhos Tutelares</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Educação em Direitos Humanos e Promoção do Direito à Cidade</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para a Pessoa Idosa</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Centros Educacionais Unificados (CEU)</t>
+  </si>
+  <si>
+    <t>Modernização Semafórica</t>
+  </si>
+  <si>
+    <t>Aposentadoria Complementar aos Servidores da São Paulo Transporte S/A</t>
+  </si>
+  <si>
+    <t>Regularização Fundiária</t>
+  </si>
+  <si>
+    <t>Intervenções em Próprios Municipais</t>
+  </si>
+  <si>
+    <t>Coleta, Transporte, Tratamento e Dest. Final Resíduos Sólidos Inertes</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Policiamento de Trânsito</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Clube da Comunidade (CDC)</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Prédios Administrativos</t>
+  </si>
+  <si>
+    <t>Programa Municipal de Apoio a Projetos Culturais (PRO-MAC)</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para a População em Situação de Rua</t>
+  </si>
+  <si>
+    <t>Ações de Fiscalização do Comércio Ilegal</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção da Agência São Paulo de Desenvolvimento - ADESAMPA</t>
+  </si>
+  <si>
+    <t>Políticas de Audiovisual</t>
+  </si>
+  <si>
+    <t>Eventos Educacionais, Culturais e Esportivos nos Centros Educacionais Unificados</t>
+  </si>
+  <si>
+    <t>Aporte para Garantia de PPP's e Projetos de Infraestrutura</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Parques Urbanos e Lineares</t>
+  </si>
+  <si>
+    <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - Educação Infantil</t>
+  </si>
+  <si>
+    <t>Construção de Ciclovias, Ciclofaixas e Ciclorrotas</t>
+  </si>
+  <si>
+    <t>Contraprestação de Parceria Público-Privada (PPP) - Terminais Urbanos</t>
+  </si>
+  <si>
+    <t>Implantação de Corredores de Ônibus Novos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação em Serviços de Saúde Animal</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Áreas Públicas</t>
+  </si>
+  <si>
+    <t>Serviços de Desfazimento e Demolição de Construções Irregulares em Áreas de Proteção Ambiental</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Descomplica SP</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Centros Culturais e Teatros</t>
+  </si>
+  <si>
+    <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Centro Educacional Unificado (CEU)</t>
+  </si>
+  <si>
+    <t>Fomento à Cooperação, Parcerias e Captação de Investimentos Internacionais</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de Sistemas de Informação e Comunicação</t>
+  </si>
+  <si>
+    <t>Programa de Atração a Filmagens - Cash Rebate</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades de Conservação</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos de Atenção Básica e Especialidades</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Mulheres</t>
+  </si>
+  <si>
+    <t>Lei de Fomento ao Teatro</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Proteção Jurídico Social</t>
+  </si>
+  <si>
+    <t>Gratificação de Municipalização - Saúde - Lei 13.510/03</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Bibliotecas Públicas</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação da Avenida Santo Amaro</t>
+  </si>
+  <si>
+    <t>Fomento à Cultura da Periferia de São Paulo</t>
+  </si>
+  <si>
+    <t>Encargos Referentes a Arrecadação</t>
+  </si>
+  <si>
+    <t>Ações de Educação Integral</t>
+  </si>
+  <si>
+    <t>Construção e Implantação do Descomplica SP</t>
+  </si>
+  <si>
+    <t>Circuito Cultural de São Paulo</t>
+  </si>
+  <si>
+    <t>Ações de Desestatização</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Centros Municipais de Educação Infantil(CEMEI)</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Sistemas de Monitoramento e Alerta de Enchentes</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção dos Centros de Apoio ao Trabalho e Empreendedorismo</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação do Autódromo de Interlagos</t>
+  </si>
+  <si>
+    <t>Inserção das Famílias no Cadastro Único</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Escolas Municipais de Educação Infantil (EMEI)</t>
+  </si>
+  <si>
+    <t>Ações de formação das Escolas de Música e Dança do Theatro Municipal e da Praça das Artes</t>
+  </si>
+  <si>
+    <t>Programação da Virada Esportiva</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção de Unidade da Fundação Paulistana - FPETC</t>
+  </si>
+  <si>
+    <t>Alfabetização na Idade Certa</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos do Departamento dos Museus Municipais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Rede Parceira - Alfabetização de Jovens e Adultos</t>
+  </si>
+  <si>
+    <t>Capacitação, Formação e Aperfeiçoamento de Servidores</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Telecentros</t>
+  </si>
+  <si>
+    <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - Ensino Fundamental</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Casas de Cultura</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção da São Paulo Investimentos e Negócios</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Praças, Canteiros Centrais e Remanescentes</t>
+  </si>
+  <si>
+    <t>Preservação do Patrimônio Histórico, Artístico, Cultural e Arqueológico</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Parques Urbanos e Lineares</t>
+  </si>
+  <si>
+    <t>Bolsa-Trabalho</t>
+  </si>
+  <si>
+    <t>Execução do Programa para a Valorização de Iniciativas Culturais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Programa Melhor em Casa</t>
+  </si>
+  <si>
+    <t>Manutenção de Unidades Habitacionais</t>
+  </si>
+  <si>
+    <t>Câmara Municipal - Comunicação</t>
+  </si>
+  <si>
+    <t>Lei de Fomento à Dança</t>
+  </si>
+  <si>
+    <t>Ações de Difusão Cultural do Theatro Municipal - Patrimônio</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Fundamental e Médio (EMEFM)</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Centro Cultural São Paulo</t>
+  </si>
+  <si>
+    <t>Realização de Projetos Culturais</t>
+  </si>
+  <si>
+    <t>Cooperação Técnica Internacional</t>
+  </si>
+  <si>
+    <t>Projetos de Fomento ao Turismo</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Serviços de DST / AIDS</t>
+  </si>
+  <si>
+    <t>Programação da Virada Cultural</t>
+  </si>
+  <si>
+    <t>Programa Jovem Monitor Cultural</t>
+  </si>
+  <si>
+    <t>Inspeção de Obras de Artes Especiais - OAE</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Pólos Regionais de Esporte</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Biblioteca Mario de Andrade</t>
+  </si>
+  <si>
+    <t>Compensações Ambientais</t>
+  </si>
+  <si>
+    <t>Compensação Financeira - Outros Fundos de Previdência</t>
+  </si>
+  <si>
+    <t>Escola Municipal de Educação Artística - EMIA</t>
+  </si>
+  <si>
+    <t>Prêmio Zé Renato</t>
+  </si>
+  <si>
+    <t>Subvenção e Contribuições a Entidades Culturais</t>
+  </si>
+  <si>
+    <t>Programação de Atividades Culturais de Casas de Cultura</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Escola Municipal de Ensino Fundamental (EMEF)</t>
+  </si>
+  <si>
+    <t>Ações para Promoção da Sustentabilidade Previdenciária</t>
+  </si>
+  <si>
+    <t>Intervenções na Área de Mobilidade Urbana</t>
+  </si>
+  <si>
+    <t>Transporte Escolar - Educação Especial</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Viveiros</t>
+  </si>
+  <si>
+    <t>Fomento às Linguagens Artísticas</t>
+  </si>
+  <si>
+    <t>Ações Permanentes de Promoção dos Direitos da População Idosa</t>
+  </si>
+  <si>
+    <t>Ações de Difusão Cultural do Theatro Municipal - Programação Artística</t>
+  </si>
+  <si>
+    <t>Sistema de Avaliação Escolar dos Alunos da Rede Municipal de Ensino</t>
+  </si>
+  <si>
+    <t>Remuneração dos Profissionais do Magistério - Centro Municipal de Educação Infantil( CEMEI)</t>
+  </si>
+  <si>
+    <t>Implantação do Memorial dos Aflitos</t>
+  </si>
+  <si>
+    <t>Programação de Atividades Culturais de Centros Culturais e Teatros</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Rede Parceira - Educação Especial</t>
+  </si>
+  <si>
+    <t>Construção da Fábrica do Samba</t>
+  </si>
+  <si>
+    <t>Suporte e Manutenção da Coordenação de Imprensa</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Centro Olímpicos</t>
+  </si>
+  <si>
+    <t>Qualificação Profissional e Empreendedora</t>
+  </si>
+  <si>
+    <t>Programa de Garantia de Renda Familiar Mínima</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Edificação da Câmara Municipal de São Paulo</t>
+  </si>
+  <si>
+    <t>Recuperação de Fachadas Históricas na Área Central</t>
+  </si>
+  <si>
+    <t>Administração do Edifício Matarazzo</t>
+  </si>
+  <si>
+    <t>Parceria Público Privada - Habitação</t>
+  </si>
+  <si>
+    <t>Programa Nacional de Apoio à Gestão Adm. e Fiscal - PNAFM</t>
+  </si>
+  <si>
+    <t>Plantio de Árvores</t>
+  </si>
+  <si>
+    <t>Acessibilidade, Ampliação, Reforma e Requalificação de Terminais de Ônibus</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Culturais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Casa da Mulher Brasileira</t>
+  </si>
+  <si>
+    <t>Ações de Difusão Cultural do Theatro Municipal - Administrativos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Equipamentos Públicos Voltados ao Atendimento da População LGBTI</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades Educacionais - Centro Integrado de Jovens e Adultos (CIEJA)</t>
+  </si>
+  <si>
+    <t>Fomento às Cadeias Produtivas, Vocações Produtivas e Projetos Locais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Serviços de Atendimento e Manejo da Fauna Silvestre</t>
+  </si>
+  <si>
+    <t>Servidores Comissionados no Hospital Serv. Públco Municipal - HSPM</t>
+  </si>
+  <si>
+    <t>Construção de Corredores de Ônibus</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para a População LGBTI+</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Juventude</t>
+  </si>
+  <si>
+    <t>Políticas de Promoção Cultural nas Bibliotecas Públicas</t>
+  </si>
+  <si>
+    <t>Políticas de promoção cultural</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos Culturais</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Ciclovias, Ciclofaixas e Ciclorrotas</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades Educacionais - Educação Indígena</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Centros de Educação Infantil (CEI)</t>
+  </si>
+  <si>
+    <t>Oficina nos Equipamentos Culturais</t>
+  </si>
+  <si>
+    <t>Construção de Escolas Municipais de Educação Infantil (EMEI)</t>
+  </si>
+  <si>
+    <t>Despesas Administrativas para Execução de Ações Judiciais - Processamento de Feitos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Bilíngue para Surdos (EMEBS)</t>
+  </si>
+  <si>
+    <t>Edição e Publicação do Diário Oficial da Cidade de São Paulo</t>
+  </si>
+  <si>
+    <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - CEU</t>
+  </si>
+  <si>
+    <t>Ações de Cooperação para o Desenvolvimento Sustentável</t>
+  </si>
+  <si>
+    <t>Projetos para Inclusão da Pessoa com Deficiência</t>
+  </si>
+  <si>
+    <t>Auxílio Funeral</t>
+  </si>
+  <si>
+    <t>PROCONECTA - Promoção da Conectividade e Inclusão Digital</t>
+  </si>
+  <si>
+    <t>Execução do Programa Museu de Arte de Rua - MAR</t>
+  </si>
+  <si>
+    <t>Fomento ao Circo/Edital Xamego</t>
+  </si>
+  <si>
+    <t>Programação de Atividades Culturais do Centro Cultural São Paulo</t>
+  </si>
+  <si>
+    <t>Rádios Comunitárias - Lei nº 16.572/2016</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações Para Criança e Adolescente</t>
+  </si>
+  <si>
+    <t>Fomento à Música</t>
+  </si>
+  <si>
+    <t>Estudos, Planos e Projetos Ambientais</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Mulheres</t>
+  </si>
+  <si>
+    <t>Apoio à Cultura Negra</t>
+  </si>
+  <si>
+    <t>Obras de Combate a Enchentes e Alagamentos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Rede de Iluminação Pública</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Centro de Referência de Segurança Alimentar e Nutricional</t>
+  </si>
+  <si>
+    <t>Programa Piá</t>
+  </si>
+  <si>
+    <t>Ações de Educação de Trânsito</t>
+  </si>
+  <si>
+    <t>Programa Vocacional</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Arquivo Histórico Municipal</t>
+  </si>
+  <si>
+    <t>Programação de Atividades Culturais do Departamento dos Museus Municipais</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção das Centrais de Triagem - Coleta Seletiva</t>
+  </si>
+  <si>
+    <t>Ações Municipais de Abastecimento</t>
+  </si>
+  <si>
+    <t>Educação Ambiental</t>
+  </si>
+  <si>
+    <t>Programação de Atividades Culturais nas Bibliotecas Públicas</t>
+  </si>
+  <si>
+    <t>Manutenção de Ciclovias, Ciclofaixas e Ciclorrotas</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento da População de Rua</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Defesa Civil</t>
+  </si>
+  <si>
+    <t>Mês do Hip Hop</t>
+  </si>
+  <si>
+    <t>Política Municipal de Desenvolvimento Econômico</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Planetários Municipais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Imigrantes</t>
+  </si>
+  <si>
+    <t>Locação Social</t>
+  </si>
+  <si>
+    <t>Programa Mãos e Mentes Paulistanas</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Públicos Voltados à Promoção da Igualdade Racial</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Conselhos e Espaços Participativos Municipais</t>
+  </si>
+  <si>
+    <t>Manutenção da Ouvidoria de Direitos Humanos</t>
+  </si>
+  <si>
+    <t>Fiscalização, Monitoramento e Controle Ambiental</t>
+  </si>
+  <si>
+    <t>Execução de Serviços Médicos de Tratamento de Radioterapia</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação nas Áreas de Parada e Plataforma de Embarque de Faixa Exclusiva de Ônibus</t>
+  </si>
+  <si>
+    <t>Reembolso ao Serviço Funerário</t>
+  </si>
+  <si>
+    <t>Melhoria de Bairros no âmbito da Subprefeitura da Capela do Socorro.</t>
+  </si>
+  <si>
+    <t>Bloqueios Judiciais</t>
+  </si>
+  <si>
+    <t>Centro Municipal para Pessoas com Transtorno do Espectro Autista</t>
+  </si>
+  <si>
+    <t>Apoio e Suporte Técnico para o Desenvolvimento de Estudos e Projetos Urbanos</t>
+  </si>
+  <si>
+    <t>Ações e Atividades Culturais da Biblioteca Mario de Andrade</t>
+  </si>
+  <si>
+    <t>Difusão, Fomento e Pesquisas Aplicadas à Gestão de Tecnologia, Inovação e Atendimento ao Cidadão</t>
+  </si>
+  <si>
+    <t>Projeto de Intervenção Urbana - PIU</t>
+  </si>
+  <si>
+    <t>Manutenção de Prédios Administrativos</t>
+  </si>
+  <si>
+    <t>Restituição de Amortização Extraordinária e Liquidação Antecipada</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Centros de Estudos de Línguas Paulistano - CELP</t>
+  </si>
+  <si>
+    <t>Programa de Articulação Criativa</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Equipamentos Públicos Voltados para Pessoa Idosa</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de Estudos, Projetos  e Instrumentos de Políticas Urbanas</t>
+  </si>
+  <si>
+    <t>Equipes de Alto Desempenho com Representatividade em Competições Locais, Regionais, Nacionais e Mundiais</t>
+  </si>
+  <si>
+    <t>Programa de Iniciação Artística para a Primeira Infância - PIAPI</t>
+  </si>
+  <si>
+    <t>Manutenção de Modalidades Desportivas do Centro Olímpico de Treinamento e Pesquisa (COTP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operação e Manutenção do Portal da PMSP_x000D__x000D_
+</t>
+  </si>
+  <si>
+    <t>Vivência Prática de Gestão de Documentos</t>
+  </si>
+  <si>
+    <t>Difusão, Fomento e Pesquisas Aplicadas para a Gestão Participativa e Desenvolvimento Urbano</t>
+  </si>
+  <si>
+    <t>Fomento às Comunidades do Samba</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Imigrantes e Promoção ao Trabalho Decente</t>
+  </si>
+  <si>
+    <t>Atualização do Currículo da Rede Municipal de Ensino</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção do VAI TEC</t>
+  </si>
+  <si>
+    <t>Ações e Atividades Culturais do Departamento do Patrimônio Histórico</t>
+  </si>
+  <si>
+    <t>Construção de Galeria, bem como Boca de Lobo para Captação de Água Pluvial, na Viela João Carlos Pereira, Altura no Número 13</t>
+  </si>
+  <si>
+    <t>Prospecção de Problemas Públicos e Ideação de Alternativas para Inovação</t>
+  </si>
+  <si>
+    <t>FUMCAD - Multas Revertidas ao Fundo</t>
+  </si>
+  <si>
+    <t>Tarifa de Arrecadação de Multas</t>
+  </si>
+  <si>
+    <t>"Comemoração do ""Dia Municipal da Cultura Evangélica"" - 09 de Julho - Lei nº 14.232 de 07 de Novembro de 2006"</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção da Infraestrutura Turística</t>
+  </si>
+  <si>
+    <t>Manutenção das Instalações da Guarda Civil Metropolitana</t>
+  </si>
+  <si>
+    <t>Programa Aldeias</t>
+  </si>
+  <si>
+    <t>Plano Municipal do Livro, Leitura, Literatura e Biblioteca (PMLLLB)</t>
+  </si>
+  <si>
+    <t>Implantação e Construção de Ecopontos</t>
+  </si>
+  <si>
+    <t>Programação de Atividades e Eventos da Cultura Reggae</t>
+  </si>
+  <si>
+    <t>Acompanhamento das Aprendizagens e Permanência Escolar</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Unidades de Conservação</t>
+  </si>
+  <si>
+    <t>Fomento e Difusão do Forró</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades Educacionais - Centro Municipal de Capacitação e Treinamento (CMCT)</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Centro Público de Economia Solidária e Direitos Humanos</t>
+  </si>
+  <si>
+    <t>Publicação de Editais e Outras Publicações Legais e de Interesse do Município</t>
+  </si>
+  <si>
+    <t>Implantação de Estrutura Turística no Triângulo Histórico</t>
+  </si>
+  <si>
+    <t>Promoção à Saúde do Servidor Municipal</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Equipamentos de Atenção Básica e Especialidades</t>
+  </si>
+  <si>
+    <t>Centro de Referência da Dança</t>
+  </si>
+  <si>
+    <t>Bolsa Atleta</t>
+  </si>
+  <si>
+    <t>Centro de Memória do Circo</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Patrulha Agroecológica Mecanizada</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Mercado Municipal</t>
+  </si>
+  <si>
+    <t>Pesquisa de Satisfação do Cidadão em Relação aos Serviços, Políticas e Programas</t>
+  </si>
+  <si>
+    <t>Reforma e Acessibilidade em Passeios Públicos</t>
+  </si>
+  <si>
+    <t>Administração do Autódromo de Interlagos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Espaços Lúdicos e Educativos</t>
+  </si>
+  <si>
+    <t>Território Hip Hop (Vocacional Hip Hop)</t>
+  </si>
+  <si>
+    <t>Gestão do Patrimônio Imobiliário Municipal</t>
+  </si>
+  <si>
+    <t>Fomento e Apoio ao Cooperativismo</t>
+  </si>
+  <si>
+    <t>Revitalização e Manutenção - Subprefeitura de Capela do Socorro</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos da Assistência Social</t>
+  </si>
+  <si>
+    <t>Implantação de Pontos e Pontões de Cultura - Cultura Viva</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos de Saúde Animal</t>
+  </si>
+  <si>
+    <t>Acordos Judiciais ou Administrativos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Serviço de Moto Verificação</t>
+  </si>
+  <si>
+    <t>Projetos Sociais Diversos</t>
+  </si>
+  <si>
+    <t>Expansão e Aperfeiçoamento das Atividades do TCM</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Central de Interpretação de Libras, Intérpretes e Guias-Intérpretes</t>
+  </si>
+  <si>
+    <t>Construção de Terminais de Ônibus</t>
+  </si>
+  <si>
+    <t>Escola do Parlamento</t>
+  </si>
+  <si>
+    <t>Ações de Audiovisual</t>
+  </si>
+  <si>
+    <t>Implantação da Casa de Cultura Cidade Ademar</t>
+  </si>
+  <si>
+    <t>Expansão e Aperfeiçoamento das Atividades da CMSP</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação das Instalações para a Guarda Civil Metropolitana</t>
+  </si>
+  <si>
+    <t>PMLLLB - Festas Literárias</t>
+  </si>
+  <si>
+    <t>Reforma da Escadaria na Viela Inominada, Localizada na Rua Rua José Ferreira Dantas, Nº 11, Jardim Boa Vista.</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Unidades Habitacionais</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Unidade de Vigilância em Saúde</t>
+  </si>
+  <si>
+    <t>Construção de Escolas Municipais de Ensino Fundamental (EMEF)</t>
+  </si>
+  <si>
+    <t>Execução de Projetos Visando o Combate das Desigualdades Raciais na Saúde</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação no Serviço de Guinchamento</t>
+  </si>
+  <si>
+    <t>Reforma da Quadra da Praça Gilberto Reis Possani, Parque São Rafael</t>
+  </si>
+  <si>
+    <t>Ações do Programa Agentes de Governo Aberto</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos do Patrimônio Histórico</t>
+  </si>
+  <si>
+    <t>Promoção da Transparência, do Acesso à Informação e do Controle Social</t>
+  </si>
+  <si>
+    <t>Incentivo à Economia Popular e Solidária</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação das Praças Digitais</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Edificação do Tribunal de Contas do Município</t>
+  </si>
+  <si>
+    <t>Restituição de Receitas Descontinuadas</t>
+  </si>
+  <si>
+    <t>Conservação e Valorização de Acervos da Biblioteca Mário de Andrade</t>
+  </si>
+  <si>
+    <t>Manutenção, Programas e Suporte da Coordenadoria de Defesa do Consumidor</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Povos Indígenas</t>
+  </si>
+  <si>
+    <t>Implementação do Selo Municipal de Direitos Humanos e Diversidade</t>
+  </si>
+  <si>
+    <t>Programa de Promoção da Imagem de São Paulo no Exterior</t>
+  </si>
+  <si>
+    <t>Programa de Gestão Cultural Comunitária de Espaços</t>
+  </si>
+  <si>
+    <t>Outras Dívidas</t>
+  </si>
+  <si>
+    <t>Benefícios Eventuais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Supervisão Geral das Juntas do Serviço Militar</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Pessoas Desaparecidas</t>
+  </si>
+  <si>
+    <t>Conservação e Valorização de Acervos do Departamento dos Museus Municipais</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Unidades de Conservação</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Promoção da Igualdade Racial</t>
+  </si>
+  <si>
+    <t>Ações e Atividades Culturais do Arquivo Histórico Municipal</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Pessoa Idosa</t>
+  </si>
+  <si>
+    <t>Implantação de Transporte Público Hidroviário</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Herbário Municipal</t>
+  </si>
+  <si>
+    <t>Comunicação e Orientação na Valorização e Cuidado na Primeira Infância</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para a Promoção do Direito à Memória e à Verdade</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da UniCEU</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Edificação da Câmara Municipal de São Paulo</t>
+  </si>
+  <si>
+    <t>Apoio e Suporte Técnico para o Desenvolvimento de Ações Pertinentes à Fiscalização e Escrituração de Certificados de Potencial Adicional de Construção - CEPACs</t>
+  </si>
+  <si>
+    <t>Apoio às Ações Municipais de Turismo</t>
+  </si>
+  <si>
+    <t>Aquisição e Construção de Prédios Administrativos</t>
+  </si>
+  <si>
+    <t>Ações Socioculturais em Espaços Cemiteriais</t>
+  </si>
+  <si>
+    <t>Ações de Pronto Atendimento Socioassistencial</t>
+  </si>
+  <si>
+    <t>Ações de Vigilância Socioassistencial</t>
+  </si>
+  <si>
+    <t>Comercialização de Artigos do Serviço Funerário</t>
+  </si>
+  <si>
+    <t>Educação Permanente dos Trabalhadores do SUAS</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Cemitério</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Crematório</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Velório</t>
+  </si>
+  <si>
+    <t>Transportes Fúnebres</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +1309,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +1361,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +1395,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +1430,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,53 +1606,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F406"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="101" customWidth="1"/>
+    <col min="2" max="2" width="47.42578125" customWidth="1"/>
+    <col min="3" max="3" width="59.85546875" customWidth="1"/>
+    <col min="4" max="4" width="64.85546875" customWidth="1"/>
+    <col min="5" max="5" width="55.140625" customWidth="1"/>
+    <col min="6" max="6" width="81.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>descricao_proj_ativ</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>valor_total</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>valor_regionalizado</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>perc_regionalizado</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>n_subpref</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Aposentadorias e Pensões</t>
-        </is>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
       </c>
       <c r="B2">
         <v>2022</v>
       </c>
       <c r="C2">
-        <v>11856006499.3</v>
+        <v>11856006499.299999</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -408,39 +1658,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Administração da Unidade</t>
-        </is>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
       </c>
       <c r="B3">
         <v>2022</v>
       </c>
       <c r="C3">
-        <v>6734920362.99</v>
+        <v>6734920362.9899998</v>
       </c>
       <c r="D3">
         <v>1130523048.48</v>
       </c>
       <c r="E3">
-        <v>0.1678598984915241</v>
+        <v>0.16785989849152411</v>
       </c>
       <c r="F3">
         <v>32</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Compensações Tarifárias do Sistema de Ônibus</t>
-        </is>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
       </c>
       <c r="B4">
         <v>2022</v>
       </c>
       <c r="C4">
-        <v>5051601002.26</v>
+        <v>5051601002.2600002</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -452,20 +1698,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Rede Parceira - Centro de Educação Infantil (CEI)</t>
-        </is>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
       </c>
       <c r="B5">
         <v>2022</v>
       </c>
       <c r="C5">
-        <v>4552083949.23</v>
+        <v>4552083949.2299995</v>
       </c>
       <c r="D5">
-        <v>4552083949.23</v>
+        <v>4552083949.2299995</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -474,39 +1718,35 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação em Atenção Hospitalar e de Urgência e Emergência</t>
-        </is>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
       </c>
       <c r="B6">
         <v>2022</v>
       </c>
       <c r="C6">
-        <v>4211981361.95</v>
+        <v>4211981361.9499998</v>
       </c>
       <c r="D6">
-        <v>105413462.29</v>
+        <v>105413462.29000001</v>
       </c>
       <c r="E6">
-        <v>0.02502704861001504</v>
+        <v>2.5027048610015042E-2</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação em Atenção Básica, Especialidades e de Serviços Auxiliares de Diagnóstico e Terapia</t>
-        </is>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
       </c>
       <c r="B7">
         <v>2022</v>
       </c>
       <c r="C7">
-        <v>3417002966.68</v>
+        <v>3417002966.6799998</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -518,17 +1758,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Obrigações e Contribuições Patronais RPPS Educação</t>
-        </is>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
       </c>
       <c r="B8">
         <v>2022</v>
       </c>
       <c r="C8">
-        <v>2669715913.16</v>
+        <v>2669715913.1599998</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -540,11 +1778,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Aporte do IRRF para cobertura do deficit atuarial do RPPS</t>
-        </is>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
       </c>
       <c r="B9">
         <v>2022</v>
@@ -562,17 +1798,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Condenações Judiciais - Créditos de Natureza Alimentar</t>
-        </is>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>14</v>
       </c>
       <c r="B10">
         <v>2022</v>
       </c>
       <c r="C10">
-        <v>2400181978.94</v>
+        <v>2400181978.9400001</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -584,11 +1818,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Concessão dos Serviços Divisíveis de Limpeza Urbana em Regime Público</t>
-        </is>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>15</v>
       </c>
       <c r="B11">
         <v>2022</v>
@@ -606,39 +1838,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Intervenções no Sistema de Drenagem</t>
-        </is>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
       </c>
       <c r="B12">
         <v>2022</v>
       </c>
       <c r="C12">
-        <v>1351707482.9</v>
+        <v>1351707482.9000001</v>
       </c>
       <c r="D12">
         <v>1133468535.73</v>
       </c>
       <c r="E12">
-        <v>0.8385457283244577</v>
+        <v>0.83854572832445773</v>
       </c>
       <c r="F12">
         <v>28</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Serviços de Engenharia de Tráfego</t>
-        </is>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
       </c>
       <c r="B13">
         <v>2022</v>
       </c>
       <c r="C13">
-        <v>1120533067.62</v>
+        <v>1120533067.6199999</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -650,17 +1878,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sistema Municipal de Regulação, Controle, Avaliação e Auditoria do SUS</t>
-        </is>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>18</v>
       </c>
       <c r="B14">
         <v>2022</v>
       </c>
       <c r="C14">
-        <v>1021947869.32</v>
+        <v>1021947869.3200001</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -672,17 +1898,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Recomposição de Depósitos Judiciais</t>
-        </is>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
       </c>
       <c r="B15">
         <v>2022</v>
       </c>
       <c r="C15">
-        <v>1008595895.68</v>
+        <v>1008595895.6799999</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -694,17 +1918,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Obrigações e Contribuições Patronais</t>
-        </is>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
       </c>
       <c r="B16">
         <v>2022</v>
       </c>
       <c r="C16">
-        <v>734754911.72</v>
+        <v>734754911.72000003</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -716,17 +1938,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alimentação Escolar</t>
-        </is>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>21</v>
       </c>
       <c r="B17">
         <v>2022</v>
       </c>
       <c r="C17">
-        <v>728989572.22</v>
+        <v>728989572.22000003</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -738,17 +1958,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Contribuição Formação Patrimônio Servidor Público - PASEP</t>
-        </is>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>22</v>
       </c>
       <c r="B18">
         <v>2022</v>
       </c>
       <c r="C18">
-        <v>720036338.9299999</v>
+        <v>720036338.92999995</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -760,20 +1978,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Intervenção, Urbanização e Melhoria de Bairros - Plano de Obras das Subprefeituras</t>
-        </is>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>23</v>
       </c>
       <c r="B19">
         <v>2022</v>
       </c>
       <c r="C19">
-        <v>615490386.89</v>
+        <v>615490386.88999999</v>
       </c>
       <c r="D19">
-        <v>614981066.28</v>
+        <v>614981066.27999997</v>
       </c>
       <c r="E19">
         <v>0.9991724962390176</v>
@@ -782,17 +1998,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Obrigações e Contribuições Patronais RPPS Saúde</t>
-        </is>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>24</v>
       </c>
       <c r="B20">
         <v>2022</v>
       </c>
       <c r="C20">
-        <v>585764415.36</v>
+        <v>585764415.36000001</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -804,11 +2018,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Condenações Judiciais - Outras Espécies</t>
-        </is>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>25</v>
       </c>
       <c r="B21">
         <v>2022</v>
@@ -826,20 +2038,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Execução do Programa de Mananciais</t>
-        </is>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>26</v>
       </c>
       <c r="B22">
         <v>2022</v>
       </c>
       <c r="C22">
-        <v>561202228.1</v>
+        <v>561202228.10000002</v>
       </c>
       <c r="D22">
-        <v>96237769.84999999</v>
+        <v>96237769.849999994</v>
       </c>
       <c r="E22">
         <v>0.1714850102712912</v>
@@ -848,17 +2058,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação em Atenção Básica, Especialidades e Vigilância da Assistência Farmacêutica</t>
-        </is>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>27</v>
       </c>
       <c r="B23">
         <v>2022</v>
       </c>
       <c r="C23">
-        <v>535612154.33</v>
+        <v>535612154.32999998</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -870,61 +2078,55 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Sistemas de Informação e Comunicação</t>
-        </is>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>28</v>
       </c>
       <c r="B24">
         <v>2022</v>
       </c>
       <c r="C24">
-        <v>527217208.29</v>
+        <v>527217208.29000002</v>
       </c>
       <c r="D24">
-        <v>4694677.4</v>
+        <v>4694677.4000000004</v>
       </c>
       <c r="E24">
-        <v>0.008904636127540161</v>
+        <v>8.9046361275401612E-3</v>
       </c>
       <c r="F24">
         <v>32</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Construção de Unidades Habitacionais</t>
-        </is>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>29</v>
       </c>
       <c r="B25">
         <v>2022</v>
       </c>
       <c r="C25">
-        <v>506662993.08</v>
+        <v>506662993.07999998</v>
       </c>
       <c r="D25">
-        <v>486448668.21</v>
+        <v>486448668.20999998</v>
       </c>
       <c r="E25">
-        <v>0.9601030169045557</v>
+        <v>0.96010301690455568</v>
       </c>
       <c r="F25">
         <v>17</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Contraprestação de Parceria Público-Privada (PPP) - Iluminação Pública</t>
-        </is>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>30</v>
       </c>
       <c r="B26">
         <v>2022</v>
       </c>
       <c r="C26">
-        <v>504315828.51</v>
+        <v>504315828.50999999</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -936,20 +2138,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População em Situação de Rua</t>
-        </is>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>31</v>
       </c>
       <c r="B27">
         <v>2022</v>
       </c>
       <c r="C27">
-        <v>497830794.9</v>
+        <v>497830794.89999998</v>
       </c>
       <c r="D27">
-        <v>497830794.9</v>
+        <v>497830794.89999998</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -958,42 +2158,38 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Aquisição de Materiais, Equipamentos e Serviços de Informação e Comunicação</t>
-        </is>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>32</v>
       </c>
       <c r="B28">
         <v>2022</v>
       </c>
       <c r="C28">
-        <v>478648145.57</v>
+        <v>478648145.56999999</v>
       </c>
       <c r="D28">
         <v>10414872.98</v>
       </c>
       <c r="E28">
-        <v>0.02175893310439427</v>
+        <v>2.1758933104394269E-2</v>
       </c>
       <c r="F28">
         <v>32</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Pavimentação e Recapeamento de Vias</t>
-        </is>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>33</v>
       </c>
       <c r="B29">
         <v>2022</v>
       </c>
       <c r="C29">
-        <v>465541359.08</v>
+        <v>465541359.07999998</v>
       </c>
       <c r="D29">
-        <v>453979389.82</v>
+        <v>453979389.81999999</v>
       </c>
       <c r="E29">
         <v>0.9751644638344299</v>
@@ -1002,11 +2198,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Intervenções no Sistema Viário</t>
-        </is>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>34</v>
       </c>
       <c r="B30">
         <v>2022</v>
@@ -1024,17 +2218,15 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Sistema Municipal de Transporte Coletivo</t>
-        </is>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>35</v>
       </c>
       <c r="B31">
         <v>2022</v>
       </c>
       <c r="C31">
-        <v>406086031.01</v>
+        <v>406086031.00999999</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1046,20 +2238,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para Crianças e Adolescentes</t>
-        </is>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>36</v>
       </c>
       <c r="B32">
         <v>2022</v>
       </c>
       <c r="C32">
-        <v>362749439.53</v>
+        <v>362749439.52999997</v>
       </c>
       <c r="D32">
-        <v>362749439.53</v>
+        <v>362749439.52999997</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -1068,20 +2258,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Ensino Fundamental (EMEF)</t>
-        </is>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>37</v>
       </c>
       <c r="B33">
         <v>2022</v>
       </c>
       <c r="C33">
-        <v>315523541.67</v>
+        <v>315523541.67000002</v>
       </c>
       <c r="D33">
-        <v>315523541.67</v>
+        <v>315523541.67000002</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -1090,20 +2278,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Manutenção de Sistemas de Drenagem</t>
-        </is>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>38</v>
       </c>
       <c r="B34">
         <v>2022</v>
       </c>
       <c r="C34">
-        <v>296180988.6</v>
+        <v>296180988.60000002</v>
       </c>
       <c r="D34">
-        <v>296180988.6</v>
+        <v>296180988.60000002</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -1112,11 +2298,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Promoção de Campanhas e Eventos de Interesse do Município</t>
-        </is>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>39</v>
       </c>
       <c r="B35">
         <v>2022</v>
@@ -1134,20 +2318,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Centros Educacionais Unificados (CEU)</t>
-        </is>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>40</v>
       </c>
       <c r="B36">
         <v>2022</v>
       </c>
       <c r="C36">
-        <v>289379724.97</v>
+        <v>289379724.97000003</v>
       </c>
       <c r="D36">
-        <v>289379724.97</v>
+        <v>289379724.97000003</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -1156,17 +2338,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Fornecimento de Uniformes e Material Escolar-Educação Infantil</t>
-        </is>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>41</v>
       </c>
       <c r="B37">
         <v>2022</v>
       </c>
       <c r="C37">
-        <v>289112565.49</v>
+        <v>289112565.49000001</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1178,17 +2358,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Serviço da Dívida Pública Interna - Refinanciamento</t>
-        </is>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>42</v>
       </c>
       <c r="B38">
         <v>2022</v>
       </c>
       <c r="C38">
-        <v>284587775.51</v>
+        <v>284587775.50999999</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1200,20 +2378,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Centros Educacionais Unificados (CEU)</t>
-        </is>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>43</v>
       </c>
       <c r="B39">
         <v>2022</v>
       </c>
       <c r="C39">
-        <v>266128601.73</v>
+        <v>266128601.72999999</v>
       </c>
       <c r="D39">
-        <v>266128601.73</v>
+        <v>266128601.72999999</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -1222,11 +2398,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Administração de Material  Médico Hospitalar e Ambulatorial em Atenção Básica, Especialidades e Vigilância</t>
-        </is>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>44</v>
       </c>
       <c r="B40">
         <v>2022</v>
@@ -1244,20 +2418,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Educação Infantil</t>
-        </is>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>45</v>
       </c>
       <c r="B41">
         <v>2022</v>
       </c>
       <c r="C41">
-        <v>236561428.4</v>
+        <v>236561428.40000001</v>
       </c>
       <c r="D41">
-        <v>236561428.4</v>
+        <v>236561428.40000001</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -1266,11 +2438,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Áreas Verdes e Vegetação Arbórea</t>
-        </is>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>46</v>
       </c>
       <c r="B42">
         <v>2022</v>
@@ -1288,20 +2458,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Ensino Fundamental</t>
-        </is>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>47</v>
       </c>
       <c r="B43">
         <v>2022</v>
       </c>
       <c r="C43">
-        <v>234121718.8</v>
+        <v>234121718.80000001</v>
       </c>
       <c r="D43">
-        <v>234121718.8</v>
+        <v>234121718.80000001</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -1310,33 +2478,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Serviços de Limpeza Urbana - Varrição e Lavagem de Áreas Públicas</t>
-        </is>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>48</v>
       </c>
       <c r="B44">
         <v>2022</v>
       </c>
       <c r="C44">
-        <v>233929969.57</v>
+        <v>233929969.56999999</v>
       </c>
       <c r="D44">
         <v>44981360.93</v>
       </c>
       <c r="E44">
-        <v>0.192285584496432</v>
+        <v>0.19228558449643199</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Fornecimento de Uniformes e Material Escolar-Ensino Fundamental</t>
-        </is>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>49</v>
       </c>
       <c r="B45">
         <v>2022</v>
@@ -1354,42 +2518,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Recuperação e Reforço de Obras de Arte Especiais - OAE</t>
-        </is>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>50</v>
       </c>
       <c r="B46">
         <v>2022</v>
       </c>
       <c r="C46">
-        <v>227860226.29</v>
+        <v>227860226.28999999</v>
       </c>
       <c r="D46">
-        <v>214082177.29</v>
+        <v>214082177.28999999</v>
       </c>
       <c r="E46">
-        <v>0.9395328916137188</v>
+        <v>0.93953289161371878</v>
       </c>
       <c r="F46">
         <v>20</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial a Crianças, Adolescentes e Jovens em Risco Social</t>
-        </is>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>51</v>
       </c>
       <c r="B47">
         <v>2022</v>
       </c>
       <c r="C47">
-        <v>226598778.33</v>
+        <v>226598778.33000001</v>
       </c>
       <c r="D47">
-        <v>226598778.33</v>
+        <v>226598778.33000001</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -1398,11 +2558,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Administração de Material Médico Hospitalar em Atenção Hospitalar, de Urgência e Emergência</t>
-        </is>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>52</v>
       </c>
       <c r="B48">
         <v>2022</v>
@@ -1420,11 +2578,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Transporte Escolar - Educação Infantil</t>
-        </is>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>53</v>
       </c>
       <c r="B49">
         <v>2022</v>
@@ -1442,17 +2598,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Serviço da Dívida Pública Interna</t>
-        </is>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>54</v>
       </c>
       <c r="B50">
         <v>2022</v>
       </c>
       <c r="C50">
-        <v>217803204.61</v>
+        <v>217803204.61000001</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -1464,11 +2618,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Publicidade Institucional</t>
-        </is>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>55</v>
       </c>
       <c r="B51">
         <v>2022</v>
@@ -1486,42 +2638,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Terminais de Ônibus</t>
-        </is>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>56</v>
       </c>
       <c r="B52">
         <v>2022</v>
       </c>
       <c r="C52">
-        <v>206442018.32</v>
+        <v>206442018.31999999</v>
       </c>
       <c r="D52">
         <v>74649268</v>
       </c>
       <c r="E52">
-        <v>0.36159919675019</v>
+        <v>0.36159919675018998</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Escolas Municipais de Educação Infantil (EMEI)</t>
-        </is>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>57</v>
       </c>
       <c r="B53">
         <v>2022</v>
       </c>
       <c r="C53">
-        <v>205086769.42</v>
+        <v>205086769.41999999</v>
       </c>
       <c r="D53">
-        <v>205086769.42</v>
+        <v>205086769.41999999</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -1530,61 +2678,55 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Parques Urbanos e Lineares</t>
-        </is>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>58</v>
       </c>
       <c r="B54">
         <v>2022</v>
       </c>
       <c r="C54">
-        <v>201702938.98</v>
+        <v>201702938.97999999</v>
       </c>
       <c r="D54">
-        <v>196045759.08</v>
+        <v>196045759.08000001</v>
       </c>
       <c r="E54">
-        <v>0.9719529128895791</v>
+        <v>0.97195291288957908</v>
       </c>
       <c r="F54">
         <v>32</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Ações e Materiais de Apoio Didático-Pedagógico Educacional</t>
-        </is>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>59</v>
       </c>
       <c r="B55">
         <v>2022</v>
       </c>
       <c r="C55">
-        <v>190864529.6</v>
+        <v>190864529.59999999</v>
       </c>
       <c r="D55">
-        <v>64735698.2</v>
+        <v>64735698.200000003</v>
       </c>
       <c r="E55">
-        <v>0.3391709205249837</v>
+        <v>0.33917092052498371</v>
       </c>
       <c r="F55">
         <v>32</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Programa Nacional de Alimentação Escolar - PNAE/ FNDE</t>
-        </is>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>60</v>
       </c>
       <c r="B56">
         <v>2022</v>
       </c>
       <c r="C56">
-        <v>183225691.6</v>
+        <v>183225691.59999999</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -1596,11 +2738,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Sistema de Remuneração Variável</t>
-        </is>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>61</v>
       </c>
       <c r="B57">
         <v>2022</v>
@@ -1618,17 +2758,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Transporte Escolar - Ensino Fundamental</t>
-        </is>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>62</v>
       </c>
       <c r="B58">
         <v>2022</v>
       </c>
       <c r="C58">
-        <v>159409713.82</v>
+        <v>159409713.81999999</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -1640,18 +2778,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avança Saúde SP - Ampliação, Reforma e Requalificação de Equipamentos de Saúde_x000D__x000D_
-</t>
-        </is>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>63</v>
       </c>
       <c r="B59">
         <v>2022</v>
       </c>
       <c r="C59">
-        <v>150551524.2</v>
+        <v>150551524.19999999</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -1663,20 +2798,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação no Serviço de Guias e Sarjetas (Vias e Logradouros)</t>
-        </is>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>64</v>
       </c>
       <c r="B60">
         <v>2022</v>
       </c>
       <c r="C60">
-        <v>146166915.49</v>
+        <v>146166915.49000001</v>
       </c>
       <c r="D60">
-        <v>146166915.49</v>
+        <v>146166915.49000001</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -1685,11 +2818,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Transporte de Pessoas com Deficiência ou Mobilidade Reduzida - ATENDE</t>
-        </is>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>65</v>
       </c>
       <c r="B61">
         <v>2022</v>
@@ -1707,20 +2838,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Centros de Educação Infantil (CEI)</t>
-        </is>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>66</v>
       </c>
       <c r="B62">
         <v>2022</v>
       </c>
       <c r="C62">
-        <v>140910802.7</v>
+        <v>140910802.69999999</v>
       </c>
       <c r="D62">
-        <v>140910802.7</v>
+        <v>140910802.69999999</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -1729,20 +2858,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Controle e Fiscalização de Tráfego</t>
-        </is>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>67</v>
       </c>
       <c r="B63">
         <v>2022</v>
       </c>
       <c r="C63">
-        <v>139656025.79</v>
+        <v>139656025.78999999</v>
       </c>
       <c r="D63">
-        <v>139656025.79</v>
+        <v>139656025.78999999</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -1751,17 +2878,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Condenações Judiciais - Créditos de Pequeno Valor</t>
-        </is>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>68</v>
       </c>
       <c r="B64">
         <v>2022</v>
       </c>
       <c r="C64">
-        <v>136579901.32</v>
+        <v>136579901.31999999</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -1773,11 +2898,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Obras e Serviços nas Áreas de Riscos Geológicos</t>
-        </is>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>69</v>
       </c>
       <c r="B65">
         <v>2022</v>
@@ -1789,26 +2912,24 @@
         <v>134621442.78</v>
       </c>
       <c r="E65">
-        <v>0.9873684031781422</v>
+        <v>0.98736840317814223</v>
       </c>
       <c r="F65">
         <v>17</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Intergeracionais de Convivência e Fortalecimento de Vínculos</t>
-        </is>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>70</v>
       </c>
       <c r="B66">
         <v>2022</v>
       </c>
       <c r="C66">
-        <v>129135564.4</v>
+        <v>129135564.40000001</v>
       </c>
       <c r="D66">
-        <v>129135564.4</v>
+        <v>129135564.40000001</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -1817,11 +2938,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Esportivos</t>
-        </is>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>71</v>
       </c>
       <c r="B67">
         <v>2022</v>
@@ -1839,11 +2958,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Encargos pela Manutenção do Fundo de Depósitos Judiciais nas quais o Município é Parte</t>
-        </is>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>72</v>
       </c>
       <c r="B68">
         <v>2022</v>
@@ -1861,17 +2978,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Projetos e Ações de Apoio Habitacional</t>
-        </is>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>73</v>
       </c>
       <c r="B69">
         <v>2022</v>
       </c>
       <c r="C69">
-        <v>123534170.71</v>
+        <v>123534170.70999999</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -1883,17 +2998,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Precatórios Pagos com Rendimentos dos Depósitos do Regime Especial</t>
-        </is>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>74</v>
       </c>
       <c r="B70">
         <v>2022</v>
       </c>
       <c r="C70">
-        <v>115606877.74</v>
+        <v>115606877.73999999</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -1905,11 +3018,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Leve-Leite</t>
-        </is>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>75</v>
       </c>
       <c r="B71">
         <v>2022</v>
@@ -1927,33 +3038,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Corredores de Ônibus</t>
-        </is>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>76</v>
       </c>
       <c r="B72">
         <v>2022</v>
       </c>
       <c r="C72">
-        <v>106545622.01</v>
+        <v>106545622.01000001</v>
       </c>
       <c r="D72">
         <v>105677307.39</v>
       </c>
       <c r="E72">
-        <v>0.99185030221215</v>
+        <v>0.99185030221214998</v>
       </c>
       <c r="F72">
         <v>2</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Sinalização do Sistema Viário</t>
-        </is>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>77</v>
       </c>
       <c r="B73">
         <v>2022</v>
@@ -1971,11 +3078,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Vigilância em Saúde</t>
-        </is>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>78</v>
       </c>
       <c r="B74">
         <v>2022</v>
@@ -1993,20 +3098,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Operação Tapa Buraco</t>
-        </is>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>79</v>
       </c>
       <c r="B75">
         <v>2022</v>
       </c>
       <c r="C75">
-        <v>99277957.44</v>
+        <v>99277957.439999998</v>
       </c>
       <c r="D75">
-        <v>99277957.44</v>
+        <v>99277957.439999998</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -2015,17 +3118,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Central de Atendimento Telefônico - 156</t>
-        </is>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>80</v>
       </c>
       <c r="B76">
         <v>2022</v>
       </c>
       <c r="C76">
-        <v>95402335.68000001</v>
+        <v>95402335.680000007</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2037,42 +3138,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Programação de Atividades Culturais</t>
-        </is>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>81</v>
       </c>
       <c r="B77">
         <v>2022</v>
       </c>
       <c r="C77">
-        <v>88341072.19</v>
+        <v>88341072.189999998</v>
       </c>
       <c r="D77">
-        <v>88241072.19</v>
+        <v>88241072.189999998</v>
       </c>
       <c r="E77">
-        <v>0.9988680237004037</v>
+        <v>0.99886802370040373</v>
       </c>
       <c r="F77">
         <v>32</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Manutenção de Vias e Áreas Públicas</t>
-        </is>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>82</v>
       </c>
       <c r="B78">
         <v>2022</v>
       </c>
       <c r="C78">
-        <v>87364388.56999999</v>
+        <v>87364388.569999993</v>
       </c>
       <c r="D78">
-        <v>87364388.56999999</v>
+        <v>87364388.569999993</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -2081,17 +3178,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Grupos Artísticos, Técnicos e Administrativos</t>
-        </is>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>83</v>
       </c>
       <c r="B79">
         <v>2022</v>
       </c>
       <c r="C79">
-        <v>87150331.64</v>
+        <v>87150331.640000001</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2103,17 +3198,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Serviço de Atendimento Médico de Urgência (SAMU)</t>
-        </is>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>84</v>
       </c>
       <c r="B80">
         <v>2022</v>
       </c>
       <c r="C80">
-        <v>84814953.73</v>
+        <v>84814953.730000004</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2125,20 +3218,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Remuneração dos Profissionais do Magistério - Ensino Fundamental</t>
-        </is>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>85</v>
       </c>
       <c r="B81">
         <v>2022</v>
       </c>
       <c r="C81">
-        <v>83729511.72</v>
+        <v>83729511.719999999</v>
       </c>
       <c r="D81">
-        <v>83729511.72</v>
+        <v>83729511.719999999</v>
       </c>
       <c r="E81">
         <v>1</v>
@@ -2147,17 +3238,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Ações de Apoio à Educação Especial</t>
-        </is>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>86</v>
       </c>
       <c r="B82">
         <v>2022</v>
       </c>
       <c r="C82">
-        <v>80872787.79000001</v>
+        <v>80872787.790000007</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2169,11 +3258,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Programa de Incentivo Fiscal Relacionado à Arena Corinthians</t>
-        </is>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>87</v>
       </c>
       <c r="B83">
         <v>2022</v>
@@ -2191,17 +3278,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Servidores Comissionados em Outras Entidades</t>
-        </is>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>88</v>
       </c>
       <c r="B84">
         <v>2022</v>
       </c>
       <c r="C84">
-        <v>67812134.2</v>
+        <v>67812134.200000003</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2213,17 +3298,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Serviço de Moradia Transitória</t>
-        </is>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>89</v>
       </c>
       <c r="B85">
         <v>2022</v>
       </c>
       <c r="C85">
-        <v>66677331.31</v>
+        <v>66677331.310000002</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2235,20 +3318,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Básica às Famílias</t>
-        </is>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>90</v>
       </c>
       <c r="B86">
         <v>2022</v>
       </c>
       <c r="C86">
-        <v>65710474.84</v>
+        <v>65710474.840000004</v>
       </c>
       <c r="D86">
-        <v>65710474.84</v>
+        <v>65710474.840000004</v>
       </c>
       <c r="E86">
         <v>1</v>
@@ -2257,20 +3338,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Urbanização de Favelas</t>
-        </is>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>91</v>
       </c>
       <c r="B87">
         <v>2022</v>
       </c>
       <c r="C87">
-        <v>63501968.29</v>
+        <v>63501968.289999999</v>
       </c>
       <c r="D87">
-        <v>48361398.46</v>
+        <v>48361398.460000001</v>
       </c>
       <c r="E87">
         <v>0.7615732198905043</v>
@@ -2279,11 +3358,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos Esportivos</t>
-        </is>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>92</v>
       </c>
       <c r="B88">
         <v>2022</v>
@@ -2301,42 +3378,38 @@
         <v>19</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Incentivo à Prática de Esportes</t>
-        </is>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>93</v>
       </c>
       <c r="B89">
         <v>2022</v>
       </c>
       <c r="C89">
-        <v>62167996.02</v>
+        <v>62167996.020000003</v>
       </c>
       <c r="D89">
-        <v>7939684.55</v>
+        <v>7939684.5499999998</v>
       </c>
       <c r="E89">
-        <v>0.1277133743774808</v>
+        <v>0.12771337437748079</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Realização de Eventos de Esporte, Lazer e Recreação</t>
-        </is>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>94</v>
       </c>
       <c r="B90">
         <v>2022</v>
       </c>
       <c r="C90">
-        <v>61554493.96</v>
+        <v>61554493.960000001</v>
       </c>
       <c r="D90">
-        <v>6768805.74</v>
+        <v>6768805.7400000002</v>
       </c>
       <c r="E90">
         <v>0.1099644445846404</v>
@@ -2345,17 +3418,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Atenção Hospitalar da Assistência Farmacêutica</t>
-        </is>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>95</v>
       </c>
       <c r="B91">
         <v>2022</v>
       </c>
       <c r="C91">
-        <v>58584852.45</v>
+        <v>58584852.450000003</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -2367,20 +3438,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Remuneração dos Profissionais do Magistério - Centro de Educação Infantil (CEI)</t>
-        </is>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>96</v>
       </c>
       <c r="B92">
         <v>2022</v>
       </c>
       <c r="C92">
-        <v>57950537.47</v>
+        <v>57950537.469999999</v>
       </c>
       <c r="D92">
-        <v>57950537.47</v>
+        <v>57950537.469999999</v>
       </c>
       <c r="E92">
         <v>1</v>
@@ -2389,17 +3458,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Capacitação, Formação e Aperfeiçoamento dos Trabalhadores</t>
-        </is>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>97</v>
       </c>
       <c r="B93">
         <v>2022</v>
       </c>
       <c r="C93">
-        <v>57662486.8</v>
+        <v>57662486.799999997</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -2411,11 +3478,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Ações Integradas de Segurança Pública - Operação Delegada - Convênio SSP SO</t>
-        </is>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>98</v>
       </c>
       <c r="B94">
         <v>2022</v>
@@ -2433,20 +3498,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Remuneração dos Profissionais do Magistério - Escola Municipal de Educação Infantil (EMEI)</t>
-        </is>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>99</v>
       </c>
       <c r="B95">
         <v>2022</v>
       </c>
       <c r="C95">
-        <v>56366375.58</v>
+        <v>56366375.579999998</v>
       </c>
       <c r="D95">
-        <v>56366375.58</v>
+        <v>56366375.579999998</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -2455,11 +3518,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação Semafórica</t>
-        </is>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>100</v>
       </c>
       <c r="B96">
         <v>2022</v>
@@ -2477,20 +3538,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à Pessoa com Deficiência</t>
-        </is>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>101</v>
       </c>
       <c r="B97">
         <v>2022</v>
       </c>
       <c r="C97">
-        <v>53786390.39</v>
+        <v>53786390.390000001</v>
       </c>
       <c r="D97">
-        <v>53786390.39</v>
+        <v>53786390.390000001</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -2499,20 +3558,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População Idosa</t>
-        </is>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>102</v>
       </c>
       <c r="B98">
         <v>2022</v>
       </c>
       <c r="C98">
-        <v>53533979.01</v>
+        <v>53533979.009999998</v>
       </c>
       <c r="D98">
-        <v>53533979.01</v>
+        <v>53533979.009999998</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2521,20 +3578,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos da Assistência Social</t>
-        </is>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>103</v>
       </c>
       <c r="B99">
         <v>2022</v>
       </c>
       <c r="C99">
-        <v>45257699.56</v>
+        <v>45257699.560000002</v>
       </c>
       <c r="D99">
-        <v>45257699.56</v>
+        <v>45257699.560000002</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -2543,17 +3598,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Administração da Carteira Imobiliária</t>
-        </is>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>104</v>
       </c>
       <c r="B100">
         <v>2022</v>
       </c>
       <c r="C100">
-        <v>44647923.19</v>
+        <v>44647923.189999998</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -2565,20 +3618,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Construção de Centros de Educação Infantil - CEI</t>
-        </is>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>105</v>
       </c>
       <c r="B101">
         <v>2022</v>
       </c>
       <c r="C101">
-        <v>44151997.36</v>
+        <v>44151997.359999999</v>
       </c>
       <c r="D101">
-        <v>44151997.36</v>
+        <v>44151997.359999999</v>
       </c>
       <c r="E101">
         <v>1</v>
@@ -2587,17 +3638,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Ações Permanentes de Promoção dos Direitos da Criança e do Adolescente</t>
-        </is>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>106</v>
       </c>
       <c r="B102">
         <v>2022</v>
       </c>
       <c r="C102">
-        <v>43802369.2</v>
+        <v>43802369.200000003</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -2609,17 +3658,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Serviço da Dívida Pública Externa</t>
-        </is>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>107</v>
       </c>
       <c r="B103">
         <v>2022</v>
       </c>
       <c r="C103">
-        <v>42307339.42</v>
+        <v>42307339.420000002</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -2631,39 +3678,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Posto do Corpo de Bombeiros</t>
-        </is>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>108</v>
       </c>
       <c r="B104">
         <v>2022</v>
       </c>
       <c r="C104">
-        <v>41633271.02</v>
+        <v>41633271.020000003</v>
       </c>
       <c r="D104">
-        <v>39741770.21</v>
+        <v>39741770.210000001</v>
       </c>
       <c r="E104">
-        <v>0.9545675666682218</v>
+        <v>0.95456756666822185</v>
       </c>
       <c r="F104">
         <v>32</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Realização de Eventos Culturais</t>
-        </is>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>109</v>
       </c>
       <c r="B105">
         <v>2022</v>
       </c>
       <c r="C105">
-        <v>39628073.49</v>
+        <v>39628073.490000002</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -2675,11 +3718,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Guarda Civil Metropolitana</t>
-        </is>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>110</v>
       </c>
       <c r="B106">
         <v>2022</v>
@@ -2691,23 +3732,21 @@
         <v>24784998.07</v>
       </c>
       <c r="E106">
-        <v>0.6288571336836826</v>
+        <v>0.62885713368368257</v>
       </c>
       <c r="F106">
         <v>32</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Administração dos Conselhos Tutelares</t>
-        </is>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>111</v>
       </c>
       <c r="B107">
         <v>2022</v>
       </c>
       <c r="C107">
-        <v>38209128.34</v>
+        <v>38209128.340000004</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -2719,17 +3758,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Educação em Direitos Humanos e Promoção do Direito à Cidade</t>
-        </is>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>112</v>
       </c>
       <c r="B108">
         <v>2022</v>
       </c>
       <c r="C108">
-        <v>35187843.23</v>
+        <v>35187843.229999997</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -2741,20 +3778,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para a Pessoa Idosa</t>
-        </is>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>113</v>
       </c>
       <c r="B109">
         <v>2022</v>
       </c>
       <c r="C109">
-        <v>34352741.96</v>
+        <v>34352741.960000001</v>
       </c>
       <c r="D109">
-        <v>34352741.96</v>
+        <v>34352741.960000001</v>
       </c>
       <c r="E109">
         <v>1</v>
@@ -2763,20 +3798,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Centros Educacionais Unificados (CEU)</t>
-        </is>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>114</v>
       </c>
       <c r="B110">
         <v>2022</v>
       </c>
       <c r="C110">
-        <v>34347863.44</v>
+        <v>34347863.439999998</v>
       </c>
       <c r="D110">
-        <v>34347863.44</v>
+        <v>34347863.439999998</v>
       </c>
       <c r="E110">
         <v>1</v>
@@ -2785,39 +3818,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Modernização Semafórica</t>
-        </is>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>115</v>
       </c>
       <c r="B111">
         <v>2022</v>
       </c>
       <c r="C111">
-        <v>34223141.49</v>
+        <v>34223141.490000002</v>
       </c>
       <c r="D111">
-        <v>7199299.68</v>
+        <v>7199299.6799999997</v>
       </c>
       <c r="E111">
-        <v>0.210363495768021</v>
+        <v>0.21036349576802099</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Aposentadoria Complementar aos Servidores da São Paulo Transporte S/A</t>
-        </is>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>116</v>
       </c>
       <c r="B112">
         <v>2022</v>
       </c>
       <c r="C112">
-        <v>33838306.65</v>
+        <v>33838306.649999999</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -2829,17 +3858,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Regularização Fundiária</t>
-        </is>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>117</v>
       </c>
       <c r="B113">
         <v>2022</v>
       </c>
       <c r="C113">
-        <v>31419509.55</v>
+        <v>31419509.550000001</v>
       </c>
       <c r="D113">
         <v>15476252.57</v>
@@ -2851,20 +3878,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Intervenções em Próprios Municipais</t>
-        </is>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>118</v>
       </c>
       <c r="B114">
         <v>2022</v>
       </c>
       <c r="C114">
-        <v>31384941.76</v>
+        <v>31384941.760000002</v>
       </c>
       <c r="D114">
-        <v>16463809.8</v>
+        <v>16463809.800000001</v>
       </c>
       <c r="E114">
         <v>0.5245767198135467</v>
@@ -2873,11 +3898,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Coleta, Transporte, Tratamento e Dest. Final Resíduos Sólidos Inertes</t>
-        </is>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>119</v>
       </c>
       <c r="B115">
         <v>2022</v>
@@ -2886,7 +3909,7 @@
         <v>30805228.5</v>
       </c>
       <c r="D115">
-        <v>5970537.350000001</v>
+        <v>5970537.3500000006</v>
       </c>
       <c r="E115">
         <v>0.1938157137837819</v>
@@ -2895,20 +3918,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Policiamento de Trânsito</t>
-        </is>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>120</v>
       </c>
       <c r="B116">
         <v>2022</v>
       </c>
       <c r="C116">
-        <v>30737267.6</v>
+        <v>30737267.600000001</v>
       </c>
       <c r="D116">
-        <v>30737267.6</v>
+        <v>30737267.600000001</v>
       </c>
       <c r="E116">
         <v>1</v>
@@ -2917,42 +3938,38 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Clube da Comunidade (CDC)</t>
-        </is>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>121</v>
       </c>
       <c r="B117">
         <v>2022</v>
       </c>
       <c r="C117">
-        <v>30668307.62</v>
+        <v>30668307.620000001</v>
       </c>
       <c r="D117">
         <v>25353641.02</v>
       </c>
       <c r="E117">
-        <v>0.8267049272541501</v>
+        <v>0.82670492725415012</v>
       </c>
       <c r="F117">
         <v>17</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Prédios Administrativos</t>
-        </is>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>122</v>
       </c>
       <c r="B118">
         <v>2022</v>
       </c>
       <c r="C118">
-        <v>29911972.74</v>
+        <v>29911972.739999998</v>
       </c>
       <c r="D118">
-        <v>29911972.74</v>
+        <v>29911972.739999998</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -2961,11 +3978,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Programa Municipal de Apoio a Projetos Culturais (PRO-MAC)</t>
-        </is>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>123</v>
       </c>
       <c r="B119">
         <v>2022</v>
@@ -2977,23 +3992,21 @@
         <v>28656</v>
       </c>
       <c r="E119">
-        <v>0.0009761541683281147</v>
+        <v>9.761541683281147E-4</v>
       </c>
       <c r="F119">
         <v>7</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para a População em Situação de Rua</t>
-        </is>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>124</v>
       </c>
       <c r="B120">
         <v>2022</v>
       </c>
       <c r="C120">
-        <v>28727744.74</v>
+        <v>28727744.739999998</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -3005,20 +4018,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Ações de Fiscalização do Comércio Ilegal</t>
-        </is>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>125</v>
       </c>
       <c r="B121">
         <v>2022</v>
       </c>
       <c r="C121">
-        <v>27949308.69</v>
+        <v>27949308.690000001</v>
       </c>
       <c r="D121">
-        <v>27949308.69</v>
+        <v>27949308.690000001</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -3027,11 +4038,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção da Agência São Paulo de Desenvolvimento - ADESAMPA</t>
-        </is>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>126</v>
       </c>
       <c r="B122">
         <v>2022</v>
@@ -3049,20 +4058,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Políticas de Audiovisual</t>
-        </is>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>127</v>
       </c>
       <c r="B123">
         <v>2022</v>
       </c>
       <c r="C123">
-        <v>27461812.88</v>
+        <v>27461812.879999999</v>
       </c>
       <c r="D123">
-        <v>27461812.88</v>
+        <v>27461812.879999999</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -3071,20 +4078,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Eventos Educacionais, Culturais e Esportivos nos Centros Educacionais Unificados</t>
-        </is>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>128</v>
       </c>
       <c r="B124">
         <v>2022</v>
       </c>
       <c r="C124">
-        <v>26571850.56</v>
+        <v>26571850.559999999</v>
       </c>
       <c r="D124">
-        <v>26571850.56</v>
+        <v>26571850.559999999</v>
       </c>
       <c r="E124">
         <v>1</v>
@@ -3093,11 +4098,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Aporte para Garantia de PPP's e Projetos de Infraestrutura</t>
-        </is>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>129</v>
       </c>
       <c r="B125">
         <v>2022</v>
@@ -3115,20 +4118,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Parques Urbanos e Lineares</t>
-        </is>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>130</v>
       </c>
       <c r="B126">
         <v>2022</v>
       </c>
       <c r="C126">
-        <v>25837166.1</v>
+        <v>25837166.100000001</v>
       </c>
       <c r="D126">
-        <v>25837166.1</v>
+        <v>25837166.100000001</v>
       </c>
       <c r="E126">
         <v>1</v>
@@ -3137,20 +4138,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - Educação Infantil</t>
-        </is>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>131</v>
       </c>
       <c r="B127">
         <v>2022</v>
       </c>
       <c r="C127">
-        <v>25670688.45</v>
+        <v>25670688.449999999</v>
       </c>
       <c r="D127">
-        <v>25670688.45</v>
+        <v>25670688.449999999</v>
       </c>
       <c r="E127">
         <v>1</v>
@@ -3159,20 +4158,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Construção de Ciclovias, Ciclofaixas e Ciclorrotas</t>
-        </is>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>132</v>
       </c>
       <c r="B128">
         <v>2022</v>
       </c>
       <c r="C128">
-        <v>23813318.79</v>
+        <v>23813318.789999999</v>
       </c>
       <c r="D128">
-        <v>23813318.79</v>
+        <v>23813318.789999999</v>
       </c>
       <c r="E128">
         <v>1</v>
@@ -3181,11 +4178,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Contraprestação de Parceria Público-Privada (PPP) - Terminais Urbanos</t>
-        </is>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>133</v>
       </c>
       <c r="B129">
         <v>2022</v>
@@ -3203,39 +4198,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Implantação de Corredores de Ônibus Novos</t>
-        </is>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>134</v>
       </c>
       <c r="B130">
         <v>2022</v>
       </c>
       <c r="C130">
-        <v>23187857.36</v>
+        <v>23187857.359999999</v>
       </c>
       <c r="D130">
         <v>18912415.66</v>
       </c>
       <c r="E130">
-        <v>0.8156172157857366</v>
+        <v>0.81561721578573665</v>
       </c>
       <c r="F130">
         <v>5</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação em Serviços de Saúde Animal</t>
-        </is>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>135</v>
       </c>
       <c r="B131">
         <v>2022</v>
       </c>
       <c r="C131">
-        <v>23054771.45</v>
+        <v>23054771.449999999</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3247,11 +4238,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Áreas Públicas</t>
-        </is>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>136</v>
       </c>
       <c r="B132">
         <v>2022</v>
@@ -3260,20 +4249,18 @@
         <v>22231986.32</v>
       </c>
       <c r="D132">
-        <v>18477677.85</v>
+        <v>18477677.850000001</v>
       </c>
       <c r="E132">
-        <v>0.8311303175540997</v>
+        <v>0.83113031755409972</v>
       </c>
       <c r="F132">
         <v>29</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Serviços de Desfazimento e Demolição de Construções Irregulares em Áreas de Proteção Ambiental</t>
-        </is>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>137</v>
       </c>
       <c r="B133">
         <v>2022</v>
@@ -3291,20 +4278,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Descomplica SP</t>
-        </is>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>138</v>
       </c>
       <c r="B134">
         <v>2022</v>
       </c>
       <c r="C134">
-        <v>21921972.54</v>
+        <v>21921972.539999999</v>
       </c>
       <c r="D134">
-        <v>21921972.54</v>
+        <v>21921972.539999999</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -3313,20 +4298,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Centros Culturais e Teatros</t>
-        </is>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>139</v>
       </c>
       <c r="B135">
         <v>2022</v>
       </c>
       <c r="C135">
-        <v>21166445.2</v>
+        <v>21166445.199999999</v>
       </c>
       <c r="D135">
-        <v>21166445.2</v>
+        <v>21166445.199999999</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -3335,20 +4318,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Centro Educacional Unificado (CEU)</t>
-        </is>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>140</v>
       </c>
       <c r="B136">
         <v>2022</v>
       </c>
       <c r="C136">
-        <v>21132114.8</v>
+        <v>21132114.800000001</v>
       </c>
       <c r="D136">
-        <v>21132114.8</v>
+        <v>21132114.800000001</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -3357,11 +4338,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Fomento à Cooperação, Parcerias e Captação de Investimentos Internacionais</t>
-        </is>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>141</v>
       </c>
       <c r="B137">
         <v>2022</v>
@@ -3379,17 +4358,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Desenvolvimento de Sistemas de Informação e Comunicação</t>
-        </is>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>142</v>
       </c>
       <c r="B138">
         <v>2022</v>
       </c>
       <c r="C138">
-        <v>20814739.88</v>
+        <v>20814739.879999999</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -3401,11 +4378,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Programa de Atração a Filmagens - Cash Rebate</t>
-        </is>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>143</v>
       </c>
       <c r="B139">
         <v>2022</v>
@@ -3423,20 +4398,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades de Conservação</t>
-        </is>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>144</v>
       </c>
       <c r="B140">
         <v>2022</v>
       </c>
       <c r="C140">
-        <v>19234719.74</v>
+        <v>19234719.739999998</v>
       </c>
       <c r="D140">
-        <v>19234719.74</v>
+        <v>19234719.739999998</v>
       </c>
       <c r="E140">
         <v>1</v>
@@ -3445,11 +4418,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos de Atenção Básica e Especialidades</t>
-        </is>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>145</v>
       </c>
       <c r="B141">
         <v>2022</v>
@@ -3467,33 +4438,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Mulheres</t>
-        </is>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>146</v>
       </c>
       <c r="B142">
         <v>2022</v>
       </c>
       <c r="C142">
-        <v>18767407.33</v>
+        <v>18767407.329999998</v>
       </c>
       <c r="D142">
         <v>11394125.51</v>
       </c>
       <c r="E142">
-        <v>0.6071230463350316</v>
+        <v>0.60712304633503156</v>
       </c>
       <c r="F142">
         <v>19</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Lei de Fomento ao Teatro</t>
-        </is>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>147</v>
       </c>
       <c r="B143">
         <v>2022</v>
@@ -3511,20 +4478,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Jurídico Social</t>
-        </is>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>148</v>
       </c>
       <c r="B144">
         <v>2022</v>
       </c>
       <c r="C144">
-        <v>16751333.54</v>
+        <v>16751333.539999999</v>
       </c>
       <c r="D144">
-        <v>16751333.54</v>
+        <v>16751333.539999999</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -3533,17 +4498,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Gratificação de Municipalização - Saúde - Lei 13.510/03</t>
-        </is>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>149</v>
       </c>
       <c r="B145">
         <v>2022</v>
       </c>
       <c r="C145">
-        <v>16583528.38</v>
+        <v>16583528.380000001</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -3555,11 +4518,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Bibliotecas Públicas</t>
-        </is>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>150</v>
       </c>
       <c r="B146">
         <v>2022</v>
@@ -3577,11 +4538,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
-        </is>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>151</v>
       </c>
       <c r="B147">
         <v>2022</v>
@@ -3593,17 +4552,15 @@
         <v>36045.4</v>
       </c>
       <c r="E147">
-        <v>0.00222270807935049</v>
+        <v>2.22270807935049E-3</v>
       </c>
       <c r="F147">
         <v>1</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação da Avenida Santo Amaro</t>
-        </is>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>152</v>
       </c>
       <c r="B148">
         <v>2022</v>
@@ -3621,20 +4578,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Fomento à Cultura da Periferia de São Paulo</t>
-        </is>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>153</v>
       </c>
       <c r="B149">
         <v>2022</v>
       </c>
       <c r="C149">
-        <v>15560079.11</v>
+        <v>15560079.109999999</v>
       </c>
       <c r="D149">
-        <v>15560079.11</v>
+        <v>15560079.109999999</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -3643,17 +4598,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Encargos Referentes a Arrecadação</t>
-        </is>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>154</v>
       </c>
       <c r="B150">
         <v>2022</v>
       </c>
       <c r="C150">
-        <v>15538669.89</v>
+        <v>15538669.890000001</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -3665,11 +4618,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Ações de Educação Integral</t>
-        </is>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>155</v>
       </c>
       <c r="B151">
         <v>2022</v>
@@ -3687,11 +4638,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Construção e Implantação do Descomplica SP</t>
-        </is>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>156</v>
       </c>
       <c r="B152">
         <v>2022</v>
@@ -3709,11 +4658,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Circuito Cultural de São Paulo</t>
-        </is>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>157</v>
       </c>
       <c r="B153">
         <v>2022</v>
@@ -3725,23 +4672,21 @@
         <v>2115002.85</v>
       </c>
       <c r="E153">
-        <v>0.1442279393612388</v>
+        <v>0.14422793936123879</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Ações de Desestatização</t>
-        </is>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>158</v>
       </c>
       <c r="B154">
         <v>2022</v>
       </c>
       <c r="C154">
-        <v>14578504.05</v>
+        <v>14578504.050000001</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -3753,11 +4698,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Centros Municipais de Educação Infantil(CEMEI)</t>
-        </is>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>159</v>
       </c>
       <c r="B155">
         <v>2022</v>
@@ -3775,20 +4718,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Sistemas de Monitoramento e Alerta de Enchentes</t>
-        </is>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>160</v>
       </c>
       <c r="B156">
         <v>2022</v>
       </c>
       <c r="C156">
-        <v>14149331.94</v>
+        <v>14149331.939999999</v>
       </c>
       <c r="D156">
-        <v>14149331.94</v>
+        <v>14149331.939999999</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -3797,20 +4738,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção dos Centros de Apoio ao Trabalho e Empreendedorismo</t>
-        </is>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>161</v>
       </c>
       <c r="B157">
         <v>2022</v>
       </c>
       <c r="C157">
-        <v>14100188.94</v>
+        <v>14100188.939999999</v>
       </c>
       <c r="D157">
-        <v>14100188.94</v>
+        <v>14100188.939999999</v>
       </c>
       <c r="E157">
         <v>1</v>
@@ -3819,11 +4758,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação do Autódromo de Interlagos</t>
-        </is>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>162</v>
       </c>
       <c r="B158">
         <v>2022</v>
@@ -3841,20 +4778,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Inserção das Famílias no Cadastro Único</t>
-        </is>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>163</v>
       </c>
       <c r="B159">
         <v>2022</v>
       </c>
       <c r="C159">
-        <v>13393117.39</v>
+        <v>13393117.390000001</v>
       </c>
       <c r="D159">
-        <v>13393117.39</v>
+        <v>13393117.390000001</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -3863,20 +4798,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Escolas Municipais de Educação Infantil (EMEI)</t>
-        </is>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>164</v>
       </c>
       <c r="B160">
         <v>2022</v>
       </c>
       <c r="C160">
-        <v>13390255.89</v>
+        <v>13390255.890000001</v>
       </c>
       <c r="D160">
-        <v>13390255.89</v>
+        <v>13390255.890000001</v>
       </c>
       <c r="E160">
         <v>1</v>
@@ -3885,20 +4818,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Ações de formação das Escolas de Música e Dança do Theatro Municipal e da Praça das Artes</t>
-        </is>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>165</v>
       </c>
       <c r="B161">
         <v>2022</v>
       </c>
       <c r="C161">
-        <v>13283396.97</v>
+        <v>13283396.970000001</v>
       </c>
       <c r="D161">
-        <v>13283396.97</v>
+        <v>13283396.970000001</v>
       </c>
       <c r="E161">
         <v>1</v>
@@ -3907,11 +4838,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Programação da Virada Esportiva</t>
-        </is>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>166</v>
       </c>
       <c r="B162">
         <v>2022</v>
@@ -3923,17 +4852,15 @@
         <v>740057.75</v>
       </c>
       <c r="E162">
-        <v>0.0563791710760245</v>
+        <v>5.6379171076024498E-2</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção de Unidade da Fundação Paulistana - FPETC</t>
-        </is>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>167</v>
       </c>
       <c r="B163">
         <v>2022</v>
@@ -3951,11 +4878,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Alfabetização na Idade Certa</t>
-        </is>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>168</v>
       </c>
       <c r="B164">
         <v>2022</v>
@@ -3973,11 +4898,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos do Departamento dos Museus Municipais</t>
-        </is>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>169</v>
       </c>
       <c r="B165">
         <v>2022</v>
@@ -3989,17 +4912,15 @@
         <v>12658860.82</v>
       </c>
       <c r="E165">
-        <v>0.9994155908541013</v>
+        <v>0.99941559085410125</v>
       </c>
       <c r="F165">
         <v>32</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Rede Parceira - Alfabetização de Jovens e Adultos</t>
-        </is>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>170</v>
       </c>
       <c r="B166">
         <v>2022</v>
@@ -4017,11 +4938,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Capacitação, Formação e Aperfeiçoamento de Servidores</t>
-        </is>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>171</v>
       </c>
       <c r="B167">
         <v>2022</v>
@@ -4033,26 +4952,24 @@
         <v>148410</v>
       </c>
       <c r="E167">
-        <v>0.01212432329634778</v>
+        <v>1.2124323296347781E-2</v>
       </c>
       <c r="F167">
         <v>3</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Telecentros</t>
-        </is>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>172</v>
       </c>
       <c r="B168">
         <v>2022</v>
       </c>
       <c r="C168">
-        <v>11968074.11</v>
+        <v>11968074.109999999</v>
       </c>
       <c r="D168">
-        <v>11968074.11</v>
+        <v>11968074.109999999</v>
       </c>
       <c r="E168">
         <v>1</v>
@@ -4061,11 +4978,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - Ensino Fundamental</t>
-        </is>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>173</v>
       </c>
       <c r="B169">
         <v>2022</v>
@@ -4083,11 +4998,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Casas de Cultura</t>
-        </is>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>174</v>
       </c>
       <c r="B170">
         <v>2022</v>
@@ -4105,17 +5018,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção da São Paulo Investimentos e Negócios</t>
-        </is>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>175</v>
       </c>
       <c r="B171">
         <v>2022</v>
       </c>
       <c r="C171">
-        <v>11387248.81</v>
+        <v>11387248.810000001</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -4127,11 +5038,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Praças, Canteiros Centrais e Remanescentes</t>
-        </is>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>176</v>
       </c>
       <c r="B172">
         <v>2022</v>
@@ -4149,11 +5058,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Preservação do Patrimônio Histórico, Artístico, Cultural e Arqueológico</t>
-        </is>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>177</v>
       </c>
       <c r="B173">
         <v>2022</v>
@@ -4171,20 +5078,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Parques Urbanos e Lineares</t>
-        </is>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>178</v>
       </c>
       <c r="B174">
         <v>2022</v>
       </c>
       <c r="C174">
-        <v>11059459.31</v>
+        <v>11059459.310000001</v>
       </c>
       <c r="D174">
-        <v>11059459.31</v>
+        <v>11059459.310000001</v>
       </c>
       <c r="E174">
         <v>1</v>
@@ -4193,11 +5098,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Bolsa-Trabalho</t>
-        </is>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>179</v>
       </c>
       <c r="B175">
         <v>2022</v>
@@ -4215,11 +5118,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Execução do Programa para a Valorização de Iniciativas Culturais</t>
-        </is>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>180</v>
       </c>
       <c r="B176">
         <v>2022</v>
@@ -4231,17 +5132,15 @@
         <v>10964074.67</v>
       </c>
       <c r="E176">
-        <v>0.9997811511837468</v>
+        <v>0.99978115118374677</v>
       </c>
       <c r="F176">
         <v>30</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Programa Melhor em Casa</t>
-        </is>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>181</v>
       </c>
       <c r="B177">
         <v>2022</v>
@@ -4259,11 +5158,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Manutenção de Unidades Habitacionais</t>
-        </is>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>182</v>
       </c>
       <c r="B178">
         <v>2022</v>
@@ -4272,20 +5169,18 @@
         <v>10776569.84</v>
       </c>
       <c r="D178">
-        <v>7181610.06</v>
+        <v>7181610.0599999996</v>
       </c>
       <c r="E178">
-        <v>0.6664096430149429</v>
+        <v>0.66640964301494288</v>
       </c>
       <c r="F178">
         <v>3</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Câmara Municipal - Comunicação</t>
-        </is>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>183</v>
       </c>
       <c r="B179">
         <v>2022</v>
@@ -4303,11 +5198,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Lei de Fomento à Dança</t>
-        </is>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>184</v>
       </c>
       <c r="B180">
         <v>2022</v>
@@ -4325,11 +5218,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Patrimônio</t>
-        </is>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>185</v>
       </c>
       <c r="B181">
         <v>2022</v>
@@ -4347,20 +5238,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Fundamental e Médio (EMEFM)</t>
-        </is>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>186</v>
       </c>
       <c r="B182">
         <v>2022</v>
       </c>
       <c r="C182">
-        <v>10344486.94</v>
+        <v>10344486.939999999</v>
       </c>
       <c r="D182">
-        <v>10344486.94</v>
+        <v>10344486.939999999</v>
       </c>
       <c r="E182">
         <v>1</v>
@@ -4369,20 +5258,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Centro Cultural São Paulo</t>
-        </is>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>187</v>
       </c>
       <c r="B183">
         <v>2022</v>
       </c>
       <c r="C183">
-        <v>10321076.05</v>
+        <v>10321076.050000001</v>
       </c>
       <c r="D183">
-        <v>10321076.05</v>
+        <v>10321076.050000001</v>
       </c>
       <c r="E183">
         <v>1</v>
@@ -4391,17 +5278,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Realização de Projetos Culturais</t>
-        </is>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>188</v>
       </c>
       <c r="B184">
         <v>2022</v>
       </c>
       <c r="C184">
-        <v>10160081.19</v>
+        <v>10160081.189999999</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -4413,11 +5298,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Cooperação Técnica Internacional</t>
-        </is>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>189</v>
       </c>
       <c r="B185">
         <v>2022</v>
@@ -4435,17 +5318,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Projetos de Fomento ao Turismo</t>
-        </is>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>190</v>
       </c>
       <c r="B186">
         <v>2022</v>
       </c>
       <c r="C186">
-        <v>9981513.9</v>
+        <v>9981513.9000000004</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -4457,17 +5338,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Serviços de DST / AIDS</t>
-        </is>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>191</v>
       </c>
       <c r="B187">
         <v>2022</v>
       </c>
       <c r="C187">
-        <v>9769126.93</v>
+        <v>9769126.9299999997</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -4479,42 +5358,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Programação da Virada Cultural</t>
-        </is>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>192</v>
       </c>
       <c r="B188">
         <v>2022</v>
       </c>
       <c r="C188">
-        <v>9690172.199999999</v>
+        <v>9690172.1999999993</v>
       </c>
       <c r="D188">
         <v>9097957</v>
       </c>
       <c r="E188">
-        <v>0.9388849663579767</v>
+        <v>0.93888496635797669</v>
       </c>
       <c r="F188">
         <v>24</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Programa Jovem Monitor Cultural</t>
-        </is>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>193</v>
       </c>
       <c r="B189">
         <v>2022</v>
       </c>
       <c r="C189">
-        <v>9674276.109999999</v>
+        <v>9674276.1099999994</v>
       </c>
       <c r="D189">
-        <v>9674276.109999999</v>
+        <v>9674276.1099999994</v>
       </c>
       <c r="E189">
         <v>1</v>
@@ -4523,11 +5398,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Inspeção de Obras de Artes Especiais - OAE</t>
-        </is>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>194</v>
       </c>
       <c r="B190">
         <v>2022</v>
@@ -4536,7 +5409,7 @@
         <v>9671093.290000001</v>
       </c>
       <c r="D190">
-        <v>5771998.94</v>
+        <v>5771998.9400000004</v>
       </c>
       <c r="E190">
         <v>0.5968300343011167</v>
@@ -4545,20 +5418,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Pólos Regionais de Esporte</t>
-        </is>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>195</v>
       </c>
       <c r="B191">
         <v>2022</v>
       </c>
       <c r="C191">
-        <v>9629770.710000001</v>
+        <v>9629770.7100000009</v>
       </c>
       <c r="D191">
-        <v>9629770.710000001</v>
+        <v>9629770.7100000009</v>
       </c>
       <c r="E191">
         <v>1</v>
@@ -4567,20 +5438,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Biblioteca Mario de Andrade</t>
-        </is>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>196</v>
       </c>
       <c r="B192">
         <v>2022</v>
       </c>
       <c r="C192">
-        <v>9620896.34</v>
+        <v>9620896.3399999999</v>
       </c>
       <c r="D192">
-        <v>9620896.34</v>
+        <v>9620896.3399999999</v>
       </c>
       <c r="E192">
         <v>1</v>
@@ -4589,20 +5458,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Compensações Ambientais</t>
-        </is>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>197</v>
       </c>
       <c r="B193">
         <v>2022</v>
       </c>
       <c r="C193">
-        <v>9556954.58</v>
+        <v>9556954.5800000001</v>
       </c>
       <c r="D193">
-        <v>9556954.58</v>
+        <v>9556954.5800000001</v>
       </c>
       <c r="E193">
         <v>1</v>
@@ -4611,17 +5478,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Compensação Financeira - Outros Fundos de Previdência</t>
-        </is>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>198</v>
       </c>
       <c r="B194">
         <v>2022</v>
       </c>
       <c r="C194">
-        <v>9491442.34</v>
+        <v>9491442.3399999999</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -4633,20 +5498,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Escola Municipal de Educação Artística - EMIA</t>
-        </is>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>199</v>
       </c>
       <c r="B195">
         <v>2022</v>
       </c>
       <c r="C195">
-        <v>9482790.99</v>
+        <v>9482790.9900000002</v>
       </c>
       <c r="D195">
-        <v>9482790.99</v>
+        <v>9482790.9900000002</v>
       </c>
       <c r="E195">
         <v>1</v>
@@ -4655,20 +5518,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Prêmio Zé Renato</t>
-        </is>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>200</v>
       </c>
       <c r="B196">
         <v>2022</v>
       </c>
       <c r="C196">
-        <v>9478914.550000001</v>
+        <v>9478914.5500000007</v>
       </c>
       <c r="D196">
-        <v>9478914.550000001</v>
+        <v>9478914.5500000007</v>
       </c>
       <c r="E196">
         <v>1</v>
@@ -4677,20 +5538,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Subvenção e Contribuições a Entidades Culturais</t>
-        </is>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>201</v>
       </c>
       <c r="B197">
         <v>2022</v>
       </c>
       <c r="C197">
-        <v>9297471.039999999</v>
+        <v>9297471.0399999991</v>
       </c>
       <c r="D197">
-        <v>9297471.039999999</v>
+        <v>9297471.0399999991</v>
       </c>
       <c r="E197">
         <v>1</v>
@@ -4699,20 +5558,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Programação de Atividades Culturais de Casas de Cultura</t>
-        </is>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>202</v>
       </c>
       <c r="B198">
         <v>2022</v>
       </c>
       <c r="C198">
-        <v>9167527.720000001</v>
+        <v>9167527.7200000007</v>
       </c>
       <c r="D198">
-        <v>9167527.720000001</v>
+        <v>9167527.7200000007</v>
       </c>
       <c r="E198">
         <v>1</v>
@@ -4721,20 +5578,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Escola Municipal de Ensino Fundamental (EMEF)</t>
-        </is>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>203</v>
       </c>
       <c r="B199">
         <v>2022</v>
       </c>
       <c r="C199">
-        <v>9050432.58</v>
+        <v>9050432.5800000001</v>
       </c>
       <c r="D199">
-        <v>9050432.58</v>
+        <v>9050432.5800000001</v>
       </c>
       <c r="E199">
         <v>1</v>
@@ -4743,11 +5598,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Ações para Promoção da Sustentabilidade Previdenciária</t>
-        </is>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>204</v>
       </c>
       <c r="B200">
         <v>2022</v>
@@ -4765,39 +5618,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Intervenções na Área de Mobilidade Urbana</t>
-        </is>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>205</v>
       </c>
       <c r="B201">
         <v>2022</v>
       </c>
       <c r="C201">
-        <v>8901911.27</v>
+        <v>8901911.2699999996</v>
       </c>
       <c r="D201">
         <v>4700473.43</v>
       </c>
       <c r="E201">
-        <v>0.5280296879436319</v>
+        <v>0.52802968794363192</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Transporte Escolar - Educação Especial</t>
-        </is>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>206</v>
       </c>
       <c r="B202">
         <v>2022</v>
       </c>
       <c r="C202">
-        <v>8848599.699999999</v>
+        <v>8848599.6999999993</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -4809,11 +5658,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Viveiros</t>
-        </is>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>207</v>
       </c>
       <c r="B203">
         <v>2022</v>
@@ -4831,39 +5678,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Fomento às Linguagens Artísticas</t>
-        </is>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>208</v>
       </c>
       <c r="B204">
         <v>2022</v>
       </c>
       <c r="C204">
-        <v>8668750.43</v>
+        <v>8668750.4299999997</v>
       </c>
       <c r="D204">
-        <v>8624381.93</v>
+        <v>8624381.9299999997</v>
       </c>
       <c r="E204">
-        <v>0.9948817882856041</v>
+        <v>0.99488178828560414</v>
       </c>
       <c r="F204">
         <v>29</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Ações Permanentes de Promoção dos Direitos da População Idosa</t>
-        </is>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>209</v>
       </c>
       <c r="B205">
         <v>2022</v>
       </c>
       <c r="C205">
-        <v>8330895.9</v>
+        <v>8330895.9000000004</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -4875,17 +5718,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Programação Artística</t>
-        </is>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>210</v>
       </c>
       <c r="B206">
         <v>2022</v>
       </c>
       <c r="C206">
-        <v>8164819.7</v>
+        <v>8164819.7000000002</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -4897,17 +5738,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Sistema de Avaliação Escolar dos Alunos da Rede Municipal de Ensino</t>
-        </is>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>211</v>
       </c>
       <c r="B207">
         <v>2022</v>
       </c>
       <c r="C207">
-        <v>8144055.060000001</v>
+        <v>8144055.0600000015</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -4919,20 +5758,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Remuneração dos Profissionais do Magistério - Centro Municipal de Educação Infantil( CEMEI)</t>
-        </is>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>212</v>
       </c>
       <c r="B208">
         <v>2022</v>
       </c>
       <c r="C208">
-        <v>8093438.78</v>
+        <v>8093438.7800000003</v>
       </c>
       <c r="D208">
-        <v>8093438.78</v>
+        <v>8093438.7800000003</v>
       </c>
       <c r="E208">
         <v>1</v>
@@ -4941,20 +5778,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Implantação do Memorial dos Aflitos</t>
-        </is>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>213</v>
       </c>
       <c r="B209">
         <v>2022</v>
       </c>
       <c r="C209">
-        <v>8091703.38</v>
+        <v>8091703.3799999999</v>
       </c>
       <c r="D209">
-        <v>8091703.38</v>
+        <v>8091703.3799999999</v>
       </c>
       <c r="E209">
         <v>1</v>
@@ -4963,20 +5798,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Programação de Atividades Culturais de Centros Culturais e Teatros</t>
-        </is>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>214</v>
       </c>
       <c r="B210">
         <v>2022</v>
       </c>
       <c r="C210">
-        <v>8079770.06</v>
+        <v>8079770.0599999996</v>
       </c>
       <c r="D210">
-        <v>8079770.06</v>
+        <v>8079770.0599999996</v>
       </c>
       <c r="E210">
         <v>1</v>
@@ -4985,20 +5818,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Rede Parceira - Educação Especial</t>
-        </is>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>215</v>
       </c>
       <c r="B211">
         <v>2022</v>
       </c>
       <c r="C211">
-        <v>7763494.99</v>
+        <v>7763494.9900000002</v>
       </c>
       <c r="D211">
-        <v>7763494.99</v>
+        <v>7763494.9900000002</v>
       </c>
       <c r="E211">
         <v>1</v>
@@ -5007,20 +5838,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Construção da Fábrica do Samba</t>
-        </is>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>216</v>
       </c>
       <c r="B212">
         <v>2022</v>
       </c>
       <c r="C212">
-        <v>7738081.35</v>
+        <v>7738081.3499999996</v>
       </c>
       <c r="D212">
-        <v>7738081.35</v>
+        <v>7738081.3499999996</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -5029,17 +5858,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Suporte e Manutenção da Coordenação de Imprensa</t>
-        </is>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>217</v>
       </c>
       <c r="B213">
         <v>2022</v>
       </c>
       <c r="C213">
-        <v>7676657.23</v>
+        <v>7676657.2300000004</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -5051,11 +5878,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Centro Olímpicos</t>
-        </is>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>218</v>
       </c>
       <c r="B214">
         <v>2022</v>
@@ -5073,11 +5898,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Qualificação Profissional e Empreendedora</t>
-        </is>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>219</v>
       </c>
       <c r="B215">
         <v>2022</v>
@@ -5095,20 +5918,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Programa de Garantia de Renda Familiar Mínima</t>
-        </is>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>220</v>
       </c>
       <c r="B216">
         <v>2022</v>
       </c>
       <c r="C216">
-        <v>7491383.61</v>
+        <v>7491383.6100000003</v>
       </c>
       <c r="D216">
-        <v>7491383.61</v>
+        <v>7491383.6100000003</v>
       </c>
       <c r="E216">
         <v>1</v>
@@ -5117,20 +5938,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Edificação da Câmara Municipal de São Paulo</t>
-        </is>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>221</v>
       </c>
       <c r="B217">
         <v>2022</v>
       </c>
       <c r="C217">
-        <v>7465375.64</v>
+        <v>7465375.6399999997</v>
       </c>
       <c r="D217">
-        <v>7465375.64</v>
+        <v>7465375.6399999997</v>
       </c>
       <c r="E217">
         <v>1</v>
@@ -5139,17 +5958,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Recuperação de Fachadas Históricas na Área Central</t>
-        </is>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>222</v>
       </c>
       <c r="B218">
         <v>2022</v>
       </c>
       <c r="C218">
-        <v>7340892.42</v>
+        <v>7340892.4199999999</v>
       </c>
       <c r="D218">
         <v>0</v>
@@ -5161,17 +5978,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Administração do Edifício Matarazzo</t>
-        </is>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>223</v>
       </c>
       <c r="B219">
         <v>2022</v>
       </c>
       <c r="C219">
-        <v>7280422.2</v>
+        <v>7280422.2000000002</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -5183,17 +5998,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Parceria Público Privada - Habitação</t>
-        </is>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>224</v>
       </c>
       <c r="B220">
         <v>2022</v>
       </c>
       <c r="C220">
-        <v>6960978.09</v>
+        <v>6960978.0899999999</v>
       </c>
       <c r="D220">
         <v>0</v>
@@ -5205,17 +6018,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Programa Nacional de Apoio à Gestão Adm. e Fiscal - PNAFM</t>
-        </is>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>225</v>
       </c>
       <c r="B221">
         <v>2022</v>
       </c>
       <c r="C221">
-        <v>6795896.8</v>
+        <v>6795896.7999999998</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -5227,20 +6038,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Plantio de Árvores</t>
-        </is>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>226</v>
       </c>
       <c r="B222">
         <v>2022</v>
       </c>
       <c r="C222">
-        <v>6594546.43</v>
+        <v>6594546.4299999997</v>
       </c>
       <c r="D222">
-        <v>6594546.43</v>
+        <v>6594546.4299999997</v>
       </c>
       <c r="E222">
         <v>1</v>
@@ -5249,64 +6058,58 @@
         <v>32</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Acessibilidade, Ampliação, Reforma e Requalificação de Terminais de Ônibus</t>
-        </is>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>227</v>
       </c>
       <c r="B223">
         <v>2022</v>
       </c>
       <c r="C223">
-        <v>6561837.649999999</v>
+        <v>6561837.6499999994</v>
       </c>
       <c r="D223">
-        <v>6515637.649999999</v>
+        <v>6515637.6499999994</v>
       </c>
       <c r="E223">
-        <v>0.9929592893844303</v>
+        <v>0.99295928938443034</v>
       </c>
       <c r="F223">
         <v>17</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Culturais</t>
-        </is>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>228</v>
       </c>
       <c r="B224">
         <v>2022</v>
       </c>
       <c r="C224">
-        <v>6325250.22</v>
+        <v>6325250.2199999997</v>
       </c>
       <c r="D224">
-        <v>6222857.03</v>
+        <v>6222857.0300000003</v>
       </c>
       <c r="E224">
-        <v>0.9838119937648886</v>
+        <v>0.98381199376488859</v>
       </c>
       <c r="F224">
         <v>32</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Casa da Mulher Brasileira</t>
-        </is>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>229</v>
       </c>
       <c r="B225">
         <v>2022</v>
       </c>
       <c r="C225">
-        <v>6248971.83</v>
+        <v>6248971.8300000001</v>
       </c>
       <c r="D225">
-        <v>6248971.83</v>
+        <v>6248971.8300000001</v>
       </c>
       <c r="E225">
         <v>1</v>
@@ -5315,17 +6118,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Administrativos</t>
-        </is>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>230</v>
       </c>
       <c r="B226">
         <v>2022</v>
       </c>
       <c r="C226">
-        <v>6237478.64</v>
+        <v>6237478.6399999997</v>
       </c>
       <c r="D226">
         <v>0</v>
@@ -5337,20 +6138,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Equipamentos Públicos Voltados ao Atendimento da População LGBTI</t>
-        </is>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>231</v>
       </c>
       <c r="B227">
         <v>2022</v>
       </c>
       <c r="C227">
-        <v>6165357.33</v>
+        <v>6165357.3300000001</v>
       </c>
       <c r="D227">
-        <v>6165357.33</v>
+        <v>6165357.3300000001</v>
       </c>
       <c r="E227">
         <v>1</v>
@@ -5359,20 +6158,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Centro Integrado de Jovens e Adultos (CIEJA)</t>
-        </is>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>232</v>
       </c>
       <c r="B228">
         <v>2022</v>
       </c>
       <c r="C228">
-        <v>5948992.72</v>
+        <v>5948992.7199999997</v>
       </c>
       <c r="D228">
-        <v>5948992.72</v>
+        <v>5948992.7199999997</v>
       </c>
       <c r="E228">
         <v>1</v>
@@ -5381,17 +6178,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Fomento às Cadeias Produtivas, Vocações Produtivas e Projetos Locais</t>
-        </is>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>233</v>
       </c>
       <c r="B229">
         <v>2022</v>
       </c>
       <c r="C229">
-        <v>5934897.28</v>
+        <v>5934897.2800000003</v>
       </c>
       <c r="D229">
         <v>0</v>
@@ -5403,17 +6198,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Serviços de Atendimento e Manejo da Fauna Silvestre</t>
-        </is>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>234</v>
       </c>
       <c r="B230">
         <v>2022</v>
       </c>
       <c r="C230">
-        <v>5792320.92</v>
+        <v>5792320.9199999999</v>
       </c>
       <c r="D230">
         <v>0</v>
@@ -5425,11 +6218,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Servidores Comissionados no Hospital Serv. Públco Municipal - HSPM</t>
-        </is>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>235</v>
       </c>
       <c r="B231">
         <v>2022</v>
@@ -5447,17 +6238,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Construção de Corredores de Ônibus</t>
-        </is>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>236</v>
       </c>
       <c r="B232">
         <v>2022</v>
       </c>
       <c r="C232">
-        <v>5287276.689999999</v>
+        <v>5287276.6899999985</v>
       </c>
       <c r="D232">
         <v>0</v>
@@ -5469,17 +6258,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para a População LGBTI+</t>
-        </is>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>237</v>
       </c>
       <c r="B233">
         <v>2022</v>
       </c>
       <c r="C233">
-        <v>5167420.9</v>
+        <v>5167420.9000000004</v>
       </c>
       <c r="D233">
         <v>0</v>
@@ -5491,17 +6278,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Juventude</t>
-        </is>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>238</v>
       </c>
       <c r="B234">
         <v>2022</v>
       </c>
       <c r="C234">
-        <v>5057261.65</v>
+        <v>5057261.6500000004</v>
       </c>
       <c r="D234">
         <v>0</v>
@@ -5513,11 +6298,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Políticas de Promoção Cultural nas Bibliotecas Públicas</t>
-        </is>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>239</v>
       </c>
       <c r="B235">
         <v>2022</v>
@@ -5535,11 +6318,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Políticas de promoção cultural</t>
-        </is>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>240</v>
       </c>
       <c r="B236">
         <v>2022</v>
@@ -5557,11 +6338,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos Culturais</t>
-        </is>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>241</v>
       </c>
       <c r="B237">
         <v>2022</v>
@@ -5579,11 +6358,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Ciclovias, Ciclofaixas e Ciclorrotas</t>
-        </is>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>242</v>
       </c>
       <c r="B238">
         <v>2022</v>
@@ -5601,11 +6378,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Educação Indígena</t>
-        </is>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>243</v>
       </c>
       <c r="B239">
         <v>2022</v>
@@ -5623,11 +6398,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Centros de Educação Infantil (CEI)</t>
-        </is>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>244</v>
       </c>
       <c r="B240">
         <v>2022</v>
@@ -5645,11 +6418,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>Oficina nos Equipamentos Culturais</t>
-        </is>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>245</v>
       </c>
       <c r="B241">
         <v>2022</v>
@@ -5667,11 +6438,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>Construção de Escolas Municipais de Educação Infantil (EMEI)</t>
-        </is>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>246</v>
       </c>
       <c r="B242">
         <v>2022</v>
@@ -5689,11 +6458,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>Despesas Administrativas para Execução de Ações Judiciais - Processamento de Feitos</t>
-        </is>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>247</v>
       </c>
       <c r="B243">
         <v>2022</v>
@@ -5711,11 +6478,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Bilíngue para Surdos (EMEBS)</t>
-        </is>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>248</v>
       </c>
       <c r="B244">
         <v>2022</v>
@@ -5733,11 +6498,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>Edição e Publicação do Diário Oficial da Cidade de São Paulo</t>
-        </is>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>249</v>
       </c>
       <c r="B245">
         <v>2022</v>
@@ -5755,11 +6518,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - CEU</t>
-        </is>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>250</v>
       </c>
       <c r="B246">
         <v>2022</v>
@@ -5777,11 +6538,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>Ações de Cooperação para o Desenvolvimento Sustentável</t>
-        </is>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>251</v>
       </c>
       <c r="B247">
         <v>2022</v>
@@ -5799,11 +6558,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Projetos para Inclusão da Pessoa com Deficiência</t>
-        </is>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>252</v>
       </c>
       <c r="B248">
         <v>2022</v>
@@ -5821,11 +6578,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Auxílio Funeral</t>
-        </is>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>253</v>
       </c>
       <c r="B249">
         <v>2022</v>
@@ -5843,11 +6598,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>PROCONECTA - Promoção da Conectividade e Inclusão Digital</t>
-        </is>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>254</v>
       </c>
       <c r="B250">
         <v>2022</v>
@@ -5859,17 +6612,15 @@
         <v>3192905.08</v>
       </c>
       <c r="E250">
-        <v>0.9388567769546545</v>
+        <v>0.93885677695465453</v>
       </c>
       <c r="F250">
         <v>1</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Execução do Programa Museu de Arte de Rua - MAR</t>
-        </is>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>255</v>
       </c>
       <c r="B251">
         <v>2022</v>
@@ -5881,17 +6632,15 @@
         <v>443498</v>
       </c>
       <c r="E251">
-        <v>0.1332248964900218</v>
+        <v>0.13322489649002181</v>
       </c>
       <c r="F251">
         <v>1</v>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>Fomento ao Circo/Edital Xamego</t>
-        </is>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>256</v>
       </c>
       <c r="B252">
         <v>2022</v>
@@ -5909,11 +6658,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>Programação de Atividades Culturais do Centro Cultural São Paulo</t>
-        </is>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>257</v>
       </c>
       <c r="B253">
         <v>2022</v>
@@ -5931,11 +6678,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>Rádios Comunitárias - Lei nº 16.572/2016</t>
-        </is>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>258</v>
       </c>
       <c r="B254">
         <v>2022</v>
@@ -5947,17 +6692,15 @@
         <v>3103200</v>
       </c>
       <c r="E254">
-        <v>0.9627699180938198</v>
+        <v>0.96276991809381984</v>
       </c>
       <c r="F254">
         <v>18</v>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações Para Criança e Adolescente</t>
-        </is>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>259</v>
       </c>
       <c r="B255">
         <v>2022</v>
@@ -5975,11 +6718,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>Fomento à Música</t>
-        </is>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>260</v>
       </c>
       <c r="B256">
         <v>2022</v>
@@ -5997,11 +6738,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>Estudos, Planos e Projetos Ambientais</t>
-        </is>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>261</v>
       </c>
       <c r="B257">
         <v>2022</v>
@@ -6013,17 +6752,15 @@
         <v>1694402.61</v>
       </c>
       <c r="E257">
-        <v>0.5524003278130974</v>
+        <v>0.55240032781309745</v>
       </c>
       <c r="F257">
         <v>4</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Mulheres</t>
-        </is>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>262</v>
       </c>
       <c r="B258">
         <v>2022</v>
@@ -6041,11 +6778,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>Apoio à Cultura Negra</t>
-        </is>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>263</v>
       </c>
       <c r="B259">
         <v>2022</v>
@@ -6057,17 +6792,15 @@
         <v>282720</v>
       </c>
       <c r="E259">
-        <v>0.0993195061086028</v>
+        <v>9.9319506108602795E-2</v>
       </c>
       <c r="F259">
         <v>1</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>Obras de Combate a Enchentes e Alagamentos</t>
-        </is>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>264</v>
       </c>
       <c r="B260">
         <v>2022</v>
@@ -6085,11 +6818,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Rede de Iluminação Pública</t>
-        </is>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>265</v>
       </c>
       <c r="B261">
         <v>2022</v>
@@ -6101,17 +6832,15 @@
         <v>18067.57</v>
       </c>
       <c r="E261">
-        <v>0.006452708964049634</v>
+        <v>6.4527089640496341E-3</v>
       </c>
       <c r="F261">
         <v>1</v>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Centro de Referência de Segurança Alimentar e Nutricional</t>
-        </is>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>266</v>
       </c>
       <c r="B262">
         <v>2022</v>
@@ -6129,11 +6858,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>Programa Piá</t>
-        </is>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>267</v>
       </c>
       <c r="B263">
         <v>2022</v>
@@ -6151,17 +6878,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>Ações de Educação de Trânsito</t>
-        </is>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>268</v>
       </c>
       <c r="B264">
         <v>2022</v>
       </c>
       <c r="C264">
-        <v>2541256.49</v>
+        <v>2541256.4900000002</v>
       </c>
       <c r="D264">
         <v>0</v>
@@ -6173,11 +6898,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>Programa Vocacional</t>
-        </is>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>269</v>
       </c>
       <c r="B265">
         <v>2022</v>
@@ -6195,20 +6918,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Arquivo Histórico Municipal</t>
-        </is>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>270</v>
       </c>
       <c r="B266">
         <v>2022</v>
       </c>
       <c r="C266">
-        <v>2444862.51</v>
+        <v>2444862.5099999998</v>
       </c>
       <c r="D266">
-        <v>2444862.51</v>
+        <v>2444862.5099999998</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -6217,11 +6938,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>Programação de Atividades Culturais do Departamento dos Museus Municipais</t>
-        </is>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>271</v>
       </c>
       <c r="B267">
         <v>2022</v>
@@ -6239,42 +6958,38 @@
         <v>6</v>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção das Centrais de Triagem - Coleta Seletiva</t>
-        </is>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>272</v>
       </c>
       <c r="B268">
         <v>2022</v>
       </c>
       <c r="C268">
-        <v>2261529.78</v>
+        <v>2261529.7799999998</v>
       </c>
       <c r="D268">
         <v>43859.48</v>
       </c>
       <c r="E268">
-        <v>0.01939372206719294</v>
+        <v>1.9393722067192941E-2</v>
       </c>
       <c r="F268">
         <v>1</v>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>Ações Municipais de Abastecimento</t>
-        </is>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>273</v>
       </c>
       <c r="B269">
         <v>2022</v>
       </c>
       <c r="C269">
-        <v>2221232.05</v>
+        <v>2221232.0499999998</v>
       </c>
       <c r="D269">
-        <v>2221232.05</v>
+        <v>2221232.0499999998</v>
       </c>
       <c r="E269">
         <v>1</v>
@@ -6283,17 +6998,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>Educação Ambiental</t>
-        </is>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>274</v>
       </c>
       <c r="B270">
         <v>2022</v>
       </c>
       <c r="C270">
-        <v>2210050.72</v>
+        <v>2210050.7200000002</v>
       </c>
       <c r="D270">
         <v>0</v>
@@ -6305,11 +7018,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>Programação de Atividades Culturais nas Bibliotecas Públicas</t>
-        </is>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>275</v>
       </c>
       <c r="B271">
         <v>2022</v>
@@ -6327,11 +7038,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>Manutenção de Ciclovias, Ciclofaixas e Ciclorrotas</t>
-        </is>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>276</v>
       </c>
       <c r="B272">
         <v>2022</v>
@@ -6349,11 +7058,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento da População de Rua</t>
-        </is>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>277</v>
       </c>
       <c r="B273">
         <v>2022</v>
@@ -6371,11 +7078,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Defesa Civil</t>
-        </is>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>278</v>
       </c>
       <c r="B274">
         <v>2022</v>
@@ -6387,17 +7092,15 @@
         <v>1960226.32</v>
       </c>
       <c r="E274">
-        <v>0.9413728976263565</v>
+        <v>0.94137289762635645</v>
       </c>
       <c r="F274">
         <v>32</v>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Mês do Hip Hop</t>
-        </is>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>279</v>
       </c>
       <c r="B275">
         <v>2022</v>
@@ -6415,11 +7118,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>Política Municipal de Desenvolvimento Econômico</t>
-        </is>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>280</v>
       </c>
       <c r="B276">
         <v>2022</v>
@@ -6437,11 +7138,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Planetários Municipais</t>
-        </is>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>281</v>
       </c>
       <c r="B277">
         <v>2022</v>
@@ -6459,11 +7158,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Imigrantes</t>
-        </is>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>282</v>
       </c>
       <c r="B278">
         <v>2022</v>
@@ -6481,11 +7178,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>Locação Social</t>
-        </is>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>283</v>
       </c>
       <c r="B279">
         <v>2022</v>
@@ -6503,11 +7198,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>Programa Mãos e Mentes Paulistanas</t>
-        </is>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>284</v>
       </c>
       <c r="B280">
         <v>2022</v>
@@ -6525,11 +7218,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados à Promoção da Igualdade Racial</t>
-        </is>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>285</v>
       </c>
       <c r="B281">
         <v>2022</v>
@@ -6547,11 +7238,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Conselhos e Espaços Participativos Municipais</t>
-        </is>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>286</v>
       </c>
       <c r="B282">
         <v>2022</v>
@@ -6563,17 +7252,15 @@
         <v>963229.24</v>
       </c>
       <c r="E282">
-        <v>0.5447600262974467</v>
+        <v>0.54476002629744669</v>
       </c>
       <c r="F282">
         <v>12</v>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>Manutenção da Ouvidoria de Direitos Humanos</t>
-        </is>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>287</v>
       </c>
       <c r="B283">
         <v>2022</v>
@@ -6591,11 +7278,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>Fiscalização, Monitoramento e Controle Ambiental</t>
-        </is>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>288</v>
       </c>
       <c r="B284">
         <v>2022</v>
@@ -6613,11 +7298,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>Execução de Serviços Médicos de Tratamento de Radioterapia</t>
-        </is>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>289</v>
       </c>
       <c r="B285">
         <v>2022</v>
@@ -6635,11 +7318,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação nas Áreas de Parada e Plataforma de Embarque de Faixa Exclusiva de Ônibus</t>
-        </is>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>290</v>
       </c>
       <c r="B286">
         <v>2022</v>
@@ -6657,11 +7338,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>Reembolso ao Serviço Funerário</t>
-        </is>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>291</v>
       </c>
       <c r="B287">
         <v>2022</v>
@@ -6679,11 +7358,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Melhoria de Bairros no âmbito da Subprefeitura da Capela do Socorro.</t>
-        </is>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>292</v>
       </c>
       <c r="B288">
         <v>2022</v>
@@ -6701,11 +7378,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>Bloqueios Judiciais</t>
-        </is>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>293</v>
       </c>
       <c r="B289">
         <v>2022</v>
@@ -6723,11 +7398,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>Centro Municipal para Pessoas com Transtorno do Espectro Autista</t>
-        </is>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>294</v>
       </c>
       <c r="B290">
         <v>2022</v>
@@ -6745,11 +7418,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>Apoio e Suporte Técnico para o Desenvolvimento de Estudos e Projetos Urbanos</t>
-        </is>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>295</v>
       </c>
       <c r="B291">
         <v>2022</v>
@@ -6767,11 +7438,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>Ações e Atividades Culturais da Biblioteca Mario de Andrade</t>
-        </is>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>296</v>
       </c>
       <c r="B292">
         <v>2022</v>
@@ -6789,11 +7458,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>Difusão, Fomento e Pesquisas Aplicadas à Gestão de Tecnologia, Inovação e Atendimento ao Cidadão</t>
-        </is>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>297</v>
       </c>
       <c r="B293">
         <v>2022</v>
@@ -6811,11 +7478,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>Projeto de Intervenção Urbana - PIU</t>
-        </is>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>298</v>
       </c>
       <c r="B294">
         <v>2022</v>
@@ -6827,17 +7492,15 @@
         <v>52127.69</v>
       </c>
       <c r="E294">
-        <v>0.03674549254232232</v>
+        <v>3.6745492542322317E-2</v>
       </c>
       <c r="F294">
         <v>1</v>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>Manutenção de Prédios Administrativos</t>
-        </is>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>299</v>
       </c>
       <c r="B295">
         <v>2022</v>
@@ -6849,17 +7512,15 @@
         <v>846052.55</v>
       </c>
       <c r="E295">
-        <v>0.5971699516279328</v>
+        <v>0.59716995162793285</v>
       </c>
       <c r="F295">
         <v>12</v>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>Restituição de Amortização Extraordinária e Liquidação Antecipada</t>
-        </is>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>300</v>
       </c>
       <c r="B296">
         <v>2022</v>
@@ -6877,11 +7538,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Centros de Estudos de Línguas Paulistano - CELP</t>
-        </is>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>301</v>
       </c>
       <c r="B297">
         <v>2022</v>
@@ -6899,11 +7558,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>Programa de Articulação Criativa</t>
-        </is>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>302</v>
       </c>
       <c r="B298">
         <v>2022</v>
@@ -6915,17 +7572,15 @@
         <v>850710</v>
       </c>
       <c r="E298">
-        <v>0.6206345616505314</v>
+        <v>0.62063456165053144</v>
       </c>
       <c r="F298">
         <v>32</v>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Equipamentos Públicos Voltados para Pessoa Idosa</t>
-        </is>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>303</v>
       </c>
       <c r="B299">
         <v>2022</v>
@@ -6943,17 +7598,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>Desenvolvimento de Estudos, Projetos  e Instrumentos de Políticas Urbanas</t>
-        </is>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>304</v>
       </c>
       <c r="B300">
         <v>2022</v>
       </c>
       <c r="C300">
-        <v>1308867.34</v>
+        <v>1308867.3400000001</v>
       </c>
       <c r="D300">
         <v>0</v>
@@ -6965,11 +7618,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>Equipes de Alto Desempenho com Representatividade em Competições Locais, Regionais, Nacionais e Mundiais</t>
-        </is>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>305</v>
       </c>
       <c r="B301">
         <v>2022</v>
@@ -6987,11 +7638,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>Programa de Iniciação Artística para a Primeira Infância - PIAPI</t>
-        </is>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>306</v>
       </c>
       <c r="B302">
         <v>2022</v>
@@ -7009,11 +7658,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>Manutenção de Modalidades Desportivas do Centro Olímpico de Treinamento e Pesquisa (COTP)</t>
-        </is>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>307</v>
       </c>
       <c r="B303">
         <v>2022</v>
@@ -7031,12 +7678,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operação e Manutenção do Portal da PMSP_x000D__x000D_
-</t>
-        </is>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>308</v>
       </c>
       <c r="B304">
         <v>2022</v>
@@ -7054,17 +7698,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>Vivência Prática de Gestão de Documentos</t>
-        </is>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>309</v>
       </c>
       <c r="B305">
         <v>2022</v>
       </c>
       <c r="C305">
-        <v>1087835.41</v>
+        <v>1087835.4099999999</v>
       </c>
       <c r="D305">
         <v>0</v>
@@ -7076,11 +7718,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>Difusão, Fomento e Pesquisas Aplicadas para a Gestão Participativa e Desenvolvimento Urbano</t>
-        </is>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>310</v>
       </c>
       <c r="B306">
         <v>2022</v>
@@ -7098,11 +7738,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>Fomento às Comunidades do Samba</t>
-        </is>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>311</v>
       </c>
       <c r="B307">
         <v>2022</v>
@@ -7120,11 +7758,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Imigrantes e Promoção ao Trabalho Decente</t>
-        </is>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>312</v>
       </c>
       <c r="B308">
         <v>2022</v>
@@ -7142,11 +7778,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Atualização do Currículo da Rede Municipal de Ensino</t>
-        </is>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>313</v>
       </c>
       <c r="B309">
         <v>2022</v>
@@ -7164,11 +7798,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção do VAI TEC</t>
-        </is>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>314</v>
       </c>
       <c r="B310">
         <v>2022</v>
@@ -7186,11 +7818,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>Ações e Atividades Culturais do Departamento do Patrimônio Histórico</t>
-        </is>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>315</v>
       </c>
       <c r="B311">
         <v>2022</v>
@@ -7202,26 +7832,24 @@
         <v>1027898.3</v>
       </c>
       <c r="E311">
-        <v>0.9994166251903381</v>
+        <v>0.99941662519033814</v>
       </c>
       <c r="F311">
         <v>31</v>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>Construção de Galeria, bem como Boca de Lobo para Captação de Água Pluvial, na Viela João Carlos Pereira, Altura no Número 13</t>
-        </is>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>316</v>
       </c>
       <c r="B312">
         <v>2022</v>
       </c>
       <c r="C312">
-        <v>954124.3200000001</v>
+        <v>954124.32000000007</v>
       </c>
       <c r="D312">
-        <v>954124.3200000001</v>
+        <v>954124.32000000007</v>
       </c>
       <c r="E312">
         <v>1</v>
@@ -7230,11 +7858,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>Prospecção de Problemas Públicos e Ideação de Alternativas para Inovação</t>
-        </is>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>317</v>
       </c>
       <c r="B313">
         <v>2022</v>
@@ -7252,11 +7878,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>FUMCAD - Multas Revertidas ao Fundo</t>
-        </is>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>318</v>
       </c>
       <c r="B314">
         <v>2022</v>
@@ -7274,11 +7898,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>Tarifa de Arrecadação de Multas</t>
-        </is>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>319</v>
       </c>
       <c r="B315">
         <v>2022</v>
@@ -7296,11 +7918,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>"Comemoração do ""Dia Municipal da Cultura Evangélica"" - 09 de Julho - Lei nº 14.232 de 07 de Novembro de 2006"</t>
-        </is>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>320</v>
       </c>
       <c r="B316">
         <v>2022</v>
@@ -7318,17 +7938,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção da Infraestrutura Turística</t>
-        </is>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>321</v>
       </c>
       <c r="B317">
         <v>2022</v>
       </c>
       <c r="C317">
-        <v>882697.9399999999</v>
+        <v>882697.94</v>
       </c>
       <c r="D317">
         <v>0</v>
@@ -7340,11 +7958,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>Manutenção das Instalações da Guarda Civil Metropolitana</t>
-        </is>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>322</v>
       </c>
       <c r="B318">
         <v>2022</v>
@@ -7362,11 +7978,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>Programa Aldeias</t>
-        </is>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>323</v>
       </c>
       <c r="B319">
         <v>2022</v>
@@ -7384,11 +7998,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>Plano Municipal do Livro, Leitura, Literatura e Biblioteca (PMLLLB)</t>
-        </is>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>324</v>
       </c>
       <c r="B320">
         <v>2022</v>
@@ -7406,20 +8018,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>Implantação e Construção de Ecopontos</t>
-        </is>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>325</v>
       </c>
       <c r="B321">
         <v>2022</v>
       </c>
       <c r="C321">
-        <v>840970.5699999999</v>
+        <v>840970.57</v>
       </c>
       <c r="D321">
-        <v>840970.5699999999</v>
+        <v>840970.57</v>
       </c>
       <c r="E321">
         <v>1</v>
@@ -7428,11 +8038,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>Programação de Atividades e Eventos da Cultura Reggae</t>
-        </is>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>326</v>
       </c>
       <c r="B322">
         <v>2022</v>
@@ -7450,11 +8058,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>Acompanhamento das Aprendizagens e Permanência Escolar</t>
-        </is>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>327</v>
       </c>
       <c r="B323">
         <v>2022</v>
@@ -7472,20 +8078,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Unidades de Conservação</t>
-        </is>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>328</v>
       </c>
       <c r="B324">
         <v>2022</v>
       </c>
       <c r="C324">
-        <v>815593.0699999999</v>
+        <v>815593.07</v>
       </c>
       <c r="D324">
-        <v>815593.0699999999</v>
+        <v>815593.07</v>
       </c>
       <c r="E324">
         <v>1</v>
@@ -7494,33 +8098,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Fomento e Difusão do Forró</t>
-        </is>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>329</v>
       </c>
       <c r="B325">
         <v>2022</v>
       </c>
       <c r="C325">
-        <v>808367.1899999999</v>
+        <v>808367.19</v>
       </c>
       <c r="D325">
-        <v>796367.1899999999</v>
+        <v>796367.19</v>
       </c>
       <c r="E325">
-        <v>0.9851552609402665</v>
+        <v>0.98515526094026651</v>
       </c>
       <c r="F325">
         <v>17</v>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Centro Municipal de Capacitação e Treinamento (CMCT)</t>
-        </is>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>330</v>
       </c>
       <c r="B326">
         <v>2022</v>
@@ -7538,11 +8138,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Centro Público de Economia Solidária e Direitos Humanos</t>
-        </is>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>331</v>
       </c>
       <c r="B327">
         <v>2022</v>
@@ -7560,11 +8158,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>Publicação de Editais e Outras Publicações Legais e de Interesse do Município</t>
-        </is>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>332</v>
       </c>
       <c r="B328">
         <v>2022</v>
@@ -7582,20 +8178,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>Implantação de Estrutura Turística no Triângulo Histórico</t>
-        </is>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>333</v>
       </c>
       <c r="B329">
         <v>2022</v>
       </c>
       <c r="C329">
-        <v>762391.5600000001</v>
+        <v>762391.56</v>
       </c>
       <c r="D329">
-        <v>762391.5600000001</v>
+        <v>762391.56</v>
       </c>
       <c r="E329">
         <v>1</v>
@@ -7604,17 +8198,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>Promoção à Saúde do Servidor Municipal</t>
-        </is>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>334</v>
       </c>
       <c r="B330">
         <v>2022</v>
       </c>
       <c r="C330">
-        <v>725838.8500000001</v>
+        <v>725838.85000000009</v>
       </c>
       <c r="D330">
         <v>0</v>
@@ -7626,11 +8218,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Equipamentos de Atenção Básica e Especialidades</t>
-        </is>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>335</v>
       </c>
       <c r="B331">
         <v>2022</v>
@@ -7648,11 +8238,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Centro de Referência da Dança</t>
-        </is>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>336</v>
       </c>
       <c r="B332">
         <v>2022</v>
@@ -7670,17 +8258,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Bolsa Atleta</t>
-        </is>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>337</v>
       </c>
       <c r="B333">
         <v>2022</v>
       </c>
       <c r="C333">
-        <v>673035.5599999999</v>
+        <v>673035.55999999994</v>
       </c>
       <c r="D333">
         <v>0</v>
@@ -7692,11 +8278,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Centro de Memória do Circo</t>
-        </is>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>338</v>
       </c>
       <c r="B334">
         <v>2022</v>
@@ -7714,11 +8298,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Patrulha Agroecológica Mecanizada</t>
-        </is>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>339</v>
       </c>
       <c r="B335">
         <v>2022</v>
@@ -7730,17 +8312,15 @@
         <v>109459.85</v>
       </c>
       <c r="E335">
-        <v>0.1896103896103896</v>
+        <v>0.18961038961038959</v>
       </c>
       <c r="F335">
         <v>1</v>
       </c>
     </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Mercado Municipal</t>
-        </is>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>340</v>
       </c>
       <c r="B336">
         <v>2022</v>
@@ -7752,17 +8332,15 @@
         <v>109830.58</v>
       </c>
       <c r="E336">
-        <v>0.1924638811006724</v>
+        <v>0.19246388110067239</v>
       </c>
       <c r="F336">
         <v>1</v>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Pesquisa de Satisfação do Cidadão em Relação aos Serviços, Políticas e Programas</t>
-        </is>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>341</v>
       </c>
       <c r="B337">
         <v>2022</v>
@@ -7780,11 +8358,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Reforma e Acessibilidade em Passeios Públicos</t>
-        </is>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>342</v>
       </c>
       <c r="B338">
         <v>2022</v>
@@ -7802,11 +8378,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>Administração do Autódromo de Interlagos</t>
-        </is>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>343</v>
       </c>
       <c r="B339">
         <v>2022</v>
@@ -7824,11 +8398,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Espaços Lúdicos e Educativos</t>
-        </is>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>344</v>
       </c>
       <c r="B340">
         <v>2022</v>
@@ -7846,11 +8418,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>Território Hip Hop (Vocacional Hip Hop)</t>
-        </is>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>345</v>
       </c>
       <c r="B341">
         <v>2022</v>
@@ -7868,11 +8438,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>Gestão do Patrimônio Imobiliário Municipal</t>
-        </is>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>346</v>
       </c>
       <c r="B342">
         <v>2022</v>
@@ -7890,11 +8458,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>Fomento e Apoio ao Cooperativismo</t>
-        </is>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>347</v>
       </c>
       <c r="B343">
         <v>2022</v>
@@ -7912,11 +8478,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Revitalização e Manutenção - Subprefeitura de Capela do Socorro</t>
-        </is>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>348</v>
       </c>
       <c r="B344">
         <v>2022</v>
@@ -7934,11 +8498,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos da Assistência Social</t>
-        </is>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>349</v>
       </c>
       <c r="B345">
         <v>2022</v>
@@ -7956,11 +8518,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Implantação de Pontos e Pontões de Cultura - Cultura Viva</t>
-        </is>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>350</v>
       </c>
       <c r="B346">
         <v>2022</v>
@@ -7978,17 +8538,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos de Saúde Animal</t>
-        </is>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>351</v>
       </c>
       <c r="B347">
         <v>2022</v>
       </c>
       <c r="C347">
-        <v>316555.85</v>
+        <v>316555.84999999998</v>
       </c>
       <c r="D347">
         <v>0</v>
@@ -8000,11 +8558,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Acordos Judiciais ou Administrativos</t>
-        </is>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>352</v>
       </c>
       <c r="B348">
         <v>2022</v>
@@ -8022,11 +8578,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Serviço de Moto Verificação</t>
-        </is>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>353</v>
       </c>
       <c r="B349">
         <v>2022</v>
@@ -8044,20 +8598,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Projetos Sociais Diversos</t>
-        </is>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>354</v>
       </c>
       <c r="B350">
         <v>2022</v>
       </c>
       <c r="C350">
-        <v>276542.6</v>
+        <v>276542.59999999998</v>
       </c>
       <c r="D350">
-        <v>276542.6</v>
+        <v>276542.59999999998</v>
       </c>
       <c r="E350">
         <v>1</v>
@@ -8066,11 +8618,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Expansão e Aperfeiçoamento das Atividades do TCM</t>
-        </is>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>355</v>
       </c>
       <c r="B351">
         <v>2022</v>
@@ -8088,11 +8638,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Central de Interpretação de Libras, Intérpretes e Guias-Intérpretes</t>
-        </is>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>356</v>
       </c>
       <c r="B352">
         <v>2022</v>
@@ -8110,11 +8658,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>Construção de Terminais de Ônibus</t>
-        </is>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>357</v>
       </c>
       <c r="B353">
         <v>2022</v>
@@ -8132,11 +8678,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>Escola do Parlamento</t>
-        </is>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>358</v>
       </c>
       <c r="B354">
         <v>2022</v>
@@ -8154,11 +8698,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Ações de Audiovisual</t>
-        </is>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>359</v>
       </c>
       <c r="B355">
         <v>2022</v>
@@ -8176,11 +8718,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Implantação da Casa de Cultura Cidade Ademar</t>
-        </is>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>360</v>
       </c>
       <c r="B356">
         <v>2022</v>
@@ -8198,11 +8738,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Expansão e Aperfeiçoamento das Atividades da CMSP</t>
-        </is>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>361</v>
       </c>
       <c r="B357">
         <v>2022</v>
@@ -8220,11 +8758,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação das Instalações para a Guarda Civil Metropolitana</t>
-        </is>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>362</v>
       </c>
       <c r="B358">
         <v>2022</v>
@@ -8242,11 +8778,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>PMLLLB - Festas Literárias</t>
-        </is>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>363</v>
       </c>
       <c r="B359">
         <v>2022</v>
@@ -8264,11 +8798,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Reforma da Escadaria na Viela Inominada, Localizada na Rua Rua José Ferreira Dantas, Nº 11, Jardim Boa Vista.</t>
-        </is>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>364</v>
       </c>
       <c r="B360">
         <v>2022</v>
@@ -8286,11 +8818,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Unidades Habitacionais</t>
-        </is>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>365</v>
       </c>
       <c r="B361">
         <v>2022</v>
@@ -8308,11 +8838,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Unidade de Vigilância em Saúde</t>
-        </is>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>366</v>
       </c>
       <c r="B362">
         <v>2022</v>
@@ -8330,11 +8858,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Construção de Escolas Municipais de Ensino Fundamental (EMEF)</t>
-        </is>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>367</v>
       </c>
       <c r="B363">
         <v>2022</v>
@@ -8352,11 +8878,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Execução de Projetos Visando o Combate das Desigualdades Raciais na Saúde</t>
-        </is>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>368</v>
       </c>
       <c r="B364">
         <v>2022</v>
@@ -8374,11 +8898,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação no Serviço de Guinchamento</t>
-        </is>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>369</v>
       </c>
       <c r="B365">
         <v>2022</v>
@@ -8396,20 +8918,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Reforma da Quadra da Praça Gilberto Reis Possani, Parque São Rafael</t>
-        </is>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>370</v>
       </c>
       <c r="B366">
         <v>2022</v>
       </c>
       <c r="C366">
-        <v>133159.64</v>
+        <v>133159.64000000001</v>
       </c>
       <c r="D366">
-        <v>133159.64</v>
+        <v>133159.64000000001</v>
       </c>
       <c r="E366">
         <v>1</v>
@@ -8418,11 +8938,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>Ações do Programa Agentes de Governo Aberto</t>
-        </is>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>371</v>
       </c>
       <c r="B367">
         <v>2022</v>
@@ -8440,11 +8958,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos do Patrimônio Histórico</t>
-        </is>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>372</v>
       </c>
       <c r="B368">
         <v>2022</v>
@@ -8456,17 +8972,15 @@
         <v>109472.2</v>
       </c>
       <c r="E368">
-        <v>0.9801093811244413</v>
+        <v>0.98010938112444135</v>
       </c>
       <c r="F368">
         <v>7</v>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>Promoção da Transparência, do Acesso à Informação e do Controle Social</t>
-        </is>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>373</v>
       </c>
       <c r="B369">
         <v>2022</v>
@@ -8484,20 +8998,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Incentivo à Economia Popular e Solidária</t>
-        </is>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>374</v>
       </c>
       <c r="B370">
         <v>2022</v>
       </c>
       <c r="C370">
-        <v>99983.39999999999</v>
+        <v>99983.4</v>
       </c>
       <c r="D370">
-        <v>99983.39999999999</v>
+        <v>99983.4</v>
       </c>
       <c r="E370">
         <v>1</v>
@@ -8506,11 +9018,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação das Praças Digitais</t>
-        </is>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>375</v>
       </c>
       <c r="B371">
         <v>2022</v>
@@ -8519,20 +9029,18 @@
         <v>98814.97</v>
       </c>
       <c r="D371">
-        <v>66883.29000000001</v>
+        <v>66883.290000000008</v>
       </c>
       <c r="E371">
-        <v>0.6768538208330176</v>
+        <v>0.67685382083301759</v>
       </c>
       <c r="F371">
         <v>1</v>
       </c>
     </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Edificação do Tribunal de Contas do Município</t>
-        </is>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>376</v>
       </c>
       <c r="B372">
         <v>2022</v>
@@ -8550,17 +9058,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Restituição de Receitas Descontinuadas</t>
-        </is>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>377</v>
       </c>
       <c r="B373">
         <v>2022</v>
       </c>
       <c r="C373">
-        <v>92905.70000000001</v>
+        <v>92905.700000000012</v>
       </c>
       <c r="D373">
         <v>0</v>
@@ -8572,20 +9078,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Conservação e Valorização de Acervos da Biblioteca Mário de Andrade</t>
-        </is>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>378</v>
       </c>
       <c r="B374">
         <v>2022</v>
       </c>
       <c r="C374">
-        <v>76969.92</v>
+        <v>76969.919999999998</v>
       </c>
       <c r="D374">
-        <v>76969.92</v>
+        <v>76969.919999999998</v>
       </c>
       <c r="E374">
         <v>1</v>
@@ -8594,11 +9098,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Manutenção, Programas e Suporte da Coordenadoria de Defesa do Consumidor</t>
-        </is>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>379</v>
       </c>
       <c r="B375">
         <v>2022</v>
@@ -8616,11 +9118,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Povos Indígenas</t>
-        </is>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>380</v>
       </c>
       <c r="B376">
         <v>2022</v>
@@ -8638,11 +9138,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Implementação do Selo Municipal de Direitos Humanos e Diversidade</t>
-        </is>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>381</v>
       </c>
       <c r="B377">
         <v>2022</v>
@@ -8660,11 +9158,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>Programa de Promoção da Imagem de São Paulo no Exterior</t>
-        </is>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>382</v>
       </c>
       <c r="B378">
         <v>2022</v>
@@ -8682,11 +9178,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>Programa de Gestão Cultural Comunitária de Espaços</t>
-        </is>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>383</v>
       </c>
       <c r="B379">
         <v>2022</v>
@@ -8704,11 +9198,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>Outras Dívidas</t>
-        </is>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>384</v>
       </c>
       <c r="B380">
         <v>2022</v>
@@ -8726,20 +9218,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>Benefícios Eventuais</t>
-        </is>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>385</v>
       </c>
       <c r="B381">
         <v>2022</v>
       </c>
       <c r="C381">
-        <v>38725.02</v>
+        <v>38725.019999999997</v>
       </c>
       <c r="D381">
-        <v>38725.02</v>
+        <v>38725.019999999997</v>
       </c>
       <c r="E381">
         <v>1</v>
@@ -8748,33 +9238,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Supervisão Geral das Juntas do Serviço Militar</t>
-        </is>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>386</v>
       </c>
       <c r="B382">
         <v>2022</v>
       </c>
       <c r="C382">
-        <v>36542.4</v>
+        <v>36542.400000000001</v>
       </c>
       <c r="D382">
         <v>32462.82</v>
       </c>
       <c r="E382">
-        <v>0.8883603704190201</v>
+        <v>0.88836037041902005</v>
       </c>
       <c r="F382">
         <v>32</v>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Pessoas Desaparecidas</t>
-        </is>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>387</v>
       </c>
       <c r="B383">
         <v>2022</v>
@@ -8792,11 +9278,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>Conservação e Valorização de Acervos do Departamento dos Museus Municipais</t>
-        </is>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>388</v>
       </c>
       <c r="B384">
         <v>2022</v>
@@ -8814,20 +9298,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Unidades de Conservação</t>
-        </is>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>389</v>
       </c>
       <c r="B385">
         <v>2022</v>
       </c>
       <c r="C385">
-        <v>23245.36</v>
+        <v>23245.360000000001</v>
       </c>
       <c r="D385">
-        <v>23245.36</v>
+        <v>23245.360000000001</v>
       </c>
       <c r="E385">
         <v>1</v>
@@ -8836,11 +9318,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Promoção da Igualdade Racial</t>
-        </is>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>390</v>
       </c>
       <c r="B386">
         <v>2022</v>
@@ -8858,11 +9338,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>Ações e Atividades Culturais do Arquivo Histórico Municipal</t>
-        </is>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>391</v>
       </c>
       <c r="B387">
         <v>2022</v>
@@ -8880,11 +9358,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Pessoa Idosa</t>
-        </is>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>392</v>
       </c>
       <c r="B388">
         <v>2022</v>
@@ -8902,11 +9378,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>Implantação de Transporte Público Hidroviário</t>
-        </is>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>393</v>
       </c>
       <c r="B389">
         <v>2022</v>
@@ -8924,11 +9398,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Herbário Municipal</t>
-        </is>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>394</v>
       </c>
       <c r="B390">
         <v>2022</v>
@@ -8946,11 +9418,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>Comunicação e Orientação na Valorização e Cuidado na Primeira Infância</t>
-        </is>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>395</v>
       </c>
       <c r="B391">
         <v>2022</v>
@@ -8968,11 +9438,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para a Promoção do Direito à Memória e à Verdade</t>
-        </is>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>396</v>
       </c>
       <c r="B392">
         <v>2022</v>
@@ -8990,11 +9458,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da UniCEU</t>
-        </is>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>397</v>
       </c>
       <c r="B393">
         <v>2022</v>
@@ -9012,11 +9478,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Edificação da Câmara Municipal de São Paulo</t>
-        </is>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>398</v>
       </c>
       <c r="B394">
         <v>2022</v>
@@ -9031,11 +9495,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>Apoio e Suporte Técnico para o Desenvolvimento de Ações Pertinentes à Fiscalização e Escrituração de Certificados de Potencial Adicional de Construção - CEPACs</t>
-        </is>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>399</v>
       </c>
       <c r="B395">
         <v>2022</v>
@@ -9050,11 +9512,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>Apoio às Ações Municipais de Turismo</t>
-        </is>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>400</v>
       </c>
       <c r="B396">
         <v>2022</v>
@@ -9069,11 +9529,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>Aquisição e Construção de Prédios Administrativos</t>
-        </is>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>401</v>
       </c>
       <c r="B397">
         <v>2022</v>
@@ -9088,11 +9546,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>Ações Socioculturais em Espaços Cemiteriais</t>
-        </is>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>402</v>
       </c>
       <c r="B398">
         <v>2022</v>
@@ -9107,11 +9563,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>Ações de Pronto Atendimento Socioassistencial</t>
-        </is>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>403</v>
       </c>
       <c r="B399">
         <v>2022</v>
@@ -9126,11 +9580,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>Ações de Vigilância Socioassistencial</t>
-        </is>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>404</v>
       </c>
       <c r="B400">
         <v>2022</v>
@@ -9145,11 +9597,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>Comercialização de Artigos do Serviço Funerário</t>
-        </is>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>405</v>
       </c>
       <c r="B401">
         <v>2022</v>
@@ -9164,11 +9614,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>Educação Permanente dos Trabalhadores do SUAS</t>
-        </is>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>406</v>
       </c>
       <c r="B402">
         <v>2022</v>
@@ -9183,11 +9631,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Cemitério</t>
-        </is>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>407</v>
       </c>
       <c r="B403">
         <v>2022</v>
@@ -9202,11 +9648,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Crematório</t>
-        </is>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>408</v>
       </c>
       <c r="B404">
         <v>2022</v>
@@ -9221,11 +9665,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Velório</t>
-        </is>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>409</v>
       </c>
       <c r="B405">
         <v>2022</v>
@@ -9240,11 +9682,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>Transportes Fúnebres</t>
-        </is>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>410</v>
       </c>
       <c r="B406">
         <v>2022</v>
@@ -9262,4 +9702,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{f398df9c-fd0c-4829-a003-c770a1c4a063}" enabled="0" method="" siteId="{f398df9c-fd0c-4829-a003-c770a1c4a063}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/R Markdown/resultados/regionalizacao_acoes_2022.xlsx
+++ b/R Markdown/resultados/regionalizacao_acoes_2022.xlsx
@@ -1,1267 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_BF4BBDDF8F79A8D366075C52F37BD2723AC9DF5B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DE54850-DE22-4EBB-8437-F2D0797F1F65}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="411">
-  <si>
-    <t>descricao_proj_ativ</t>
-  </si>
-  <si>
-    <t>ano</t>
-  </si>
-  <si>
-    <t>valor_total</t>
-  </si>
-  <si>
-    <t>valor_regionalizado</t>
-  </si>
-  <si>
-    <t>perc_regionalizado</t>
-  </si>
-  <si>
-    <t>n_subpref</t>
-  </si>
-  <si>
-    <t>Aposentadorias e Pensões</t>
-  </si>
-  <si>
-    <t>Administração da Unidade</t>
-  </si>
-  <si>
-    <t>Compensações Tarifárias do Sistema de Ônibus</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Rede Parceira - Centro de Educação Infantil (CEI)</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação em Atenção Hospitalar e de Urgência e Emergência</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação em Atenção Básica, Especialidades e de Serviços Auxiliares de Diagnóstico e Terapia</t>
-  </si>
-  <si>
-    <t>Obrigações e Contribuições Patronais RPPS Educação</t>
-  </si>
-  <si>
-    <t>Aporte do IRRF para cobertura do deficit atuarial do RPPS</t>
-  </si>
-  <si>
-    <t>Condenações Judiciais - Créditos de Natureza Alimentar</t>
-  </si>
-  <si>
-    <t>Concessão dos Serviços Divisíveis de Limpeza Urbana em Regime Público</t>
-  </si>
-  <si>
-    <t>Intervenções no Sistema de Drenagem</t>
-  </si>
-  <si>
-    <t>Serviços de Engenharia de Tráfego</t>
-  </si>
-  <si>
-    <t>Sistema Municipal de Regulação, Controle, Avaliação e Auditoria do SUS</t>
-  </si>
-  <si>
-    <t>Recomposição de Depósitos Judiciais</t>
-  </si>
-  <si>
-    <t>Obrigações e Contribuições Patronais</t>
-  </si>
-  <si>
-    <t>Alimentação Escolar</t>
-  </si>
-  <si>
-    <t>Contribuição Formação Patrimônio Servidor Público - PASEP</t>
-  </si>
-  <si>
-    <t>Intervenção, Urbanização e Melhoria de Bairros - Plano de Obras das Subprefeituras</t>
-  </si>
-  <si>
-    <t>Obrigações e Contribuições Patronais RPPS Saúde</t>
-  </si>
-  <si>
-    <t>Condenações Judiciais - Outras Espécies</t>
-  </si>
-  <si>
-    <t>Execução do Programa de Mananciais</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação em Atenção Básica, Especialidades e Vigilância da Assistência Farmacêutica</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Sistemas de Informação e Comunicação</t>
-  </si>
-  <si>
-    <t>Construção de Unidades Habitacionais</t>
-  </si>
-  <si>
-    <t>Contraprestação de Parceria Público-Privada (PPP) - Iluminação Pública</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População em Situação de Rua</t>
-  </si>
-  <si>
-    <t>Aquisição de Materiais, Equipamentos e Serviços de Informação e Comunicação</t>
-  </si>
-  <si>
-    <t>Pavimentação e Recapeamento de Vias</t>
-  </si>
-  <si>
-    <t>Intervenções no Sistema Viário</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação do Sistema Municipal de Transporte Coletivo</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para Crianças e Adolescentes</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Ensino Fundamental (EMEF)</t>
-  </si>
-  <si>
-    <t>Manutenção de Sistemas de Drenagem</t>
-  </si>
-  <si>
-    <t>Promoção de Campanhas e Eventos de Interesse do Município</t>
-  </si>
-  <si>
-    <t>Construção e Implantação de Centros Educacionais Unificados (CEU)</t>
-  </si>
-  <si>
-    <t>Fornecimento de Uniformes e Material Escolar-Educação Infantil</t>
-  </si>
-  <si>
-    <t>Serviço da Dívida Pública Interna - Refinanciamento</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Centros Educacionais Unificados (CEU)</t>
-  </si>
-  <si>
-    <t>Administração de Material  Médico Hospitalar e Ambulatorial em Atenção Básica, Especialidades e Vigilância</t>
-  </si>
-  <si>
-    <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Educação Infantil</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Áreas Verdes e Vegetação Arbórea</t>
-  </si>
-  <si>
-    <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Ensino Fundamental</t>
-  </si>
-  <si>
-    <t>Serviços de Limpeza Urbana - Varrição e Lavagem de Áreas Públicas</t>
-  </si>
-  <si>
-    <t>Fornecimento de Uniformes e Material Escolar-Ensino Fundamental</t>
-  </si>
-  <si>
-    <t>Recuperação e Reforço de Obras de Arte Especiais - OAE</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos de Proteção Social Especial a Crianças, Adolescentes e Jovens em Risco Social</t>
-  </si>
-  <si>
-    <t>Administração de Material Médico Hospitalar em Atenção Hospitalar, de Urgência e Emergência</t>
-  </si>
-  <si>
-    <t>Transporte Escolar - Educação Infantil</t>
-  </si>
-  <si>
-    <t>Serviço da Dívida Pública Interna</t>
-  </si>
-  <si>
-    <t>Publicidade Institucional</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Terminais de Ônibus</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Escolas Municipais de Educação Infantil (EMEI)</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Parques Urbanos e Lineares</t>
-  </si>
-  <si>
-    <t>Ações e Materiais de Apoio Didático-Pedagógico Educacional</t>
-  </si>
-  <si>
-    <t>Programa Nacional de Alimentação Escolar - PNAE/ FNDE</t>
-  </si>
-  <si>
-    <t>Sistema de Remuneração Variável</t>
-  </si>
-  <si>
-    <t>Transporte Escolar - Ensino Fundamental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avança Saúde SP - Ampliação, Reforma e Requalificação de Equipamentos de Saúde_x000D__x000D_
-</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação no Serviço de Guias e Sarjetas (Vias e Logradouros)</t>
-  </si>
-  <si>
-    <t>Transporte de Pessoas com Deficiência ou Mobilidade Reduzida - ATENDE</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Centros de Educação Infantil (CEI)</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação do Controle e Fiscalização de Tráfego</t>
-  </si>
-  <si>
-    <t>Condenações Judiciais - Créditos de Pequeno Valor</t>
-  </si>
-  <si>
-    <t>Obras e Serviços nas Áreas de Riscos Geológicos</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos Intergeracionais de Convivência e Fortalecimento de Vínculos</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos Esportivos</t>
-  </si>
-  <si>
-    <t>Encargos pela Manutenção do Fundo de Depósitos Judiciais nas quais o Município é Parte</t>
-  </si>
-  <si>
-    <t>Projetos e Ações de Apoio Habitacional</t>
-  </si>
-  <si>
-    <t>Precatórios Pagos com Rendimentos dos Depósitos do Regime Especial</t>
-  </si>
-  <si>
-    <t>Leve-Leite</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Corredores de Ônibus</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Sinalização do Sistema Viário</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Vigilância em Saúde</t>
-  </si>
-  <si>
-    <t>Operação Tapa Buraco</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Central de Atendimento Telefônico - 156</t>
-  </si>
-  <si>
-    <t>Programação de Atividades Culturais</t>
-  </si>
-  <si>
-    <t>Manutenção de Vias e Áreas Públicas</t>
-  </si>
-  <si>
-    <t>Ações de Difusão Cultural do Theatro Municipal - Grupos Artísticos, Técnicos e Administrativos</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Serviço de Atendimento Médico de Urgência (SAMU)</t>
-  </si>
-  <si>
-    <t>Remuneração dos Profissionais do Magistério - Ensino Fundamental</t>
-  </si>
-  <si>
-    <t>Ações de Apoio à Educação Especial</t>
-  </si>
-  <si>
-    <t>Programa de Incentivo Fiscal Relacionado à Arena Corinthians</t>
-  </si>
-  <si>
-    <t>Servidores Comissionados em Outras Entidades</t>
-  </si>
-  <si>
-    <t>Serviço de Moradia Transitória</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos de Proteção Social Básica às Famílias</t>
-  </si>
-  <si>
-    <t>Urbanização de Favelas</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Equipamentos Esportivos</t>
-  </si>
-  <si>
-    <t>Incentivo à Prática de Esportes</t>
-  </si>
-  <si>
-    <t>Realização de Eventos de Esporte, Lazer e Recreação</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Atenção Hospitalar da Assistência Farmacêutica</t>
-  </si>
-  <si>
-    <t>Remuneração dos Profissionais do Magistério - Centro de Educação Infantil (CEI)</t>
-  </si>
-  <si>
-    <t>Capacitação, Formação e Aperfeiçoamento dos Trabalhadores</t>
-  </si>
-  <si>
-    <t>Ações Integradas de Segurança Pública - Operação Delegada - Convênio SSP SO</t>
-  </si>
-  <si>
-    <t>Remuneração dos Profissionais do Magistério - Escola Municipal de Educação Infantil (EMEI)</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação Semafórica</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à Pessoa com Deficiência</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População Idosa</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos da Assistência Social</t>
-  </si>
-  <si>
-    <t>Administração da Carteira Imobiliária</t>
-  </si>
-  <si>
-    <t>Construção de Centros de Educação Infantil - CEI</t>
-  </si>
-  <si>
-    <t>Ações Permanentes de Promoção dos Direitos da Criança e do Adolescente</t>
-  </si>
-  <si>
-    <t>Serviço da Dívida Pública Externa</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Posto do Corpo de Bombeiros</t>
-  </si>
-  <si>
-    <t>Realização de Eventos Culturais</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Guarda Civil Metropolitana</t>
-  </si>
-  <si>
-    <t>Administração dos Conselhos Tutelares</t>
-  </si>
-  <si>
-    <t>Políticas, Programas e Ações para Educação em Direitos Humanos e Promoção do Direito à Cidade</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para a Pessoa Idosa</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Centros Educacionais Unificados (CEU)</t>
-  </si>
-  <si>
-    <t>Modernização Semafórica</t>
-  </si>
-  <si>
-    <t>Aposentadoria Complementar aos Servidores da São Paulo Transporte S/A</t>
-  </si>
-  <si>
-    <t>Regularização Fundiária</t>
-  </si>
-  <si>
-    <t>Intervenções em Próprios Municipais</t>
-  </si>
-  <si>
-    <t>Coleta, Transporte, Tratamento e Dest. Final Resíduos Sólidos Inertes</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação do Policiamento de Trânsito</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Clube da Comunidade (CDC)</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Prédios Administrativos</t>
-  </si>
-  <si>
-    <t>Programa Municipal de Apoio a Projetos Culturais (PRO-MAC)</t>
-  </si>
-  <si>
-    <t>Políticas, Programas e Ações para a População em Situação de Rua</t>
-  </si>
-  <si>
-    <t>Ações de Fiscalização do Comércio Ilegal</t>
-  </si>
-  <si>
-    <t>Operação e Manutenção da Agência São Paulo de Desenvolvimento - ADESAMPA</t>
-  </si>
-  <si>
-    <t>Políticas de Audiovisual</t>
-  </si>
-  <si>
-    <t>Eventos Educacionais, Culturais e Esportivos nos Centros Educacionais Unificados</t>
-  </si>
-  <si>
-    <t>Aporte para Garantia de PPP's e Projetos de Infraestrutura</t>
-  </si>
-  <si>
-    <t>Construção e Implantação de Parques Urbanos e Lineares</t>
-  </si>
-  <si>
-    <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - Educação Infantil</t>
-  </si>
-  <si>
-    <t>Construção de Ciclovias, Ciclofaixas e Ciclorrotas</t>
-  </si>
-  <si>
-    <t>Contraprestação de Parceria Público-Privada (PPP) - Terminais Urbanos</t>
-  </si>
-  <si>
-    <t>Implantação de Corredores de Ônibus Novos</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação em Serviços de Saúde Animal</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Áreas Públicas</t>
-  </si>
-  <si>
-    <t>Serviços de Desfazimento e Demolição de Construções Irregulares em Áreas de Proteção Ambiental</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação do Descomplica SP</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Centros Culturais e Teatros</t>
-  </si>
-  <si>
-    <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Centro Educacional Unificado (CEU)</t>
-  </si>
-  <si>
-    <t>Fomento à Cooperação, Parcerias e Captação de Investimentos Internacionais</t>
-  </si>
-  <si>
-    <t>Desenvolvimento de Sistemas de Informação e Comunicação</t>
-  </si>
-  <si>
-    <t>Programa de Atração a Filmagens - Cash Rebate</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Unidades de Conservação</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Equipamentos de Atenção Básica e Especialidades</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Mulheres</t>
-  </si>
-  <si>
-    <t>Lei de Fomento ao Teatro</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos de Proteção Jurídico Social</t>
-  </si>
-  <si>
-    <t>Gratificação de Municipalização - Saúde - Lei 13.510/03</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Bibliotecas Públicas</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação da Avenida Santo Amaro</t>
-  </si>
-  <si>
-    <t>Fomento à Cultura da Periferia de São Paulo</t>
-  </si>
-  <si>
-    <t>Encargos Referentes a Arrecadação</t>
-  </si>
-  <si>
-    <t>Ações de Educação Integral</t>
-  </si>
-  <si>
-    <t>Construção e Implantação do Descomplica SP</t>
-  </si>
-  <si>
-    <t>Circuito Cultural de São Paulo</t>
-  </si>
-  <si>
-    <t>Ações de Desestatização</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Centros Municipais de Educação Infantil(CEMEI)</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação dos Sistemas de Monitoramento e Alerta de Enchentes</t>
-  </si>
-  <si>
-    <t>Operação e Manutenção dos Centros de Apoio ao Trabalho e Empreendedorismo</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação do Autódromo de Interlagos</t>
-  </si>
-  <si>
-    <t>Inserção das Famílias no Cadastro Único</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Escolas Municipais de Educação Infantil (EMEI)</t>
-  </si>
-  <si>
-    <t>Ações de formação das Escolas de Música e Dança do Theatro Municipal e da Praça das Artes</t>
-  </si>
-  <si>
-    <t>Programação da Virada Esportiva</t>
-  </si>
-  <si>
-    <t>Operação e Manutenção de Unidade da Fundação Paulistana - FPETC</t>
-  </si>
-  <si>
-    <t>Alfabetização na Idade Certa</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos do Departamento dos Museus Municipais</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Rede Parceira - Alfabetização de Jovens e Adultos</t>
-  </si>
-  <si>
-    <t>Capacitação, Formação e Aperfeiçoamento de Servidores</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Telecentros</t>
-  </si>
-  <si>
-    <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - Ensino Fundamental</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Casas de Cultura</t>
-  </si>
-  <si>
-    <t>Operação e Manutenção da São Paulo Investimentos e Negócios</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Praças, Canteiros Centrais e Remanescentes</t>
-  </si>
-  <si>
-    <t>Preservação do Patrimônio Histórico, Artístico, Cultural e Arqueológico</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Parques Urbanos e Lineares</t>
-  </si>
-  <si>
-    <t>Bolsa-Trabalho</t>
-  </si>
-  <si>
-    <t>Execução do Programa para a Valorização de Iniciativas Culturais</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação do Programa Melhor em Casa</t>
-  </si>
-  <si>
-    <t>Manutenção de Unidades Habitacionais</t>
-  </si>
-  <si>
-    <t>Câmara Municipal - Comunicação</t>
-  </si>
-  <si>
-    <t>Lei de Fomento à Dança</t>
-  </si>
-  <si>
-    <t>Ações de Difusão Cultural do Theatro Municipal - Patrimônio</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Fundamental e Médio (EMEFM)</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação do Centro Cultural São Paulo</t>
-  </si>
-  <si>
-    <t>Realização de Projetos Culturais</t>
-  </si>
-  <si>
-    <t>Cooperação Técnica Internacional</t>
-  </si>
-  <si>
-    <t>Projetos de Fomento ao Turismo</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação dos Serviços de DST / AIDS</t>
-  </si>
-  <si>
-    <t>Programação da Virada Cultural</t>
-  </si>
-  <si>
-    <t>Programa Jovem Monitor Cultural</t>
-  </si>
-  <si>
-    <t>Inspeção de Obras de Artes Especiais - OAE</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação dos Pólos Regionais de Esporte</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Biblioteca Mario de Andrade</t>
-  </si>
-  <si>
-    <t>Compensações Ambientais</t>
-  </si>
-  <si>
-    <t>Compensação Financeira - Outros Fundos de Previdência</t>
-  </si>
-  <si>
-    <t>Escola Municipal de Educação Artística - EMIA</t>
-  </si>
-  <si>
-    <t>Prêmio Zé Renato</t>
-  </si>
-  <si>
-    <t>Subvenção e Contribuições a Entidades Culturais</t>
-  </si>
-  <si>
-    <t>Programação de Atividades Culturais de Casas de Cultura</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Escola Municipal de Ensino Fundamental (EMEF)</t>
-  </si>
-  <si>
-    <t>Ações para Promoção da Sustentabilidade Previdenciária</t>
-  </si>
-  <si>
-    <t>Intervenções na Área de Mobilidade Urbana</t>
-  </si>
-  <si>
-    <t>Transporte Escolar - Educação Especial</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Viveiros</t>
-  </si>
-  <si>
-    <t>Fomento às Linguagens Artísticas</t>
-  </si>
-  <si>
-    <t>Ações Permanentes de Promoção dos Direitos da População Idosa</t>
-  </si>
-  <si>
-    <t>Ações de Difusão Cultural do Theatro Municipal - Programação Artística</t>
-  </si>
-  <si>
-    <t>Sistema de Avaliação Escolar dos Alunos da Rede Municipal de Ensino</t>
-  </si>
-  <si>
-    <t>Remuneração dos Profissionais do Magistério - Centro Municipal de Educação Infantil( CEMEI)</t>
-  </si>
-  <si>
-    <t>Implantação do Memorial dos Aflitos</t>
-  </si>
-  <si>
-    <t>Programação de Atividades Culturais de Centros Culturais e Teatros</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Rede Parceira - Educação Especial</t>
-  </si>
-  <si>
-    <t>Construção da Fábrica do Samba</t>
-  </si>
-  <si>
-    <t>Suporte e Manutenção da Coordenação de Imprensa</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Centro Olímpicos</t>
-  </si>
-  <si>
-    <t>Qualificação Profissional e Empreendedora</t>
-  </si>
-  <si>
-    <t>Programa de Garantia de Renda Familiar Mínima</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Edificação da Câmara Municipal de São Paulo</t>
-  </si>
-  <si>
-    <t>Recuperação de Fachadas Históricas na Área Central</t>
-  </si>
-  <si>
-    <t>Administração do Edifício Matarazzo</t>
-  </si>
-  <si>
-    <t>Parceria Público Privada - Habitação</t>
-  </si>
-  <si>
-    <t>Programa Nacional de Apoio à Gestão Adm. e Fiscal - PNAFM</t>
-  </si>
-  <si>
-    <t>Plantio de Árvores</t>
-  </si>
-  <si>
-    <t>Acessibilidade, Ampliação, Reforma e Requalificação de Terminais de Ônibus</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos Culturais</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Casa da Mulher Brasileira</t>
-  </si>
-  <si>
-    <t>Ações de Difusão Cultural do Theatro Municipal - Administrativos</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação dos Equipamentos Públicos Voltados ao Atendimento da População LGBTI</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Unidades Educacionais - Centro Integrado de Jovens e Adultos (CIEJA)</t>
-  </si>
-  <si>
-    <t>Fomento às Cadeias Produtivas, Vocações Produtivas e Projetos Locais</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação dos Serviços de Atendimento e Manejo da Fauna Silvestre</t>
-  </si>
-  <si>
-    <t>Servidores Comissionados no Hospital Serv. Públco Municipal - HSPM</t>
-  </si>
-  <si>
-    <t>Construção de Corredores de Ônibus</t>
-  </si>
-  <si>
-    <t>Políticas, Programas e Ações para a População LGBTI+</t>
-  </si>
-  <si>
-    <t>Políticas, Programas e Ações para Juventude</t>
-  </si>
-  <si>
-    <t>Políticas de Promoção Cultural nas Bibliotecas Públicas</t>
-  </si>
-  <si>
-    <t>Políticas de promoção cultural</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Equipamentos Culturais</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Ciclovias, Ciclofaixas e Ciclorrotas</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Unidades Educacionais - Educação Indígena</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Centros de Educação Infantil (CEI)</t>
-  </si>
-  <si>
-    <t>Oficina nos Equipamentos Culturais</t>
-  </si>
-  <si>
-    <t>Construção de Escolas Municipais de Educação Infantil (EMEI)</t>
-  </si>
-  <si>
-    <t>Despesas Administrativas para Execução de Ações Judiciais - Processamento de Feitos</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Bilíngue para Surdos (EMEBS)</t>
-  </si>
-  <si>
-    <t>Edição e Publicação do Diário Oficial da Cidade de São Paulo</t>
-  </si>
-  <si>
-    <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - CEU</t>
-  </si>
-  <si>
-    <t>Ações de Cooperação para o Desenvolvimento Sustentável</t>
-  </si>
-  <si>
-    <t>Projetos para Inclusão da Pessoa com Deficiência</t>
-  </si>
-  <si>
-    <t>Auxílio Funeral</t>
-  </si>
-  <si>
-    <t>PROCONECTA - Promoção da Conectividade e Inclusão Digital</t>
-  </si>
-  <si>
-    <t>Execução do Programa Museu de Arte de Rua - MAR</t>
-  </si>
-  <si>
-    <t>Fomento ao Circo/Edital Xamego</t>
-  </si>
-  <si>
-    <t>Programação de Atividades Culturais do Centro Cultural São Paulo</t>
-  </si>
-  <si>
-    <t>Rádios Comunitárias - Lei nº 16.572/2016</t>
-  </si>
-  <si>
-    <t>Políticas, Programas e Ações Para Criança e Adolescente</t>
-  </si>
-  <si>
-    <t>Fomento à Música</t>
-  </si>
-  <si>
-    <t>Estudos, Planos e Projetos Ambientais</t>
-  </si>
-  <si>
-    <t>Políticas, Programas e Ações para Mulheres</t>
-  </si>
-  <si>
-    <t>Apoio à Cultura Negra</t>
-  </si>
-  <si>
-    <t>Obras de Combate a Enchentes e Alagamentos</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Rede de Iluminação Pública</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Centro de Referência de Segurança Alimentar e Nutricional</t>
-  </si>
-  <si>
-    <t>Programa Piá</t>
-  </si>
-  <si>
-    <t>Ações de Educação de Trânsito</t>
-  </si>
-  <si>
-    <t>Programa Vocacional</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação do Arquivo Histórico Municipal</t>
-  </si>
-  <si>
-    <t>Programação de Atividades Culturais do Departamento dos Museus Municipais</t>
-  </si>
-  <si>
-    <t>Operação e Manutenção das Centrais de Triagem - Coleta Seletiva</t>
-  </si>
-  <si>
-    <t>Ações Municipais de Abastecimento</t>
-  </si>
-  <si>
-    <t>Educação Ambiental</t>
-  </si>
-  <si>
-    <t>Programação de Atividades Culturais nas Bibliotecas Públicas</t>
-  </si>
-  <si>
-    <t>Manutenção de Ciclovias, Ciclofaixas e Ciclorrotas</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento da População de Rua</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Defesa Civil</t>
-  </si>
-  <si>
-    <t>Mês do Hip Hop</t>
-  </si>
-  <si>
-    <t>Política Municipal de Desenvolvimento Econômico</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação dos Planetários Municipais</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Imigrantes</t>
-  </si>
-  <si>
-    <t>Locação Social</t>
-  </si>
-  <si>
-    <t>Programa Mãos e Mentes Paulistanas</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos Públicos Voltados à Promoção da Igualdade Racial</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação dos Conselhos e Espaços Participativos Municipais</t>
-  </si>
-  <si>
-    <t>Manutenção da Ouvidoria de Direitos Humanos</t>
-  </si>
-  <si>
-    <t>Fiscalização, Monitoramento e Controle Ambiental</t>
-  </si>
-  <si>
-    <t>Execução de Serviços Médicos de Tratamento de Radioterapia</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação nas Áreas de Parada e Plataforma de Embarque de Faixa Exclusiva de Ônibus</t>
-  </si>
-  <si>
-    <t>Reembolso ao Serviço Funerário</t>
-  </si>
-  <si>
-    <t>Melhoria de Bairros no âmbito da Subprefeitura da Capela do Socorro.</t>
-  </si>
-  <si>
-    <t>Bloqueios Judiciais</t>
-  </si>
-  <si>
-    <t>Centro Municipal para Pessoas com Transtorno do Espectro Autista</t>
-  </si>
-  <si>
-    <t>Apoio e Suporte Técnico para o Desenvolvimento de Estudos e Projetos Urbanos</t>
-  </si>
-  <si>
-    <t>Ações e Atividades Culturais da Biblioteca Mario de Andrade</t>
-  </si>
-  <si>
-    <t>Difusão, Fomento e Pesquisas Aplicadas à Gestão de Tecnologia, Inovação e Atendimento ao Cidadão</t>
-  </si>
-  <si>
-    <t>Projeto de Intervenção Urbana - PIU</t>
-  </si>
-  <si>
-    <t>Manutenção de Prédios Administrativos</t>
-  </si>
-  <si>
-    <t>Restituição de Amortização Extraordinária e Liquidação Antecipada</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação dos Centros de Estudos de Línguas Paulistano - CELP</t>
-  </si>
-  <si>
-    <t>Programa de Articulação Criativa</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação dos Equipamentos Públicos Voltados para Pessoa Idosa</t>
-  </si>
-  <si>
-    <t>Desenvolvimento de Estudos, Projetos  e Instrumentos de Políticas Urbanas</t>
-  </si>
-  <si>
-    <t>Equipes de Alto Desempenho com Representatividade em Competições Locais, Regionais, Nacionais e Mundiais</t>
-  </si>
-  <si>
-    <t>Programa de Iniciação Artística para a Primeira Infância - PIAPI</t>
-  </si>
-  <si>
-    <t>Manutenção de Modalidades Desportivas do Centro Olímpico de Treinamento e Pesquisa (COTP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operação e Manutenção do Portal da PMSP_x000D__x000D_
-</t>
-  </si>
-  <si>
-    <t>Vivência Prática de Gestão de Documentos</t>
-  </si>
-  <si>
-    <t>Difusão, Fomento e Pesquisas Aplicadas para a Gestão Participativa e Desenvolvimento Urbano</t>
-  </si>
-  <si>
-    <t>Fomento às Comunidades do Samba</t>
-  </si>
-  <si>
-    <t>Políticas, Programas e Ações para Imigrantes e Promoção ao Trabalho Decente</t>
-  </si>
-  <si>
-    <t>Atualização do Currículo da Rede Municipal de Ensino</t>
-  </si>
-  <si>
-    <t>Operação e Manutenção do VAI TEC</t>
-  </si>
-  <si>
-    <t>Ações e Atividades Culturais do Departamento do Patrimônio Histórico</t>
-  </si>
-  <si>
-    <t>Construção de Galeria, bem como Boca de Lobo para Captação de Água Pluvial, na Viela João Carlos Pereira, Altura no Número 13</t>
-  </si>
-  <si>
-    <t>Prospecção de Problemas Públicos e Ideação de Alternativas para Inovação</t>
-  </si>
-  <si>
-    <t>FUMCAD - Multas Revertidas ao Fundo</t>
-  </si>
-  <si>
-    <t>Tarifa de Arrecadação de Multas</t>
-  </si>
-  <si>
-    <t>"Comemoração do ""Dia Municipal da Cultura Evangélica"" - 09 de Julho - Lei nº 14.232 de 07 de Novembro de 2006"</t>
-  </si>
-  <si>
-    <t>Operação e Manutenção da Infraestrutura Turística</t>
-  </si>
-  <si>
-    <t>Manutenção das Instalações da Guarda Civil Metropolitana</t>
-  </si>
-  <si>
-    <t>Programa Aldeias</t>
-  </si>
-  <si>
-    <t>Plano Municipal do Livro, Leitura, Literatura e Biblioteca (PMLLLB)</t>
-  </si>
-  <si>
-    <t>Implantação e Construção de Ecopontos</t>
-  </si>
-  <si>
-    <t>Programação de Atividades e Eventos da Cultura Reggae</t>
-  </si>
-  <si>
-    <t>Acompanhamento das Aprendizagens e Permanência Escolar</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Unidades de Conservação</t>
-  </si>
-  <si>
-    <t>Fomento e Difusão do Forró</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Unidades Educacionais - Centro Municipal de Capacitação e Treinamento (CMCT)</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação do Centro Público de Economia Solidária e Direitos Humanos</t>
-  </si>
-  <si>
-    <t>Publicação de Editais e Outras Publicações Legais e de Interesse do Município</t>
-  </si>
-  <si>
-    <t>Implantação de Estrutura Turística no Triângulo Histórico</t>
-  </si>
-  <si>
-    <t>Promoção à Saúde do Servidor Municipal</t>
-  </si>
-  <si>
-    <t>Construção e Implantação de Equipamentos de Atenção Básica e Especialidades</t>
-  </si>
-  <si>
-    <t>Centro de Referência da Dança</t>
-  </si>
-  <si>
-    <t>Bolsa Atleta</t>
-  </si>
-  <si>
-    <t>Centro de Memória do Circo</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Patrulha Agroecológica Mecanizada</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Mercado Municipal</t>
-  </si>
-  <si>
-    <t>Pesquisa de Satisfação do Cidadão em Relação aos Serviços, Políticas e Programas</t>
-  </si>
-  <si>
-    <t>Reforma e Acessibilidade em Passeios Públicos</t>
-  </si>
-  <si>
-    <t>Administração do Autódromo de Interlagos</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Espaços Lúdicos e Educativos</t>
-  </si>
-  <si>
-    <t>Território Hip Hop (Vocacional Hip Hop)</t>
-  </si>
-  <si>
-    <t>Gestão do Patrimônio Imobiliário Municipal</t>
-  </si>
-  <si>
-    <t>Fomento e Apoio ao Cooperativismo</t>
-  </si>
-  <si>
-    <t>Revitalização e Manutenção - Subprefeitura de Capela do Socorro</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Equipamentos da Assistência Social</t>
-  </si>
-  <si>
-    <t>Implantação de Pontos e Pontões de Cultura - Cultura Viva</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Equipamentos de Saúde Animal</t>
-  </si>
-  <si>
-    <t>Acordos Judiciais ou Administrativos</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação do Serviço de Moto Verificação</t>
-  </si>
-  <si>
-    <t>Projetos Sociais Diversos</t>
-  </si>
-  <si>
-    <t>Expansão e Aperfeiçoamento das Atividades do TCM</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Central de Interpretação de Libras, Intérpretes e Guias-Intérpretes</t>
-  </si>
-  <si>
-    <t>Construção de Terminais de Ônibus</t>
-  </si>
-  <si>
-    <t>Escola do Parlamento</t>
-  </si>
-  <si>
-    <t>Ações de Audiovisual</t>
-  </si>
-  <si>
-    <t>Implantação da Casa de Cultura Cidade Ademar</t>
-  </si>
-  <si>
-    <t>Expansão e Aperfeiçoamento das Atividades da CMSP</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação das Instalações para a Guarda Civil Metropolitana</t>
-  </si>
-  <si>
-    <t>PMLLLB - Festas Literárias</t>
-  </si>
-  <si>
-    <t>Reforma da Escadaria na Viela Inominada, Localizada na Rua Rua José Ferreira Dantas, Nº 11, Jardim Boa Vista.</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Unidades Habitacionais</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Unidade de Vigilância em Saúde</t>
-  </si>
-  <si>
-    <t>Construção de Escolas Municipais de Ensino Fundamental (EMEF)</t>
-  </si>
-  <si>
-    <t>Execução de Projetos Visando o Combate das Desigualdades Raciais na Saúde</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação no Serviço de Guinchamento</t>
-  </si>
-  <si>
-    <t>Reforma da Quadra da Praça Gilberto Reis Possani, Parque São Rafael</t>
-  </si>
-  <si>
-    <t>Ações do Programa Agentes de Governo Aberto</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Equipamentos do Patrimônio Histórico</t>
-  </si>
-  <si>
-    <t>Promoção da Transparência, do Acesso à Informação e do Controle Social</t>
-  </si>
-  <si>
-    <t>Incentivo à Economia Popular e Solidária</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação das Praças Digitais</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Edificação do Tribunal de Contas do Município</t>
-  </si>
-  <si>
-    <t>Restituição de Receitas Descontinuadas</t>
-  </si>
-  <si>
-    <t>Conservação e Valorização de Acervos da Biblioteca Mário de Andrade</t>
-  </si>
-  <si>
-    <t>Manutenção, Programas e Suporte da Coordenadoria de Defesa do Consumidor</t>
-  </si>
-  <si>
-    <t>Políticas, Programas e Ações para Povos Indígenas</t>
-  </si>
-  <si>
-    <t>Implementação do Selo Municipal de Direitos Humanos e Diversidade</t>
-  </si>
-  <si>
-    <t>Programa de Promoção da Imagem de São Paulo no Exterior</t>
-  </si>
-  <si>
-    <t>Programa de Gestão Cultural Comunitária de Espaços</t>
-  </si>
-  <si>
-    <t>Outras Dívidas</t>
-  </si>
-  <si>
-    <t>Benefícios Eventuais</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da Supervisão Geral das Juntas do Serviço Militar</t>
-  </si>
-  <si>
-    <t>Políticas, Programas e Ações para Pessoas Desaparecidas</t>
-  </si>
-  <si>
-    <t>Conservação e Valorização de Acervos do Departamento dos Museus Municipais</t>
-  </si>
-  <si>
-    <t>Construção e Implantação de Unidades de Conservação</t>
-  </si>
-  <si>
-    <t>Políticas, Programas e Ações para Promoção da Igualdade Racial</t>
-  </si>
-  <si>
-    <t>Ações e Atividades Culturais do Arquivo Histórico Municipal</t>
-  </si>
-  <si>
-    <t>Políticas, Programas e Ações para Pessoa Idosa</t>
-  </si>
-  <si>
-    <t>Implantação de Transporte Público Hidroviário</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação do Herbário Municipal</t>
-  </si>
-  <si>
-    <t>Comunicação e Orientação na Valorização e Cuidado na Primeira Infância</t>
-  </si>
-  <si>
-    <t>Políticas, Programas e Ações para a Promoção do Direito à Memória e à Verdade</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação da UniCEU</t>
-  </si>
-  <si>
-    <t>Ampliação, Reforma e Requalificação de Edificação da Câmara Municipal de São Paulo</t>
-  </si>
-  <si>
-    <t>Apoio e Suporte Técnico para o Desenvolvimento de Ações Pertinentes à Fiscalização e Escrituração de Certificados de Potencial Adicional de Construção - CEPACs</t>
-  </si>
-  <si>
-    <t>Apoio às Ações Municipais de Turismo</t>
-  </si>
-  <si>
-    <t>Aquisição e Construção de Prédios Administrativos</t>
-  </si>
-  <si>
-    <t>Ações Socioculturais em Espaços Cemiteriais</t>
-  </si>
-  <si>
-    <t>Ações de Pronto Atendimento Socioassistencial</t>
-  </si>
-  <si>
-    <t>Ações de Vigilância Socioassistencial</t>
-  </si>
-  <si>
-    <t>Comercialização de Artigos do Serviço Funerário</t>
-  </si>
-  <si>
-    <t>Educação Permanente dos Trabalhadores do SUAS</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Cemitério</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Crematório</t>
-  </si>
-  <si>
-    <t>Manutenção e Operação de Velório</t>
-  </si>
-  <si>
-    <t>Transportes Fúnebres</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1309,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1361,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1395,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1430,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1606,47 +350,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F406"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="101" customWidth="1"/>
-    <col min="2" max="2" width="47.42578125" customWidth="1"/>
-    <col min="3" max="3" width="59.85546875" customWidth="1"/>
-    <col min="4" max="4" width="64.85546875" customWidth="1"/>
-    <col min="5" max="5" width="55.140625" customWidth="1"/>
-    <col min="6" max="6" width="81.140625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>descricao_proj_ativ</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>valor_total</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>valor_regionalizado</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>perc_regionalizado</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>n_subpref</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aposentadorias e Pensões</t>
+        </is>
       </c>
       <c r="B2">
         <v>2022</v>
       </c>
       <c r="C2">
-        <v>11856006499.299999</v>
+        <v>11856006499.3</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1658,35 +408,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Administração da Unidade</t>
+        </is>
       </c>
       <c r="B3">
         <v>2022</v>
       </c>
       <c r="C3">
-        <v>6734920362.9899998</v>
+        <v>6734920362.99</v>
       </c>
       <c r="D3">
         <v>1130523048.48</v>
       </c>
       <c r="E3">
-        <v>0.16785989849152411</v>
+        <v>0.1678598984915241</v>
       </c>
       <c r="F3">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compensações Tarifárias do Sistema de Ônibus</t>
+        </is>
       </c>
       <c r="B4">
         <v>2022</v>
       </c>
       <c r="C4">
-        <v>5051601002.2600002</v>
+        <v>5051601002.26</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1698,18 +452,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Rede Parceira - Centro de Educação Infantil (CEI)</t>
+        </is>
       </c>
       <c r="B5">
         <v>2022</v>
       </c>
       <c r="C5">
-        <v>4552083949.2299995</v>
+        <v>4552083949.23</v>
       </c>
       <c r="D5">
-        <v>4552083949.2299995</v>
+        <v>4552083949.23</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1718,35 +474,39 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação em Atenção Hospitalar e de Urgência e Emergência</t>
+        </is>
       </c>
       <c r="B6">
         <v>2022</v>
       </c>
       <c r="C6">
-        <v>4211981361.9499998</v>
+        <v>4211981361.95</v>
       </c>
       <c r="D6">
-        <v>105413462.29000001</v>
+        <v>105413462.29</v>
       </c>
       <c r="E6">
-        <v>2.5027048610015042E-2</v>
+        <v>0.02502704861001504</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação em Atenção Básica, Especialidades e de Serviços Auxiliares de Diagnóstico e Terapia</t>
+        </is>
       </c>
       <c r="B7">
         <v>2022</v>
       </c>
       <c r="C7">
-        <v>3417002966.6799998</v>
+        <v>3417002966.68</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1758,15 +518,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Obrigações e Contribuições Patronais RPPS Educação</t>
+        </is>
       </c>
       <c r="B8">
         <v>2022</v>
       </c>
       <c r="C8">
-        <v>2669715913.1599998</v>
+        <v>2669715913.16</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1778,9 +540,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Aporte do IRRF para cobertura do deficit atuarial do RPPS</t>
+        </is>
       </c>
       <c r="B9">
         <v>2022</v>
@@ -1798,15 +562,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Condenações Judiciais - Créditos de Natureza Alimentar</t>
+        </is>
       </c>
       <c r="B10">
         <v>2022</v>
       </c>
       <c r="C10">
-        <v>2400181978.9400001</v>
+        <v>2400181978.94</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1818,9 +584,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>15</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Concessão dos Serviços Divisíveis de Limpeza Urbana em Regime Público</t>
+        </is>
       </c>
       <c r="B11">
         <v>2022</v>
@@ -1838,35 +606,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>16</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Intervenções no Sistema de Drenagem</t>
+        </is>
       </c>
       <c r="B12">
         <v>2022</v>
       </c>
       <c r="C12">
-        <v>1351707482.9000001</v>
+        <v>1351707482.9</v>
       </c>
       <c r="D12">
         <v>1133468535.73</v>
       </c>
       <c r="E12">
-        <v>0.83854572832445773</v>
+        <v>0.8385457283244577</v>
       </c>
       <c r="F12">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>17</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Serviços de Engenharia de Tráfego</t>
+        </is>
       </c>
       <c r="B13">
         <v>2022</v>
       </c>
       <c r="C13">
-        <v>1120533067.6199999</v>
+        <v>1120533067.62</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1878,15 +650,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>18</v>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sistema Municipal de Regulação, Controle, Avaliação e Auditoria do SUS</t>
+        </is>
       </c>
       <c r="B14">
         <v>2022</v>
       </c>
       <c r="C14">
-        <v>1021947869.3200001</v>
+        <v>1021947869.32</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1898,15 +672,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>19</v>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Recomposição de Depósitos Judiciais</t>
+        </is>
       </c>
       <c r="B15">
         <v>2022</v>
       </c>
       <c r="C15">
-        <v>1008595895.6799999</v>
+        <v>1008595895.68</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1918,15 +694,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>20</v>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Obrigações e Contribuições Patronais</t>
+        </is>
       </c>
       <c r="B16">
         <v>2022</v>
       </c>
       <c r="C16">
-        <v>734754911.72000003</v>
+        <v>734754911.72</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1938,15 +716,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>21</v>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Alimentação Escolar</t>
+        </is>
       </c>
       <c r="B17">
         <v>2022</v>
       </c>
       <c r="C17">
-        <v>728989572.22000003</v>
+        <v>728989572.22</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1958,15 +738,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>22</v>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Contribuição Formação Patrimônio Servidor Público - PASEP</t>
+        </is>
       </c>
       <c r="B18">
         <v>2022</v>
       </c>
       <c r="C18">
-        <v>720036338.92999995</v>
+        <v>720036338.9299999</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1978,18 +760,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>23</v>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Intervenção, Urbanização e Melhoria de Bairros - Plano de Obras das Subprefeituras</t>
+        </is>
       </c>
       <c r="B19">
         <v>2022</v>
       </c>
       <c r="C19">
-        <v>615490386.88999999</v>
+        <v>615490386.89</v>
       </c>
       <c r="D19">
-        <v>614981066.27999997</v>
+        <v>614981066.28</v>
       </c>
       <c r="E19">
         <v>0.9991724962390176</v>
@@ -1998,15 +782,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>24</v>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Obrigações e Contribuições Patronais RPPS Saúde</t>
+        </is>
       </c>
       <c r="B20">
         <v>2022</v>
       </c>
       <c r="C20">
-        <v>585764415.36000001</v>
+        <v>585764415.36</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -2018,9 +804,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>25</v>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Condenações Judiciais - Outras Espécies</t>
+        </is>
       </c>
       <c r="B21">
         <v>2022</v>
@@ -2038,18 +826,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>26</v>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Execução do Programa de Mananciais</t>
+        </is>
       </c>
       <c r="B22">
         <v>2022</v>
       </c>
       <c r="C22">
-        <v>561202228.10000002</v>
+        <v>561202228.1</v>
       </c>
       <c r="D22">
-        <v>96237769.849999994</v>
+        <v>96237769.84999999</v>
       </c>
       <c r="E22">
         <v>0.1714850102712912</v>
@@ -2058,15 +848,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>27</v>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação em Atenção Básica, Especialidades e Vigilância da Assistência Farmacêutica</t>
+        </is>
       </c>
       <c r="B23">
         <v>2022</v>
       </c>
       <c r="C23">
-        <v>535612154.32999998</v>
+        <v>535612154.33</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2078,55 +870,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>28</v>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Sistemas de Informação e Comunicação</t>
+        </is>
       </c>
       <c r="B24">
         <v>2022</v>
       </c>
       <c r="C24">
-        <v>527217208.29000002</v>
+        <v>527217208.29</v>
       </c>
       <c r="D24">
-        <v>4694677.4000000004</v>
+        <v>4694677.4</v>
       </c>
       <c r="E24">
-        <v>8.9046361275401612E-3</v>
+        <v>0.008904636127540161</v>
       </c>
       <c r="F24">
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>29</v>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Construção de Unidades Habitacionais</t>
+        </is>
       </c>
       <c r="B25">
         <v>2022</v>
       </c>
       <c r="C25">
-        <v>506662993.07999998</v>
+        <v>506662993.08</v>
       </c>
       <c r="D25">
-        <v>486448668.20999998</v>
+        <v>486448668.21</v>
       </c>
       <c r="E25">
-        <v>0.96010301690455568</v>
+        <v>0.9601030169045557</v>
       </c>
       <c r="F25">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>30</v>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Contraprestação de Parceria Público-Privada (PPP) - Iluminação Pública</t>
+        </is>
       </c>
       <c r="B26">
         <v>2022</v>
       </c>
       <c r="C26">
-        <v>504315828.50999999</v>
+        <v>504315828.51</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -2138,18 +936,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>31</v>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População em Situação de Rua</t>
+        </is>
       </c>
       <c r="B27">
         <v>2022</v>
       </c>
       <c r="C27">
-        <v>497830794.89999998</v>
+        <v>497830794.9</v>
       </c>
       <c r="D27">
-        <v>497830794.89999998</v>
+        <v>497830794.9</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2158,38 +958,42 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>32</v>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Aquisição de Materiais, Equipamentos e Serviços de Informação e Comunicação</t>
+        </is>
       </c>
       <c r="B28">
         <v>2022</v>
       </c>
       <c r="C28">
-        <v>478648145.56999999</v>
+        <v>478648145.57</v>
       </c>
       <c r="D28">
         <v>10414872.98</v>
       </c>
       <c r="E28">
-        <v>2.1758933104394269E-2</v>
+        <v>0.02175893310439427</v>
       </c>
       <c r="F28">
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>33</v>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Pavimentação e Recapeamento de Vias</t>
+        </is>
       </c>
       <c r="B29">
         <v>2022</v>
       </c>
       <c r="C29">
-        <v>465541359.07999998</v>
+        <v>465541359.08</v>
       </c>
       <c r="D29">
-        <v>453979389.81999999</v>
+        <v>453979389.82</v>
       </c>
       <c r="E29">
         <v>0.9751644638344299</v>
@@ -2198,9 +1002,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>34</v>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Intervenções no Sistema Viário</t>
+        </is>
       </c>
       <c r="B30">
         <v>2022</v>
@@ -2218,15 +1024,17 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>35</v>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação do Sistema Municipal de Transporte Coletivo</t>
+        </is>
       </c>
       <c r="B31">
         <v>2022</v>
       </c>
       <c r="C31">
-        <v>406086031.00999999</v>
+        <v>406086031.01</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2238,18 +1046,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>36</v>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para Crianças e Adolescentes</t>
+        </is>
       </c>
       <c r="B32">
         <v>2022</v>
       </c>
       <c r="C32">
-        <v>362749439.52999997</v>
+        <v>362749439.53</v>
       </c>
       <c r="D32">
-        <v>362749439.52999997</v>
+        <v>362749439.53</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -2258,18 +1068,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>37</v>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Ensino Fundamental (EMEF)</t>
+        </is>
       </c>
       <c r="B33">
         <v>2022</v>
       </c>
       <c r="C33">
-        <v>315523541.67000002</v>
+        <v>315523541.67</v>
       </c>
       <c r="D33">
-        <v>315523541.67000002</v>
+        <v>315523541.67</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -2278,18 +1090,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>38</v>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Manutenção de Sistemas de Drenagem</t>
+        </is>
       </c>
       <c r="B34">
         <v>2022</v>
       </c>
       <c r="C34">
-        <v>296180988.60000002</v>
+        <v>296180988.6</v>
       </c>
       <c r="D34">
-        <v>296180988.60000002</v>
+        <v>296180988.6</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2298,9 +1112,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>39</v>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Promoção de Campanhas e Eventos de Interesse do Município</t>
+        </is>
       </c>
       <c r="B35">
         <v>2022</v>
@@ -2318,18 +1134,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>40</v>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Construção e Implantação de Centros Educacionais Unificados (CEU)</t>
+        </is>
       </c>
       <c r="B36">
         <v>2022</v>
       </c>
       <c r="C36">
-        <v>289379724.97000003</v>
+        <v>289379724.97</v>
       </c>
       <c r="D36">
-        <v>289379724.97000003</v>
+        <v>289379724.97</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -2338,15 +1156,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>41</v>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Fornecimento de Uniformes e Material Escolar-Educação Infantil</t>
+        </is>
       </c>
       <c r="B37">
         <v>2022</v>
       </c>
       <c r="C37">
-        <v>289112565.49000001</v>
+        <v>289112565.49</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2358,15 +1178,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>42</v>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Serviço da Dívida Pública Interna - Refinanciamento</t>
+        </is>
       </c>
       <c r="B38">
         <v>2022</v>
       </c>
       <c r="C38">
-        <v>284587775.50999999</v>
+        <v>284587775.51</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2378,18 +1200,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>43</v>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Centros Educacionais Unificados (CEU)</t>
+        </is>
       </c>
       <c r="B39">
         <v>2022</v>
       </c>
       <c r="C39">
-        <v>266128601.72999999</v>
+        <v>266128601.73</v>
       </c>
       <c r="D39">
-        <v>266128601.72999999</v>
+        <v>266128601.73</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -2398,9 +1222,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>44</v>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Administração de Material  Médico Hospitalar e Ambulatorial em Atenção Básica, Especialidades e Vigilância</t>
+        </is>
       </c>
       <c r="B40">
         <v>2022</v>
@@ -2418,18 +1244,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>45</v>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Educação Infantil</t>
+        </is>
       </c>
       <c r="B41">
         <v>2022</v>
       </c>
       <c r="C41">
-        <v>236561428.40000001</v>
+        <v>236561428.4</v>
       </c>
       <c r="D41">
-        <v>236561428.40000001</v>
+        <v>236561428.4</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -2438,9 +1266,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>46</v>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Áreas Verdes e Vegetação Arbórea</t>
+        </is>
       </c>
       <c r="B42">
         <v>2022</v>
@@ -2458,18 +1288,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>47</v>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Ensino Fundamental</t>
+        </is>
       </c>
       <c r="B43">
         <v>2022</v>
       </c>
       <c r="C43">
-        <v>234121718.80000001</v>
+        <v>234121718.8</v>
       </c>
       <c r="D43">
-        <v>234121718.80000001</v>
+        <v>234121718.8</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -2478,29 +1310,33 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>48</v>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Serviços de Limpeza Urbana - Varrição e Lavagem de Áreas Públicas</t>
+        </is>
       </c>
       <c r="B44">
         <v>2022</v>
       </c>
       <c r="C44">
-        <v>233929969.56999999</v>
+        <v>233929969.57</v>
       </c>
       <c r="D44">
         <v>44981360.93</v>
       </c>
       <c r="E44">
-        <v>0.19228558449643199</v>
+        <v>0.192285584496432</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>49</v>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Fornecimento de Uniformes e Material Escolar-Ensino Fundamental</t>
+        </is>
       </c>
       <c r="B45">
         <v>2022</v>
@@ -2518,38 +1354,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>50</v>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Recuperação e Reforço de Obras de Arte Especiais - OAE</t>
+        </is>
       </c>
       <c r="B46">
         <v>2022</v>
       </c>
       <c r="C46">
-        <v>227860226.28999999</v>
+        <v>227860226.29</v>
       </c>
       <c r="D46">
-        <v>214082177.28999999</v>
+        <v>214082177.29</v>
       </c>
       <c r="E46">
-        <v>0.93953289161371878</v>
+        <v>0.9395328916137188</v>
       </c>
       <c r="F46">
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>51</v>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial a Crianças, Adolescentes e Jovens em Risco Social</t>
+        </is>
       </c>
       <c r="B47">
         <v>2022</v>
       </c>
       <c r="C47">
-        <v>226598778.33000001</v>
+        <v>226598778.33</v>
       </c>
       <c r="D47">
-        <v>226598778.33000001</v>
+        <v>226598778.33</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -2558,9 +1398,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>52</v>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Administração de Material Médico Hospitalar em Atenção Hospitalar, de Urgência e Emergência</t>
+        </is>
       </c>
       <c r="B48">
         <v>2022</v>
@@ -2578,9 +1420,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>53</v>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Transporte Escolar - Educação Infantil</t>
+        </is>
       </c>
       <c r="B49">
         <v>2022</v>
@@ -2598,15 +1442,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>54</v>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Serviço da Dívida Pública Interna</t>
+        </is>
       </c>
       <c r="B50">
         <v>2022</v>
       </c>
       <c r="C50">
-        <v>217803204.61000001</v>
+        <v>217803204.61</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2618,9 +1464,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>55</v>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Publicidade Institucional</t>
+        </is>
       </c>
       <c r="B51">
         <v>2022</v>
@@ -2638,38 +1486,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>56</v>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Terminais de Ônibus</t>
+        </is>
       </c>
       <c r="B52">
         <v>2022</v>
       </c>
       <c r="C52">
-        <v>206442018.31999999</v>
+        <v>206442018.32</v>
       </c>
       <c r="D52">
         <v>74649268</v>
       </c>
       <c r="E52">
-        <v>0.36159919675018998</v>
+        <v>0.36159919675019</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>57</v>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Escolas Municipais de Educação Infantil (EMEI)</t>
+        </is>
       </c>
       <c r="B53">
         <v>2022</v>
       </c>
       <c r="C53">
-        <v>205086769.41999999</v>
+        <v>205086769.42</v>
       </c>
       <c r="D53">
-        <v>205086769.41999999</v>
+        <v>205086769.42</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -2678,55 +1530,61 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>58</v>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Parques Urbanos e Lineares</t>
+        </is>
       </c>
       <c r="B54">
         <v>2022</v>
       </c>
       <c r="C54">
-        <v>201702938.97999999</v>
+        <v>201702938.98</v>
       </c>
       <c r="D54">
-        <v>196045759.08000001</v>
+        <v>196045759.08</v>
       </c>
       <c r="E54">
-        <v>0.97195291288957908</v>
+        <v>0.9719529128895791</v>
       </c>
       <c r="F54">
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>59</v>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ações e Materiais de Apoio Didático-Pedagógico Educacional</t>
+        </is>
       </c>
       <c r="B55">
         <v>2022</v>
       </c>
       <c r="C55">
-        <v>190864529.59999999</v>
+        <v>190864529.6</v>
       </c>
       <c r="D55">
-        <v>64735698.200000003</v>
+        <v>64735698.2</v>
       </c>
       <c r="E55">
-        <v>0.33917092052498371</v>
+        <v>0.3391709205249837</v>
       </c>
       <c r="F55">
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>60</v>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Programa Nacional de Alimentação Escolar - PNAE/ FNDE</t>
+        </is>
       </c>
       <c r="B56">
         <v>2022</v>
       </c>
       <c r="C56">
-        <v>183225691.59999999</v>
+        <v>183225691.6</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2738,9 +1596,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>61</v>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sistema de Remuneração Variável</t>
+        </is>
       </c>
       <c r="B57">
         <v>2022</v>
@@ -2758,15 +1618,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>62</v>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Transporte Escolar - Ensino Fundamental</t>
+        </is>
       </c>
       <c r="B58">
         <v>2022</v>
       </c>
       <c r="C58">
-        <v>159409713.81999999</v>
+        <v>159409713.82</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2778,15 +1640,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>63</v>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avança Saúde SP - Ampliação, Reforma e Requalificação de Equipamentos de Saúde_x000D__x000D_
+</t>
+        </is>
       </c>
       <c r="B59">
         <v>2022</v>
       </c>
       <c r="C59">
-        <v>150551524.19999999</v>
+        <v>150551524.2</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2798,18 +1663,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>64</v>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação no Serviço de Guias e Sarjetas (Vias e Logradouros)</t>
+        </is>
       </c>
       <c r="B60">
         <v>2022</v>
       </c>
       <c r="C60">
-        <v>146166915.49000001</v>
+        <v>146166915.49</v>
       </c>
       <c r="D60">
-        <v>146166915.49000001</v>
+        <v>146166915.49</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -2818,9 +1685,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>65</v>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Transporte de Pessoas com Deficiência ou Mobilidade Reduzida - ATENDE</t>
+        </is>
       </c>
       <c r="B61">
         <v>2022</v>
@@ -2838,18 +1707,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>66</v>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Centros de Educação Infantil (CEI)</t>
+        </is>
       </c>
       <c r="B62">
         <v>2022</v>
       </c>
       <c r="C62">
-        <v>140910802.69999999</v>
+        <v>140910802.7</v>
       </c>
       <c r="D62">
-        <v>140910802.69999999</v>
+        <v>140910802.7</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -2858,18 +1729,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>67</v>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação do Controle e Fiscalização de Tráfego</t>
+        </is>
       </c>
       <c r="B63">
         <v>2022</v>
       </c>
       <c r="C63">
-        <v>139656025.78999999</v>
+        <v>139656025.79</v>
       </c>
       <c r="D63">
-        <v>139656025.78999999</v>
+        <v>139656025.79</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -2878,15 +1751,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>68</v>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Condenações Judiciais - Créditos de Pequeno Valor</t>
+        </is>
       </c>
       <c r="B64">
         <v>2022</v>
       </c>
       <c r="C64">
-        <v>136579901.31999999</v>
+        <v>136579901.32</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2898,9 +1773,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>69</v>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Obras e Serviços nas Áreas de Riscos Geológicos</t>
+        </is>
       </c>
       <c r="B65">
         <v>2022</v>
@@ -2912,24 +1789,26 @@
         <v>134621442.78</v>
       </c>
       <c r="E65">
-        <v>0.98736840317814223</v>
+        <v>0.9873684031781422</v>
       </c>
       <c r="F65">
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>70</v>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos Intergeracionais de Convivência e Fortalecimento de Vínculos</t>
+        </is>
       </c>
       <c r="B66">
         <v>2022</v>
       </c>
       <c r="C66">
-        <v>129135564.40000001</v>
+        <v>129135564.4</v>
       </c>
       <c r="D66">
-        <v>129135564.40000001</v>
+        <v>129135564.4</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -2938,9 +1817,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>71</v>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos Esportivos</t>
+        </is>
       </c>
       <c r="B67">
         <v>2022</v>
@@ -2958,9 +1839,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>72</v>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Encargos pela Manutenção do Fundo de Depósitos Judiciais nas quais o Município é Parte</t>
+        </is>
       </c>
       <c r="B68">
         <v>2022</v>
@@ -2978,15 +1861,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>73</v>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Projetos e Ações de Apoio Habitacional</t>
+        </is>
       </c>
       <c r="B69">
         <v>2022</v>
       </c>
       <c r="C69">
-        <v>123534170.70999999</v>
+        <v>123534170.71</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2998,15 +1883,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>74</v>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Precatórios Pagos com Rendimentos dos Depósitos do Regime Especial</t>
+        </is>
       </c>
       <c r="B70">
         <v>2022</v>
       </c>
       <c r="C70">
-        <v>115606877.73999999</v>
+        <v>115606877.74</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -3018,9 +1905,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>75</v>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Leve-Leite</t>
+        </is>
       </c>
       <c r="B71">
         <v>2022</v>
@@ -3038,29 +1927,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>76</v>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Corredores de Ônibus</t>
+        </is>
       </c>
       <c r="B72">
         <v>2022</v>
       </c>
       <c r="C72">
-        <v>106545622.01000001</v>
+        <v>106545622.01</v>
       </c>
       <c r="D72">
         <v>105677307.39</v>
       </c>
       <c r="E72">
-        <v>0.99185030221214998</v>
+        <v>0.99185030221215</v>
       </c>
       <c r="F72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>77</v>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Sinalização do Sistema Viário</t>
+        </is>
       </c>
       <c r="B73">
         <v>2022</v>
@@ -3078,9 +1971,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>78</v>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Vigilância em Saúde</t>
+        </is>
       </c>
       <c r="B74">
         <v>2022</v>
@@ -3098,18 +1993,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>79</v>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Operação Tapa Buraco</t>
+        </is>
       </c>
       <c r="B75">
         <v>2022</v>
       </c>
       <c r="C75">
-        <v>99277957.439999998</v>
+        <v>99277957.44</v>
       </c>
       <c r="D75">
-        <v>99277957.439999998</v>
+        <v>99277957.44</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -3118,15 +2015,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>80</v>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Central de Atendimento Telefônico - 156</t>
+        </is>
       </c>
       <c r="B76">
         <v>2022</v>
       </c>
       <c r="C76">
-        <v>95402335.680000007</v>
+        <v>95402335.68000001</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3138,38 +2037,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>81</v>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Programação de Atividades Culturais</t>
+        </is>
       </c>
       <c r="B77">
         <v>2022</v>
       </c>
       <c r="C77">
-        <v>88341072.189999998</v>
+        <v>88341072.19</v>
       </c>
       <c r="D77">
-        <v>88241072.189999998</v>
+        <v>88241072.19</v>
       </c>
       <c r="E77">
-        <v>0.99886802370040373</v>
+        <v>0.9988680237004037</v>
       </c>
       <c r="F77">
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>82</v>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Manutenção de Vias e Áreas Públicas</t>
+        </is>
       </c>
       <c r="B78">
         <v>2022</v>
       </c>
       <c r="C78">
-        <v>87364388.569999993</v>
+        <v>87364388.56999999</v>
       </c>
       <c r="D78">
-        <v>87364388.569999993</v>
+        <v>87364388.56999999</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -3178,15 +2081,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>83</v>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ações de Difusão Cultural do Theatro Municipal - Grupos Artísticos, Técnicos e Administrativos</t>
+        </is>
       </c>
       <c r="B79">
         <v>2022</v>
       </c>
       <c r="C79">
-        <v>87150331.640000001</v>
+        <v>87150331.64</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3198,15 +2103,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>84</v>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Serviço de Atendimento Médico de Urgência (SAMU)</t>
+        </is>
       </c>
       <c r="B80">
         <v>2022</v>
       </c>
       <c r="C80">
-        <v>84814953.730000004</v>
+        <v>84814953.73</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3218,18 +2125,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>85</v>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Remuneração dos Profissionais do Magistério - Ensino Fundamental</t>
+        </is>
       </c>
       <c r="B81">
         <v>2022</v>
       </c>
       <c r="C81">
-        <v>83729511.719999999</v>
+        <v>83729511.72</v>
       </c>
       <c r="D81">
-        <v>83729511.719999999</v>
+        <v>83729511.72</v>
       </c>
       <c r="E81">
         <v>1</v>
@@ -3238,15 +2147,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>86</v>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Ações de Apoio à Educação Especial</t>
+        </is>
       </c>
       <c r="B82">
         <v>2022</v>
       </c>
       <c r="C82">
-        <v>80872787.790000007</v>
+        <v>80872787.79000001</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3258,9 +2169,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>87</v>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Programa de Incentivo Fiscal Relacionado à Arena Corinthians</t>
+        </is>
       </c>
       <c r="B83">
         <v>2022</v>
@@ -3278,15 +2191,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>88</v>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Servidores Comissionados em Outras Entidades</t>
+        </is>
       </c>
       <c r="B84">
         <v>2022</v>
       </c>
       <c r="C84">
-        <v>67812134.200000003</v>
+        <v>67812134.2</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3298,15 +2213,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>89</v>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Serviço de Moradia Transitória</t>
+        </is>
       </c>
       <c r="B85">
         <v>2022</v>
       </c>
       <c r="C85">
-        <v>66677331.310000002</v>
+        <v>66677331.31</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3318,18 +2235,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>90</v>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos de Proteção Social Básica às Famílias</t>
+        </is>
       </c>
       <c r="B86">
         <v>2022</v>
       </c>
       <c r="C86">
-        <v>65710474.840000004</v>
+        <v>65710474.84</v>
       </c>
       <c r="D86">
-        <v>65710474.840000004</v>
+        <v>65710474.84</v>
       </c>
       <c r="E86">
         <v>1</v>
@@ -3338,18 +2257,20 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>91</v>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Urbanização de Favelas</t>
+        </is>
       </c>
       <c r="B87">
         <v>2022</v>
       </c>
       <c r="C87">
-        <v>63501968.289999999</v>
+        <v>63501968.29</v>
       </c>
       <c r="D87">
-        <v>48361398.460000001</v>
+        <v>48361398.46</v>
       </c>
       <c r="E87">
         <v>0.7615732198905043</v>
@@ -3358,9 +2279,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>92</v>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos Esportivos</t>
+        </is>
       </c>
       <c r="B88">
         <v>2022</v>
@@ -3378,38 +2301,42 @@
         <v>19</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>93</v>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Incentivo à Prática de Esportes</t>
+        </is>
       </c>
       <c r="B89">
         <v>2022</v>
       </c>
       <c r="C89">
-        <v>62167996.020000003</v>
+        <v>62167996.02</v>
       </c>
       <c r="D89">
-        <v>7939684.5499999998</v>
+        <v>7939684.55</v>
       </c>
       <c r="E89">
-        <v>0.12771337437748079</v>
+        <v>0.1277133743774808</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>94</v>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Realização de Eventos de Esporte, Lazer e Recreação</t>
+        </is>
       </c>
       <c r="B90">
         <v>2022</v>
       </c>
       <c r="C90">
-        <v>61554493.960000001</v>
+        <v>61554493.96</v>
       </c>
       <c r="D90">
-        <v>6768805.7400000002</v>
+        <v>6768805.74</v>
       </c>
       <c r="E90">
         <v>0.1099644445846404</v>
@@ -3418,15 +2345,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>95</v>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Atenção Hospitalar da Assistência Farmacêutica</t>
+        </is>
       </c>
       <c r="B91">
         <v>2022</v>
       </c>
       <c r="C91">
-        <v>58584852.450000003</v>
+        <v>58584852.45</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3438,18 +2367,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>96</v>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Remuneração dos Profissionais do Magistério - Centro de Educação Infantil (CEI)</t>
+        </is>
       </c>
       <c r="B92">
         <v>2022</v>
       </c>
       <c r="C92">
-        <v>57950537.469999999</v>
+        <v>57950537.47</v>
       </c>
       <c r="D92">
-        <v>57950537.469999999</v>
+        <v>57950537.47</v>
       </c>
       <c r="E92">
         <v>1</v>
@@ -3458,15 +2389,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>97</v>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Capacitação, Formação e Aperfeiçoamento dos Trabalhadores</t>
+        </is>
       </c>
       <c r="B93">
         <v>2022</v>
       </c>
       <c r="C93">
-        <v>57662486.799999997</v>
+        <v>57662486.8</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3478,9 +2411,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>98</v>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Ações Integradas de Segurança Pública - Operação Delegada - Convênio SSP SO</t>
+        </is>
       </c>
       <c r="B94">
         <v>2022</v>
@@ -3498,18 +2433,20 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>99</v>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Remuneração dos Profissionais do Magistério - Escola Municipal de Educação Infantil (EMEI)</t>
+        </is>
       </c>
       <c r="B95">
         <v>2022</v>
       </c>
       <c r="C95">
-        <v>56366375.579999998</v>
+        <v>56366375.58</v>
       </c>
       <c r="D95">
-        <v>56366375.579999998</v>
+        <v>56366375.58</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -3518,9 +2455,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>100</v>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação Semafórica</t>
+        </is>
       </c>
       <c r="B96">
         <v>2022</v>
@@ -3538,18 +2477,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>101</v>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à Pessoa com Deficiência</t>
+        </is>
       </c>
       <c r="B97">
         <v>2022</v>
       </c>
       <c r="C97">
-        <v>53786390.390000001</v>
+        <v>53786390.39</v>
       </c>
       <c r="D97">
-        <v>53786390.390000001</v>
+        <v>53786390.39</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -3558,18 +2499,20 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>102</v>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População Idosa</t>
+        </is>
       </c>
       <c r="B98">
         <v>2022</v>
       </c>
       <c r="C98">
-        <v>53533979.009999998</v>
+        <v>53533979.01</v>
       </c>
       <c r="D98">
-        <v>53533979.009999998</v>
+        <v>53533979.01</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -3578,18 +2521,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>103</v>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos da Assistência Social</t>
+        </is>
       </c>
       <c r="B99">
         <v>2022</v>
       </c>
       <c r="C99">
-        <v>45257699.560000002</v>
+        <v>45257699.56</v>
       </c>
       <c r="D99">
-        <v>45257699.560000002</v>
+        <v>45257699.56</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -3598,15 +2543,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>104</v>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Administração da Carteira Imobiliária</t>
+        </is>
       </c>
       <c r="B100">
         <v>2022</v>
       </c>
       <c r="C100">
-        <v>44647923.189999998</v>
+        <v>44647923.19</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3618,18 +2565,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>105</v>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Construção de Centros de Educação Infantil - CEI</t>
+        </is>
       </c>
       <c r="B101">
         <v>2022</v>
       </c>
       <c r="C101">
-        <v>44151997.359999999</v>
+        <v>44151997.36</v>
       </c>
       <c r="D101">
-        <v>44151997.359999999</v>
+        <v>44151997.36</v>
       </c>
       <c r="E101">
         <v>1</v>
@@ -3638,15 +2587,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>106</v>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Ações Permanentes de Promoção dos Direitos da Criança e do Adolescente</t>
+        </is>
       </c>
       <c r="B102">
         <v>2022</v>
       </c>
       <c r="C102">
-        <v>43802369.200000003</v>
+        <v>43802369.2</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3658,15 +2609,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>107</v>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Serviço da Dívida Pública Externa</t>
+        </is>
       </c>
       <c r="B103">
         <v>2022</v>
       </c>
       <c r="C103">
-        <v>42307339.420000002</v>
+        <v>42307339.42</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3678,35 +2631,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>108</v>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Posto do Corpo de Bombeiros</t>
+        </is>
       </c>
       <c r="B104">
         <v>2022</v>
       </c>
       <c r="C104">
-        <v>41633271.020000003</v>
+        <v>41633271.02</v>
       </c>
       <c r="D104">
-        <v>39741770.210000001</v>
+        <v>39741770.21</v>
       </c>
       <c r="E104">
-        <v>0.95456756666822185</v>
+        <v>0.9545675666682218</v>
       </c>
       <c r="F104">
         <v>32</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>109</v>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Realização de Eventos Culturais</t>
+        </is>
       </c>
       <c r="B105">
         <v>2022</v>
       </c>
       <c r="C105">
-        <v>39628073.490000002</v>
+        <v>39628073.49</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -3718,9 +2675,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>110</v>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Guarda Civil Metropolitana</t>
+        </is>
       </c>
       <c r="B106">
         <v>2022</v>
@@ -3732,21 +2691,23 @@
         <v>24784998.07</v>
       </c>
       <c r="E106">
-        <v>0.62885713368368257</v>
+        <v>0.6288571336836826</v>
       </c>
       <c r="F106">
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>111</v>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Administração dos Conselhos Tutelares</t>
+        </is>
       </c>
       <c r="B107">
         <v>2022</v>
       </c>
       <c r="C107">
-        <v>38209128.340000004</v>
+        <v>38209128.34</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -3758,15 +2719,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>112</v>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Políticas, Programas e Ações para Educação em Direitos Humanos e Promoção do Direito à Cidade</t>
+        </is>
       </c>
       <c r="B108">
         <v>2022</v>
       </c>
       <c r="C108">
-        <v>35187843.229999997</v>
+        <v>35187843.23</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3778,18 +2741,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>113</v>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para a Pessoa Idosa</t>
+        </is>
       </c>
       <c r="B109">
         <v>2022</v>
       </c>
       <c r="C109">
-        <v>34352741.960000001</v>
+        <v>34352741.96</v>
       </c>
       <c r="D109">
-        <v>34352741.960000001</v>
+        <v>34352741.96</v>
       </c>
       <c r="E109">
         <v>1</v>
@@ -3798,18 +2763,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>114</v>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Centros Educacionais Unificados (CEU)</t>
+        </is>
       </c>
       <c r="B110">
         <v>2022</v>
       </c>
       <c r="C110">
-        <v>34347863.439999998</v>
+        <v>34347863.44</v>
       </c>
       <c r="D110">
-        <v>34347863.439999998</v>
+        <v>34347863.44</v>
       </c>
       <c r="E110">
         <v>1</v>
@@ -3818,35 +2785,39 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>115</v>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Modernização Semafórica</t>
+        </is>
       </c>
       <c r="B111">
         <v>2022</v>
       </c>
       <c r="C111">
-        <v>34223141.490000002</v>
+        <v>34223141.49</v>
       </c>
       <c r="D111">
-        <v>7199299.6799999997</v>
+        <v>7199299.68</v>
       </c>
       <c r="E111">
-        <v>0.21036349576802099</v>
+        <v>0.210363495768021</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>116</v>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Aposentadoria Complementar aos Servidores da São Paulo Transporte S/A</t>
+        </is>
       </c>
       <c r="B112">
         <v>2022</v>
       </c>
       <c r="C112">
-        <v>33838306.649999999</v>
+        <v>33838306.65</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3858,15 +2829,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>117</v>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Regularização Fundiária</t>
+        </is>
       </c>
       <c r="B113">
         <v>2022</v>
       </c>
       <c r="C113">
-        <v>31419509.550000001</v>
+        <v>31419509.55</v>
       </c>
       <c r="D113">
         <v>15476252.57</v>
@@ -3878,18 +2851,20 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>118</v>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Intervenções em Próprios Municipais</t>
+        </is>
       </c>
       <c r="B114">
         <v>2022</v>
       </c>
       <c r="C114">
-        <v>31384941.760000002</v>
+        <v>31384941.76</v>
       </c>
       <c r="D114">
-        <v>16463809.800000001</v>
+        <v>16463809.8</v>
       </c>
       <c r="E114">
         <v>0.5245767198135467</v>
@@ -3898,9 +2873,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>119</v>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Coleta, Transporte, Tratamento e Dest. Final Resíduos Sólidos Inertes</t>
+        </is>
       </c>
       <c r="B115">
         <v>2022</v>
@@ -3909,7 +2886,7 @@
         <v>30805228.5</v>
       </c>
       <c r="D115">
-        <v>5970537.3500000006</v>
+        <v>5970537.350000001</v>
       </c>
       <c r="E115">
         <v>0.1938157137837819</v>
@@ -3918,18 +2895,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>120</v>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação do Policiamento de Trânsito</t>
+        </is>
       </c>
       <c r="B116">
         <v>2022</v>
       </c>
       <c r="C116">
-        <v>30737267.600000001</v>
+        <v>30737267.6</v>
       </c>
       <c r="D116">
-        <v>30737267.600000001</v>
+        <v>30737267.6</v>
       </c>
       <c r="E116">
         <v>1</v>
@@ -3938,38 +2917,42 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>121</v>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Clube da Comunidade (CDC)</t>
+        </is>
       </c>
       <c r="B117">
         <v>2022</v>
       </c>
       <c r="C117">
-        <v>30668307.620000001</v>
+        <v>30668307.62</v>
       </c>
       <c r="D117">
         <v>25353641.02</v>
       </c>
       <c r="E117">
-        <v>0.82670492725415012</v>
+        <v>0.8267049272541501</v>
       </c>
       <c r="F117">
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>122</v>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Prédios Administrativos</t>
+        </is>
       </c>
       <c r="B118">
         <v>2022</v>
       </c>
       <c r="C118">
-        <v>29911972.739999998</v>
+        <v>29911972.74</v>
       </c>
       <c r="D118">
-        <v>29911972.739999998</v>
+        <v>29911972.74</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -3978,9 +2961,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>123</v>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Programa Municipal de Apoio a Projetos Culturais (PRO-MAC)</t>
+        </is>
       </c>
       <c r="B119">
         <v>2022</v>
@@ -3992,21 +2977,23 @@
         <v>28656</v>
       </c>
       <c r="E119">
-        <v>9.761541683281147E-4</v>
+        <v>0.0009761541683281147</v>
       </c>
       <c r="F119">
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>124</v>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Políticas, Programas e Ações para a População em Situação de Rua</t>
+        </is>
       </c>
       <c r="B120">
         <v>2022</v>
       </c>
       <c r="C120">
-        <v>28727744.739999998</v>
+        <v>28727744.74</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -4018,18 +3005,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>125</v>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Ações de Fiscalização do Comércio Ilegal</t>
+        </is>
       </c>
       <c r="B121">
         <v>2022</v>
       </c>
       <c r="C121">
-        <v>27949308.690000001</v>
+        <v>27949308.69</v>
       </c>
       <c r="D121">
-        <v>27949308.690000001</v>
+        <v>27949308.69</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -4038,9 +3027,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>126</v>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Operação e Manutenção da Agência São Paulo de Desenvolvimento - ADESAMPA</t>
+        </is>
       </c>
       <c r="B122">
         <v>2022</v>
@@ -4058,18 +3049,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>127</v>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Políticas de Audiovisual</t>
+        </is>
       </c>
       <c r="B123">
         <v>2022</v>
       </c>
       <c r="C123">
-        <v>27461812.879999999</v>
+        <v>27461812.88</v>
       </c>
       <c r="D123">
-        <v>27461812.879999999</v>
+        <v>27461812.88</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -4078,18 +3071,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>128</v>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Eventos Educacionais, Culturais e Esportivos nos Centros Educacionais Unificados</t>
+        </is>
       </c>
       <c r="B124">
         <v>2022</v>
       </c>
       <c r="C124">
-        <v>26571850.559999999</v>
+        <v>26571850.56</v>
       </c>
       <c r="D124">
-        <v>26571850.559999999</v>
+        <v>26571850.56</v>
       </c>
       <c r="E124">
         <v>1</v>
@@ -4098,9 +3093,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>129</v>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Aporte para Garantia de PPP's e Projetos de Infraestrutura</t>
+        </is>
       </c>
       <c r="B125">
         <v>2022</v>
@@ -4118,18 +3115,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>130</v>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Construção e Implantação de Parques Urbanos e Lineares</t>
+        </is>
       </c>
       <c r="B126">
         <v>2022</v>
       </c>
       <c r="C126">
-        <v>25837166.100000001</v>
+        <v>25837166.1</v>
       </c>
       <c r="D126">
-        <v>25837166.100000001</v>
+        <v>25837166.1</v>
       </c>
       <c r="E126">
         <v>1</v>
@@ -4138,18 +3137,20 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>131</v>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - Educação Infantil</t>
+        </is>
       </c>
       <c r="B127">
         <v>2022</v>
       </c>
       <c r="C127">
-        <v>25670688.449999999</v>
+        <v>25670688.45</v>
       </c>
       <c r="D127">
-        <v>25670688.449999999</v>
+        <v>25670688.45</v>
       </c>
       <c r="E127">
         <v>1</v>
@@ -4158,18 +3159,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>132</v>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Construção de Ciclovias, Ciclofaixas e Ciclorrotas</t>
+        </is>
       </c>
       <c r="B128">
         <v>2022</v>
       </c>
       <c r="C128">
-        <v>23813318.789999999</v>
+        <v>23813318.79</v>
       </c>
       <c r="D128">
-        <v>23813318.789999999</v>
+        <v>23813318.79</v>
       </c>
       <c r="E128">
         <v>1</v>
@@ -4178,9 +3181,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>133</v>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Contraprestação de Parceria Público-Privada (PPP) - Terminais Urbanos</t>
+        </is>
       </c>
       <c r="B129">
         <v>2022</v>
@@ -4198,35 +3203,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>134</v>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Implantação de Corredores de Ônibus Novos</t>
+        </is>
       </c>
       <c r="B130">
         <v>2022</v>
       </c>
       <c r="C130">
-        <v>23187857.359999999</v>
+        <v>23187857.36</v>
       </c>
       <c r="D130">
         <v>18912415.66</v>
       </c>
       <c r="E130">
-        <v>0.81561721578573665</v>
+        <v>0.8156172157857366</v>
       </c>
       <c r="F130">
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>135</v>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação em Serviços de Saúde Animal</t>
+        </is>
       </c>
       <c r="B131">
         <v>2022</v>
       </c>
       <c r="C131">
-        <v>23054771.449999999</v>
+        <v>23054771.45</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -4238,9 +3247,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>136</v>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Áreas Públicas</t>
+        </is>
       </c>
       <c r="B132">
         <v>2022</v>
@@ -4249,18 +3260,20 @@
         <v>22231986.32</v>
       </c>
       <c r="D132">
-        <v>18477677.850000001</v>
+        <v>18477677.85</v>
       </c>
       <c r="E132">
-        <v>0.83113031755409972</v>
+        <v>0.8311303175540997</v>
       </c>
       <c r="F132">
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>137</v>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Serviços de Desfazimento e Demolição de Construções Irregulares em Áreas de Proteção Ambiental</t>
+        </is>
       </c>
       <c r="B133">
         <v>2022</v>
@@ -4278,18 +3291,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>138</v>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação do Descomplica SP</t>
+        </is>
       </c>
       <c r="B134">
         <v>2022</v>
       </c>
       <c r="C134">
-        <v>21921972.539999999</v>
+        <v>21921972.54</v>
       </c>
       <c r="D134">
-        <v>21921972.539999999</v>
+        <v>21921972.54</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -4298,18 +3313,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>139</v>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Centros Culturais e Teatros</t>
+        </is>
       </c>
       <c r="B135">
         <v>2022</v>
       </c>
       <c r="C135">
-        <v>21166445.199999999</v>
+        <v>21166445.2</v>
       </c>
       <c r="D135">
-        <v>21166445.199999999</v>
+        <v>21166445.2</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -4318,18 +3335,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>140</v>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Centro Educacional Unificado (CEU)</t>
+        </is>
       </c>
       <c r="B136">
         <v>2022</v>
       </c>
       <c r="C136">
-        <v>21132114.800000001</v>
+        <v>21132114.8</v>
       </c>
       <c r="D136">
-        <v>21132114.800000001</v>
+        <v>21132114.8</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -4338,9 +3357,11 @@
         <v>19</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>141</v>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Fomento à Cooperação, Parcerias e Captação de Investimentos Internacionais</t>
+        </is>
       </c>
       <c r="B137">
         <v>2022</v>
@@ -4358,15 +3379,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>142</v>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Desenvolvimento de Sistemas de Informação e Comunicação</t>
+        </is>
       </c>
       <c r="B138">
         <v>2022</v>
       </c>
       <c r="C138">
-        <v>20814739.879999999</v>
+        <v>20814739.88</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -4378,9 +3401,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>143</v>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Programa de Atração a Filmagens - Cash Rebate</t>
+        </is>
       </c>
       <c r="B139">
         <v>2022</v>
@@ -4398,18 +3423,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>144</v>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Unidades de Conservação</t>
+        </is>
       </c>
       <c r="B140">
         <v>2022</v>
       </c>
       <c r="C140">
-        <v>19234719.739999998</v>
+        <v>19234719.74</v>
       </c>
       <c r="D140">
-        <v>19234719.739999998</v>
+        <v>19234719.74</v>
       </c>
       <c r="E140">
         <v>1</v>
@@ -4418,9 +3445,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>145</v>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos de Atenção Básica e Especialidades</t>
+        </is>
       </c>
       <c r="B141">
         <v>2022</v>
@@ -4438,29 +3467,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>146</v>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Mulheres</t>
+        </is>
       </c>
       <c r="B142">
         <v>2022</v>
       </c>
       <c r="C142">
-        <v>18767407.329999998</v>
+        <v>18767407.33</v>
       </c>
       <c r="D142">
         <v>11394125.51</v>
       </c>
       <c r="E142">
-        <v>0.60712304633503156</v>
+        <v>0.6071230463350316</v>
       </c>
       <c r="F142">
         <v>19</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>147</v>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Lei de Fomento ao Teatro</t>
+        </is>
       </c>
       <c r="B143">
         <v>2022</v>
@@ -4478,18 +3511,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>148</v>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos de Proteção Jurídico Social</t>
+        </is>
       </c>
       <c r="B144">
         <v>2022</v>
       </c>
       <c r="C144">
-        <v>16751333.539999999</v>
+        <v>16751333.54</v>
       </c>
       <c r="D144">
-        <v>16751333.539999999</v>
+        <v>16751333.54</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -4498,15 +3533,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>149</v>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Gratificação de Municipalização - Saúde - Lei 13.510/03</t>
+        </is>
       </c>
       <c r="B145">
         <v>2022</v>
       </c>
       <c r="C145">
-        <v>16583528.380000001</v>
+        <v>16583528.38</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -4518,9 +3555,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>150</v>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Bibliotecas Públicas</t>
+        </is>
       </c>
       <c r="B146">
         <v>2022</v>
@@ -4538,9 +3577,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>151</v>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
+        </is>
       </c>
       <c r="B147">
         <v>2022</v>
@@ -4552,15 +3593,17 @@
         <v>36045.4</v>
       </c>
       <c r="E147">
-        <v>2.22270807935049E-3</v>
+        <v>0.00222270807935049</v>
       </c>
       <c r="F147">
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>152</v>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação da Avenida Santo Amaro</t>
+        </is>
       </c>
       <c r="B148">
         <v>2022</v>
@@ -4578,18 +3621,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>153</v>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Fomento à Cultura da Periferia de São Paulo</t>
+        </is>
       </c>
       <c r="B149">
         <v>2022</v>
       </c>
       <c r="C149">
-        <v>15560079.109999999</v>
+        <v>15560079.11</v>
       </c>
       <c r="D149">
-        <v>15560079.109999999</v>
+        <v>15560079.11</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -4598,15 +3643,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>154</v>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Encargos Referentes a Arrecadação</t>
+        </is>
       </c>
       <c r="B150">
         <v>2022</v>
       </c>
       <c r="C150">
-        <v>15538669.890000001</v>
+        <v>15538669.89</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -4618,9 +3665,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>155</v>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Ações de Educação Integral</t>
+        </is>
       </c>
       <c r="B151">
         <v>2022</v>
@@ -4638,9 +3687,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>156</v>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Construção e Implantação do Descomplica SP</t>
+        </is>
       </c>
       <c r="B152">
         <v>2022</v>
@@ -4658,9 +3709,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>157</v>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Circuito Cultural de São Paulo</t>
+        </is>
       </c>
       <c r="B153">
         <v>2022</v>
@@ -4672,21 +3725,23 @@
         <v>2115002.85</v>
       </c>
       <c r="E153">
-        <v>0.14422793936123879</v>
+        <v>0.1442279393612388</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>158</v>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Ações de Desestatização</t>
+        </is>
       </c>
       <c r="B154">
         <v>2022</v>
       </c>
       <c r="C154">
-        <v>14578504.050000001</v>
+        <v>14578504.05</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -4698,9 +3753,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>159</v>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Centros Municipais de Educação Infantil(CEMEI)</t>
+        </is>
       </c>
       <c r="B155">
         <v>2022</v>
@@ -4718,18 +3775,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>160</v>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação dos Sistemas de Monitoramento e Alerta de Enchentes</t>
+        </is>
       </c>
       <c r="B156">
         <v>2022</v>
       </c>
       <c r="C156">
-        <v>14149331.939999999</v>
+        <v>14149331.94</v>
       </c>
       <c r="D156">
-        <v>14149331.939999999</v>
+        <v>14149331.94</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -4738,18 +3797,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>161</v>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Operação e Manutenção dos Centros de Apoio ao Trabalho e Empreendedorismo</t>
+        </is>
       </c>
       <c r="B157">
         <v>2022</v>
       </c>
       <c r="C157">
-        <v>14100188.939999999</v>
+        <v>14100188.94</v>
       </c>
       <c r="D157">
-        <v>14100188.939999999</v>
+        <v>14100188.94</v>
       </c>
       <c r="E157">
         <v>1</v>
@@ -4758,9 +3819,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>162</v>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação do Autódromo de Interlagos</t>
+        </is>
       </c>
       <c r="B158">
         <v>2022</v>
@@ -4778,18 +3841,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>163</v>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Inserção das Famílias no Cadastro Único</t>
+        </is>
       </c>
       <c r="B159">
         <v>2022</v>
       </c>
       <c r="C159">
-        <v>13393117.390000001</v>
+        <v>13393117.39</v>
       </c>
       <c r="D159">
-        <v>13393117.390000001</v>
+        <v>13393117.39</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -4798,18 +3863,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>164</v>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Escolas Municipais de Educação Infantil (EMEI)</t>
+        </is>
       </c>
       <c r="B160">
         <v>2022</v>
       </c>
       <c r="C160">
-        <v>13390255.890000001</v>
+        <v>13390255.89</v>
       </c>
       <c r="D160">
-        <v>13390255.890000001</v>
+        <v>13390255.89</v>
       </c>
       <c r="E160">
         <v>1</v>
@@ -4818,18 +3885,20 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>165</v>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Ações de formação das Escolas de Música e Dança do Theatro Municipal e da Praça das Artes</t>
+        </is>
       </c>
       <c r="B161">
         <v>2022</v>
       </c>
       <c r="C161">
-        <v>13283396.970000001</v>
+        <v>13283396.97</v>
       </c>
       <c r="D161">
-        <v>13283396.970000001</v>
+        <v>13283396.97</v>
       </c>
       <c r="E161">
         <v>1</v>
@@ -4838,9 +3907,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>166</v>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Programação da Virada Esportiva</t>
+        </is>
       </c>
       <c r="B162">
         <v>2022</v>
@@ -4852,15 +3923,17 @@
         <v>740057.75</v>
       </c>
       <c r="E162">
-        <v>5.6379171076024498E-2</v>
+        <v>0.0563791710760245</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>167</v>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Operação e Manutenção de Unidade da Fundação Paulistana - FPETC</t>
+        </is>
       </c>
       <c r="B163">
         <v>2022</v>
@@ -4878,9 +3951,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>168</v>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Alfabetização na Idade Certa</t>
+        </is>
       </c>
       <c r="B164">
         <v>2022</v>
@@ -4898,9 +3973,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>169</v>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos do Departamento dos Museus Municipais</t>
+        </is>
       </c>
       <c r="B165">
         <v>2022</v>
@@ -4912,15 +3989,17 @@
         <v>12658860.82</v>
       </c>
       <c r="E165">
-        <v>0.99941559085410125</v>
+        <v>0.9994155908541013</v>
       </c>
       <c r="F165">
         <v>32</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>170</v>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Rede Parceira - Alfabetização de Jovens e Adultos</t>
+        </is>
       </c>
       <c r="B166">
         <v>2022</v>
@@ -4938,9 +4017,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>171</v>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Capacitação, Formação e Aperfeiçoamento de Servidores</t>
+        </is>
       </c>
       <c r="B167">
         <v>2022</v>
@@ -4952,24 +4033,26 @@
         <v>148410</v>
       </c>
       <c r="E167">
-        <v>1.2124323296347781E-2</v>
+        <v>0.01212432329634778</v>
       </c>
       <c r="F167">
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>172</v>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Telecentros</t>
+        </is>
       </c>
       <c r="B168">
         <v>2022</v>
       </c>
       <c r="C168">
-        <v>11968074.109999999</v>
+        <v>11968074.11</v>
       </c>
       <c r="D168">
-        <v>11968074.109999999</v>
+        <v>11968074.11</v>
       </c>
       <c r="E168">
         <v>1</v>
@@ -4978,9 +4061,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>173</v>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - Ensino Fundamental</t>
+        </is>
       </c>
       <c r="B169">
         <v>2022</v>
@@ -4998,9 +4083,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>174</v>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Casas de Cultura</t>
+        </is>
       </c>
       <c r="B170">
         <v>2022</v>
@@ -5018,15 +4105,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>175</v>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Operação e Manutenção da São Paulo Investimentos e Negócios</t>
+        </is>
       </c>
       <c r="B171">
         <v>2022</v>
       </c>
       <c r="C171">
-        <v>11387248.810000001</v>
+        <v>11387248.81</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -5038,9 +4127,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>176</v>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Praças, Canteiros Centrais e Remanescentes</t>
+        </is>
       </c>
       <c r="B172">
         <v>2022</v>
@@ -5058,9 +4149,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>177</v>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Preservação do Patrimônio Histórico, Artístico, Cultural e Arqueológico</t>
+        </is>
       </c>
       <c r="B173">
         <v>2022</v>
@@ -5078,18 +4171,20 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>178</v>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Parques Urbanos e Lineares</t>
+        </is>
       </c>
       <c r="B174">
         <v>2022</v>
       </c>
       <c r="C174">
-        <v>11059459.310000001</v>
+        <v>11059459.31</v>
       </c>
       <c r="D174">
-        <v>11059459.310000001</v>
+        <v>11059459.31</v>
       </c>
       <c r="E174">
         <v>1</v>
@@ -5098,9 +4193,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>179</v>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Bolsa-Trabalho</t>
+        </is>
       </c>
       <c r="B175">
         <v>2022</v>
@@ -5118,9 +4215,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>180</v>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Execução do Programa para a Valorização de Iniciativas Culturais</t>
+        </is>
       </c>
       <c r="B176">
         <v>2022</v>
@@ -5132,15 +4231,17 @@
         <v>10964074.67</v>
       </c>
       <c r="E176">
-        <v>0.99978115118374677</v>
+        <v>0.9997811511837468</v>
       </c>
       <c r="F176">
         <v>30</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>181</v>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação do Programa Melhor em Casa</t>
+        </is>
       </c>
       <c r="B177">
         <v>2022</v>
@@ -5158,9 +4259,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>182</v>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Manutenção de Unidades Habitacionais</t>
+        </is>
       </c>
       <c r="B178">
         <v>2022</v>
@@ -5169,18 +4272,20 @@
         <v>10776569.84</v>
       </c>
       <c r="D178">
-        <v>7181610.0599999996</v>
+        <v>7181610.06</v>
       </c>
       <c r="E178">
-        <v>0.66640964301494288</v>
+        <v>0.6664096430149429</v>
       </c>
       <c r="F178">
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>183</v>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Câmara Municipal - Comunicação</t>
+        </is>
       </c>
       <c r="B179">
         <v>2022</v>
@@ -5198,9 +4303,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>184</v>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Lei de Fomento à Dança</t>
+        </is>
       </c>
       <c r="B180">
         <v>2022</v>
@@ -5218,9 +4325,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>185</v>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Ações de Difusão Cultural do Theatro Municipal - Patrimônio</t>
+        </is>
       </c>
       <c r="B181">
         <v>2022</v>
@@ -5238,18 +4347,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>186</v>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Fundamental e Médio (EMEFM)</t>
+        </is>
       </c>
       <c r="B182">
         <v>2022</v>
       </c>
       <c r="C182">
-        <v>10344486.939999999</v>
+        <v>10344486.94</v>
       </c>
       <c r="D182">
-        <v>10344486.939999999</v>
+        <v>10344486.94</v>
       </c>
       <c r="E182">
         <v>1</v>
@@ -5258,18 +4369,20 @@
         <v>29</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>187</v>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação do Centro Cultural São Paulo</t>
+        </is>
       </c>
       <c r="B183">
         <v>2022</v>
       </c>
       <c r="C183">
-        <v>10321076.050000001</v>
+        <v>10321076.05</v>
       </c>
       <c r="D183">
-        <v>10321076.050000001</v>
+        <v>10321076.05</v>
       </c>
       <c r="E183">
         <v>1</v>
@@ -5278,15 +4391,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>188</v>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Realização de Projetos Culturais</t>
+        </is>
       </c>
       <c r="B184">
         <v>2022</v>
       </c>
       <c r="C184">
-        <v>10160081.189999999</v>
+        <v>10160081.19</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -5298,9 +4413,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>189</v>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Cooperação Técnica Internacional</t>
+        </is>
       </c>
       <c r="B185">
         <v>2022</v>
@@ -5318,15 +4435,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>190</v>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Projetos de Fomento ao Turismo</t>
+        </is>
       </c>
       <c r="B186">
         <v>2022</v>
       </c>
       <c r="C186">
-        <v>9981513.9000000004</v>
+        <v>9981513.9</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -5338,15 +4457,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>191</v>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação dos Serviços de DST / AIDS</t>
+        </is>
       </c>
       <c r="B187">
         <v>2022</v>
       </c>
       <c r="C187">
-        <v>9769126.9299999997</v>
+        <v>9769126.93</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -5358,38 +4479,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>192</v>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Programação da Virada Cultural</t>
+        </is>
       </c>
       <c r="B188">
         <v>2022</v>
       </c>
       <c r="C188">
-        <v>9690172.1999999993</v>
+        <v>9690172.199999999</v>
       </c>
       <c r="D188">
         <v>9097957</v>
       </c>
       <c r="E188">
-        <v>0.93888496635797669</v>
+        <v>0.9388849663579767</v>
       </c>
       <c r="F188">
         <v>24</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>193</v>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Programa Jovem Monitor Cultural</t>
+        </is>
       </c>
       <c r="B189">
         <v>2022</v>
       </c>
       <c r="C189">
-        <v>9674276.1099999994</v>
+        <v>9674276.109999999</v>
       </c>
       <c r="D189">
-        <v>9674276.1099999994</v>
+        <v>9674276.109999999</v>
       </c>
       <c r="E189">
         <v>1</v>
@@ -5398,9 +4523,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>194</v>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Inspeção de Obras de Artes Especiais - OAE</t>
+        </is>
       </c>
       <c r="B190">
         <v>2022</v>
@@ -5409,7 +4536,7 @@
         <v>9671093.290000001</v>
       </c>
       <c r="D190">
-        <v>5771998.9400000004</v>
+        <v>5771998.94</v>
       </c>
       <c r="E190">
         <v>0.5968300343011167</v>
@@ -5418,18 +4545,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>195</v>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação dos Pólos Regionais de Esporte</t>
+        </is>
       </c>
       <c r="B191">
         <v>2022</v>
       </c>
       <c r="C191">
-        <v>9629770.7100000009</v>
+        <v>9629770.710000001</v>
       </c>
       <c r="D191">
-        <v>9629770.7100000009</v>
+        <v>9629770.710000001</v>
       </c>
       <c r="E191">
         <v>1</v>
@@ -5438,18 +4567,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>196</v>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Biblioteca Mario de Andrade</t>
+        </is>
       </c>
       <c r="B192">
         <v>2022</v>
       </c>
       <c r="C192">
-        <v>9620896.3399999999</v>
+        <v>9620896.34</v>
       </c>
       <c r="D192">
-        <v>9620896.3399999999</v>
+        <v>9620896.34</v>
       </c>
       <c r="E192">
         <v>1</v>
@@ -5458,18 +4589,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>197</v>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Compensações Ambientais</t>
+        </is>
       </c>
       <c r="B193">
         <v>2022</v>
       </c>
       <c r="C193">
-        <v>9556954.5800000001</v>
+        <v>9556954.58</v>
       </c>
       <c r="D193">
-        <v>9556954.5800000001</v>
+        <v>9556954.58</v>
       </c>
       <c r="E193">
         <v>1</v>
@@ -5478,15 +4611,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>198</v>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Compensação Financeira - Outros Fundos de Previdência</t>
+        </is>
       </c>
       <c r="B194">
         <v>2022</v>
       </c>
       <c r="C194">
-        <v>9491442.3399999999</v>
+        <v>9491442.34</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -5498,18 +4633,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>199</v>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Escola Municipal de Educação Artística - EMIA</t>
+        </is>
       </c>
       <c r="B195">
         <v>2022</v>
       </c>
       <c r="C195">
-        <v>9482790.9900000002</v>
+        <v>9482790.99</v>
       </c>
       <c r="D195">
-        <v>9482790.9900000002</v>
+        <v>9482790.99</v>
       </c>
       <c r="E195">
         <v>1</v>
@@ -5518,18 +4655,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>200</v>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Prêmio Zé Renato</t>
+        </is>
       </c>
       <c r="B196">
         <v>2022</v>
       </c>
       <c r="C196">
-        <v>9478914.5500000007</v>
+        <v>9478914.550000001</v>
       </c>
       <c r="D196">
-        <v>9478914.5500000007</v>
+        <v>9478914.550000001</v>
       </c>
       <c r="E196">
         <v>1</v>
@@ -5538,18 +4677,20 @@
         <v>6</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>201</v>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Subvenção e Contribuições a Entidades Culturais</t>
+        </is>
       </c>
       <c r="B197">
         <v>2022</v>
       </c>
       <c r="C197">
-        <v>9297471.0399999991</v>
+        <v>9297471.039999999</v>
       </c>
       <c r="D197">
-        <v>9297471.0399999991</v>
+        <v>9297471.039999999</v>
       </c>
       <c r="E197">
         <v>1</v>
@@ -5558,18 +4699,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>202</v>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Programação de Atividades Culturais de Casas de Cultura</t>
+        </is>
       </c>
       <c r="B198">
         <v>2022</v>
       </c>
       <c r="C198">
-        <v>9167527.7200000007</v>
+        <v>9167527.720000001</v>
       </c>
       <c r="D198">
-        <v>9167527.7200000007</v>
+        <v>9167527.720000001</v>
       </c>
       <c r="E198">
         <v>1</v>
@@ -5578,18 +4721,20 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>203</v>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Escola Municipal de Ensino Fundamental (EMEF)</t>
+        </is>
       </c>
       <c r="B199">
         <v>2022</v>
       </c>
       <c r="C199">
-        <v>9050432.5800000001</v>
+        <v>9050432.58</v>
       </c>
       <c r="D199">
-        <v>9050432.5800000001</v>
+        <v>9050432.58</v>
       </c>
       <c r="E199">
         <v>1</v>
@@ -5598,9 +4743,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>204</v>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Ações para Promoção da Sustentabilidade Previdenciária</t>
+        </is>
       </c>
       <c r="B200">
         <v>2022</v>
@@ -5618,35 +4765,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>205</v>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Intervenções na Área de Mobilidade Urbana</t>
+        </is>
       </c>
       <c r="B201">
         <v>2022</v>
       </c>
       <c r="C201">
-        <v>8901911.2699999996</v>
+        <v>8901911.27</v>
       </c>
       <c r="D201">
         <v>4700473.43</v>
       </c>
       <c r="E201">
-        <v>0.52802968794363192</v>
+        <v>0.5280296879436319</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>206</v>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Transporte Escolar - Educação Especial</t>
+        </is>
       </c>
       <c r="B202">
         <v>2022</v>
       </c>
       <c r="C202">
-        <v>8848599.6999999993</v>
+        <v>8848599.699999999</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -5658,9 +4809,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>207</v>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Viveiros</t>
+        </is>
       </c>
       <c r="B203">
         <v>2022</v>
@@ -5678,35 +4831,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>208</v>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Fomento às Linguagens Artísticas</t>
+        </is>
       </c>
       <c r="B204">
         <v>2022</v>
       </c>
       <c r="C204">
-        <v>8668750.4299999997</v>
+        <v>8668750.43</v>
       </c>
       <c r="D204">
-        <v>8624381.9299999997</v>
+        <v>8624381.93</v>
       </c>
       <c r="E204">
-        <v>0.99488178828560414</v>
+        <v>0.9948817882856041</v>
       </c>
       <c r="F204">
         <v>29</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>209</v>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Ações Permanentes de Promoção dos Direitos da População Idosa</t>
+        </is>
       </c>
       <c r="B205">
         <v>2022</v>
       </c>
       <c r="C205">
-        <v>8330895.9000000004</v>
+        <v>8330895.9</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -5718,15 +4875,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>210</v>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Ações de Difusão Cultural do Theatro Municipal - Programação Artística</t>
+        </is>
       </c>
       <c r="B206">
         <v>2022</v>
       </c>
       <c r="C206">
-        <v>8164819.7000000002</v>
+        <v>8164819.7</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -5738,15 +4897,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>211</v>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Sistema de Avaliação Escolar dos Alunos da Rede Municipal de Ensino</t>
+        </is>
       </c>
       <c r="B207">
         <v>2022</v>
       </c>
       <c r="C207">
-        <v>8144055.0600000015</v>
+        <v>8144055.060000001</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -5758,18 +4919,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>212</v>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Remuneração dos Profissionais do Magistério - Centro Municipal de Educação Infantil( CEMEI)</t>
+        </is>
       </c>
       <c r="B208">
         <v>2022</v>
       </c>
       <c r="C208">
-        <v>8093438.7800000003</v>
+        <v>8093438.78</v>
       </c>
       <c r="D208">
-        <v>8093438.7800000003</v>
+        <v>8093438.78</v>
       </c>
       <c r="E208">
         <v>1</v>
@@ -5778,18 +4941,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>213</v>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Implantação do Memorial dos Aflitos</t>
+        </is>
       </c>
       <c r="B209">
         <v>2022</v>
       </c>
       <c r="C209">
-        <v>8091703.3799999999</v>
+        <v>8091703.38</v>
       </c>
       <c r="D209">
-        <v>8091703.3799999999</v>
+        <v>8091703.38</v>
       </c>
       <c r="E209">
         <v>1</v>
@@ -5798,18 +4963,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>214</v>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Programação de Atividades Culturais de Centros Culturais e Teatros</t>
+        </is>
       </c>
       <c r="B210">
         <v>2022</v>
       </c>
       <c r="C210">
-        <v>8079770.0599999996</v>
+        <v>8079770.06</v>
       </c>
       <c r="D210">
-        <v>8079770.0599999996</v>
+        <v>8079770.06</v>
       </c>
       <c r="E210">
         <v>1</v>
@@ -5818,18 +4985,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>215</v>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Rede Parceira - Educação Especial</t>
+        </is>
       </c>
       <c r="B211">
         <v>2022</v>
       </c>
       <c r="C211">
-        <v>7763494.9900000002</v>
+        <v>7763494.99</v>
       </c>
       <c r="D211">
-        <v>7763494.9900000002</v>
+        <v>7763494.99</v>
       </c>
       <c r="E211">
         <v>1</v>
@@ -5838,18 +5007,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>216</v>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Construção da Fábrica do Samba</t>
+        </is>
       </c>
       <c r="B212">
         <v>2022</v>
       </c>
       <c r="C212">
-        <v>7738081.3499999996</v>
+        <v>7738081.35</v>
       </c>
       <c r="D212">
-        <v>7738081.3499999996</v>
+        <v>7738081.35</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -5858,15 +5029,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>217</v>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Suporte e Manutenção da Coordenação de Imprensa</t>
+        </is>
       </c>
       <c r="B213">
         <v>2022</v>
       </c>
       <c r="C213">
-        <v>7676657.2300000004</v>
+        <v>7676657.23</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -5878,9 +5051,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>218</v>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Centro Olímpicos</t>
+        </is>
       </c>
       <c r="B214">
         <v>2022</v>
@@ -5898,9 +5073,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>219</v>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Qualificação Profissional e Empreendedora</t>
+        </is>
       </c>
       <c r="B215">
         <v>2022</v>
@@ -5918,18 +5095,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>220</v>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Programa de Garantia de Renda Familiar Mínima</t>
+        </is>
       </c>
       <c r="B216">
         <v>2022</v>
       </c>
       <c r="C216">
-        <v>7491383.6100000003</v>
+        <v>7491383.61</v>
       </c>
       <c r="D216">
-        <v>7491383.6100000003</v>
+        <v>7491383.61</v>
       </c>
       <c r="E216">
         <v>1</v>
@@ -5938,18 +5117,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>221</v>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Edificação da Câmara Municipal de São Paulo</t>
+        </is>
       </c>
       <c r="B217">
         <v>2022</v>
       </c>
       <c r="C217">
-        <v>7465375.6399999997</v>
+        <v>7465375.64</v>
       </c>
       <c r="D217">
-        <v>7465375.6399999997</v>
+        <v>7465375.64</v>
       </c>
       <c r="E217">
         <v>1</v>
@@ -5958,15 +5139,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>222</v>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Recuperação de Fachadas Históricas na Área Central</t>
+        </is>
       </c>
       <c r="B218">
         <v>2022</v>
       </c>
       <c r="C218">
-        <v>7340892.4199999999</v>
+        <v>7340892.42</v>
       </c>
       <c r="D218">
         <v>0</v>
@@ -5978,15 +5161,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>223</v>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Administração do Edifício Matarazzo</t>
+        </is>
       </c>
       <c r="B219">
         <v>2022</v>
       </c>
       <c r="C219">
-        <v>7280422.2000000002</v>
+        <v>7280422.2</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -5998,15 +5183,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>224</v>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Parceria Público Privada - Habitação</t>
+        </is>
       </c>
       <c r="B220">
         <v>2022</v>
       </c>
       <c r="C220">
-        <v>6960978.0899999999</v>
+        <v>6960978.09</v>
       </c>
       <c r="D220">
         <v>0</v>
@@ -6018,15 +5205,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>225</v>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Programa Nacional de Apoio à Gestão Adm. e Fiscal - PNAFM</t>
+        </is>
       </c>
       <c r="B221">
         <v>2022</v>
       </c>
       <c r="C221">
-        <v>6795896.7999999998</v>
+        <v>6795896.8</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -6038,18 +5227,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>226</v>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Plantio de Árvores</t>
+        </is>
       </c>
       <c r="B222">
         <v>2022</v>
       </c>
       <c r="C222">
-        <v>6594546.4299999997</v>
+        <v>6594546.43</v>
       </c>
       <c r="D222">
-        <v>6594546.4299999997</v>
+        <v>6594546.43</v>
       </c>
       <c r="E222">
         <v>1</v>
@@ -6058,58 +5249,64 @@
         <v>32</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>227</v>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Acessibilidade, Ampliação, Reforma e Requalificação de Terminais de Ônibus</t>
+        </is>
       </c>
       <c r="B223">
         <v>2022</v>
       </c>
       <c r="C223">
-        <v>6561837.6499999994</v>
+        <v>6561837.649999999</v>
       </c>
       <c r="D223">
-        <v>6515637.6499999994</v>
+        <v>6515637.649999999</v>
       </c>
       <c r="E223">
-        <v>0.99295928938443034</v>
+        <v>0.9929592893844303</v>
       </c>
       <c r="F223">
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>228</v>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos Culturais</t>
+        </is>
       </c>
       <c r="B224">
         <v>2022</v>
       </c>
       <c r="C224">
-        <v>6325250.2199999997</v>
+        <v>6325250.22</v>
       </c>
       <c r="D224">
-        <v>6222857.0300000003</v>
+        <v>6222857.03</v>
       </c>
       <c r="E224">
-        <v>0.98381199376488859</v>
+        <v>0.9838119937648886</v>
       </c>
       <c r="F224">
         <v>32</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>229</v>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Casa da Mulher Brasileira</t>
+        </is>
       </c>
       <c r="B225">
         <v>2022</v>
       </c>
       <c r="C225">
-        <v>6248971.8300000001</v>
+        <v>6248971.83</v>
       </c>
       <c r="D225">
-        <v>6248971.8300000001</v>
+        <v>6248971.83</v>
       </c>
       <c r="E225">
         <v>1</v>
@@ -6118,15 +5315,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>230</v>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Ações de Difusão Cultural do Theatro Municipal - Administrativos</t>
+        </is>
       </c>
       <c r="B226">
         <v>2022</v>
       </c>
       <c r="C226">
-        <v>6237478.6399999997</v>
+        <v>6237478.64</v>
       </c>
       <c r="D226">
         <v>0</v>
@@ -6138,18 +5337,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>231</v>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação dos Equipamentos Públicos Voltados ao Atendimento da População LGBTI</t>
+        </is>
       </c>
       <c r="B227">
         <v>2022</v>
       </c>
       <c r="C227">
-        <v>6165357.3300000001</v>
+        <v>6165357.33</v>
       </c>
       <c r="D227">
-        <v>6165357.3300000001</v>
+        <v>6165357.33</v>
       </c>
       <c r="E227">
         <v>1</v>
@@ -6158,18 +5359,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>232</v>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Unidades Educacionais - Centro Integrado de Jovens e Adultos (CIEJA)</t>
+        </is>
       </c>
       <c r="B228">
         <v>2022</v>
       </c>
       <c r="C228">
-        <v>5948992.7199999997</v>
+        <v>5948992.72</v>
       </c>
       <c r="D228">
-        <v>5948992.7199999997</v>
+        <v>5948992.72</v>
       </c>
       <c r="E228">
         <v>1</v>
@@ -6178,15 +5381,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>233</v>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Fomento às Cadeias Produtivas, Vocações Produtivas e Projetos Locais</t>
+        </is>
       </c>
       <c r="B229">
         <v>2022</v>
       </c>
       <c r="C229">
-        <v>5934897.2800000003</v>
+        <v>5934897.28</v>
       </c>
       <c r="D229">
         <v>0</v>
@@ -6198,15 +5403,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>234</v>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação dos Serviços de Atendimento e Manejo da Fauna Silvestre</t>
+        </is>
       </c>
       <c r="B230">
         <v>2022</v>
       </c>
       <c r="C230">
-        <v>5792320.9199999999</v>
+        <v>5792320.92</v>
       </c>
       <c r="D230">
         <v>0</v>
@@ -6218,9 +5425,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>235</v>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Servidores Comissionados no Hospital Serv. Públco Municipal - HSPM</t>
+        </is>
       </c>
       <c r="B231">
         <v>2022</v>
@@ -6238,15 +5447,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>236</v>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Construção de Corredores de Ônibus</t>
+        </is>
       </c>
       <c r="B232">
         <v>2022</v>
       </c>
       <c r="C232">
-        <v>5287276.6899999985</v>
+        <v>5287276.689999999</v>
       </c>
       <c r="D232">
         <v>0</v>
@@ -6258,15 +5469,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>237</v>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Políticas, Programas e Ações para a População LGBTI+</t>
+        </is>
       </c>
       <c r="B233">
         <v>2022</v>
       </c>
       <c r="C233">
-        <v>5167420.9000000004</v>
+        <v>5167420.9</v>
       </c>
       <c r="D233">
         <v>0</v>
@@ -6278,15 +5491,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>238</v>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Políticas, Programas e Ações para Juventude</t>
+        </is>
       </c>
       <c r="B234">
         <v>2022</v>
       </c>
       <c r="C234">
-        <v>5057261.6500000004</v>
+        <v>5057261.65</v>
       </c>
       <c r="D234">
         <v>0</v>
@@ -6298,9 +5513,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>239</v>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Políticas de Promoção Cultural nas Bibliotecas Públicas</t>
+        </is>
       </c>
       <c r="B235">
         <v>2022</v>
@@ -6318,9 +5535,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>240</v>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Políticas de promoção cultural</t>
+        </is>
       </c>
       <c r="B236">
         <v>2022</v>
@@ -6338,9 +5557,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>241</v>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos Culturais</t>
+        </is>
       </c>
       <c r="B237">
         <v>2022</v>
@@ -6358,9 +5579,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>242</v>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Ciclovias, Ciclofaixas e Ciclorrotas</t>
+        </is>
       </c>
       <c r="B238">
         <v>2022</v>
@@ -6378,9 +5601,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>243</v>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Unidades Educacionais - Educação Indígena</t>
+        </is>
       </c>
       <c r="B239">
         <v>2022</v>
@@ -6398,9 +5623,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>244</v>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Centros de Educação Infantil (CEI)</t>
+        </is>
       </c>
       <c r="B240">
         <v>2022</v>
@@ -6418,9 +5645,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>245</v>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Oficina nos Equipamentos Culturais</t>
+        </is>
       </c>
       <c r="B241">
         <v>2022</v>
@@ -6438,9 +5667,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>246</v>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Construção de Escolas Municipais de Educação Infantil (EMEI)</t>
+        </is>
       </c>
       <c r="B242">
         <v>2022</v>
@@ -6458,9 +5689,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>247</v>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Despesas Administrativas para Execução de Ações Judiciais - Processamento de Feitos</t>
+        </is>
       </c>
       <c r="B243">
         <v>2022</v>
@@ -6478,9 +5711,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>248</v>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Bilíngue para Surdos (EMEBS)</t>
+        </is>
       </c>
       <c r="B244">
         <v>2022</v>
@@ -6498,9 +5733,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
-        <v>249</v>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Edição e Publicação do Diário Oficial da Cidade de São Paulo</t>
+        </is>
       </c>
       <c r="B245">
         <v>2022</v>
@@ -6518,9 +5755,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
-        <v>250</v>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - CEU</t>
+        </is>
       </c>
       <c r="B246">
         <v>2022</v>
@@ -6538,9 +5777,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>251</v>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Ações de Cooperação para o Desenvolvimento Sustentável</t>
+        </is>
       </c>
       <c r="B247">
         <v>2022</v>
@@ -6558,9 +5799,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>252</v>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Projetos para Inclusão da Pessoa com Deficiência</t>
+        </is>
       </c>
       <c r="B248">
         <v>2022</v>
@@ -6578,9 +5821,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>253</v>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Auxílio Funeral</t>
+        </is>
       </c>
       <c r="B249">
         <v>2022</v>
@@ -6598,9 +5843,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
-        <v>254</v>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>PROCONECTA - Promoção da Conectividade e Inclusão Digital</t>
+        </is>
       </c>
       <c r="B250">
         <v>2022</v>
@@ -6612,15 +5859,17 @@
         <v>3192905.08</v>
       </c>
       <c r="E250">
-        <v>0.93885677695465453</v>
+        <v>0.9388567769546545</v>
       </c>
       <c r="F250">
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>255</v>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Execução do Programa Museu de Arte de Rua - MAR</t>
+        </is>
       </c>
       <c r="B251">
         <v>2022</v>
@@ -6632,15 +5881,17 @@
         <v>443498</v>
       </c>
       <c r="E251">
-        <v>0.13322489649002181</v>
+        <v>0.1332248964900218</v>
       </c>
       <c r="F251">
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>256</v>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Fomento ao Circo/Edital Xamego</t>
+        </is>
       </c>
       <c r="B252">
         <v>2022</v>
@@ -6658,9 +5909,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>257</v>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Programação de Atividades Culturais do Centro Cultural São Paulo</t>
+        </is>
       </c>
       <c r="B253">
         <v>2022</v>
@@ -6678,9 +5931,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>258</v>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Rádios Comunitárias - Lei nº 16.572/2016</t>
+        </is>
       </c>
       <c r="B254">
         <v>2022</v>
@@ -6692,15 +5947,17 @@
         <v>3103200</v>
       </c>
       <c r="E254">
-        <v>0.96276991809381984</v>
+        <v>0.9627699180938198</v>
       </c>
       <c r="F254">
         <v>18</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>259</v>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Políticas, Programas e Ações Para Criança e Adolescente</t>
+        </is>
       </c>
       <c r="B255">
         <v>2022</v>
@@ -6718,9 +5975,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>260</v>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Fomento à Música</t>
+        </is>
       </c>
       <c r="B256">
         <v>2022</v>
@@ -6738,9 +5997,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>261</v>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Estudos, Planos e Projetos Ambientais</t>
+        </is>
       </c>
       <c r="B257">
         <v>2022</v>
@@ -6752,15 +6013,17 @@
         <v>1694402.61</v>
       </c>
       <c r="E257">
-        <v>0.55240032781309745</v>
+        <v>0.5524003278130974</v>
       </c>
       <c r="F257">
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
-        <v>262</v>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Políticas, Programas e Ações para Mulheres</t>
+        </is>
       </c>
       <c r="B258">
         <v>2022</v>
@@ -6778,9 +6041,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
-        <v>263</v>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Apoio à Cultura Negra</t>
+        </is>
       </c>
       <c r="B259">
         <v>2022</v>
@@ -6792,15 +6057,17 @@
         <v>282720</v>
       </c>
       <c r="E259">
-        <v>9.9319506108602795E-2</v>
+        <v>0.0993195061086028</v>
       </c>
       <c r="F259">
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
-        <v>264</v>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Obras de Combate a Enchentes e Alagamentos</t>
+        </is>
       </c>
       <c r="B260">
         <v>2022</v>
@@ -6818,9 +6085,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>265</v>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Rede de Iluminação Pública</t>
+        </is>
       </c>
       <c r="B261">
         <v>2022</v>
@@ -6832,15 +6101,17 @@
         <v>18067.57</v>
       </c>
       <c r="E261">
-        <v>6.4527089640496341E-3</v>
+        <v>0.006452708964049634</v>
       </c>
       <c r="F261">
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>266</v>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Centro de Referência de Segurança Alimentar e Nutricional</t>
+        </is>
       </c>
       <c r="B262">
         <v>2022</v>
@@ -6858,9 +6129,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>267</v>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Programa Piá</t>
+        </is>
       </c>
       <c r="B263">
         <v>2022</v>
@@ -6878,15 +6151,17 @@
         <v>27</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>268</v>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Ações de Educação de Trânsito</t>
+        </is>
       </c>
       <c r="B264">
         <v>2022</v>
       </c>
       <c r="C264">
-        <v>2541256.4900000002</v>
+        <v>2541256.49</v>
       </c>
       <c r="D264">
         <v>0</v>
@@ -6898,9 +6173,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>269</v>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Programa Vocacional</t>
+        </is>
       </c>
       <c r="B265">
         <v>2022</v>
@@ -6918,18 +6195,20 @@
         <v>23</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>270</v>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação do Arquivo Histórico Municipal</t>
+        </is>
       </c>
       <c r="B266">
         <v>2022</v>
       </c>
       <c r="C266">
-        <v>2444862.5099999998</v>
+        <v>2444862.51</v>
       </c>
       <c r="D266">
-        <v>2444862.5099999998</v>
+        <v>2444862.51</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -6938,9 +6217,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>271</v>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Programação de Atividades Culturais do Departamento dos Museus Municipais</t>
+        </is>
       </c>
       <c r="B267">
         <v>2022</v>
@@ -6958,38 +6239,42 @@
         <v>6</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
-        <v>272</v>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Operação e Manutenção das Centrais de Triagem - Coleta Seletiva</t>
+        </is>
       </c>
       <c r="B268">
         <v>2022</v>
       </c>
       <c r="C268">
-        <v>2261529.7799999998</v>
+        <v>2261529.78</v>
       </c>
       <c r="D268">
         <v>43859.48</v>
       </c>
       <c r="E268">
-        <v>1.9393722067192941E-2</v>
+        <v>0.01939372206719294</v>
       </c>
       <c r="F268">
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
-        <v>273</v>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Ações Municipais de Abastecimento</t>
+        </is>
       </c>
       <c r="B269">
         <v>2022</v>
       </c>
       <c r="C269">
-        <v>2221232.0499999998</v>
+        <v>2221232.05</v>
       </c>
       <c r="D269">
-        <v>2221232.0499999998</v>
+        <v>2221232.05</v>
       </c>
       <c r="E269">
         <v>1</v>
@@ -6998,15 +6283,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
-        <v>274</v>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Educação Ambiental</t>
+        </is>
       </c>
       <c r="B270">
         <v>2022</v>
       </c>
       <c r="C270">
-        <v>2210050.7200000002</v>
+        <v>2210050.72</v>
       </c>
       <c r="D270">
         <v>0</v>
@@ -7018,9 +6305,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>275</v>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Programação de Atividades Culturais nas Bibliotecas Públicas</t>
+        </is>
       </c>
       <c r="B271">
         <v>2022</v>
@@ -7038,9 +6327,11 @@
         <v>27</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
-        <v>276</v>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Manutenção de Ciclovias, Ciclofaixas e Ciclorrotas</t>
+        </is>
       </c>
       <c r="B272">
         <v>2022</v>
@@ -7058,9 +6349,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>277</v>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento da População de Rua</t>
+        </is>
       </c>
       <c r="B273">
         <v>2022</v>
@@ -7078,9 +6371,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>278</v>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Defesa Civil</t>
+        </is>
       </c>
       <c r="B274">
         <v>2022</v>
@@ -7092,15 +6387,17 @@
         <v>1960226.32</v>
       </c>
       <c r="E274">
-        <v>0.94137289762635645</v>
+        <v>0.9413728976263565</v>
       </c>
       <c r="F274">
         <v>32</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>279</v>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Mês do Hip Hop</t>
+        </is>
       </c>
       <c r="B275">
         <v>2022</v>
@@ -7118,9 +6415,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>280</v>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Política Municipal de Desenvolvimento Econômico</t>
+        </is>
       </c>
       <c r="B276">
         <v>2022</v>
@@ -7138,9 +6437,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>281</v>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação dos Planetários Municipais</t>
+        </is>
       </c>
       <c r="B277">
         <v>2022</v>
@@ -7158,9 +6459,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>282</v>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Imigrantes</t>
+        </is>
       </c>
       <c r="B278">
         <v>2022</v>
@@ -7178,9 +6481,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
-        <v>283</v>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Locação Social</t>
+        </is>
       </c>
       <c r="B279">
         <v>2022</v>
@@ -7198,9 +6503,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
-        <v>284</v>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Programa Mãos e Mentes Paulistanas</t>
+        </is>
       </c>
       <c r="B280">
         <v>2022</v>
@@ -7218,9 +6525,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
-        <v>285</v>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos Públicos Voltados à Promoção da Igualdade Racial</t>
+        </is>
       </c>
       <c r="B281">
         <v>2022</v>
@@ -7238,9 +6547,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
-        <v>286</v>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação dos Conselhos e Espaços Participativos Municipais</t>
+        </is>
       </c>
       <c r="B282">
         <v>2022</v>
@@ -7252,15 +6563,17 @@
         <v>963229.24</v>
       </c>
       <c r="E282">
-        <v>0.54476002629744669</v>
+        <v>0.5447600262974467</v>
       </c>
       <c r="F282">
         <v>12</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
-        <v>287</v>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Manutenção da Ouvidoria de Direitos Humanos</t>
+        </is>
       </c>
       <c r="B283">
         <v>2022</v>
@@ -7278,9 +6591,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
-        <v>288</v>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Fiscalização, Monitoramento e Controle Ambiental</t>
+        </is>
       </c>
       <c r="B284">
         <v>2022</v>
@@ -7298,9 +6613,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
-        <v>289</v>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Execução de Serviços Médicos de Tratamento de Radioterapia</t>
+        </is>
       </c>
       <c r="B285">
         <v>2022</v>
@@ -7318,9 +6635,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
-        <v>290</v>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação nas Áreas de Parada e Plataforma de Embarque de Faixa Exclusiva de Ônibus</t>
+        </is>
       </c>
       <c r="B286">
         <v>2022</v>
@@ -7338,9 +6657,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
-        <v>291</v>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Reembolso ao Serviço Funerário</t>
+        </is>
       </c>
       <c r="B287">
         <v>2022</v>
@@ -7358,9 +6679,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
-        <v>292</v>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Melhoria de Bairros no âmbito da Subprefeitura da Capela do Socorro.</t>
+        </is>
       </c>
       <c r="B288">
         <v>2022</v>
@@ -7378,9 +6701,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
-        <v>293</v>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Bloqueios Judiciais</t>
+        </is>
       </c>
       <c r="B289">
         <v>2022</v>
@@ -7398,9 +6723,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
-        <v>294</v>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Centro Municipal para Pessoas com Transtorno do Espectro Autista</t>
+        </is>
       </c>
       <c r="B290">
         <v>2022</v>
@@ -7418,9 +6745,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
-        <v>295</v>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Apoio e Suporte Técnico para o Desenvolvimento de Estudos e Projetos Urbanos</t>
+        </is>
       </c>
       <c r="B291">
         <v>2022</v>
@@ -7438,9 +6767,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
-        <v>296</v>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Ações e Atividades Culturais da Biblioteca Mario de Andrade</t>
+        </is>
       </c>
       <c r="B292">
         <v>2022</v>
@@ -7458,9 +6789,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
-        <v>297</v>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Difusão, Fomento e Pesquisas Aplicadas à Gestão de Tecnologia, Inovação e Atendimento ao Cidadão</t>
+        </is>
       </c>
       <c r="B293">
         <v>2022</v>
@@ -7478,9 +6811,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>298</v>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Projeto de Intervenção Urbana - PIU</t>
+        </is>
       </c>
       <c r="B294">
         <v>2022</v>
@@ -7492,15 +6827,17 @@
         <v>52127.69</v>
       </c>
       <c r="E294">
-        <v>3.6745492542322317E-2</v>
+        <v>0.03674549254232232</v>
       </c>
       <c r="F294">
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>299</v>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Manutenção de Prédios Administrativos</t>
+        </is>
       </c>
       <c r="B295">
         <v>2022</v>
@@ -7512,15 +6849,17 @@
         <v>846052.55</v>
       </c>
       <c r="E295">
-        <v>0.59716995162793285</v>
+        <v>0.5971699516279328</v>
       </c>
       <c r="F295">
         <v>12</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>300</v>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Restituição de Amortização Extraordinária e Liquidação Antecipada</t>
+        </is>
       </c>
       <c r="B296">
         <v>2022</v>
@@ -7538,9 +6877,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>301</v>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação dos Centros de Estudos de Línguas Paulistano - CELP</t>
+        </is>
       </c>
       <c r="B297">
         <v>2022</v>
@@ -7558,9 +6899,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>302</v>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Programa de Articulação Criativa</t>
+        </is>
       </c>
       <c r="B298">
         <v>2022</v>
@@ -7572,15 +6915,17 @@
         <v>850710</v>
       </c>
       <c r="E298">
-        <v>0.62063456165053144</v>
+        <v>0.6206345616505314</v>
       </c>
       <c r="F298">
         <v>32</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>303</v>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação dos Equipamentos Públicos Voltados para Pessoa Idosa</t>
+        </is>
       </c>
       <c r="B299">
         <v>2022</v>
@@ -7598,15 +6943,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
-        <v>304</v>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Desenvolvimento de Estudos, Projetos  e Instrumentos de Políticas Urbanas</t>
+        </is>
       </c>
       <c r="B300">
         <v>2022</v>
       </c>
       <c r="C300">
-        <v>1308867.3400000001</v>
+        <v>1308867.34</v>
       </c>
       <c r="D300">
         <v>0</v>
@@ -7618,9 +6965,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>305</v>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Equipes de Alto Desempenho com Representatividade em Competições Locais, Regionais, Nacionais e Mundiais</t>
+        </is>
       </c>
       <c r="B301">
         <v>2022</v>
@@ -7638,9 +6987,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>306</v>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Programa de Iniciação Artística para a Primeira Infância - PIAPI</t>
+        </is>
       </c>
       <c r="B302">
         <v>2022</v>
@@ -7658,9 +7009,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>307</v>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Manutenção de Modalidades Desportivas do Centro Olímpico de Treinamento e Pesquisa (COTP)</t>
+        </is>
       </c>
       <c r="B303">
         <v>2022</v>
@@ -7678,9 +7031,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>308</v>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operação e Manutenção do Portal da PMSP_x000D__x000D_
+</t>
+        </is>
       </c>
       <c r="B304">
         <v>2022</v>
@@ -7698,15 +7054,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>309</v>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Vivência Prática de Gestão de Documentos</t>
+        </is>
       </c>
       <c r="B305">
         <v>2022</v>
       </c>
       <c r="C305">
-        <v>1087835.4099999999</v>
+        <v>1087835.41</v>
       </c>
       <c r="D305">
         <v>0</v>
@@ -7718,9 +7076,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>310</v>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Difusão, Fomento e Pesquisas Aplicadas para a Gestão Participativa e Desenvolvimento Urbano</t>
+        </is>
       </c>
       <c r="B306">
         <v>2022</v>
@@ -7738,9 +7098,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>311</v>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Fomento às Comunidades do Samba</t>
+        </is>
       </c>
       <c r="B307">
         <v>2022</v>
@@ -7758,9 +7120,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>312</v>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Políticas, Programas e Ações para Imigrantes e Promoção ao Trabalho Decente</t>
+        </is>
       </c>
       <c r="B308">
         <v>2022</v>
@@ -7778,9 +7142,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>313</v>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Atualização do Currículo da Rede Municipal de Ensino</t>
+        </is>
       </c>
       <c r="B309">
         <v>2022</v>
@@ -7798,9 +7164,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
-        <v>314</v>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Operação e Manutenção do VAI TEC</t>
+        </is>
       </c>
       <c r="B310">
         <v>2022</v>
@@ -7818,9 +7186,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
-        <v>315</v>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Ações e Atividades Culturais do Departamento do Patrimônio Histórico</t>
+        </is>
       </c>
       <c r="B311">
         <v>2022</v>
@@ -7832,24 +7202,26 @@
         <v>1027898.3</v>
       </c>
       <c r="E311">
-        <v>0.99941662519033814</v>
+        <v>0.9994166251903381</v>
       </c>
       <c r="F311">
         <v>31</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
-        <v>316</v>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Construção de Galeria, bem como Boca de Lobo para Captação de Água Pluvial, na Viela João Carlos Pereira, Altura no Número 13</t>
+        </is>
       </c>
       <c r="B312">
         <v>2022</v>
       </c>
       <c r="C312">
-        <v>954124.32000000007</v>
+        <v>954124.3200000001</v>
       </c>
       <c r="D312">
-        <v>954124.32000000007</v>
+        <v>954124.3200000001</v>
       </c>
       <c r="E312">
         <v>1</v>
@@ -7858,9 +7230,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>317</v>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Prospecção de Problemas Públicos e Ideação de Alternativas para Inovação</t>
+        </is>
       </c>
       <c r="B313">
         <v>2022</v>
@@ -7878,9 +7252,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>318</v>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>FUMCAD - Multas Revertidas ao Fundo</t>
+        </is>
       </c>
       <c r="B314">
         <v>2022</v>
@@ -7898,9 +7274,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>319</v>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Tarifa de Arrecadação de Multas</t>
+        </is>
       </c>
       <c r="B315">
         <v>2022</v>
@@ -7918,9 +7296,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>320</v>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>"Comemoração do ""Dia Municipal da Cultura Evangélica"" - 09 de Julho - Lei nº 14.232 de 07 de Novembro de 2006"</t>
+        </is>
       </c>
       <c r="B316">
         <v>2022</v>
@@ -7938,15 +7318,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
-        <v>321</v>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Operação e Manutenção da Infraestrutura Turística</t>
+        </is>
       </c>
       <c r="B317">
         <v>2022</v>
       </c>
       <c r="C317">
-        <v>882697.94</v>
+        <v>882697.9399999999</v>
       </c>
       <c r="D317">
         <v>0</v>
@@ -7958,9 +7340,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
-        <v>322</v>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Manutenção das Instalações da Guarda Civil Metropolitana</t>
+        </is>
       </c>
       <c r="B318">
         <v>2022</v>
@@ -7978,9 +7362,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
-        <v>323</v>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Programa Aldeias</t>
+        </is>
       </c>
       <c r="B319">
         <v>2022</v>
@@ -7998,9 +7384,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
-        <v>324</v>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Plano Municipal do Livro, Leitura, Literatura e Biblioteca (PMLLLB)</t>
+        </is>
       </c>
       <c r="B320">
         <v>2022</v>
@@ -8018,18 +7406,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
-        <v>325</v>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Implantação e Construção de Ecopontos</t>
+        </is>
       </c>
       <c r="B321">
         <v>2022</v>
       </c>
       <c r="C321">
-        <v>840970.57</v>
+        <v>840970.5699999999</v>
       </c>
       <c r="D321">
-        <v>840970.57</v>
+        <v>840970.5699999999</v>
       </c>
       <c r="E321">
         <v>1</v>
@@ -8038,9 +7428,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
-        <v>326</v>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Programação de Atividades e Eventos da Cultura Reggae</t>
+        </is>
       </c>
       <c r="B322">
         <v>2022</v>
@@ -8058,9 +7450,11 @@
         <v>19</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
-        <v>327</v>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Acompanhamento das Aprendizagens e Permanência Escolar</t>
+        </is>
       </c>
       <c r="B323">
         <v>2022</v>
@@ -8078,18 +7472,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A324" t="s">
-        <v>328</v>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Unidades de Conservação</t>
+        </is>
       </c>
       <c r="B324">
         <v>2022</v>
       </c>
       <c r="C324">
-        <v>815593.07</v>
+        <v>815593.0699999999</v>
       </c>
       <c r="D324">
-        <v>815593.07</v>
+        <v>815593.0699999999</v>
       </c>
       <c r="E324">
         <v>1</v>
@@ -8098,29 +7494,33 @@
         <v>2</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
-        <v>329</v>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Fomento e Difusão do Forró</t>
+        </is>
       </c>
       <c r="B325">
         <v>2022</v>
       </c>
       <c r="C325">
-        <v>808367.19</v>
+        <v>808367.1899999999</v>
       </c>
       <c r="D325">
-        <v>796367.19</v>
+        <v>796367.1899999999</v>
       </c>
       <c r="E325">
-        <v>0.98515526094026651</v>
+        <v>0.9851552609402665</v>
       </c>
       <c r="F325">
         <v>17</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
-        <v>330</v>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Unidades Educacionais - Centro Municipal de Capacitação e Treinamento (CMCT)</t>
+        </is>
       </c>
       <c r="B326">
         <v>2022</v>
@@ -8138,9 +7538,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A327" t="s">
-        <v>331</v>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação do Centro Público de Economia Solidária e Direitos Humanos</t>
+        </is>
       </c>
       <c r="B327">
         <v>2022</v>
@@ -8158,9 +7560,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
-        <v>332</v>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Publicação de Editais e Outras Publicações Legais e de Interesse do Município</t>
+        </is>
       </c>
       <c r="B328">
         <v>2022</v>
@@ -8178,18 +7582,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
-        <v>333</v>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Implantação de Estrutura Turística no Triângulo Histórico</t>
+        </is>
       </c>
       <c r="B329">
         <v>2022</v>
       </c>
       <c r="C329">
-        <v>762391.56</v>
+        <v>762391.5600000001</v>
       </c>
       <c r="D329">
-        <v>762391.56</v>
+        <v>762391.5600000001</v>
       </c>
       <c r="E329">
         <v>1</v>
@@ -8198,15 +7604,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
-        <v>334</v>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Promoção à Saúde do Servidor Municipal</t>
+        </is>
       </c>
       <c r="B330">
         <v>2022</v>
       </c>
       <c r="C330">
-        <v>725838.85000000009</v>
+        <v>725838.8500000001</v>
       </c>
       <c r="D330">
         <v>0</v>
@@ -8218,9 +7626,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
-        <v>335</v>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Construção e Implantação de Equipamentos de Atenção Básica e Especialidades</t>
+        </is>
       </c>
       <c r="B331">
         <v>2022</v>
@@ -8238,9 +7648,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
-        <v>336</v>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Centro de Referência da Dança</t>
+        </is>
       </c>
       <c r="B332">
         <v>2022</v>
@@ -8258,15 +7670,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A333" t="s">
-        <v>337</v>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Bolsa Atleta</t>
+        </is>
       </c>
       <c r="B333">
         <v>2022</v>
       </c>
       <c r="C333">
-        <v>673035.55999999994</v>
+        <v>673035.5599999999</v>
       </c>
       <c r="D333">
         <v>0</v>
@@ -8278,9 +7692,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>338</v>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Centro de Memória do Circo</t>
+        </is>
       </c>
       <c r="B334">
         <v>2022</v>
@@ -8298,9 +7714,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
-        <v>339</v>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Patrulha Agroecológica Mecanizada</t>
+        </is>
       </c>
       <c r="B335">
         <v>2022</v>
@@ -8312,15 +7730,17 @@
         <v>109459.85</v>
       </c>
       <c r="E335">
-        <v>0.18961038961038959</v>
+        <v>0.1896103896103896</v>
       </c>
       <c r="F335">
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
-        <v>340</v>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Mercado Municipal</t>
+        </is>
       </c>
       <c r="B336">
         <v>2022</v>
@@ -8332,15 +7752,17 @@
         <v>109830.58</v>
       </c>
       <c r="E336">
-        <v>0.19246388110067239</v>
+        <v>0.1924638811006724</v>
       </c>
       <c r="F336">
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
-        <v>341</v>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Pesquisa de Satisfação do Cidadão em Relação aos Serviços, Políticas e Programas</t>
+        </is>
       </c>
       <c r="B337">
         <v>2022</v>
@@ -8358,9 +7780,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
-        <v>342</v>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Reforma e Acessibilidade em Passeios Públicos</t>
+        </is>
       </c>
       <c r="B338">
         <v>2022</v>
@@ -8378,9 +7802,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
-        <v>343</v>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Administração do Autódromo de Interlagos</t>
+        </is>
       </c>
       <c r="B339">
         <v>2022</v>
@@ -8398,9 +7824,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
-        <v>344</v>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Espaços Lúdicos e Educativos</t>
+        </is>
       </c>
       <c r="B340">
         <v>2022</v>
@@ -8418,9 +7846,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A341" t="s">
-        <v>345</v>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Território Hip Hop (Vocacional Hip Hop)</t>
+        </is>
       </c>
       <c r="B341">
         <v>2022</v>
@@ -8438,9 +7868,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
-        <v>346</v>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Gestão do Patrimônio Imobiliário Municipal</t>
+        </is>
       </c>
       <c r="B342">
         <v>2022</v>
@@ -8458,9 +7890,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
-        <v>347</v>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Fomento e Apoio ao Cooperativismo</t>
+        </is>
       </c>
       <c r="B343">
         <v>2022</v>
@@ -8478,9 +7912,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
-        <v>348</v>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Revitalização e Manutenção - Subprefeitura de Capela do Socorro</t>
+        </is>
       </c>
       <c r="B344">
         <v>2022</v>
@@ -8498,9 +7934,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
-        <v>349</v>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos da Assistência Social</t>
+        </is>
       </c>
       <c r="B345">
         <v>2022</v>
@@ -8518,9 +7956,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
-        <v>350</v>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Implantação de Pontos e Pontões de Cultura - Cultura Viva</t>
+        </is>
       </c>
       <c r="B346">
         <v>2022</v>
@@ -8538,15 +7978,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A347" t="s">
-        <v>351</v>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos de Saúde Animal</t>
+        </is>
       </c>
       <c r="B347">
         <v>2022</v>
       </c>
       <c r="C347">
-        <v>316555.84999999998</v>
+        <v>316555.85</v>
       </c>
       <c r="D347">
         <v>0</v>
@@ -8558,9 +8000,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
-        <v>352</v>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Acordos Judiciais ou Administrativos</t>
+        </is>
       </c>
       <c r="B348">
         <v>2022</v>
@@ -8578,9 +8022,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A349" t="s">
-        <v>353</v>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação do Serviço de Moto Verificação</t>
+        </is>
       </c>
       <c r="B349">
         <v>2022</v>
@@ -8598,18 +8044,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A350" t="s">
-        <v>354</v>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Projetos Sociais Diversos</t>
+        </is>
       </c>
       <c r="B350">
         <v>2022</v>
       </c>
       <c r="C350">
-        <v>276542.59999999998</v>
+        <v>276542.6</v>
       </c>
       <c r="D350">
-        <v>276542.59999999998</v>
+        <v>276542.6</v>
       </c>
       <c r="E350">
         <v>1</v>
@@ -8618,9 +8066,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A351" t="s">
-        <v>355</v>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Expansão e Aperfeiçoamento das Atividades do TCM</t>
+        </is>
       </c>
       <c r="B351">
         <v>2022</v>
@@ -8638,9 +8088,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A352" t="s">
-        <v>356</v>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Central de Interpretação de Libras, Intérpretes e Guias-Intérpretes</t>
+        </is>
       </c>
       <c r="B352">
         <v>2022</v>
@@ -8658,9 +8110,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A353" t="s">
-        <v>357</v>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Construção de Terminais de Ônibus</t>
+        </is>
       </c>
       <c r="B353">
         <v>2022</v>
@@ -8678,9 +8132,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
-        <v>358</v>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Escola do Parlamento</t>
+        </is>
       </c>
       <c r="B354">
         <v>2022</v>
@@ -8698,9 +8154,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A355" t="s">
-        <v>359</v>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Ações de Audiovisual</t>
+        </is>
       </c>
       <c r="B355">
         <v>2022</v>
@@ -8718,9 +8176,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A356" t="s">
-        <v>360</v>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Implantação da Casa de Cultura Cidade Ademar</t>
+        </is>
       </c>
       <c r="B356">
         <v>2022</v>
@@ -8738,9 +8198,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A357" t="s">
-        <v>361</v>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Expansão e Aperfeiçoamento das Atividades da CMSP</t>
+        </is>
       </c>
       <c r="B357">
         <v>2022</v>
@@ -8758,9 +8220,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A358" t="s">
-        <v>362</v>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação das Instalações para a Guarda Civil Metropolitana</t>
+        </is>
       </c>
       <c r="B358">
         <v>2022</v>
@@ -8778,9 +8242,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A359" t="s">
-        <v>363</v>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>PMLLLB - Festas Literárias</t>
+        </is>
       </c>
       <c r="B359">
         <v>2022</v>
@@ -8798,9 +8264,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A360" t="s">
-        <v>364</v>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Reforma da Escadaria na Viela Inominada, Localizada na Rua Rua José Ferreira Dantas, Nº 11, Jardim Boa Vista.</t>
+        </is>
       </c>
       <c r="B360">
         <v>2022</v>
@@ -8818,9 +8286,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A361" t="s">
-        <v>365</v>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Unidades Habitacionais</t>
+        </is>
       </c>
       <c r="B361">
         <v>2022</v>
@@ -8838,9 +8308,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A362" t="s">
-        <v>366</v>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Unidade de Vigilância em Saúde</t>
+        </is>
       </c>
       <c r="B362">
         <v>2022</v>
@@ -8858,9 +8330,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A363" t="s">
-        <v>367</v>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Construção de Escolas Municipais de Ensino Fundamental (EMEF)</t>
+        </is>
       </c>
       <c r="B363">
         <v>2022</v>
@@ -8878,9 +8352,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A364" t="s">
-        <v>368</v>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Execução de Projetos Visando o Combate das Desigualdades Raciais na Saúde</t>
+        </is>
       </c>
       <c r="B364">
         <v>2022</v>
@@ -8898,9 +8374,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A365" t="s">
-        <v>369</v>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação no Serviço de Guinchamento</t>
+        </is>
       </c>
       <c r="B365">
         <v>2022</v>
@@ -8918,18 +8396,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A366" t="s">
-        <v>370</v>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Reforma da Quadra da Praça Gilberto Reis Possani, Parque São Rafael</t>
+        </is>
       </c>
       <c r="B366">
         <v>2022</v>
       </c>
       <c r="C366">
-        <v>133159.64000000001</v>
+        <v>133159.64</v>
       </c>
       <c r="D366">
-        <v>133159.64000000001</v>
+        <v>133159.64</v>
       </c>
       <c r="E366">
         <v>1</v>
@@ -8938,9 +8418,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A367" t="s">
-        <v>371</v>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Ações do Programa Agentes de Governo Aberto</t>
+        </is>
       </c>
       <c r="B367">
         <v>2022</v>
@@ -8958,9 +8440,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A368" t="s">
-        <v>372</v>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Equipamentos do Patrimônio Histórico</t>
+        </is>
       </c>
       <c r="B368">
         <v>2022</v>
@@ -8972,15 +8456,17 @@
         <v>109472.2</v>
       </c>
       <c r="E368">
-        <v>0.98010938112444135</v>
+        <v>0.9801093811244413</v>
       </c>
       <c r="F368">
         <v>7</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A369" t="s">
-        <v>373</v>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Promoção da Transparência, do Acesso à Informação e do Controle Social</t>
+        </is>
       </c>
       <c r="B369">
         <v>2022</v>
@@ -8998,18 +8484,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A370" t="s">
-        <v>374</v>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Incentivo à Economia Popular e Solidária</t>
+        </is>
       </c>
       <c r="B370">
         <v>2022</v>
       </c>
       <c r="C370">
-        <v>99983.4</v>
+        <v>99983.39999999999</v>
       </c>
       <c r="D370">
-        <v>99983.4</v>
+        <v>99983.39999999999</v>
       </c>
       <c r="E370">
         <v>1</v>
@@ -9018,9 +8506,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A371" t="s">
-        <v>375</v>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação das Praças Digitais</t>
+        </is>
       </c>
       <c r="B371">
         <v>2022</v>
@@ -9029,18 +8519,20 @@
         <v>98814.97</v>
       </c>
       <c r="D371">
-        <v>66883.290000000008</v>
+        <v>66883.29000000001</v>
       </c>
       <c r="E371">
-        <v>0.67685382083301759</v>
+        <v>0.6768538208330176</v>
       </c>
       <c r="F371">
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A372" t="s">
-        <v>376</v>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Edificação do Tribunal de Contas do Município</t>
+        </is>
       </c>
       <c r="B372">
         <v>2022</v>
@@ -9058,15 +8550,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A373" t="s">
-        <v>377</v>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Restituição de Receitas Descontinuadas</t>
+        </is>
       </c>
       <c r="B373">
         <v>2022</v>
       </c>
       <c r="C373">
-        <v>92905.700000000012</v>
+        <v>92905.70000000001</v>
       </c>
       <c r="D373">
         <v>0</v>
@@ -9078,18 +8572,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A374" t="s">
-        <v>378</v>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Conservação e Valorização de Acervos da Biblioteca Mário de Andrade</t>
+        </is>
       </c>
       <c r="B374">
         <v>2022</v>
       </c>
       <c r="C374">
-        <v>76969.919999999998</v>
+        <v>76969.92</v>
       </c>
       <c r="D374">
-        <v>76969.919999999998</v>
+        <v>76969.92</v>
       </c>
       <c r="E374">
         <v>1</v>
@@ -9098,9 +8594,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A375" t="s">
-        <v>379</v>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Manutenção, Programas e Suporte da Coordenadoria de Defesa do Consumidor</t>
+        </is>
       </c>
       <c r="B375">
         <v>2022</v>
@@ -9118,9 +8616,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A376" t="s">
-        <v>380</v>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Políticas, Programas e Ações para Povos Indígenas</t>
+        </is>
       </c>
       <c r="B376">
         <v>2022</v>
@@ -9138,9 +8638,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A377" t="s">
-        <v>381</v>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Implementação do Selo Municipal de Direitos Humanos e Diversidade</t>
+        </is>
       </c>
       <c r="B377">
         <v>2022</v>
@@ -9158,9 +8660,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A378" t="s">
-        <v>382</v>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Programa de Promoção da Imagem de São Paulo no Exterior</t>
+        </is>
       </c>
       <c r="B378">
         <v>2022</v>
@@ -9178,9 +8682,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A379" t="s">
-        <v>383</v>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Programa de Gestão Cultural Comunitária de Espaços</t>
+        </is>
       </c>
       <c r="B379">
         <v>2022</v>
@@ -9198,9 +8704,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A380" t="s">
-        <v>384</v>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Outras Dívidas</t>
+        </is>
       </c>
       <c r="B380">
         <v>2022</v>
@@ -9218,18 +8726,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A381" t="s">
-        <v>385</v>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Benefícios Eventuais</t>
+        </is>
       </c>
       <c r="B381">
         <v>2022</v>
       </c>
       <c r="C381">
-        <v>38725.019999999997</v>
+        <v>38725.02</v>
       </c>
       <c r="D381">
-        <v>38725.019999999997</v>
+        <v>38725.02</v>
       </c>
       <c r="E381">
         <v>1</v>
@@ -9238,29 +8748,33 @@
         <v>3</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A382" t="s">
-        <v>386</v>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Supervisão Geral das Juntas do Serviço Militar</t>
+        </is>
       </c>
       <c r="B382">
         <v>2022</v>
       </c>
       <c r="C382">
-        <v>36542.400000000001</v>
+        <v>36542.4</v>
       </c>
       <c r="D382">
         <v>32462.82</v>
       </c>
       <c r="E382">
-        <v>0.88836037041902005</v>
+        <v>0.8883603704190201</v>
       </c>
       <c r="F382">
         <v>32</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A383" t="s">
-        <v>387</v>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Políticas, Programas e Ações para Pessoas Desaparecidas</t>
+        </is>
       </c>
       <c r="B383">
         <v>2022</v>
@@ -9278,9 +8792,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A384" t="s">
-        <v>388</v>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Conservação e Valorização de Acervos do Departamento dos Museus Municipais</t>
+        </is>
       </c>
       <c r="B384">
         <v>2022</v>
@@ -9298,18 +8814,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A385" t="s">
-        <v>389</v>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Construção e Implantação de Unidades de Conservação</t>
+        </is>
       </c>
       <c r="B385">
         <v>2022</v>
       </c>
       <c r="C385">
-        <v>23245.360000000001</v>
+        <v>23245.36</v>
       </c>
       <c r="D385">
-        <v>23245.360000000001</v>
+        <v>23245.36</v>
       </c>
       <c r="E385">
         <v>1</v>
@@ -9318,9 +8836,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A386" t="s">
-        <v>390</v>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Políticas, Programas e Ações para Promoção da Igualdade Racial</t>
+        </is>
       </c>
       <c r="B386">
         <v>2022</v>
@@ -9338,9 +8858,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A387" t="s">
-        <v>391</v>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Ações e Atividades Culturais do Arquivo Histórico Municipal</t>
+        </is>
       </c>
       <c r="B387">
         <v>2022</v>
@@ -9358,9 +8880,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A388" t="s">
-        <v>392</v>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Políticas, Programas e Ações para Pessoa Idosa</t>
+        </is>
       </c>
       <c r="B388">
         <v>2022</v>
@@ -9378,9 +8902,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A389" t="s">
-        <v>393</v>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Implantação de Transporte Público Hidroviário</t>
+        </is>
       </c>
       <c r="B389">
         <v>2022</v>
@@ -9398,9 +8924,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A390" t="s">
-        <v>394</v>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação do Herbário Municipal</t>
+        </is>
       </c>
       <c r="B390">
         <v>2022</v>
@@ -9418,9 +8946,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A391" t="s">
-        <v>395</v>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Comunicação e Orientação na Valorização e Cuidado na Primeira Infância</t>
+        </is>
       </c>
       <c r="B391">
         <v>2022</v>
@@ -9438,9 +8968,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A392" t="s">
-        <v>396</v>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Políticas, Programas e Ações para a Promoção do Direito à Memória e à Verdade</t>
+        </is>
       </c>
       <c r="B392">
         <v>2022</v>
@@ -9458,9 +8990,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A393" t="s">
-        <v>397</v>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da UniCEU</t>
+        </is>
       </c>
       <c r="B393">
         <v>2022</v>
@@ -9478,9 +9012,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A394" t="s">
-        <v>398</v>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Ampliação, Reforma e Requalificação de Edificação da Câmara Municipal de São Paulo</t>
+        </is>
       </c>
       <c r="B394">
         <v>2022</v>
@@ -9495,9 +9031,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A395" t="s">
-        <v>399</v>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Apoio e Suporte Técnico para o Desenvolvimento de Ações Pertinentes à Fiscalização e Escrituração de Certificados de Potencial Adicional de Construção - CEPACs</t>
+        </is>
       </c>
       <c r="B395">
         <v>2022</v>
@@ -9512,9 +9050,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A396" t="s">
-        <v>400</v>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Apoio às Ações Municipais de Turismo</t>
+        </is>
       </c>
       <c r="B396">
         <v>2022</v>
@@ -9529,9 +9069,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A397" t="s">
-        <v>401</v>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Aquisição e Construção de Prédios Administrativos</t>
+        </is>
       </c>
       <c r="B397">
         <v>2022</v>
@@ -9546,9 +9088,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A398" t="s">
-        <v>402</v>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Ações Socioculturais em Espaços Cemiteriais</t>
+        </is>
       </c>
       <c r="B398">
         <v>2022</v>
@@ -9563,9 +9107,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A399" t="s">
-        <v>403</v>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Ações de Pronto Atendimento Socioassistencial</t>
+        </is>
       </c>
       <c r="B399">
         <v>2022</v>
@@ -9580,9 +9126,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A400" t="s">
-        <v>404</v>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Ações de Vigilância Socioassistencial</t>
+        </is>
       </c>
       <c r="B400">
         <v>2022</v>
@@ -9597,9 +9145,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A401" t="s">
-        <v>405</v>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Comercialização de Artigos do Serviço Funerário</t>
+        </is>
       </c>
       <c r="B401">
         <v>2022</v>
@@ -9614,9 +9164,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A402" t="s">
-        <v>406</v>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Educação Permanente dos Trabalhadores do SUAS</t>
+        </is>
       </c>
       <c r="B402">
         <v>2022</v>
@@ -9631,9 +9183,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A403" t="s">
-        <v>407</v>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Cemitério</t>
+        </is>
       </c>
       <c r="B403">
         <v>2022</v>
@@ -9648,9 +9202,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A404" t="s">
-        <v>408</v>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Crematório</t>
+        </is>
       </c>
       <c r="B404">
         <v>2022</v>
@@ -9665,9 +9221,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A405" t="s">
-        <v>409</v>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação de Velório</t>
+        </is>
       </c>
       <c r="B405">
         <v>2022</v>
@@ -9682,9 +9240,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A406" t="s">
-        <v>410</v>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Transportes Fúnebres</t>
+        </is>
       </c>
       <c r="B406">
         <v>2022</v>
@@ -9702,10 +9262,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{f398df9c-fd0c-4829-a003-c770a1c4a063}" enabled="0" method="" siteId="{f398df9c-fd0c-4829-a003-c770a1c4a063}" removed="1"/>
-</clbl:labelList>
 </file>
--- a/R Markdown/resultados/regionalizacao_acoes_2022.xlsx
+++ b/R Markdown/resultados/regionalizacao_acoes_2022.xlsx
@@ -418,13 +418,13 @@
         <v>2022</v>
       </c>
       <c r="C3">
-        <v>6734920362.99</v>
+        <v>6739633637.42</v>
       </c>
       <c r="D3">
-        <v>1130523048.48</v>
+        <v>1130527143.8</v>
       </c>
       <c r="E3">
-        <v>0.1678598984915241</v>
+        <v>0.1677431155193737</v>
       </c>
       <c r="F3">
         <v>32</v>
@@ -433,14 +433,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compensações Tarifárias do Sistema de Ônibus</t>
+          <t>Aporte do IRRF para cobertura do deficit atuarial do RPPS</t>
         </is>
       </c>
       <c r="B4">
         <v>2022</v>
       </c>
       <c r="C4">
-        <v>5051601002.26</v>
+        <v>5146428410</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -455,102 +455,102 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Rede Parceira - Centro de Educação Infantil (CEI)</t>
+          <t>Compensações Tarifárias do Sistema de Ônibus</t>
         </is>
       </c>
       <c r="B5">
         <v>2022</v>
       </c>
       <c r="C5">
-        <v>4552083949.23</v>
+        <v>5051601002.26</v>
       </c>
       <c r="D5">
-        <v>4552083949.23</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Manutenção e Operação em Atenção Hospitalar e de Urgência e Emergência</t>
+          <t>Manutenção e Operação da Rede Parceira - Centro de Educação Infantil (CEI)</t>
         </is>
       </c>
       <c r="B6">
         <v>2022</v>
       </c>
       <c r="C6">
-        <v>4211981361.95</v>
+        <v>4553913338.66</v>
       </c>
       <c r="D6">
-        <v>105413462.29</v>
+        <v>4553913338.66</v>
       </c>
       <c r="E6">
-        <v>0.02502704861001504</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Manutenção e Operação em Atenção Básica, Especialidades e de Serviços Auxiliares de Diagnóstico e Terapia</t>
+          <t>Manutenção e Operação em Atenção Hospitalar e de Urgência e Emergência</t>
         </is>
       </c>
       <c r="B7">
         <v>2022</v>
       </c>
       <c r="C7">
-        <v>3417002966.68</v>
+        <v>4212056992.75</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>105413462.29</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>0.02502659922965023</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Obrigações e Contribuições Patronais RPPS Educação</t>
+          <t>Manutenção e Operação em Atenção Básica, Especialidades e de Serviços Auxiliares de Diagnóstico e Terapia</t>
         </is>
       </c>
       <c r="B8">
         <v>2022</v>
       </c>
       <c r="C8">
-        <v>2669715913.16</v>
+        <v>3418669810.98</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>86250</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2.522911096093117E-05</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aporte do IRRF para cobertura do deficit atuarial do RPPS</t>
+          <t>Obrigações e Contribuições Patronais RPPS Educação</t>
         </is>
       </c>
       <c r="B9">
         <v>2022</v>
       </c>
       <c r="C9">
-        <v>2573214205</v>
+        <v>2669715913.16</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -616,16 +616,16 @@
         <v>2022</v>
       </c>
       <c r="C12">
-        <v>1351707482.9</v>
+        <v>1357003875.94</v>
       </c>
       <c r="D12">
-        <v>1133468535.73</v>
+        <v>1138746085.54</v>
       </c>
       <c r="E12">
-        <v>0.8385457283244577</v>
+        <v>0.8391619992619311</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -704,7 +704,7 @@
         <v>2022</v>
       </c>
       <c r="C16">
-        <v>734754911.72</v>
+        <v>868968590.3</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -726,7 +726,7 @@
         <v>2022</v>
       </c>
       <c r="C17">
-        <v>728989572.22</v>
+        <v>729386320.15</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -770,13 +770,13 @@
         <v>2022</v>
       </c>
       <c r="C19">
-        <v>615490386.89</v>
+        <v>623844420.89</v>
       </c>
       <c r="D19">
-        <v>614981066.28</v>
+        <v>623335100.28</v>
       </c>
       <c r="E19">
-        <v>0.9991724962390176</v>
+        <v>0.9991835775187772</v>
       </c>
       <c r="F19">
         <v>32</v>
@@ -807,111 +807,111 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Condenações Judiciais - Outras Espécies</t>
+          <t>Execução do Programa de Mananciais</t>
         </is>
       </c>
       <c r="B21">
         <v>2022</v>
       </c>
       <c r="C21">
-        <v>562455807</v>
+        <v>576759981.1</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>96237769.84999999</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>0.1668593054366476</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Execução do Programa de Mananciais</t>
+          <t>Condenações Judiciais - Outras Espécies</t>
         </is>
       </c>
       <c r="B22">
         <v>2022</v>
       </c>
       <c r="C22">
-        <v>561202228.1</v>
+        <v>562455807</v>
       </c>
       <c r="D22">
-        <v>96237769.84999999</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>0.1714850102712912</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Manutenção e Operação em Atenção Básica, Especialidades e Vigilância da Assistência Farmacêutica</t>
+          <t>Construção de Unidades Habitacionais</t>
         </is>
       </c>
       <c r="B23">
         <v>2022</v>
       </c>
       <c r="C23">
-        <v>535612154.33</v>
+        <v>544790540.67</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>491389542.46</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>0.9019788446687679</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Sistemas de Informação e Comunicação</t>
+          <t>Manutenção e Operação em Atenção Básica, Especialidades e Vigilância da Assistência Farmacêutica</t>
         </is>
       </c>
       <c r="B24">
         <v>2022</v>
       </c>
       <c r="C24">
-        <v>527217208.29</v>
+        <v>535738311.36</v>
       </c>
       <c r="D24">
-        <v>4694677.4</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>0.008904636127540161</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Construção de Unidades Habitacionais</t>
+          <t>Manutenção e Operação de Sistemas de Informação e Comunicação</t>
         </is>
       </c>
       <c r="B25">
         <v>2022</v>
       </c>
       <c r="C25">
-        <v>506662993.08</v>
+        <v>530124215.82</v>
       </c>
       <c r="D25">
-        <v>486448668.21</v>
+        <v>4694677.4</v>
       </c>
       <c r="E25">
-        <v>0.9601030169045557</v>
+        <v>0.008855806356135306</v>
       </c>
       <c r="F25">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
@@ -968,13 +968,13 @@
         <v>2022</v>
       </c>
       <c r="C28">
-        <v>478648145.57</v>
+        <v>485681491.6</v>
       </c>
       <c r="D28">
-        <v>10414872.98</v>
+        <v>10418377.46</v>
       </c>
       <c r="E28">
-        <v>0.02175893310439427</v>
+        <v>0.0214510489697236</v>
       </c>
       <c r="F28">
         <v>32</v>
@@ -1012,13 +1012,13 @@
         <v>2022</v>
       </c>
       <c r="C30">
-        <v>414331183.63</v>
+        <v>414333609.65</v>
       </c>
       <c r="D30">
-        <v>364247456.69</v>
+        <v>364249882.71</v>
       </c>
       <c r="E30">
-        <v>0.8791215121651933</v>
+        <v>0.8791222199369556</v>
       </c>
       <c r="F30">
         <v>24</v>
@@ -1078,10 +1078,10 @@
         <v>2022</v>
       </c>
       <c r="C33">
-        <v>315523541.67</v>
+        <v>320002939.17</v>
       </c>
       <c r="D33">
-        <v>315523541.67</v>
+        <v>320002939.17</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -1100,10 +1100,10 @@
         <v>2022</v>
       </c>
       <c r="C34">
-        <v>296180988.6</v>
+        <v>296225530.98</v>
       </c>
       <c r="D34">
-        <v>296180988.6</v>
+        <v>296225530.98</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -1166,7 +1166,7 @@
         <v>2022</v>
       </c>
       <c r="C37">
-        <v>289112565.49</v>
+        <v>289331875.49</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1210,10 +1210,10 @@
         <v>2022</v>
       </c>
       <c r="C39">
-        <v>266128601.73</v>
+        <v>267551161.94</v>
       </c>
       <c r="D39">
-        <v>266128601.73</v>
+        <v>267551161.94</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -1232,7 +1232,7 @@
         <v>2022</v>
       </c>
       <c r="C40">
-        <v>264746430.59</v>
+        <v>264775588.37</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1247,190 +1247,190 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Educação Infantil</t>
+          <t>Fornecimento de Uniformes e Material Escolar-Ensino Fundamental</t>
         </is>
       </c>
       <c r="B41">
         <v>2022</v>
       </c>
       <c r="C41">
-        <v>236561428.4</v>
+        <v>258779271.61</v>
       </c>
       <c r="D41">
-        <v>236561428.4</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Áreas Verdes e Vegetação Arbórea</t>
+          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Educação Infantil</t>
         </is>
       </c>
       <c r="B42">
         <v>2022</v>
       </c>
       <c r="C42">
-        <v>235088324.22</v>
+        <v>236665367.4</v>
       </c>
       <c r="D42">
-        <v>235088324.22</v>
+        <v>236665367.4</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Ensino Fundamental</t>
+          <t>Manutenção e Operação de Áreas Verdes e Vegetação Arbórea</t>
         </is>
       </c>
       <c r="B43">
         <v>2022</v>
       </c>
       <c r="C43">
-        <v>234121718.8</v>
+        <v>235088324.22</v>
       </c>
       <c r="D43">
-        <v>234121718.8</v>
+        <v>235088324.22</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Serviços de Limpeza Urbana - Varrição e Lavagem de Áreas Públicas</t>
+          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Ensino Fundamental</t>
         </is>
       </c>
       <c r="B44">
         <v>2022</v>
       </c>
       <c r="C44">
-        <v>233929969.57</v>
+        <v>234121718.8</v>
       </c>
       <c r="D44">
-        <v>44981360.93</v>
+        <v>234121718.8</v>
       </c>
       <c r="E44">
-        <v>0.192285584496432</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fornecimento de Uniformes e Material Escolar-Ensino Fundamental</t>
+          <t>Serviços de Limpeza Urbana - Varrição e Lavagem de Áreas Públicas</t>
         </is>
       </c>
       <c r="B45">
         <v>2022</v>
       </c>
       <c r="C45">
-        <v>232688344.25</v>
+        <v>233929969.57</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>44981360.93</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>0.192285584496432</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Recuperação e Reforço de Obras de Arte Especiais - OAE</t>
+          <t>Ações e Materiais de Apoio Didático-Pedagógico Educacional</t>
         </is>
       </c>
       <c r="B46">
         <v>2022</v>
       </c>
       <c r="C46">
-        <v>227860226.29</v>
+        <v>228279521.67</v>
       </c>
       <c r="D46">
-        <v>214082177.29</v>
+        <v>64735698.2</v>
       </c>
       <c r="E46">
-        <v>0.9395328916137188</v>
+        <v>0.2835808386421174</v>
       </c>
       <c r="F46">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial a Crianças, Adolescentes e Jovens em Risco Social</t>
+          <t>Recuperação e Reforço de Obras de Arte Especiais - OAE</t>
         </is>
       </c>
       <c r="B47">
         <v>2022</v>
       </c>
       <c r="C47">
-        <v>226598778.33</v>
+        <v>228107086.45</v>
       </c>
       <c r="D47">
-        <v>226598778.33</v>
+        <v>214329037.45</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0.9395983298264603</v>
       </c>
       <c r="F47">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Administração de Material Médico Hospitalar em Atenção Hospitalar, de Urgência e Emergência</t>
+          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial a Crianças, Adolescentes e Jovens em Risco Social</t>
         </is>
       </c>
       <c r="B48">
         <v>2022</v>
       </c>
       <c r="C48">
-        <v>223793133.44</v>
+        <v>226598778.33</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>226598778.33</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Transporte Escolar - Educação Infantil</t>
+          <t>Administração de Material Médico Hospitalar em Atenção Hospitalar, de Urgência e Emergência</t>
         </is>
       </c>
       <c r="B49">
         <v>2022</v>
       </c>
       <c r="C49">
-        <v>220261500.19</v>
+        <v>223939574.56</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -1445,14 +1445,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Serviço da Dívida Pública Interna</t>
+          <t>Transporte Escolar - Educação Infantil</t>
         </is>
       </c>
       <c r="B50">
         <v>2022</v>
       </c>
       <c r="C50">
-        <v>217803204.61</v>
+        <v>220737011.44</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -1467,14 +1467,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Publicidade Institucional</t>
+          <t>Serviço da Dívida Pública Interna</t>
         </is>
       </c>
       <c r="B51">
         <v>2022</v>
       </c>
       <c r="C51">
-        <v>210361330.31</v>
+        <v>217803204.61</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -1489,64 +1489,64 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Terminais de Ônibus</t>
+          <t>Publicidade Institucional</t>
         </is>
       </c>
       <c r="B52">
         <v>2022</v>
       </c>
       <c r="C52">
-        <v>206442018.32</v>
+        <v>210361330.31</v>
       </c>
       <c r="D52">
-        <v>74649268</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>0.36159919675019</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Escolas Municipais de Educação Infantil (EMEI)</t>
+          <t>Manutenção e Operação de Terminais de Ônibus</t>
         </is>
       </c>
       <c r="B53">
         <v>2022</v>
       </c>
       <c r="C53">
-        <v>205086769.42</v>
+        <v>206442018.32</v>
       </c>
       <c r="D53">
-        <v>205086769.42</v>
+        <v>74649268</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>0.36159919675019</v>
       </c>
       <c r="F53">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Parques Urbanos e Lineares</t>
+          <t>Manutenção e Operação de Escolas Municipais de Educação Infantil (EMEI)</t>
         </is>
       </c>
       <c r="B54">
         <v>2022</v>
       </c>
       <c r="C54">
-        <v>201702938.98</v>
+        <v>206265629.52</v>
       </c>
       <c r="D54">
-        <v>196045759.08</v>
+        <v>206265629.52</v>
       </c>
       <c r="E54">
-        <v>0.9719529128895791</v>
+        <v>1</v>
       </c>
       <c r="F54">
         <v>32</v>
@@ -1555,20 +1555,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ações e Materiais de Apoio Didático-Pedagógico Educacional</t>
+          <t>Manutenção e Operação de Parques Urbanos e Lineares</t>
         </is>
       </c>
       <c r="B55">
         <v>2022</v>
       </c>
       <c r="C55">
-        <v>190864529.6</v>
+        <v>201740601.24</v>
       </c>
       <c r="D55">
-        <v>64735698.2</v>
+        <v>196083421.34</v>
       </c>
       <c r="E55">
-        <v>0.3391709205249837</v>
+        <v>0.9719581489039484</v>
       </c>
       <c r="F55">
         <v>32</v>
@@ -1584,7 +1584,7 @@
         <v>2022</v>
       </c>
       <c r="C56">
-        <v>183225691.6</v>
+        <v>185462609.16</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>2022</v>
       </c>
       <c r="C58">
-        <v>159409713.82</v>
+        <v>159982587.27</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -1673,10 +1673,10 @@
         <v>2022</v>
       </c>
       <c r="C60">
-        <v>146166915.49</v>
+        <v>146188754.11</v>
       </c>
       <c r="D60">
-        <v>146166915.49</v>
+        <v>146188754.11</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -1688,111 +1688,111 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Transporte de Pessoas com Deficiência ou Mobilidade Reduzida - ATENDE</t>
+          <t>Manutenção e Operação do Controle e Fiscalização de Tráfego</t>
         </is>
       </c>
       <c r="B61">
         <v>2022</v>
       </c>
       <c r="C61">
-        <v>141682050.88</v>
+        <v>142974106.09</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>142974106.09</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Centros de Educação Infantil (CEI)</t>
+          <t>Transporte de Pessoas com Deficiência ou Mobilidade Reduzida - ATENDE</t>
         </is>
       </c>
       <c r="B62">
         <v>2022</v>
       </c>
       <c r="C62">
-        <v>140910802.7</v>
+        <v>141682050.88</v>
       </c>
       <c r="D62">
-        <v>140910802.7</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Controle e Fiscalização de Tráfego</t>
+          <t>Manutenção e Operação de Centros de Educação Infantil (CEI)</t>
         </is>
       </c>
       <c r="B63">
         <v>2022</v>
       </c>
       <c r="C63">
-        <v>139656025.79</v>
+        <v>141415242.01</v>
       </c>
       <c r="D63">
-        <v>139656025.79</v>
+        <v>141415242.01</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Condenações Judiciais - Créditos de Pequeno Valor</t>
+          <t>Obras e Serviços nas Áreas de Riscos Geológicos</t>
         </is>
       </c>
       <c r="B64">
         <v>2022</v>
       </c>
       <c r="C64">
-        <v>136579901.32</v>
+        <v>137399734.26</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>135677495.85</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>0.987465489512949</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Obras e Serviços nas Áreas de Riscos Geológicos</t>
+          <t>Condenações Judiciais - Créditos de Pequeno Valor</t>
         </is>
       </c>
       <c r="B65">
         <v>2022</v>
       </c>
       <c r="C65">
-        <v>136343681.19</v>
+        <v>136579901.32</v>
       </c>
       <c r="D65">
-        <v>134621442.78</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>0.9873684031781422</v>
+        <v>0</v>
       </c>
       <c r="F65">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1974,171 +1974,171 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Vigilância em Saúde</t>
+          <t>Ampliação, Reforma e Requalificação de Escola Municipal de Ensino Fundamental (EMEF)</t>
         </is>
       </c>
       <c r="B74">
         <v>2022</v>
       </c>
       <c r="C74">
-        <v>100867343.92</v>
+        <v>102055558.61</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>102055558.61</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Operação Tapa Buraco</t>
+          <t>Manutenção e Operação de Vigilância em Saúde</t>
         </is>
       </c>
       <c r="B75">
         <v>2022</v>
       </c>
       <c r="C75">
-        <v>99277957.44</v>
+        <v>101521681.74</v>
       </c>
       <c r="D75">
-        <v>99277957.44</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Central de Atendimento Telefônico - 156</t>
+          <t>Operação Tapa Buraco</t>
         </is>
       </c>
       <c r="B76">
         <v>2022</v>
       </c>
       <c r="C76">
-        <v>95402335.68000001</v>
+        <v>100251929.16</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>100251929.16</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Programação de Atividades Culturais</t>
+          <t>Manutenção e Operação da Central de Atendimento Telefônico - 156</t>
         </is>
       </c>
       <c r="B77">
         <v>2022</v>
       </c>
       <c r="C77">
-        <v>88341072.19</v>
+        <v>95402335.68000001</v>
       </c>
       <c r="D77">
-        <v>88241072.19</v>
+        <v>0</v>
       </c>
       <c r="E77">
-        <v>0.9988680237004037</v>
+        <v>0</v>
       </c>
       <c r="F77">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Manutenção de Vias e Áreas Públicas</t>
+          <t>Ampliação, Reforma e Requalificação de Centros Educacionais Unificados (CEU)</t>
         </is>
       </c>
       <c r="B78">
         <v>2022</v>
       </c>
       <c r="C78">
-        <v>87364388.56999999</v>
+        <v>93342978.55</v>
       </c>
       <c r="D78">
-        <v>87364388.56999999</v>
+        <v>93342978.55</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="F78">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Grupos Artísticos, Técnicos e Administrativos</t>
+          <t>Urbanização de Favelas</t>
         </is>
       </c>
       <c r="B79">
         <v>2022</v>
       </c>
       <c r="C79">
-        <v>87150331.64</v>
+        <v>88806824.48999999</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>52184096.23</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>0.5876135818354381</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Serviço de Atendimento Médico de Urgência (SAMU)</t>
+          <t>Programação de Atividades Culturais</t>
         </is>
       </c>
       <c r="B80">
         <v>2022</v>
       </c>
       <c r="C80">
-        <v>84814953.73</v>
+        <v>88421072.19</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>88321072.19</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>0.9988690478692102</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Remuneração dos Profissionais do Magistério - Ensino Fundamental</t>
+          <t>Manutenção de Vias e Áreas Públicas</t>
         </is>
       </c>
       <c r="B81">
         <v>2022</v>
       </c>
       <c r="C81">
-        <v>83729511.72</v>
+        <v>87371543.77</v>
       </c>
       <c r="D81">
-        <v>83729511.72</v>
+        <v>87371543.77</v>
       </c>
       <c r="E81">
         <v>1</v>
@@ -2150,14 +2150,14 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ações de Apoio à Educação Especial</t>
+          <t>Ações de Difusão Cultural do Theatro Municipal - Grupos Artísticos, Técnicos e Administrativos</t>
         </is>
       </c>
       <c r="B82">
         <v>2022</v>
       </c>
       <c r="C82">
-        <v>80872787.79000001</v>
+        <v>87150331.64</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2172,14 +2172,14 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Programa de Incentivo Fiscal Relacionado à Arena Corinthians</t>
+          <t>Manutenção e Operação de Serviço de Atendimento Médico de Urgência (SAMU)</t>
         </is>
       </c>
       <c r="B83">
         <v>2022</v>
       </c>
       <c r="C83">
-        <v>69966090</v>
+        <v>84815287.54000001</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2194,36 +2194,36 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Servidores Comissionados em Outras Entidades</t>
+          <t>Remuneração dos Profissionais do Magistério - Ensino Fundamental</t>
         </is>
       </c>
       <c r="B84">
         <v>2022</v>
       </c>
       <c r="C84">
-        <v>67812134.2</v>
+        <v>83729511.72</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>83729511.72</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Serviço de Moradia Transitória</t>
+          <t>Ações de Apoio à Educação Especial</t>
         </is>
       </c>
       <c r="B85">
         <v>2022</v>
       </c>
       <c r="C85">
-        <v>66677331.31</v>
+        <v>80981631.95</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2238,45 +2238,45 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Básica às Famílias</t>
+          <t>Ampliação, Reforma e Requalificação de Escolas Municipais de Educação Infantil (EMEI)</t>
         </is>
       </c>
       <c r="B86">
         <v>2022</v>
       </c>
       <c r="C86">
-        <v>65710474.84</v>
+        <v>70755978.81999999</v>
       </c>
       <c r="D86">
-        <v>65710474.84</v>
+        <v>70755978.81999999</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
       <c r="F86">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Urbanização de Favelas</t>
+          <t>Programa de Incentivo Fiscal Relacionado à Arena Corinthians</t>
         </is>
       </c>
       <c r="B87">
         <v>2022</v>
       </c>
       <c r="C87">
-        <v>63501968.29</v>
+        <v>69966090</v>
       </c>
       <c r="D87">
-        <v>48361398.46</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>0.7615732198905043</v>
+        <v>0</v>
       </c>
       <c r="F87">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2289,10 +2289,10 @@
         <v>2022</v>
       </c>
       <c r="C88">
-        <v>62672168.68</v>
+        <v>69337978.63</v>
       </c>
       <c r="D88">
-        <v>62672168.68</v>
+        <v>69337978.63</v>
       </c>
       <c r="E88">
         <v>1</v>
@@ -2304,42 +2304,42 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Incentivo à Prática de Esportes</t>
+          <t>Servidores Comissionados em Outras Entidades</t>
         </is>
       </c>
       <c r="B89">
         <v>2022</v>
       </c>
       <c r="C89">
-        <v>62167996.02</v>
+        <v>67812134.2</v>
       </c>
       <c r="D89">
-        <v>7939684.55</v>
+        <v>0</v>
       </c>
       <c r="E89">
-        <v>0.1277133743774808</v>
+        <v>0</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Realização de Eventos de Esporte, Lazer e Recreação</t>
+          <t>Serviço de Moradia Transitória</t>
         </is>
       </c>
       <c r="B90">
         <v>2022</v>
       </c>
       <c r="C90">
-        <v>61554493.96</v>
+        <v>66990081.31</v>
       </c>
       <c r="D90">
-        <v>6768805.74</v>
+        <v>29550</v>
       </c>
       <c r="E90">
-        <v>0.1099644445846404</v>
+        <v>0.0004411100781212053</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -2348,105 +2348,105 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Atenção Hospitalar da Assistência Farmacêutica</t>
+          <t>Manutenção e Operação de Equipamentos de Proteção Social Básica às Famílias</t>
         </is>
       </c>
       <c r="B91">
         <v>2022</v>
       </c>
       <c r="C91">
-        <v>58584852.45</v>
+        <v>65710474.84</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>65710474.84</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Remuneração dos Profissionais do Magistério - Centro de Educação Infantil (CEI)</t>
+          <t>Incentivo à Prática de Esportes</t>
         </is>
       </c>
       <c r="B92">
         <v>2022</v>
       </c>
       <c r="C92">
-        <v>57950537.47</v>
+        <v>62167996.02</v>
       </c>
       <c r="D92">
-        <v>57950537.47</v>
+        <v>7939684.55</v>
       </c>
       <c r="E92">
-        <v>1</v>
+        <v>0.1277133743774808</v>
       </c>
       <c r="F92">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Capacitação, Formação e Aperfeiçoamento dos Trabalhadores</t>
+          <t>Realização de Eventos de Esporte, Lazer e Recreação</t>
         </is>
       </c>
       <c r="B93">
         <v>2022</v>
       </c>
       <c r="C93">
-        <v>57662486.8</v>
+        <v>61554493.96</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>6768805.74</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>0.1099644445846404</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ações Integradas de Segurança Pública - Operação Delegada - Convênio SSP SO</t>
+          <t>Manutenção e Operação da Atenção Hospitalar da Assistência Farmacêutica</t>
         </is>
       </c>
       <c r="B94">
         <v>2022</v>
       </c>
       <c r="C94">
-        <v>57226279.57</v>
+        <v>58637101.9</v>
       </c>
       <c r="D94">
-        <v>57226279.57</v>
+        <v>0</v>
       </c>
       <c r="E94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Remuneração dos Profissionais do Magistério - Escola Municipal de Educação Infantil (EMEI)</t>
+          <t>Remuneração dos Profissionais do Magistério - Centro de Educação Infantil (CEI)</t>
         </is>
       </c>
       <c r="B95">
         <v>2022</v>
       </c>
       <c r="C95">
-        <v>56366375.58</v>
+        <v>57950537.47</v>
       </c>
       <c r="D95">
-        <v>56366375.58</v>
+        <v>57950537.47</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -2458,83 +2458,83 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Manutenção e Operação Semafórica</t>
+          <t>Capacitação, Formação e Aperfeiçoamento dos Trabalhadores</t>
         </is>
       </c>
       <c r="B96">
         <v>2022</v>
       </c>
       <c r="C96">
-        <v>54628234.07</v>
+        <v>57662486.8</v>
       </c>
       <c r="D96">
-        <v>54628234.07</v>
+        <v>0</v>
       </c>
       <c r="E96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à Pessoa com Deficiência</t>
+          <t>Ações Integradas de Segurança Pública - Operação Delegada - Convênio SSP SO</t>
         </is>
       </c>
       <c r="B97">
         <v>2022</v>
       </c>
       <c r="C97">
-        <v>53786390.39</v>
+        <v>57226279.57</v>
       </c>
       <c r="D97">
-        <v>53786390.39</v>
+        <v>57226279.57</v>
       </c>
       <c r="E97">
         <v>1</v>
       </c>
       <c r="F97">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População Idosa</t>
+          <t>Remuneração dos Profissionais do Magistério - Escola Municipal de Educação Infantil (EMEI)</t>
         </is>
       </c>
       <c r="B98">
         <v>2022</v>
       </c>
       <c r="C98">
-        <v>53533979.01</v>
+        <v>56366375.58</v>
       </c>
       <c r="D98">
-        <v>53533979.01</v>
+        <v>56366375.58</v>
       </c>
       <c r="E98">
         <v>1</v>
       </c>
       <c r="F98">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos da Assistência Social</t>
+          <t>Manutenção e Operação Semafórica</t>
         </is>
       </c>
       <c r="B99">
         <v>2022</v>
       </c>
       <c r="C99">
-        <v>45257699.56</v>
+        <v>54628234.07</v>
       </c>
       <c r="D99">
-        <v>45257699.56</v>
+        <v>54628234.07</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -2546,23 +2546,23 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Administração da Carteira Imobiliária</t>
+          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à Pessoa com Deficiência</t>
         </is>
       </c>
       <c r="B100">
         <v>2022</v>
       </c>
       <c r="C100">
-        <v>44647923.19</v>
+        <v>53786390.39</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>53786390.39</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101">
@@ -2575,10 +2575,10 @@
         <v>2022</v>
       </c>
       <c r="C101">
-        <v>44151997.36</v>
+        <v>53622726.74</v>
       </c>
       <c r="D101">
-        <v>44151997.36</v>
+        <v>53622726.74</v>
       </c>
       <c r="E101">
         <v>1</v>
@@ -2590,80 +2590,80 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ações Permanentes de Promoção dos Direitos da Criança e do Adolescente</t>
+          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População Idosa</t>
         </is>
       </c>
       <c r="B102">
         <v>2022</v>
       </c>
       <c r="C102">
-        <v>43802369.2</v>
+        <v>53533979.01</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>53533979.01</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Serviço da Dívida Pública Externa</t>
+          <t>Manutenção e Operação de Equipamentos da Assistência Social</t>
         </is>
       </c>
       <c r="B103">
         <v>2022</v>
       </c>
       <c r="C103">
-        <v>42307339.42</v>
+        <v>45257699.56</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>45257699.56</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Posto do Corpo de Bombeiros</t>
+          <t>Administração da Carteira Imobiliária</t>
         </is>
       </c>
       <c r="B104">
         <v>2022</v>
       </c>
       <c r="C104">
-        <v>41633271.02</v>
+        <v>44647923.19</v>
       </c>
       <c r="D104">
-        <v>39741770.21</v>
+        <v>0</v>
       </c>
       <c r="E104">
-        <v>0.9545675666682218</v>
+        <v>0</v>
       </c>
       <c r="F104">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Realização de Eventos Culturais</t>
+          <t>Ações Permanentes de Promoção dos Direitos da Criança e do Adolescente</t>
         </is>
       </c>
       <c r="B105">
         <v>2022</v>
       </c>
       <c r="C105">
-        <v>39628073.49</v>
+        <v>43802369.2</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -2678,20 +2678,20 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Guarda Civil Metropolitana</t>
+          <t>Manutenção e Operação de Posto do Corpo de Bombeiros</t>
         </is>
       </c>
       <c r="B106">
         <v>2022</v>
       </c>
       <c r="C106">
-        <v>39412764.43</v>
+        <v>42700893.14</v>
       </c>
       <c r="D106">
-        <v>24784998.07</v>
+        <v>39748304.79</v>
       </c>
       <c r="E106">
-        <v>0.6288571336836826</v>
+        <v>0.9308541781475252</v>
       </c>
       <c r="F106">
         <v>32</v>
@@ -2700,14 +2700,14 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Administração dos Conselhos Tutelares</t>
+          <t>Serviço da Dívida Pública Externa</t>
         </is>
       </c>
       <c r="B107">
         <v>2022</v>
       </c>
       <c r="C107">
-        <v>38209128.34</v>
+        <v>42307339.42</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -2722,262 +2722,262 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Educação em Direitos Humanos e Promoção do Direito à Cidade</t>
+          <t>Manutenção e Operação da Guarda Civil Metropolitana</t>
         </is>
       </c>
       <c r="B108">
         <v>2022</v>
       </c>
       <c r="C108">
-        <v>35187843.23</v>
+        <v>40057110.1</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>25273954.78</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>0.6309480318701274</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para a Pessoa Idosa</t>
+          <t>Realização de Eventos Culturais</t>
         </is>
       </c>
       <c r="B109">
         <v>2022</v>
       </c>
       <c r="C109">
-        <v>34352741.96</v>
+        <v>39628073.49</v>
       </c>
       <c r="D109">
-        <v>34352741.96</v>
+        <v>0</v>
       </c>
       <c r="E109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F109">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Centros Educacionais Unificados (CEU)</t>
+          <t>Administração dos Conselhos Tutelares</t>
         </is>
       </c>
       <c r="B110">
         <v>2022</v>
       </c>
       <c r="C110">
-        <v>34347863.44</v>
+        <v>38179464.01</v>
       </c>
       <c r="D110">
-        <v>34347863.44</v>
+        <v>335.67</v>
       </c>
       <c r="E110">
-        <v>1</v>
+        <v>8.791899223940939E-06</v>
       </c>
       <c r="F110">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Modernização Semafórica</t>
+          <t>Políticas, Programas e Ações para Educação em Direitos Humanos e Promoção do Direito à Cidade</t>
         </is>
       </c>
       <c r="B111">
         <v>2022</v>
       </c>
       <c r="C111">
-        <v>34223141.49</v>
+        <v>35187843.23</v>
       </c>
       <c r="D111">
-        <v>7199299.68</v>
+        <v>0</v>
       </c>
       <c r="E111">
-        <v>0.210363495768021</v>
+        <v>0</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Aposentadoria Complementar aos Servidores da São Paulo Transporte S/A</t>
+          <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para a Pessoa Idosa</t>
         </is>
       </c>
       <c r="B112">
         <v>2022</v>
       </c>
       <c r="C112">
-        <v>33838306.65</v>
+        <v>34352741.96</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>34352741.96</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Regularização Fundiária</t>
+          <t>Modernização Semafórica</t>
         </is>
       </c>
       <c r="B113">
         <v>2022</v>
       </c>
       <c r="C113">
-        <v>31419509.55</v>
+        <v>34223141.49</v>
       </c>
       <c r="D113">
-        <v>15476252.57</v>
+        <v>7199299.68</v>
       </c>
       <c r="E113">
-        <v>0.4925682415688758</v>
+        <v>0.210363495768021</v>
       </c>
       <c r="F113">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Intervenções em Próprios Municipais</t>
+          <t>Aposentadoria Complementar aos Servidores da São Paulo Transporte S/A</t>
         </is>
       </c>
       <c r="B114">
         <v>2022</v>
       </c>
       <c r="C114">
-        <v>31384941.76</v>
+        <v>33838306.65</v>
       </c>
       <c r="D114">
-        <v>16463809.8</v>
+        <v>0</v>
       </c>
       <c r="E114">
-        <v>0.5245767198135467</v>
+        <v>0</v>
       </c>
       <c r="F114">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Coleta, Transporte, Tratamento e Dest. Final Resíduos Sólidos Inertes</t>
+          <t>Ampliação, Reforma e Requalificação de Clube da Comunidade (CDC)</t>
         </is>
       </c>
       <c r="B115">
         <v>2022</v>
       </c>
       <c r="C115">
-        <v>30805228.5</v>
+        <v>32117822.91</v>
       </c>
       <c r="D115">
-        <v>5970537.350000001</v>
+        <v>26797603.56</v>
       </c>
       <c r="E115">
-        <v>0.1938157137837819</v>
+        <v>0.8343530517336674</v>
       </c>
       <c r="F115">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Policiamento de Trânsito</t>
+          <t>Regularização Fundiária</t>
         </is>
       </c>
       <c r="B116">
         <v>2022</v>
       </c>
       <c r="C116">
-        <v>30737267.6</v>
+        <v>31419509.55</v>
       </c>
       <c r="D116">
-        <v>30737267.6</v>
+        <v>15476252.57</v>
       </c>
       <c r="E116">
-        <v>1</v>
+        <v>0.4925682415688758</v>
       </c>
       <c r="F116">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Clube da Comunidade (CDC)</t>
+          <t>Intervenções em Próprios Municipais</t>
         </is>
       </c>
       <c r="B117">
         <v>2022</v>
       </c>
       <c r="C117">
-        <v>30668307.62</v>
+        <v>31384941.76</v>
       </c>
       <c r="D117">
-        <v>25353641.02</v>
+        <v>16463809.8</v>
       </c>
       <c r="E117">
-        <v>0.8267049272541501</v>
+        <v>0.5245767198135467</v>
       </c>
       <c r="F117">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Prédios Administrativos</t>
+          <t>Coleta, Transporte, Tratamento e Dest. Final Resíduos Sólidos Inertes</t>
         </is>
       </c>
       <c r="B118">
         <v>2022</v>
       </c>
       <c r="C118">
-        <v>29911972.74</v>
+        <v>30805228.5</v>
       </c>
       <c r="D118">
-        <v>29911972.74</v>
+        <v>5970537.350000001</v>
       </c>
       <c r="E118">
-        <v>1</v>
+        <v>0.1938157137837819</v>
       </c>
       <c r="F118">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Programa Municipal de Apoio a Projetos Culturais (PRO-MAC)</t>
+          <t>Manutenção e Operação do Policiamento de Trânsito</t>
         </is>
       </c>
       <c r="B119">
         <v>2022</v>
       </c>
       <c r="C119">
-        <v>29356018.68</v>
+        <v>30737267.6</v>
       </c>
       <c r="D119">
-        <v>28656</v>
+        <v>30737267.6</v>
       </c>
       <c r="E119">
-        <v>0.0009761541683281147</v>
+        <v>1</v>
       </c>
       <c r="F119">
         <v>7</v>
@@ -2986,58 +2986,58 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para a População em Situação de Rua</t>
+          <t>Ampliação, Reforma e Requalificação de Prédios Administrativos</t>
         </is>
       </c>
       <c r="B120">
         <v>2022</v>
       </c>
       <c r="C120">
-        <v>28727744.74</v>
+        <v>30707043.03</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>30707043.03</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ações de Fiscalização do Comércio Ilegal</t>
+          <t>Programa Municipal de Apoio a Projetos Culturais (PRO-MAC)</t>
         </is>
       </c>
       <c r="B121">
         <v>2022</v>
       </c>
       <c r="C121">
-        <v>27949308.69</v>
+        <v>29356018.68</v>
       </c>
       <c r="D121">
-        <v>27949308.69</v>
+        <v>28656</v>
       </c>
       <c r="E121">
-        <v>1</v>
+        <v>0.0009761541683281147</v>
       </c>
       <c r="F121">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Operação e Manutenção da Agência São Paulo de Desenvolvimento - ADESAMPA</t>
+          <t>Políticas, Programas e Ações para a População em Situação de Rua</t>
         </is>
       </c>
       <c r="B122">
         <v>2022</v>
       </c>
       <c r="C122">
-        <v>27800000</v>
+        <v>28757744.74</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -3052,17 +3052,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Políticas de Audiovisual</t>
+          <t>Ações de Fiscalização do Comércio Ilegal</t>
         </is>
       </c>
       <c r="B123">
         <v>2022</v>
       </c>
       <c r="C123">
-        <v>27461812.88</v>
+        <v>27949308.69</v>
       </c>
       <c r="D123">
-        <v>27461812.88</v>
+        <v>27949308.69</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -3074,168 +3074,168 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Eventos Educacionais, Culturais e Esportivos nos Centros Educacionais Unificados</t>
+          <t>Operação e Manutenção da Agência São Paulo de Desenvolvimento - ADESAMPA</t>
         </is>
       </c>
       <c r="B124">
         <v>2022</v>
       </c>
       <c r="C124">
-        <v>26571850.56</v>
+        <v>27800000</v>
       </c>
       <c r="D124">
-        <v>26571850.56</v>
+        <v>0</v>
       </c>
       <c r="E124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Aporte para Garantia de PPP's e Projetos de Infraestrutura</t>
+          <t>Políticas de Audiovisual</t>
         </is>
       </c>
       <c r="B125">
         <v>2022</v>
       </c>
       <c r="C125">
-        <v>26223126</v>
+        <v>27461812.88</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>27461812.88</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Construção e Implantação de Parques Urbanos e Lineares</t>
+          <t>Eventos Educacionais, Culturais e Esportivos nos Centros Educacionais Unificados</t>
         </is>
       </c>
       <c r="B126">
         <v>2022</v>
       </c>
       <c r="C126">
-        <v>25837166.1</v>
+        <v>26571850.56</v>
       </c>
       <c r="D126">
-        <v>25837166.1</v>
+        <v>26571850.56</v>
       </c>
       <c r="E126">
         <v>1</v>
       </c>
       <c r="F126">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - Educação Infantil</t>
+          <t>Aporte para Garantia de PPP's e Projetos de Infraestrutura</t>
         </is>
       </c>
       <c r="B127">
         <v>2022</v>
       </c>
       <c r="C127">
-        <v>25670688.45</v>
+        <v>26223126</v>
       </c>
       <c r="D127">
-        <v>25670688.45</v>
+        <v>0</v>
       </c>
       <c r="E127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F127">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Construção de Ciclovias, Ciclofaixas e Ciclorrotas</t>
+          <t>Construção e Implantação de Parques Urbanos e Lineares</t>
         </is>
       </c>
       <c r="B128">
         <v>2022</v>
       </c>
       <c r="C128">
-        <v>23813318.79</v>
+        <v>25837166.1</v>
       </c>
       <c r="D128">
-        <v>23813318.79</v>
+        <v>25837166.1</v>
       </c>
       <c r="E128">
         <v>1</v>
       </c>
       <c r="F128">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Contraprestação de Parceria Público-Privada (PPP) - Terminais Urbanos</t>
+          <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - Educação Infantil</t>
         </is>
       </c>
       <c r="B129">
         <v>2022</v>
       </c>
       <c r="C129">
-        <v>23540000</v>
+        <v>25676806.61</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>25676806.61</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Implantação de Corredores de Ônibus Novos</t>
+          <t>Construção de Ciclovias, Ciclofaixas e Ciclorrotas</t>
         </is>
       </c>
       <c r="B130">
         <v>2022</v>
       </c>
       <c r="C130">
-        <v>23187857.36</v>
+        <v>23813318.79</v>
       </c>
       <c r="D130">
-        <v>18912415.66</v>
+        <v>23813318.79</v>
       </c>
       <c r="E130">
-        <v>0.8156172157857366</v>
+        <v>1</v>
       </c>
       <c r="F130">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Manutenção e Operação em Serviços de Saúde Animal</t>
+          <t>Contraprestação de Parceria Público-Privada (PPP) - Terminais Urbanos</t>
         </is>
       </c>
       <c r="B131">
         <v>2022</v>
       </c>
       <c r="C131">
-        <v>23054771.45</v>
+        <v>23540000</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3250,45 +3250,45 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Áreas Públicas</t>
+          <t>Implantação de Corredores de Ônibus Novos</t>
         </is>
       </c>
       <c r="B132">
         <v>2022</v>
       </c>
       <c r="C132">
-        <v>22231986.32</v>
+        <v>23187857.36</v>
       </c>
       <c r="D132">
-        <v>18477677.85</v>
+        <v>18912415.66</v>
       </c>
       <c r="E132">
-        <v>0.8311303175540997</v>
+        <v>0.8156172157857366</v>
       </c>
       <c r="F132">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Serviços de Desfazimento e Demolição de Construções Irregulares em Áreas de Proteção Ambiental</t>
+          <t>Manutenção e Operação em Serviços de Saúde Animal</t>
         </is>
       </c>
       <c r="B133">
         <v>2022</v>
       </c>
       <c r="C133">
-        <v>22184275.32</v>
+        <v>23054771.45</v>
       </c>
       <c r="D133">
-        <v>22184275.32</v>
+        <v>0</v>
       </c>
       <c r="E133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -3301,10 +3301,10 @@
         <v>2022</v>
       </c>
       <c r="C134">
-        <v>21921972.54</v>
+        <v>22628034.65</v>
       </c>
       <c r="D134">
-        <v>21921972.54</v>
+        <v>22628034.65</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -3316,58 +3316,58 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Centros Culturais e Teatros</t>
+          <t>Ampliação, Reforma e Requalificação de Áreas Públicas</t>
         </is>
       </c>
       <c r="B135">
         <v>2022</v>
       </c>
       <c r="C135">
-        <v>21166445.2</v>
+        <v>22246375.88</v>
       </c>
       <c r="D135">
-        <v>21166445.2</v>
+        <v>18492067.41</v>
       </c>
       <c r="E135">
-        <v>1</v>
+        <v>0.8312395470502137</v>
       </c>
       <c r="F135">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Centro Educacional Unificado (CEU)</t>
+          <t>Serviços de Desfazimento e Demolição de Construções Irregulares em Áreas de Proteção Ambiental</t>
         </is>
       </c>
       <c r="B136">
         <v>2022</v>
       </c>
       <c r="C136">
-        <v>21132114.8</v>
+        <v>22184275.32</v>
       </c>
       <c r="D136">
-        <v>21132114.8</v>
+        <v>22184275.32</v>
       </c>
       <c r="E136">
         <v>1</v>
       </c>
       <c r="F136">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Fomento à Cooperação, Parcerias e Captação de Investimentos Internacionais</t>
+          <t>Desenvolvimento de Sistemas de Informação e Comunicação</t>
         </is>
       </c>
       <c r="B137">
         <v>2022</v>
       </c>
       <c r="C137">
-        <v>20855162.68</v>
+        <v>21440313.57</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -3382,80 +3382,80 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Desenvolvimento de Sistemas de Informação e Comunicação</t>
+          <t>Manutenção e Operação de Centros Culturais e Teatros</t>
         </is>
       </c>
       <c r="B138">
         <v>2022</v>
       </c>
       <c r="C138">
-        <v>20814739.88</v>
+        <v>21166445.2</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>21166445.2</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Programa de Atração a Filmagens - Cash Rebate</t>
+          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Centro Educacional Unificado (CEU)</t>
         </is>
       </c>
       <c r="B139">
         <v>2022</v>
       </c>
       <c r="C139">
-        <v>20000000</v>
+        <v>21132114.8</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>21132114.8</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Unidades de Conservação</t>
+          <t>Fomento à Cooperação, Parcerias e Captação de Investimentos Internacionais</t>
         </is>
       </c>
       <c r="B140">
         <v>2022</v>
       </c>
       <c r="C140">
-        <v>19234719.74</v>
+        <v>20855162.68</v>
       </c>
       <c r="D140">
-        <v>19234719.74</v>
+        <v>0</v>
       </c>
       <c r="E140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F140">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos de Atenção Básica e Especialidades</t>
+          <t>Programa de Atração a Filmagens - Cash Rebate</t>
         </is>
       </c>
       <c r="B141">
         <v>2022</v>
       </c>
       <c r="C141">
-        <v>19221068.84</v>
+        <v>20000000</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -3470,221 +3470,221 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Mulheres</t>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos de Atenção Básica e Especialidades</t>
         </is>
       </c>
       <c r="B142">
         <v>2022</v>
       </c>
       <c r="C142">
-        <v>18767407.33</v>
+        <v>19390231.49</v>
       </c>
       <c r="D142">
-        <v>11394125.51</v>
+        <v>0</v>
       </c>
       <c r="E142">
-        <v>0.6071230463350316</v>
+        <v>0</v>
       </c>
       <c r="F142">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Lei de Fomento ao Teatro</t>
+          <t>Manutenção e Operação de Unidades de Conservação</t>
         </is>
       </c>
       <c r="B143">
         <v>2022</v>
       </c>
       <c r="C143">
-        <v>18098877.23</v>
+        <v>19234719.74</v>
       </c>
       <c r="D143">
-        <v>17774750.07</v>
+        <v>19234719.74</v>
       </c>
       <c r="E143">
-        <v>0.9820913111967664</v>
+        <v>1</v>
       </c>
       <c r="F143">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Jurídico Social</t>
+          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Mulheres</t>
         </is>
       </c>
       <c r="B144">
         <v>2022</v>
       </c>
       <c r="C144">
-        <v>16751333.54</v>
+        <v>18767407.33</v>
       </c>
       <c r="D144">
-        <v>16751333.54</v>
+        <v>11394125.51</v>
       </c>
       <c r="E144">
-        <v>1</v>
+        <v>0.6071230463350316</v>
       </c>
       <c r="F144">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Gratificação de Municipalização - Saúde - Lei 13.510/03</t>
+          <t>Lei de Fomento ao Teatro</t>
         </is>
       </c>
       <c r="B145">
         <v>2022</v>
       </c>
       <c r="C145">
-        <v>16583528.38</v>
+        <v>18198204.68</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>17874077.52</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>0.9821890584428793</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Bibliotecas Públicas</t>
+          <t>Manutenção e Operação de Equipamentos de Proteção Jurídico Social</t>
         </is>
       </c>
       <c r="B146">
         <v>2022</v>
       </c>
       <c r="C146">
-        <v>16390596.58</v>
+        <v>16751333.54</v>
       </c>
       <c r="D146">
-        <v>16390596.58</v>
+        <v>16751333.54</v>
       </c>
       <c r="E146">
         <v>1</v>
       </c>
       <c r="F146">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
+          <t>Gratificação de Municipalização - Saúde - Lei 13.510/03</t>
         </is>
       </c>
       <c r="B147">
         <v>2022</v>
       </c>
       <c r="C147">
-        <v>16216884.41</v>
+        <v>16583528.38</v>
       </c>
       <c r="D147">
-        <v>36045.4</v>
+        <v>0</v>
       </c>
       <c r="E147">
-        <v>0.00222270807935049</v>
+        <v>0</v>
       </c>
       <c r="F147">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação da Avenida Santo Amaro</t>
+          <t>Manutenção e Operação de Bibliotecas Públicas</t>
         </is>
       </c>
       <c r="B148">
         <v>2022</v>
       </c>
       <c r="C148">
-        <v>15913787.17</v>
+        <v>16390596.58</v>
       </c>
       <c r="D148">
-        <v>15913787.17</v>
+        <v>16390596.58</v>
       </c>
       <c r="E148">
         <v>1</v>
       </c>
       <c r="F148">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Fomento à Cultura da Periferia de São Paulo</t>
+          <t>Ampliação, Reforma e Requalificação de Centros de Educação Infantil (CEI)</t>
         </is>
       </c>
       <c r="B149">
         <v>2022</v>
       </c>
       <c r="C149">
-        <v>15560079.11</v>
+        <v>16323625</v>
       </c>
       <c r="D149">
-        <v>15560079.11</v>
+        <v>16323625</v>
       </c>
       <c r="E149">
         <v>1</v>
       </c>
       <c r="F149">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Encargos Referentes a Arrecadação</t>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
         </is>
       </c>
       <c r="B150">
         <v>2022</v>
       </c>
       <c r="C150">
-        <v>15538669.89</v>
+        <v>16216884.41</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>36045.4</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>0.00222270807935049</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ações de Educação Integral</t>
+          <t>Ampliação, Reforma e Requalificação da Avenida Santo Amaro</t>
         </is>
       </c>
       <c r="B151">
         <v>2022</v>
       </c>
       <c r="C151">
-        <v>14760590.35</v>
+        <v>15913787.17</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>15913787.17</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -3697,10 +3697,10 @@
         <v>2022</v>
       </c>
       <c r="C152">
-        <v>14669266.33</v>
+        <v>15896691.85</v>
       </c>
       <c r="D152">
-        <v>14669266.33</v>
+        <v>15896691.85</v>
       </c>
       <c r="E152">
         <v>1</v>
@@ -3712,86 +3712,86 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Circuito Cultural de São Paulo</t>
+          <t>Ações de Educação Integral</t>
         </is>
       </c>
       <c r="B153">
         <v>2022</v>
       </c>
       <c r="C153">
-        <v>14664307.48</v>
+        <v>15571518.85</v>
       </c>
       <c r="D153">
-        <v>2115002.85</v>
+        <v>0</v>
       </c>
       <c r="E153">
-        <v>0.1442279393612388</v>
+        <v>0</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Ações de Desestatização</t>
+          <t>Fomento à Cultura da Periferia de São Paulo</t>
         </is>
       </c>
       <c r="B154">
         <v>2022</v>
       </c>
       <c r="C154">
-        <v>14578504.05</v>
+        <v>15560079.11</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>15560079.11</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Centros Municipais de Educação Infantil(CEMEI)</t>
+          <t>Encargos Referentes a Arrecadação</t>
         </is>
       </c>
       <c r="B155">
         <v>2022</v>
       </c>
       <c r="C155">
-        <v>14282509.85</v>
+        <v>15538669.89</v>
       </c>
       <c r="D155">
-        <v>14282509.85</v>
+        <v>0</v>
       </c>
       <c r="E155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F155">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Sistemas de Monitoramento e Alerta de Enchentes</t>
+          <t>Circuito Cultural de São Paulo</t>
         </is>
       </c>
       <c r="B156">
         <v>2022</v>
       </c>
       <c r="C156">
-        <v>14149331.94</v>
+        <v>14664307.48</v>
       </c>
       <c r="D156">
-        <v>14149331.94</v>
+        <v>2115002.85</v>
       </c>
       <c r="E156">
-        <v>1</v>
+        <v>0.1442279393612388</v>
       </c>
       <c r="F156">
         <v>1</v>
@@ -3800,262 +3800,262 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Operação e Manutenção dos Centros de Apoio ao Trabalho e Empreendedorismo</t>
+          <t>Manutenção e Operação de Centros Municipais de Educação Infantil(CEMEI)</t>
         </is>
       </c>
       <c r="B157">
         <v>2022</v>
       </c>
       <c r="C157">
-        <v>14100188.94</v>
+        <v>14643604.44</v>
       </c>
       <c r="D157">
-        <v>14100188.94</v>
+        <v>14643604.44</v>
       </c>
       <c r="E157">
         <v>1</v>
       </c>
       <c r="F157">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação do Autódromo de Interlagos</t>
+          <t>Ações de Desestatização</t>
         </is>
       </c>
       <c r="B158">
         <v>2022</v>
       </c>
       <c r="C158">
-        <v>13646766.35</v>
+        <v>14578504.05</v>
       </c>
       <c r="D158">
-        <v>13646766.35</v>
+        <v>0</v>
       </c>
       <c r="E158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F158">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Inserção das Famílias no Cadastro Único</t>
+          <t>Manutenção e Operação dos Sistemas de Monitoramento e Alerta de Enchentes</t>
         </is>
       </c>
       <c r="B159">
         <v>2022</v>
       </c>
       <c r="C159">
-        <v>13393117.39</v>
+        <v>14149331.94</v>
       </c>
       <c r="D159">
-        <v>13393117.39</v>
+        <v>14149331.94</v>
       </c>
       <c r="E159">
         <v>1</v>
       </c>
       <c r="F159">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Escolas Municipais de Educação Infantil (EMEI)</t>
+          <t>Operação e Manutenção dos Centros de Apoio ao Trabalho e Empreendedorismo</t>
         </is>
       </c>
       <c r="B160">
         <v>2022</v>
       </c>
       <c r="C160">
-        <v>13390255.89</v>
+        <v>14100188.94</v>
       </c>
       <c r="D160">
-        <v>13390255.89</v>
+        <v>14100188.94</v>
       </c>
       <c r="E160">
         <v>1</v>
       </c>
       <c r="F160">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ações de formação das Escolas de Música e Dança do Theatro Municipal e da Praça das Artes</t>
+          <t>Ampliação, Reforma e Requalificação do Autódromo de Interlagos</t>
         </is>
       </c>
       <c r="B161">
         <v>2022</v>
       </c>
       <c r="C161">
-        <v>13283396.97</v>
+        <v>13646766.35</v>
       </c>
       <c r="D161">
-        <v>13283396.97</v>
+        <v>13646766.35</v>
       </c>
       <c r="E161">
         <v>1</v>
       </c>
       <c r="F161">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Programação da Virada Esportiva</t>
+          <t>Inserção das Famílias no Cadastro Único</t>
         </is>
       </c>
       <c r="B162">
         <v>2022</v>
       </c>
       <c r="C162">
-        <v>13126439</v>
+        <v>13393117.39</v>
       </c>
       <c r="D162">
-        <v>740057.75</v>
+        <v>13393117.39</v>
       </c>
       <c r="E162">
-        <v>0.0563791710760245</v>
+        <v>1</v>
       </c>
       <c r="F162">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Operação e Manutenção de Unidade da Fundação Paulistana - FPETC</t>
+          <t>Ações de formação das Escolas de Música e Dança do Theatro Municipal e da Praça das Artes</t>
         </is>
       </c>
       <c r="B163">
         <v>2022</v>
       </c>
       <c r="C163">
-        <v>13017851.25</v>
+        <v>13283396.97</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>13283396.97</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Alfabetização na Idade Certa</t>
+          <t>Programação da Virada Esportiva</t>
         </is>
       </c>
       <c r="B164">
         <v>2022</v>
       </c>
       <c r="C164">
-        <v>12830710.76</v>
+        <v>13126439</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>740057.75</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>0.0563791710760245</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos do Departamento dos Museus Municipais</t>
+          <t>Operação e Manutenção de Unidade da Fundação Paulistana - FPETC</t>
         </is>
       </c>
       <c r="B165">
         <v>2022</v>
       </c>
       <c r="C165">
-        <v>12666263.1</v>
+        <v>13017851.25</v>
       </c>
       <c r="D165">
-        <v>12658860.82</v>
+        <v>0</v>
       </c>
       <c r="E165">
-        <v>0.9994155908541013</v>
+        <v>0</v>
       </c>
       <c r="F165">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Rede Parceira - Alfabetização de Jovens e Adultos</t>
+          <t>Alfabetização na Idade Certa</t>
         </is>
       </c>
       <c r="B166">
         <v>2022</v>
       </c>
       <c r="C166">
-        <v>12482544.18</v>
+        <v>12830710.76</v>
       </c>
       <c r="D166">
-        <v>12482544.18</v>
+        <v>0</v>
       </c>
       <c r="E166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F166">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Capacitação, Formação e Aperfeiçoamento de Servidores</t>
+          <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - Ensino Fundamental</t>
         </is>
       </c>
       <c r="B167">
         <v>2022</v>
       </c>
       <c r="C167">
-        <v>12240683.16</v>
+        <v>12705170.01</v>
       </c>
       <c r="D167">
-        <v>148410</v>
+        <v>12705170.01</v>
       </c>
       <c r="E167">
-        <v>0.01212432329634778</v>
+        <v>1</v>
       </c>
       <c r="F167">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Telecentros</t>
+          <t>Manutenção e Operação de Equipamentos do Departamento dos Museus Municipais</t>
         </is>
       </c>
       <c r="B168">
         <v>2022</v>
       </c>
       <c r="C168">
-        <v>11968074.11</v>
+        <v>12666263.1</v>
       </c>
       <c r="D168">
-        <v>11968074.11</v>
+        <v>12658860.82</v>
       </c>
       <c r="E168">
-        <v>1</v>
+        <v>0.9994155908541013</v>
       </c>
       <c r="F168">
         <v>32</v>
@@ -4064,146 +4064,146 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Conservação e Manutenção de Segundo Escalão de Unidades Educacionais - Ensino Fundamental</t>
+          <t>Manutenção e Operação da Rede Parceira - Alfabetização de Jovens e Adultos</t>
         </is>
       </c>
       <c r="B169">
         <v>2022</v>
       </c>
       <c r="C169">
-        <v>11694306.59</v>
+        <v>12482544.18</v>
       </c>
       <c r="D169">
-        <v>11694306.59</v>
+        <v>12482544.18</v>
       </c>
       <c r="E169">
         <v>1</v>
       </c>
       <c r="F169">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Casas de Cultura</t>
+          <t>Sistema de Avaliação Escolar dos Alunos da Rede Municipal de Ensino</t>
         </is>
       </c>
       <c r="B170">
         <v>2022</v>
       </c>
       <c r="C170">
-        <v>11637013.24</v>
+        <v>12360600.58</v>
       </c>
       <c r="D170">
-        <v>11637013.24</v>
+        <v>0</v>
       </c>
       <c r="E170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F170">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Operação e Manutenção da São Paulo Investimentos e Negócios</t>
+          <t>Capacitação, Formação e Aperfeiçoamento de Servidores</t>
         </is>
       </c>
       <c r="B171">
         <v>2022</v>
       </c>
       <c r="C171">
-        <v>11387248.81</v>
+        <v>12354560.69</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>148410</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>0.01201256796772431</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Praças, Canteiros Centrais e Remanescentes</t>
+          <t>Manutenção e Operação de Telecentros</t>
         </is>
       </c>
       <c r="B172">
         <v>2022</v>
       </c>
       <c r="C172">
-        <v>11361283.77</v>
+        <v>12001984.88</v>
       </c>
       <c r="D172">
-        <v>11361283.77</v>
+        <v>12001984.88</v>
       </c>
       <c r="E172">
         <v>1</v>
       </c>
       <c r="F172">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Preservação do Patrimônio Histórico, Artístico, Cultural e Arqueológico</t>
+          <t>Manutenção e Operação de Casas de Cultura</t>
         </is>
       </c>
       <c r="B173">
         <v>2022</v>
       </c>
       <c r="C173">
-        <v>11272604.43</v>
+        <v>11637013.24</v>
       </c>
       <c r="D173">
-        <v>11272604.43</v>
+        <v>11637013.24</v>
       </c>
       <c r="E173">
         <v>1</v>
       </c>
       <c r="F173">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Parques Urbanos e Lineares</t>
+          <t>Lei de Fomento à Dança</t>
         </is>
       </c>
       <c r="B174">
         <v>2022</v>
       </c>
       <c r="C174">
-        <v>11059459.31</v>
+        <v>11471768.69</v>
       </c>
       <c r="D174">
-        <v>11059459.31</v>
+        <v>11304568.69</v>
       </c>
       <c r="E174">
-        <v>1</v>
+        <v>0.98542508966854</v>
       </c>
       <c r="F174">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Bolsa-Trabalho</t>
+          <t>Operação e Manutenção da São Paulo Investimentos e Negócios</t>
         </is>
       </c>
       <c r="B175">
         <v>2022</v>
       </c>
       <c r="C175">
-        <v>11046413.85</v>
+        <v>11387248.81</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -4218,80 +4218,80 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Execução do Programa para a Valorização de Iniciativas Culturais</t>
+          <t>Manutenção e Operação de Praças, Canteiros Centrais e Remanescentes</t>
         </is>
       </c>
       <c r="B176">
         <v>2022</v>
       </c>
       <c r="C176">
-        <v>10966474.67</v>
+        <v>11361283.77</v>
       </c>
       <c r="D176">
-        <v>10964074.67</v>
+        <v>11361283.77</v>
       </c>
       <c r="E176">
-        <v>0.9997811511837468</v>
+        <v>1</v>
       </c>
       <c r="F176">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Programa Melhor em Casa</t>
+          <t>Preservação do Patrimônio Histórico, Artístico, Cultural e Arqueológico</t>
         </is>
       </c>
       <c r="B177">
         <v>2022</v>
       </c>
       <c r="C177">
-        <v>10848000</v>
+        <v>11272604.43</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>11272604.43</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Manutenção de Unidades Habitacionais</t>
+          <t>Ampliação, Reforma e Requalificação de Parques Urbanos e Lineares</t>
         </is>
       </c>
       <c r="B178">
         <v>2022</v>
       </c>
       <c r="C178">
-        <v>10776569.84</v>
+        <v>11059459.31</v>
       </c>
       <c r="D178">
-        <v>7181610.06</v>
+        <v>11059459.31</v>
       </c>
       <c r="E178">
-        <v>0.6664096430149429</v>
+        <v>1</v>
       </c>
       <c r="F178">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Câmara Municipal - Comunicação</t>
+          <t>Bolsa-Trabalho</t>
         </is>
       </c>
       <c r="B179">
         <v>2022</v>
       </c>
       <c r="C179">
-        <v>10644960.32</v>
+        <v>11045159.43</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -4306,36 +4306,36 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Lei de Fomento à Dança</t>
+          <t>Execução do Programa para a Valorização de Iniciativas Culturais</t>
         </is>
       </c>
       <c r="B180">
         <v>2022</v>
       </c>
       <c r="C180">
-        <v>10618149.01</v>
+        <v>10966474.67</v>
       </c>
       <c r="D180">
-        <v>10450949.01</v>
+        <v>10964074.67</v>
       </c>
       <c r="E180">
-        <v>0.9842533760034321</v>
+        <v>0.9997811511837468</v>
       </c>
       <c r="F180">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Patrimônio</t>
+          <t>Manutenção e Operação do Programa Melhor em Casa</t>
         </is>
       </c>
       <c r="B181">
         <v>2022</v>
       </c>
       <c r="C181">
-        <v>10413440</v>
+        <v>10848000</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -4350,58 +4350,58 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Fundamental e Médio (EMEFM)</t>
+          <t>Manutenção de Unidades Habitacionais</t>
         </is>
       </c>
       <c r="B182">
         <v>2022</v>
       </c>
       <c r="C182">
-        <v>10344486.94</v>
+        <v>10776569.84</v>
       </c>
       <c r="D182">
-        <v>10344486.94</v>
+        <v>7181610.06</v>
       </c>
       <c r="E182">
-        <v>1</v>
+        <v>0.6664096430149429</v>
       </c>
       <c r="F182">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Centro Cultural São Paulo</t>
+          <t>Câmara Municipal - Comunicação</t>
         </is>
       </c>
       <c r="B183">
         <v>2022</v>
       </c>
       <c r="C183">
-        <v>10321076.05</v>
+        <v>10644960.32</v>
       </c>
       <c r="D183">
-        <v>10321076.05</v>
+        <v>0</v>
       </c>
       <c r="E183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F183">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Realização de Projetos Culturais</t>
+          <t>Ações de Difusão Cultural do Theatro Municipal - Patrimônio</t>
         </is>
       </c>
       <c r="B184">
         <v>2022</v>
       </c>
       <c r="C184">
-        <v>10160081.19</v>
+        <v>10413440</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -4416,58 +4416,58 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Cooperação Técnica Internacional</t>
+          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Fundamental e Médio (EMEFM)</t>
         </is>
       </c>
       <c r="B185">
         <v>2022</v>
       </c>
       <c r="C185">
-        <v>10000000</v>
+        <v>10392655.57</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>10392655.57</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Projetos de Fomento ao Turismo</t>
+          <t>Manutenção e Operação do Centro Cultural São Paulo</t>
         </is>
       </c>
       <c r="B186">
         <v>2022</v>
       </c>
       <c r="C186">
-        <v>9981513.9</v>
+        <v>10321076.05</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>10321076.05</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Serviços de DST / AIDS</t>
+          <t>Realização de Projetos Culturais</t>
         </is>
       </c>
       <c r="B187">
         <v>2022</v>
       </c>
       <c r="C187">
-        <v>9769126.93</v>
+        <v>10160081.19</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -4482,344 +4482,344 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Programação da Virada Cultural</t>
+          <t>Projetos para Inclusão da Pessoa com Deficiência</t>
         </is>
       </c>
       <c r="B188">
         <v>2022</v>
       </c>
       <c r="C188">
-        <v>9690172.199999999</v>
+        <v>10134782.96</v>
       </c>
       <c r="D188">
-        <v>9097957</v>
+        <v>0</v>
       </c>
       <c r="E188">
-        <v>0.9388849663579767</v>
+        <v>0</v>
       </c>
       <c r="F188">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Programa Jovem Monitor Cultural</t>
+          <t>Cooperação Técnica Internacional</t>
         </is>
       </c>
       <c r="B189">
         <v>2022</v>
       </c>
       <c r="C189">
-        <v>9674276.109999999</v>
+        <v>10000000</v>
       </c>
       <c r="D189">
-        <v>9674276.109999999</v>
+        <v>0</v>
       </c>
       <c r="E189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F189">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Inspeção de Obras de Artes Especiais - OAE</t>
+          <t>Projetos de Fomento ao Turismo</t>
         </is>
       </c>
       <c r="B190">
         <v>2022</v>
       </c>
       <c r="C190">
-        <v>9671093.290000001</v>
+        <v>9981513.9</v>
       </c>
       <c r="D190">
-        <v>5771998.94</v>
+        <v>0</v>
       </c>
       <c r="E190">
-        <v>0.5968300343011167</v>
+        <v>0</v>
       </c>
       <c r="F190">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Pólos Regionais de Esporte</t>
+          <t>Manutenção e Operação dos Serviços de DST / AIDS</t>
         </is>
       </c>
       <c r="B191">
         <v>2022</v>
       </c>
       <c r="C191">
-        <v>9629770.710000001</v>
+        <v>9767626.93</v>
       </c>
       <c r="D191">
-        <v>9629770.710000001</v>
+        <v>0</v>
       </c>
       <c r="E191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F191">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Biblioteca Mario de Andrade</t>
+          <t>Inspeção de Obras de Artes Especiais - OAE</t>
         </is>
       </c>
       <c r="B192">
         <v>2022</v>
       </c>
       <c r="C192">
-        <v>9620896.34</v>
+        <v>9693658.119999999</v>
       </c>
       <c r="D192">
-        <v>9620896.34</v>
+        <v>5794563.77</v>
       </c>
       <c r="E192">
-        <v>1</v>
+        <v>0.5977685305452056</v>
       </c>
       <c r="F192">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Compensações Ambientais</t>
+          <t>Programação da Virada Cultural</t>
         </is>
       </c>
       <c r="B193">
         <v>2022</v>
       </c>
       <c r="C193">
-        <v>9556954.58</v>
+        <v>9690172.199999999</v>
       </c>
       <c r="D193">
-        <v>9556954.58</v>
+        <v>9097957</v>
       </c>
       <c r="E193">
-        <v>1</v>
+        <v>0.9388849663579767</v>
       </c>
       <c r="F193">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Compensação Financeira - Outros Fundos de Previdência</t>
+          <t>Programa Jovem Monitor Cultural</t>
         </is>
       </c>
       <c r="B194">
         <v>2022</v>
       </c>
       <c r="C194">
-        <v>9491442.34</v>
+        <v>9674276.109999999</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>9674276.109999999</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Escola Municipal de Educação Artística - EMIA</t>
+          <t>Manutenção e Operação dos Pólos Regionais de Esporte</t>
         </is>
       </c>
       <c r="B195">
         <v>2022</v>
       </c>
       <c r="C195">
-        <v>9482790.99</v>
+        <v>9629770.710000001</v>
       </c>
       <c r="D195">
-        <v>9482790.99</v>
+        <v>9629770.710000001</v>
       </c>
       <c r="E195">
         <v>1</v>
       </c>
       <c r="F195">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Prêmio Zé Renato</t>
+          <t>Manutenção e Operação da Biblioteca Mario de Andrade</t>
         </is>
       </c>
       <c r="B196">
         <v>2022</v>
       </c>
       <c r="C196">
-        <v>9478914.550000001</v>
+        <v>9620896.34</v>
       </c>
       <c r="D196">
-        <v>9478914.550000001</v>
+        <v>9620896.34</v>
       </c>
       <c r="E196">
         <v>1</v>
       </c>
       <c r="F196">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Subvenção e Contribuições a Entidades Culturais</t>
+          <t>Compensações Ambientais</t>
         </is>
       </c>
       <c r="B197">
         <v>2022</v>
       </c>
       <c r="C197">
-        <v>9297471.039999999</v>
+        <v>9556954.58</v>
       </c>
       <c r="D197">
-        <v>9297471.039999999</v>
+        <v>9556954.58</v>
       </c>
       <c r="E197">
         <v>1</v>
       </c>
       <c r="F197">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Programação de Atividades Culturais de Casas de Cultura</t>
+          <t>Compensação Financeira - Outros Fundos de Previdência</t>
         </is>
       </c>
       <c r="B198">
         <v>2022</v>
       </c>
       <c r="C198">
-        <v>9167527.720000001</v>
+        <v>9491442.34</v>
       </c>
       <c r="D198">
-        <v>9167527.720000001</v>
+        <v>0</v>
       </c>
       <c r="E198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F198">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Escola Municipal de Ensino Fundamental (EMEF)</t>
+          <t>Escola Municipal de Educação Artística - EMIA</t>
         </is>
       </c>
       <c r="B199">
         <v>2022</v>
       </c>
       <c r="C199">
-        <v>9050432.58</v>
+        <v>9482790.99</v>
       </c>
       <c r="D199">
-        <v>9050432.58</v>
+        <v>9482790.99</v>
       </c>
       <c r="E199">
         <v>1</v>
       </c>
       <c r="F199">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Ações para Promoção da Sustentabilidade Previdenciária</t>
+          <t>Prêmio Zé Renato</t>
         </is>
       </c>
       <c r="B200">
         <v>2022</v>
       </c>
       <c r="C200">
-        <v>8904000</v>
+        <v>9478914.550000001</v>
       </c>
       <c r="D200">
-        <v>0</v>
+        <v>9478914.550000001</v>
       </c>
       <c r="E200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Intervenções na Área de Mobilidade Urbana</t>
+          <t>Subvenção e Contribuições a Entidades Culturais</t>
         </is>
       </c>
       <c r="B201">
         <v>2022</v>
       </c>
       <c r="C201">
-        <v>8901911.27</v>
+        <v>9297471.039999999</v>
       </c>
       <c r="D201">
-        <v>4700473.43</v>
+        <v>9297471.039999999</v>
       </c>
       <c r="E201">
-        <v>0.5280296879436319</v>
+        <v>1</v>
       </c>
       <c r="F201">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Transporte Escolar - Educação Especial</t>
+          <t>Programação de Atividades Culturais de Casas de Cultura</t>
         </is>
       </c>
       <c r="B202">
         <v>2022</v>
       </c>
       <c r="C202">
-        <v>8848599.699999999</v>
+        <v>9167527.720000001</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>9167527.720000001</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Viveiros</t>
+          <t>Ações para Promoção da Sustentabilidade Previdenciária</t>
         </is>
       </c>
       <c r="B203">
         <v>2022</v>
       </c>
       <c r="C203">
-        <v>8790405</v>
+        <v>8904000</v>
       </c>
       <c r="D203">
         <v>0</v>
@@ -4834,36 +4834,36 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Fomento às Linguagens Artísticas</t>
+          <t>Intervenções na Área de Mobilidade Urbana</t>
         </is>
       </c>
       <c r="B204">
         <v>2022</v>
       </c>
       <c r="C204">
-        <v>8668750.43</v>
+        <v>8901911.27</v>
       </c>
       <c r="D204">
-        <v>8624381.93</v>
+        <v>4700473.43</v>
       </c>
       <c r="E204">
-        <v>0.9948817882856041</v>
+        <v>0.5280296879436319</v>
       </c>
       <c r="F204">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Ações Permanentes de Promoção dos Direitos da População Idosa</t>
+          <t>Transporte Escolar - Educação Especial</t>
         </is>
       </c>
       <c r="B205">
         <v>2022</v>
       </c>
       <c r="C205">
-        <v>8330895.9</v>
+        <v>8878706.08</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -4878,14 +4878,14 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Programação Artística</t>
+          <t>Manutenção e Operação de Viveiros</t>
         </is>
       </c>
       <c r="B206">
         <v>2022</v>
       </c>
       <c r="C206">
-        <v>8164819.7</v>
+        <v>8790405</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -4900,190 +4900,190 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Sistema de Avaliação Escolar dos Alunos da Rede Municipal de Ensino</t>
+          <t>Fomento às Linguagens Artísticas</t>
         </is>
       </c>
       <c r="B207">
         <v>2022</v>
       </c>
       <c r="C207">
-        <v>8144055.060000001</v>
+        <v>8668750.43</v>
       </c>
       <c r="D207">
-        <v>0</v>
+        <v>8624381.93</v>
       </c>
       <c r="E207">
-        <v>0</v>
+        <v>0.9948817882856041</v>
       </c>
       <c r="F207">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Remuneração dos Profissionais do Magistério - Centro Municipal de Educação Infantil( CEMEI)</t>
+          <t>Ações Permanentes de Promoção dos Direitos da População Idosa</t>
         </is>
       </c>
       <c r="B208">
         <v>2022</v>
       </c>
       <c r="C208">
-        <v>8093438.78</v>
+        <v>8330895.9</v>
       </c>
       <c r="D208">
-        <v>8093438.78</v>
+        <v>0</v>
       </c>
       <c r="E208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F208">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Implantação do Memorial dos Aflitos</t>
+          <t>Ações de Difusão Cultural do Theatro Municipal - Programação Artística</t>
         </is>
       </c>
       <c r="B209">
         <v>2022</v>
       </c>
       <c r="C209">
-        <v>8091703.38</v>
+        <v>8164819.7</v>
       </c>
       <c r="D209">
-        <v>8091703.38</v>
+        <v>0</v>
       </c>
       <c r="E209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F209">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Programação de Atividades Culturais de Centros Culturais e Teatros</t>
+          <t>Remuneração dos Profissionais do Magistério - Centro Municipal de Educação Infantil( CEMEI)</t>
         </is>
       </c>
       <c r="B210">
         <v>2022</v>
       </c>
       <c r="C210">
-        <v>8079770.06</v>
+        <v>8093438.78</v>
       </c>
       <c r="D210">
-        <v>8079770.06</v>
+        <v>8093438.78</v>
       </c>
       <c r="E210">
         <v>1</v>
       </c>
       <c r="F210">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Rede Parceira - Educação Especial</t>
+          <t>Implantação do Memorial dos Aflitos</t>
         </is>
       </c>
       <c r="B211">
         <v>2022</v>
       </c>
       <c r="C211">
-        <v>7763494.99</v>
+        <v>8091703.38</v>
       </c>
       <c r="D211">
-        <v>7763494.99</v>
+        <v>8091703.38</v>
       </c>
       <c r="E211">
         <v>1</v>
       </c>
       <c r="F211">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Construção da Fábrica do Samba</t>
+          <t>Programação de Atividades Culturais de Centros Culturais e Teatros</t>
         </is>
       </c>
       <c r="B212">
         <v>2022</v>
       </c>
       <c r="C212">
-        <v>7738081.35</v>
+        <v>8079770.06</v>
       </c>
       <c r="D212">
-        <v>7738081.35</v>
+        <v>8079770.06</v>
       </c>
       <c r="E212">
         <v>1</v>
       </c>
       <c r="F212">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Suporte e Manutenção da Coordenação de Imprensa</t>
+          <t>Manutenção e Operação da Rede Parceira - Educação Especial</t>
         </is>
       </c>
       <c r="B213">
         <v>2022</v>
       </c>
       <c r="C213">
-        <v>7676657.23</v>
+        <v>7763494.99</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>7763494.99</v>
       </c>
       <c r="E213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Centro Olímpicos</t>
+          <t>Construção da Fábrica do Samba</t>
         </is>
       </c>
       <c r="B214">
         <v>2022</v>
       </c>
       <c r="C214">
-        <v>7499000</v>
+        <v>7738081.35</v>
       </c>
       <c r="D214">
-        <v>0</v>
+        <v>7738081.35</v>
       </c>
       <c r="E214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F214">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Qualificação Profissional e Empreendedora</t>
+          <t>Suporte e Manutenção da Coordenação de Imprensa</t>
         </is>
       </c>
       <c r="B215">
         <v>2022</v>
       </c>
       <c r="C215">
-        <v>7496752.96</v>
+        <v>7676657.23</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -5098,102 +5098,102 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Programa de Garantia de Renda Familiar Mínima</t>
+          <t>Ampliação, Reforma e Requalificação de Centro Olímpicos</t>
         </is>
       </c>
       <c r="B216">
         <v>2022</v>
       </c>
       <c r="C216">
-        <v>7491383.61</v>
+        <v>7499000</v>
       </c>
       <c r="D216">
-        <v>7491383.61</v>
+        <v>0</v>
       </c>
       <c r="E216">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F216">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Edificação da Câmara Municipal de São Paulo</t>
+          <t>Qualificação Profissional e Empreendedora</t>
         </is>
       </c>
       <c r="B217">
         <v>2022</v>
       </c>
       <c r="C217">
-        <v>7465375.64</v>
+        <v>7496752.96</v>
       </c>
       <c r="D217">
-        <v>7465375.64</v>
+        <v>0</v>
       </c>
       <c r="E217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F217">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Recuperação de Fachadas Históricas na Área Central</t>
+          <t>Programa de Garantia de Renda Familiar Mínima</t>
         </is>
       </c>
       <c r="B218">
         <v>2022</v>
       </c>
       <c r="C218">
-        <v>7340892.42</v>
+        <v>7491383.61</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>7491383.61</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Administração do Edifício Matarazzo</t>
+          <t>Manutenção e Operação de Edificação da Câmara Municipal de São Paulo</t>
         </is>
       </c>
       <c r="B219">
         <v>2022</v>
       </c>
       <c r="C219">
-        <v>7280422.2</v>
+        <v>7465375.64</v>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>7465375.64</v>
       </c>
       <c r="E219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F219">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Parceria Público Privada - Habitação</t>
+          <t>Programa Nacional de Apoio à Gestão Adm. e Fiscal - PNAFM</t>
         </is>
       </c>
       <c r="B220">
         <v>2022</v>
       </c>
       <c r="C220">
-        <v>6960978.09</v>
+        <v>7379923.59</v>
       </c>
       <c r="D220">
         <v>0</v>
@@ -5208,14 +5208,14 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Programa Nacional de Apoio à Gestão Adm. e Fiscal - PNAFM</t>
+          <t>Recuperação de Fachadas Históricas na Área Central</t>
         </is>
       </c>
       <c r="B221">
         <v>2022</v>
       </c>
       <c r="C221">
-        <v>6795896.8</v>
+        <v>7340892.42</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -5230,64 +5230,64 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Plantio de Árvores</t>
+          <t>Administração do Edifício Matarazzo</t>
         </is>
       </c>
       <c r="B222">
         <v>2022</v>
       </c>
       <c r="C222">
-        <v>6594546.43</v>
+        <v>7280422.2</v>
       </c>
       <c r="D222">
-        <v>6594546.43</v>
+        <v>0</v>
       </c>
       <c r="E222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F222">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Acessibilidade, Ampliação, Reforma e Requalificação de Terminais de Ônibus</t>
+          <t>Parceria Público Privada - Habitação</t>
         </is>
       </c>
       <c r="B223">
         <v>2022</v>
       </c>
       <c r="C223">
-        <v>6561837.649999999</v>
+        <v>6960978.09</v>
       </c>
       <c r="D223">
-        <v>6515637.649999999</v>
+        <v>0</v>
       </c>
       <c r="E223">
-        <v>0.9929592893844303</v>
+        <v>0</v>
       </c>
       <c r="F223">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos Culturais</t>
+          <t>Plantio de Árvores</t>
         </is>
       </c>
       <c r="B224">
         <v>2022</v>
       </c>
       <c r="C224">
-        <v>6325250.22</v>
+        <v>6615902.66</v>
       </c>
       <c r="D224">
-        <v>6222857.03</v>
+        <v>6615902.66</v>
       </c>
       <c r="E224">
-        <v>0.9838119937648886</v>
+        <v>1</v>
       </c>
       <c r="F224">
         <v>32</v>
@@ -5296,36 +5296,36 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Casa da Mulher Brasileira</t>
+          <t>Acessibilidade, Ampliação, Reforma e Requalificação de Terminais de Ônibus</t>
         </is>
       </c>
       <c r="B225">
         <v>2022</v>
       </c>
       <c r="C225">
-        <v>6248971.83</v>
+        <v>6561837.649999999</v>
       </c>
       <c r="D225">
-        <v>6248971.83</v>
+        <v>6515637.649999999</v>
       </c>
       <c r="E225">
-        <v>1</v>
+        <v>0.9929592893844303</v>
       </c>
       <c r="F225">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Administrativos</t>
+          <t>Construção de Corredores de Ônibus</t>
         </is>
       </c>
       <c r="B226">
         <v>2022</v>
       </c>
       <c r="C226">
-        <v>6237478.64</v>
+        <v>6490580.36</v>
       </c>
       <c r="D226">
         <v>0</v>
@@ -5340,58 +5340,58 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Equipamentos Públicos Voltados ao Atendimento da População LGBTI</t>
+          <t>Manutenção e Operação de Equipamentos Culturais</t>
         </is>
       </c>
       <c r="B227">
         <v>2022</v>
       </c>
       <c r="C227">
-        <v>6165357.33</v>
+        <v>6325250.22</v>
       </c>
       <c r="D227">
-        <v>6165357.33</v>
+        <v>6222857.03</v>
       </c>
       <c r="E227">
-        <v>1</v>
+        <v>0.9838119937648886</v>
       </c>
       <c r="F227">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Centro Integrado de Jovens e Adultos (CIEJA)</t>
+          <t>Manutenção e Operação da Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="B228">
         <v>2022</v>
       </c>
       <c r="C228">
-        <v>5948992.72</v>
+        <v>6248971.83</v>
       </c>
       <c r="D228">
-        <v>5948992.72</v>
+        <v>6248971.83</v>
       </c>
       <c r="E228">
         <v>1</v>
       </c>
       <c r="F228">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Fomento às Cadeias Produtivas, Vocações Produtivas e Projetos Locais</t>
+          <t>Ações de Difusão Cultural do Theatro Municipal - Administrativos</t>
         </is>
       </c>
       <c r="B229">
         <v>2022</v>
       </c>
       <c r="C229">
-        <v>5934897.28</v>
+        <v>6237478.64</v>
       </c>
       <c r="D229">
         <v>0</v>
@@ -5406,58 +5406,58 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Serviços de Atendimento e Manejo da Fauna Silvestre</t>
+          <t>Manutenção e Operação dos Equipamentos Públicos Voltados ao Atendimento da População LGBTI</t>
         </is>
       </c>
       <c r="B230">
         <v>2022</v>
       </c>
       <c r="C230">
-        <v>5792320.92</v>
+        <v>6165357.33</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>6165357.33</v>
       </c>
       <c r="E230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F230">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Servidores Comissionados no Hospital Serv. Públco Municipal - HSPM</t>
+          <t>Manutenção e Operação de Unidades Educacionais - Centro Integrado de Jovens e Adultos (CIEJA)</t>
         </is>
       </c>
       <c r="B231">
         <v>2022</v>
       </c>
       <c r="C231">
-        <v>5301596.72</v>
+        <v>6016808.78</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>6016808.78</v>
       </c>
       <c r="E231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F231">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Construção de Corredores de Ônibus</t>
+          <t>Fomento às Cadeias Produtivas, Vocações Produtivas e Projetos Locais</t>
         </is>
       </c>
       <c r="B232">
         <v>2022</v>
       </c>
       <c r="C232">
-        <v>5287276.689999999</v>
+        <v>5934897.28</v>
       </c>
       <c r="D232">
         <v>0</v>
@@ -5472,14 +5472,14 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para a População LGBTI+</t>
+          <t>Manutenção e Operação dos Serviços de Atendimento e Manejo da Fauna Silvestre</t>
         </is>
       </c>
       <c r="B233">
         <v>2022</v>
       </c>
       <c r="C233">
-        <v>5167420.9</v>
+        <v>5792320.92</v>
       </c>
       <c r="D233">
         <v>0</v>
@@ -5494,58 +5494,58 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Juventude</t>
+          <t>Construção de Escolas Municipais de Educação Infantil (EMEI)</t>
         </is>
       </c>
       <c r="B234">
         <v>2022</v>
       </c>
       <c r="C234">
-        <v>5057261.65</v>
+        <v>5394195.55</v>
       </c>
       <c r="D234">
-        <v>0</v>
+        <v>5394195.55</v>
       </c>
       <c r="E234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F234">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Políticas de Promoção Cultural nas Bibliotecas Públicas</t>
+          <t>Servidores Comissionados no Hospital Serv. Públco Municipal - HSPM</t>
         </is>
       </c>
       <c r="B235">
         <v>2022</v>
       </c>
       <c r="C235">
-        <v>5013286.41</v>
+        <v>5301596.72</v>
       </c>
       <c r="D235">
-        <v>5013286.41</v>
+        <v>0</v>
       </c>
       <c r="E235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F235">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Políticas de promoção cultural</t>
+          <t>Políticas, Programas e Ações para a População LGBTI+</t>
         </is>
       </c>
       <c r="B236">
         <v>2022</v>
       </c>
       <c r="C236">
-        <v>4955600</v>
+        <v>5167420.9</v>
       </c>
       <c r="D236">
         <v>0</v>
@@ -5560,133 +5560,133 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos Culturais</t>
+          <t>Políticas de Promoção Cultural nas Bibliotecas Públicas</t>
         </is>
       </c>
       <c r="B237">
         <v>2022</v>
       </c>
       <c r="C237">
-        <v>4746017.07</v>
+        <v>5013286.41</v>
       </c>
       <c r="D237">
-        <v>4746017.07</v>
+        <v>5013286.41</v>
       </c>
       <c r="E237">
         <v>1</v>
       </c>
       <c r="F237">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Ciclovias, Ciclofaixas e Ciclorrotas</t>
+          <t>Políticas de promoção cultural</t>
         </is>
       </c>
       <c r="B238">
         <v>2022</v>
       </c>
       <c r="C238">
-        <v>4700738.59</v>
+        <v>4955600</v>
       </c>
       <c r="D238">
-        <v>4700738.59</v>
+        <v>0</v>
       </c>
       <c r="E238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F238">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Educação Indígena</t>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos Culturais</t>
         </is>
       </c>
       <c r="B239">
         <v>2022</v>
       </c>
       <c r="C239">
-        <v>4517975.08</v>
+        <v>4746017.07</v>
       </c>
       <c r="D239">
-        <v>4517975.08</v>
+        <v>4746017.07</v>
       </c>
       <c r="E239">
         <v>1</v>
       </c>
       <c r="F239">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Centros de Educação Infantil (CEI)</t>
+          <t>Ampliação, Reforma e Requalificação de Ciclovias, Ciclofaixas e Ciclorrotas</t>
         </is>
       </c>
       <c r="B240">
         <v>2022</v>
       </c>
       <c r="C240">
-        <v>4303115.63</v>
+        <v>4700738.59</v>
       </c>
       <c r="D240">
-        <v>4303115.63</v>
+        <v>4700738.59</v>
       </c>
       <c r="E240">
         <v>1</v>
       </c>
       <c r="F240">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Oficina nos Equipamentos Culturais</t>
+          <t>Manutenção e Operação de Unidades Educacionais - Educação Indígena</t>
         </is>
       </c>
       <c r="B241">
         <v>2022</v>
       </c>
       <c r="C241">
-        <v>4191828</v>
+        <v>4529383.09</v>
       </c>
       <c r="D241">
-        <v>4191828</v>
+        <v>4529383.09</v>
       </c>
       <c r="E241">
         <v>1</v>
       </c>
       <c r="F241">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Construção de Escolas Municipais de Educação Infantil (EMEI)</t>
+          <t>Oficina nos Equipamentos Culturais</t>
         </is>
       </c>
       <c r="B242">
         <v>2022</v>
       </c>
       <c r="C242">
-        <v>4183246.79</v>
+        <v>4191828</v>
       </c>
       <c r="D242">
-        <v>4183246.79</v>
+        <v>4191828</v>
       </c>
       <c r="E242">
         <v>1</v>
       </c>
       <c r="F242">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="243">
@@ -5721,10 +5721,10 @@
         <v>2022</v>
       </c>
       <c r="C244">
-        <v>4095486.01</v>
+        <v>4097102.01</v>
       </c>
       <c r="D244">
-        <v>4095486.01</v>
+        <v>4097102.01</v>
       </c>
       <c r="E244">
         <v>1</v>
@@ -5802,14 +5802,14 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Projetos para Inclusão da Pessoa com Deficiência</t>
+          <t>Auxílio Funeral</t>
         </is>
       </c>
       <c r="B248">
         <v>2022</v>
       </c>
       <c r="C248">
-        <v>3681632</v>
+        <v>3471968.03</v>
       </c>
       <c r="D248">
         <v>0</v>
@@ -5824,42 +5824,42 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Auxílio Funeral</t>
+          <t>PROCONECTA - Promoção da Conectividade e Inclusão Digital</t>
         </is>
       </c>
       <c r="B249">
         <v>2022</v>
       </c>
       <c r="C249">
-        <v>3441086.24</v>
+        <v>3400843.62</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>3192905.08</v>
       </c>
       <c r="E249">
-        <v>0</v>
+        <v>0.9388567769546545</v>
       </c>
       <c r="F249">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PROCONECTA - Promoção da Conectividade e Inclusão Digital</t>
+          <t>Execução do Programa Museu de Arte de Rua - MAR</t>
         </is>
       </c>
       <c r="B250">
         <v>2022</v>
       </c>
       <c r="C250">
-        <v>3400843.62</v>
+        <v>3328942.35</v>
       </c>
       <c r="D250">
-        <v>3192905.08</v>
+        <v>443498</v>
       </c>
       <c r="E250">
-        <v>0.9388567769546545</v>
+        <v>0.1332248964900218</v>
       </c>
       <c r="F250">
         <v>1</v>
@@ -5868,168 +5868,168 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Execução do Programa Museu de Arte de Rua - MAR</t>
+          <t>Fomento ao Circo/Edital Xamego</t>
         </is>
       </c>
       <c r="B251">
         <v>2022</v>
       </c>
       <c r="C251">
-        <v>3328942.35</v>
+        <v>3317603.16</v>
       </c>
       <c r="D251">
-        <v>443498</v>
+        <v>3317603.16</v>
       </c>
       <c r="E251">
-        <v>0.1332248964900218</v>
+        <v>1</v>
       </c>
       <c r="F251">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Fomento ao Circo/Edital Xamego</t>
+          <t>Programação de Atividades Culturais do Centro Cultural São Paulo</t>
         </is>
       </c>
       <c r="B252">
         <v>2022</v>
       </c>
       <c r="C252">
-        <v>3311603.16</v>
+        <v>3223201</v>
       </c>
       <c r="D252">
-        <v>3311603.16</v>
+        <v>3223201</v>
       </c>
       <c r="E252">
         <v>1</v>
       </c>
       <c r="F252">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Programação de Atividades Culturais do Centro Cultural São Paulo</t>
+          <t>Rádios Comunitárias - Lei nº 16.572/2016</t>
         </is>
       </c>
       <c r="B253">
         <v>2022</v>
       </c>
       <c r="C253">
-        <v>3223201</v>
+        <v>3223200</v>
       </c>
       <c r="D253">
-        <v>3223201</v>
+        <v>3103200</v>
       </c>
       <c r="E253">
-        <v>1</v>
+        <v>0.9627699180938198</v>
       </c>
       <c r="F253">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Rádios Comunitárias - Lei nº 16.572/2016</t>
+          <t>Políticas, Programas e Ações Para Criança e Adolescente</t>
         </is>
       </c>
       <c r="B254">
         <v>2022</v>
       </c>
       <c r="C254">
-        <v>3223200</v>
+        <v>3134020.96</v>
       </c>
       <c r="D254">
-        <v>3103200</v>
+        <v>0</v>
       </c>
       <c r="E254">
-        <v>0.9627699180938198</v>
+        <v>0</v>
       </c>
       <c r="F254">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações Para Criança e Adolescente</t>
+          <t>Fomento à Música</t>
         </is>
       </c>
       <c r="B255">
         <v>2022</v>
       </c>
       <c r="C255">
-        <v>3134020.96</v>
+        <v>3095934.07</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>3095934.07</v>
       </c>
       <c r="E255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F255">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Fomento à Música</t>
+          <t>Estudos, Planos e Projetos Ambientais</t>
         </is>
       </c>
       <c r="B256">
         <v>2022</v>
       </c>
       <c r="C256">
-        <v>3095934.07</v>
+        <v>3067345.41</v>
       </c>
       <c r="D256">
-        <v>3095934.07</v>
+        <v>1694402.61</v>
       </c>
       <c r="E256">
-        <v>1</v>
+        <v>0.5524003278130974</v>
       </c>
       <c r="F256">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Estudos, Planos e Projetos Ambientais</t>
+          <t>Políticas, Programas e Ações para Mulheres</t>
         </is>
       </c>
       <c r="B257">
         <v>2022</v>
       </c>
       <c r="C257">
-        <v>3067345.41</v>
+        <v>2987683.37</v>
       </c>
       <c r="D257">
-        <v>1694402.61</v>
+        <v>0</v>
       </c>
       <c r="E257">
-        <v>0.5524003278130974</v>
+        <v>0</v>
       </c>
       <c r="F257">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Mulheres</t>
+          <t>Centro Municipal para Pessoas com Transtorno do Espectro Autista</t>
         </is>
       </c>
       <c r="B258">
         <v>2022</v>
       </c>
       <c r="C258">
-        <v>2987683.37</v>
+        <v>2855949.71</v>
       </c>
       <c r="D258">
         <v>0</v>
@@ -6214,7 +6214,7 @@
         <v>1</v>
       </c>
       <c r="F266">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="267">
@@ -6352,14 +6352,14 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento da População de Rua</t>
+          <t>Políticas, Programas e Ações para Juventude</t>
         </is>
       </c>
       <c r="B273">
         <v>2022</v>
       </c>
       <c r="C273">
-        <v>2096889.41</v>
+        <v>2140694.18</v>
       </c>
       <c r="D273">
         <v>0</v>
@@ -6381,13 +6381,13 @@
         <v>2022</v>
       </c>
       <c r="C274">
-        <v>2082305.88</v>
+        <v>2106978.26</v>
       </c>
       <c r="D274">
-        <v>1960226.32</v>
+        <v>1983745.22</v>
       </c>
       <c r="E274">
-        <v>0.9413728976263565</v>
+        <v>0.9415119546606049</v>
       </c>
       <c r="F274">
         <v>32</v>
@@ -6396,212 +6396,212 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Mês do Hip Hop</t>
+          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento da População de Rua</t>
         </is>
       </c>
       <c r="B275">
         <v>2022</v>
       </c>
       <c r="C275">
-        <v>2052615</v>
+        <v>2096889.41</v>
       </c>
       <c r="D275">
-        <v>2052615</v>
+        <v>0</v>
       </c>
       <c r="E275">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F275">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Política Municipal de Desenvolvimento Econômico</t>
+          <t>Mês do Hip Hop</t>
         </is>
       </c>
       <c r="B276">
         <v>2022</v>
       </c>
       <c r="C276">
-        <v>1976288.32</v>
+        <v>2052615</v>
       </c>
       <c r="D276">
-        <v>1976288.32</v>
+        <v>2052615</v>
       </c>
       <c r="E276">
         <v>1</v>
       </c>
       <c r="F276">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Planetários Municipais</t>
+          <t>Política Municipal de Desenvolvimento Econômico</t>
         </is>
       </c>
       <c r="B277">
         <v>2022</v>
       </c>
       <c r="C277">
-        <v>1855106.33</v>
+        <v>1976288.32</v>
       </c>
       <c r="D277">
-        <v>1855106.33</v>
+        <v>1976288.32</v>
       </c>
       <c r="E277">
         <v>1</v>
       </c>
       <c r="F277">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Imigrantes</t>
+          <t>Manutenção e Operação dos Conselhos e Espaços Participativos Municipais</t>
         </is>
       </c>
       <c r="B278">
         <v>2022</v>
       </c>
       <c r="C278">
-        <v>1853241.87</v>
+        <v>1907450.27</v>
       </c>
       <c r="D278">
-        <v>1853241.87</v>
+        <v>963222.1</v>
       </c>
       <c r="E278">
-        <v>1</v>
+        <v>0.504978879475584</v>
       </c>
       <c r="F278">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Locação Social</t>
+          <t>Manutenção e Operação dos Planetários Municipais</t>
         </is>
       </c>
       <c r="B279">
         <v>2022</v>
       </c>
       <c r="C279">
-        <v>1831222.85</v>
+        <v>1855106.33</v>
       </c>
       <c r="D279">
-        <v>1831222.85</v>
+        <v>1855106.33</v>
       </c>
       <c r="E279">
         <v>1</v>
       </c>
       <c r="F279">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Programa Mãos e Mentes Paulistanas</t>
+          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Imigrantes</t>
         </is>
       </c>
       <c r="B280">
         <v>2022</v>
       </c>
       <c r="C280">
-        <v>1820029.36</v>
+        <v>1853241.87</v>
       </c>
       <c r="D280">
-        <v>0</v>
+        <v>1853241.87</v>
       </c>
       <c r="E280">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F280">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados à Promoção da Igualdade Racial</t>
+          <t>Locação Social</t>
         </is>
       </c>
       <c r="B281">
         <v>2022</v>
       </c>
       <c r="C281">
-        <v>1787614.07</v>
+        <v>1831222.85</v>
       </c>
       <c r="D281">
-        <v>1787614.07</v>
+        <v>1831222.85</v>
       </c>
       <c r="E281">
         <v>1</v>
       </c>
       <c r="F281">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Conselhos e Espaços Participativos Municipais</t>
+          <t>Programa Mãos e Mentes Paulistanas</t>
         </is>
       </c>
       <c r="B282">
         <v>2022</v>
       </c>
       <c r="C282">
-        <v>1768171.66</v>
+        <v>1820029.36</v>
       </c>
       <c r="D282">
-        <v>963229.24</v>
+        <v>0</v>
       </c>
       <c r="E282">
-        <v>0.5447600262974467</v>
+        <v>0</v>
       </c>
       <c r="F282">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Manutenção da Ouvidoria de Direitos Humanos</t>
+          <t>Manutenção e Operação de Equipamentos Públicos Voltados à Promoção da Igualdade Racial</t>
         </is>
       </c>
       <c r="B283">
         <v>2022</v>
       </c>
       <c r="C283">
-        <v>1758858.95</v>
+        <v>1787614.07</v>
       </c>
       <c r="D283">
-        <v>0</v>
+        <v>1787614.07</v>
       </c>
       <c r="E283">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F283">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Fiscalização, Monitoramento e Controle Ambiental</t>
+          <t>Manutenção da Ouvidoria de Direitos Humanos</t>
         </is>
       </c>
       <c r="B284">
         <v>2022</v>
       </c>
       <c r="C284">
-        <v>1750829.72</v>
+        <v>1758858.95</v>
       </c>
       <c r="D284">
         <v>0</v>
@@ -6616,39 +6616,39 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Execução de Serviços Médicos de Tratamento de Radioterapia</t>
+          <t>Fiscalização, Monitoramento e Controle Ambiental</t>
         </is>
       </c>
       <c r="B285">
         <v>2022</v>
       </c>
       <c r="C285">
-        <v>1690909.84</v>
+        <v>1750829.72</v>
       </c>
       <c r="D285">
-        <v>1690909.84</v>
+        <v>0</v>
       </c>
       <c r="E285">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F285">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação nas Áreas de Parada e Plataforma de Embarque de Faixa Exclusiva de Ônibus</t>
+          <t>Execução de Serviços Médicos de Tratamento de Radioterapia</t>
         </is>
       </c>
       <c r="B286">
         <v>2022</v>
       </c>
       <c r="C286">
-        <v>1604380.67</v>
+        <v>1690909.84</v>
       </c>
       <c r="D286">
-        <v>1604380.67</v>
+        <v>1690909.84</v>
       </c>
       <c r="E286">
         <v>1</v>
@@ -6660,80 +6660,80 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Reembolso ao Serviço Funerário</t>
+          <t>Ampliação, Reforma e Requalificação nas Áreas de Parada e Plataforma de Embarque de Faixa Exclusiva de Ônibus</t>
         </is>
       </c>
       <c r="B287">
         <v>2022</v>
       </c>
       <c r="C287">
-        <v>1582987.84</v>
+        <v>1604380.67</v>
       </c>
       <c r="D287">
-        <v>0</v>
+        <v>1604380.67</v>
       </c>
       <c r="E287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Melhoria de Bairros no âmbito da Subprefeitura da Capela do Socorro.</t>
+          <t>Reembolso ao Serviço Funerário</t>
         </is>
       </c>
       <c r="B288">
         <v>2022</v>
       </c>
       <c r="C288">
-        <v>1565851.89</v>
+        <v>1582987.84</v>
       </c>
       <c r="D288">
-        <v>1565851.89</v>
+        <v>0</v>
       </c>
       <c r="E288">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F288">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Bloqueios Judiciais</t>
+          <t>Melhoria de Bairros no âmbito da Subprefeitura da Capela do Socorro.</t>
         </is>
       </c>
       <c r="B289">
         <v>2022</v>
       </c>
       <c r="C289">
-        <v>1563984.67</v>
+        <v>1565851.89</v>
       </c>
       <c r="D289">
-        <v>0</v>
+        <v>1565851.89</v>
       </c>
       <c r="E289">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F289">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Centro Municipal para Pessoas com Transtorno do Espectro Autista</t>
+          <t>Bloqueios Judiciais</t>
         </is>
       </c>
       <c r="B290">
         <v>2022</v>
       </c>
       <c r="C290">
-        <v>1513770.31</v>
+        <v>1563984.67</v>
       </c>
       <c r="D290">
         <v>0</v>
@@ -6814,279 +6814,279 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Projeto de Intervenção Urbana - PIU</t>
+          <t>Ampliação, Reforma e Requalificação das Instalações para a Guarda Civil Metropolitana</t>
         </is>
       </c>
       <c r="B294">
         <v>2022</v>
       </c>
       <c r="C294">
-        <v>1418614.54</v>
+        <v>1419935.82</v>
       </c>
       <c r="D294">
-        <v>52127.69</v>
+        <v>1419935.82</v>
       </c>
       <c r="E294">
-        <v>0.03674549254232232</v>
+        <v>1</v>
       </c>
       <c r="F294">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Manutenção de Prédios Administrativos</t>
+          <t>Projeto de Intervenção Urbana - PIU</t>
         </is>
       </c>
       <c r="B295">
         <v>2022</v>
       </c>
       <c r="C295">
-        <v>1416770.13</v>
+        <v>1418614.54</v>
       </c>
       <c r="D295">
-        <v>846052.55</v>
+        <v>52127.69</v>
       </c>
       <c r="E295">
-        <v>0.5971699516279328</v>
+        <v>0.03674549254232232</v>
       </c>
       <c r="F295">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Restituição de Amortização Extraordinária e Liquidação Antecipada</t>
+          <t>Manutenção de Prédios Administrativos</t>
         </is>
       </c>
       <c r="B296">
         <v>2022</v>
       </c>
       <c r="C296">
-        <v>1394724.28</v>
+        <v>1416770.13</v>
       </c>
       <c r="D296">
-        <v>0</v>
+        <v>846052.55</v>
       </c>
       <c r="E296">
-        <v>0</v>
+        <v>0.5971699516279328</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Centros de Estudos de Línguas Paulistano - CELP</t>
+          <t>Restituição de Amortização Extraordinária e Liquidação Antecipada</t>
         </is>
       </c>
       <c r="B297">
         <v>2022</v>
       </c>
       <c r="C297">
-        <v>1373250.8</v>
+        <v>1394724.28</v>
       </c>
       <c r="D297">
-        <v>1373250.8</v>
+        <v>0</v>
       </c>
       <c r="E297">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F297">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Programa de Articulação Criativa</t>
+          <t>Manutenção e Operação de Cemitério</t>
         </is>
       </c>
       <c r="B298">
         <v>2022</v>
       </c>
       <c r="C298">
-        <v>1370710</v>
+        <v>1375121.32</v>
       </c>
       <c r="D298">
-        <v>850710</v>
+        <v>0</v>
       </c>
       <c r="E298">
-        <v>0.6206345616505314</v>
+        <v>0</v>
       </c>
       <c r="F298">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Equipamentos Públicos Voltados para Pessoa Idosa</t>
+          <t>Manutenção e Operação dos Centros de Estudos de Línguas Paulistano - CELP</t>
         </is>
       </c>
       <c r="B299">
         <v>2022</v>
       </c>
       <c r="C299">
-        <v>1357907.89</v>
+        <v>1373250.8</v>
       </c>
       <c r="D299">
-        <v>1357907.89</v>
+        <v>1373250.8</v>
       </c>
       <c r="E299">
         <v>1</v>
       </c>
       <c r="F299">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Desenvolvimento de Estudos, Projetos  e Instrumentos de Políticas Urbanas</t>
+          <t>Programa de Articulação Criativa</t>
         </is>
       </c>
       <c r="B300">
         <v>2022</v>
       </c>
       <c r="C300">
-        <v>1308867.34</v>
+        <v>1370710</v>
       </c>
       <c r="D300">
-        <v>0</v>
+        <v>850710</v>
       </c>
       <c r="E300">
-        <v>0</v>
+        <v>0.6206345616505314</v>
       </c>
       <c r="F300">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Equipes de Alto Desempenho com Representatividade em Competições Locais, Regionais, Nacionais e Mundiais</t>
+          <t>Manutenção e Operação dos Equipamentos Públicos Voltados para Pessoa Idosa</t>
         </is>
       </c>
       <c r="B301">
         <v>2022</v>
       </c>
       <c r="C301">
-        <v>1300000</v>
+        <v>1357907.89</v>
       </c>
       <c r="D301">
-        <v>0</v>
+        <v>1357907.89</v>
       </c>
       <c r="E301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F301">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Programa de Iniciação Artística para a Primeira Infância - PIAPI</t>
+          <t>Desenvolvimento de Estudos, Projetos  e Instrumentos de Políticas Urbanas</t>
         </is>
       </c>
       <c r="B302">
         <v>2022</v>
       </c>
       <c r="C302">
-        <v>1293600</v>
+        <v>1308867.34</v>
       </c>
       <c r="D302">
-        <v>1293600</v>
+        <v>0</v>
       </c>
       <c r="E302">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F302">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Manutenção de Modalidades Desportivas do Centro Olímpico de Treinamento e Pesquisa (COTP)</t>
+          <t>Equipes de Alto Desempenho com Representatividade em Competições Locais, Regionais, Nacionais e Mundiais</t>
         </is>
       </c>
       <c r="B303">
         <v>2022</v>
       </c>
       <c r="C303">
-        <v>1238246.2</v>
+        <v>1300000</v>
       </c>
       <c r="D303">
-        <v>1238246.2</v>
+        <v>0</v>
       </c>
       <c r="E303">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F303">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
+          <t>Programa de Iniciação Artística para a Primeira Infância - PIAPI</t>
+        </is>
+      </c>
+      <c r="B304">
+        <v>2022</v>
+      </c>
+      <c r="C304">
+        <v>1293600</v>
+      </c>
+      <c r="D304">
+        <v>1293600</v>
+      </c>
+      <c r="E304">
+        <v>1</v>
+      </c>
+      <c r="F304">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Manutenção de Modalidades Desportivas do Centro Olímpico de Treinamento e Pesquisa (COTP)</t>
+        </is>
+      </c>
+      <c r="B305">
+        <v>2022</v>
+      </c>
+      <c r="C305">
+        <v>1238246.2</v>
+      </c>
+      <c r="D305">
+        <v>1238246.2</v>
+      </c>
+      <c r="E305">
+        <v>1</v>
+      </c>
+      <c r="F305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
           <t xml:space="preserve">Operação e Manutenção do Portal da PMSP_x000D__x000D_
 </t>
         </is>
       </c>
-      <c r="B304">
-        <v>2022</v>
-      </c>
-      <c r="C304">
+      <c r="B306">
+        <v>2022</v>
+      </c>
+      <c r="C306">
         <v>1229726.23</v>
-      </c>
-      <c r="D304">
-        <v>0</v>
-      </c>
-      <c r="E304">
-        <v>0</v>
-      </c>
-      <c r="F304">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>Vivência Prática de Gestão de Documentos</t>
-        </is>
-      </c>
-      <c r="B305">
-        <v>2022</v>
-      </c>
-      <c r="C305">
-        <v>1087835.41</v>
-      </c>
-      <c r="D305">
-        <v>0</v>
-      </c>
-      <c r="E305">
-        <v>0</v>
-      </c>
-      <c r="F305">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>Difusão, Fomento e Pesquisas Aplicadas para a Gestão Participativa e Desenvolvimento Urbano</t>
-        </is>
-      </c>
-      <c r="B306">
-        <v>2022</v>
-      </c>
-      <c r="C306">
-        <v>1085620.82</v>
       </c>
       <c r="D306">
         <v>0</v>
@@ -7101,14 +7101,14 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Fomento às Comunidades do Samba</t>
+          <t>Vivência Prática de Gestão de Documentos</t>
         </is>
       </c>
       <c r="B307">
         <v>2022</v>
       </c>
       <c r="C307">
-        <v>1079100</v>
+        <v>1087835.41</v>
       </c>
       <c r="D307">
         <v>0</v>
@@ -7123,14 +7123,14 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Imigrantes e Promoção ao Trabalho Decente</t>
+          <t>Difusão, Fomento e Pesquisas Aplicadas para a Gestão Participativa e Desenvolvimento Urbano</t>
         </is>
       </c>
       <c r="B308">
         <v>2022</v>
       </c>
       <c r="C308">
-        <v>1063000</v>
+        <v>1085620.82</v>
       </c>
       <c r="D308">
         <v>0</v>
@@ -7145,14 +7145,14 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Atualização do Currículo da Rede Municipal de Ensino</t>
+          <t>Fomento às Comunidades do Samba</t>
         </is>
       </c>
       <c r="B309">
         <v>2022</v>
       </c>
       <c r="C309">
-        <v>1061320</v>
+        <v>1079100</v>
       </c>
       <c r="D309">
         <v>0</v>
@@ -7167,14 +7167,14 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Operação e Manutenção do VAI TEC</t>
+          <t>Políticas, Programas e Ações para Imigrantes e Promoção ao Trabalho Decente</t>
         </is>
       </c>
       <c r="B310">
         <v>2022</v>
       </c>
       <c r="C310">
-        <v>1032200</v>
+        <v>1063000</v>
       </c>
       <c r="D310">
         <v>0</v>
@@ -7189,102 +7189,102 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Ações e Atividades Culturais do Departamento do Patrimônio Histórico</t>
+          <t>Atualização do Currículo da Rede Municipal de Ensino</t>
         </is>
       </c>
       <c r="B311">
         <v>2022</v>
       </c>
       <c r="C311">
-        <v>1028498.3</v>
+        <v>1061320</v>
       </c>
       <c r="D311">
-        <v>1027898.3</v>
+        <v>0</v>
       </c>
       <c r="E311">
-        <v>0.9994166251903381</v>
+        <v>0</v>
       </c>
       <c r="F311">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Construção de Galeria, bem como Boca de Lobo para Captação de Água Pluvial, na Viela João Carlos Pereira, Altura no Número 13</t>
+          <t>Operação e Manutenção do VAI TEC</t>
         </is>
       </c>
       <c r="B312">
         <v>2022</v>
       </c>
       <c r="C312">
-        <v>954124.3200000001</v>
+        <v>1032200</v>
       </c>
       <c r="D312">
-        <v>954124.3200000001</v>
+        <v>0</v>
       </c>
       <c r="E312">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F312">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Prospecção de Problemas Públicos e Ideação de Alternativas para Inovação</t>
+          <t>Ações e Atividades Culturais do Departamento do Patrimônio Histórico</t>
         </is>
       </c>
       <c r="B313">
         <v>2022</v>
       </c>
       <c r="C313">
-        <v>952500</v>
+        <v>1028498.3</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>1027898.3</v>
       </c>
       <c r="E313">
-        <v>0</v>
+        <v>0.9994166251903381</v>
       </c>
       <c r="F313">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>FUMCAD - Multas Revertidas ao Fundo</t>
+          <t>Construção de Galeria, bem como Boca de Lobo para Captação de Água Pluvial, na Viela João Carlos Pereira, Altura no Número 13</t>
         </is>
       </c>
       <c r="B314">
         <v>2022</v>
       </c>
       <c r="C314">
-        <v>950785.38</v>
+        <v>954124.3200000001</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>954124.3200000001</v>
       </c>
       <c r="E314">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F314">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Tarifa de Arrecadação de Multas</t>
+          <t>Prospecção de Problemas Públicos e Ideação de Alternativas para Inovação</t>
         </is>
       </c>
       <c r="B315">
         <v>2022</v>
       </c>
       <c r="C315">
-        <v>932248.01</v>
+        <v>952500</v>
       </c>
       <c r="D315">
         <v>0</v>
@@ -7299,14 +7299,14 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>"Comemoração do ""Dia Municipal da Cultura Evangélica"" - 09 de Julho - Lei nº 14.232 de 07 de Novembro de 2006"</t>
+          <t>FUMCAD - Multas Revertidas ao Fundo</t>
         </is>
       </c>
       <c r="B316">
         <v>2022</v>
       </c>
       <c r="C316">
-        <v>885000</v>
+        <v>950785.38</v>
       </c>
       <c r="D316">
         <v>0</v>
@@ -7321,14 +7321,14 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Operação e Manutenção da Infraestrutura Turística</t>
+          <t>Tarifa de Arrecadação de Multas</t>
         </is>
       </c>
       <c r="B317">
         <v>2022</v>
       </c>
       <c r="C317">
-        <v>882697.9399999999</v>
+        <v>932248.01</v>
       </c>
       <c r="D317">
         <v>0</v>
@@ -7343,58 +7343,58 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Manutenção das Instalações da Guarda Civil Metropolitana</t>
+          <t>Implantação de Estrutura Turística no Triângulo Histórico</t>
         </is>
       </c>
       <c r="B318">
         <v>2022</v>
       </c>
       <c r="C318">
-        <v>871573.38</v>
+        <v>896239.02</v>
       </c>
       <c r="D318">
-        <v>871573.38</v>
+        <v>896239.02</v>
       </c>
       <c r="E318">
         <v>1</v>
       </c>
       <c r="F318">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Programa Aldeias</t>
+          <t>"Comemoração do ""Dia Municipal da Cultura Evangélica"" - 09 de Julho - Lei nº 14.232 de 07 de Novembro de 2006"</t>
         </is>
       </c>
       <c r="B319">
         <v>2022</v>
       </c>
       <c r="C319">
-        <v>860000</v>
+        <v>885000</v>
       </c>
       <c r="D319">
-        <v>860000</v>
+        <v>0</v>
       </c>
       <c r="E319">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F319">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Plano Municipal do Livro, Leitura, Literatura e Biblioteca (PMLLLB)</t>
+          <t>Operação e Manutenção da Infraestrutura Turística</t>
         </is>
       </c>
       <c r="B320">
         <v>2022</v>
       </c>
       <c r="C320">
-        <v>848400</v>
+        <v>882697.9399999999</v>
       </c>
       <c r="D320">
         <v>0</v>
@@ -7409,58 +7409,58 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Implantação e Construção de Ecopontos</t>
+          <t>Manutenção das Instalações da Guarda Civil Metropolitana</t>
         </is>
       </c>
       <c r="B321">
         <v>2022</v>
       </c>
       <c r="C321">
-        <v>840970.5699999999</v>
+        <v>871573.38</v>
       </c>
       <c r="D321">
-        <v>840970.5699999999</v>
+        <v>871573.38</v>
       </c>
       <c r="E321">
         <v>1</v>
       </c>
       <c r="F321">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Programação de Atividades e Eventos da Cultura Reggae</t>
+          <t>Programa Aldeias</t>
         </is>
       </c>
       <c r="B322">
         <v>2022</v>
       </c>
       <c r="C322">
-        <v>826294</v>
+        <v>860000</v>
       </c>
       <c r="D322">
-        <v>826294</v>
+        <v>860000</v>
       </c>
       <c r="E322">
         <v>1</v>
       </c>
       <c r="F322">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Acompanhamento das Aprendizagens e Permanência Escolar</t>
+          <t>Plano Municipal do Livro, Leitura, Literatura e Biblioteca (PMLLLB)</t>
         </is>
       </c>
       <c r="B323">
         <v>2022</v>
       </c>
       <c r="C323">
-        <v>823896.08</v>
+        <v>848400</v>
       </c>
       <c r="D323">
         <v>0</v>
@@ -7475,17 +7475,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Unidades de Conservação</t>
+          <t>Implantação e Construção de Ecopontos</t>
         </is>
       </c>
       <c r="B324">
         <v>2022</v>
       </c>
       <c r="C324">
-        <v>815593.0699999999</v>
+        <v>840970.5699999999</v>
       </c>
       <c r="D324">
-        <v>815593.0699999999</v>
+        <v>840970.5699999999</v>
       </c>
       <c r="E324">
         <v>1</v>
@@ -7497,124 +7497,124 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Fomento e Difusão do Forró</t>
+          <t>Programação de Atividades e Eventos da Cultura Reggae</t>
         </is>
       </c>
       <c r="B325">
         <v>2022</v>
       </c>
       <c r="C325">
-        <v>808367.1899999999</v>
+        <v>836174</v>
       </c>
       <c r="D325">
-        <v>796367.1899999999</v>
+        <v>836174</v>
       </c>
       <c r="E325">
-        <v>0.9851552609402665</v>
+        <v>1</v>
       </c>
       <c r="F325">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Centro Municipal de Capacitação e Treinamento (CMCT)</t>
+          <t>Acompanhamento das Aprendizagens e Permanência Escolar</t>
         </is>
       </c>
       <c r="B326">
         <v>2022</v>
       </c>
       <c r="C326">
-        <v>795573.16</v>
+        <v>823896.08</v>
       </c>
       <c r="D326">
-        <v>795573.16</v>
+        <v>0</v>
       </c>
       <c r="E326">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F326">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Centro Público de Economia Solidária e Direitos Humanos</t>
+          <t>Fomento e Difusão do Forró</t>
         </is>
       </c>
       <c r="B327">
         <v>2022</v>
       </c>
       <c r="C327">
-        <v>791828.37</v>
+        <v>820367.1899999999</v>
       </c>
       <c r="D327">
-        <v>0</v>
+        <v>808367.1899999999</v>
       </c>
       <c r="E327">
-        <v>0</v>
+        <v>0.9853724037890886</v>
       </c>
       <c r="F327">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Publicação de Editais e Outras Publicações Legais e de Interesse do Município</t>
+          <t>Ampliação, Reforma e Requalificação de Unidades de Conservação</t>
         </is>
       </c>
       <c r="B328">
         <v>2022</v>
       </c>
       <c r="C328">
-        <v>763559.38</v>
+        <v>815593.0699999999</v>
       </c>
       <c r="D328">
-        <v>0</v>
+        <v>815593.0699999999</v>
       </c>
       <c r="E328">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F328">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Implantação de Estrutura Turística no Triângulo Histórico</t>
+          <t>Manutenção e Operação de Unidades Educacionais - Centro Municipal de Capacitação e Treinamento (CMCT)</t>
         </is>
       </c>
       <c r="B329">
         <v>2022</v>
       </c>
       <c r="C329">
-        <v>762391.5600000001</v>
+        <v>798678.16</v>
       </c>
       <c r="D329">
-        <v>762391.5600000001</v>
+        <v>798678.16</v>
       </c>
       <c r="E329">
         <v>1</v>
       </c>
       <c r="F329">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Promoção à Saúde do Servidor Municipal</t>
+          <t>Manutenção e Operação do Centro Público de Economia Solidária e Direitos Humanos</t>
         </is>
       </c>
       <c r="B330">
         <v>2022</v>
       </c>
       <c r="C330">
-        <v>725838.8500000001</v>
+        <v>791828.37</v>
       </c>
       <c r="D330">
         <v>0</v>
@@ -7629,14 +7629,14 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Construção e Implantação de Equipamentos de Atenção Básica e Especialidades</t>
+          <t>Publicação de Editais e Outras Publicações Legais e de Interesse do Município</t>
         </is>
       </c>
       <c r="B331">
         <v>2022</v>
       </c>
       <c r="C331">
-        <v>707876.46</v>
+        <v>763559.38</v>
       </c>
       <c r="D331">
         <v>0</v>
@@ -7651,36 +7651,36 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Centro de Referência da Dança</t>
+          <t>Promoção à Saúde do Servidor Municipal</t>
         </is>
       </c>
       <c r="B332">
         <v>2022</v>
       </c>
       <c r="C332">
-        <v>686500</v>
+        <v>725838.8500000001</v>
       </c>
       <c r="D332">
-        <v>686500</v>
+        <v>0</v>
       </c>
       <c r="E332">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F332">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Bolsa Atleta</t>
+          <t>Construção e Implantação de Equipamentos de Atenção Básica e Especialidades</t>
         </is>
       </c>
       <c r="B333">
         <v>2022</v>
       </c>
       <c r="C333">
-        <v>673035.5599999999</v>
+        <v>707876.46</v>
       </c>
       <c r="D333">
         <v>0</v>
@@ -7695,108 +7695,108 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Centro de Memória do Circo</t>
+          <t>Centro de Referência da Dança</t>
         </is>
       </c>
       <c r="B334">
         <v>2022</v>
       </c>
       <c r="C334">
-        <v>598000</v>
+        <v>686500</v>
       </c>
       <c r="D334">
-        <v>598000</v>
+        <v>686500</v>
       </c>
       <c r="E334">
         <v>1</v>
       </c>
       <c r="F334">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Patrulha Agroecológica Mecanizada</t>
+          <t>Bolsa Atleta</t>
         </is>
       </c>
       <c r="B335">
         <v>2022</v>
       </c>
       <c r="C335">
-        <v>577288.25</v>
+        <v>673035.5599999999</v>
       </c>
       <c r="D335">
-        <v>109459.85</v>
+        <v>0</v>
       </c>
       <c r="E335">
-        <v>0.1896103896103896</v>
+        <v>0</v>
       </c>
       <c r="F335">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Mercado Municipal</t>
+          <t>Manutenção e Operação da Central de Interpretação de Libras, Intérpretes e Guias-Intérpretes</t>
         </is>
       </c>
       <c r="B336">
         <v>2022</v>
       </c>
       <c r="C336">
-        <v>570655.54</v>
+        <v>644755.14</v>
       </c>
       <c r="D336">
-        <v>109830.58</v>
+        <v>0</v>
       </c>
       <c r="E336">
-        <v>0.1924638811006724</v>
+        <v>0</v>
       </c>
       <c r="F336">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Pesquisa de Satisfação do Cidadão em Relação aos Serviços, Políticas e Programas</t>
+          <t>Centro de Memória do Circo</t>
         </is>
       </c>
       <c r="B337">
         <v>2022</v>
       </c>
       <c r="C337">
-        <v>558000</v>
+        <v>598000</v>
       </c>
       <c r="D337">
-        <v>0</v>
+        <v>598000</v>
       </c>
       <c r="E337">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F337">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Reforma e Acessibilidade em Passeios Públicos</t>
+          <t>Manutenção e Operação da Patrulha Agroecológica Mecanizada</t>
         </is>
       </c>
       <c r="B338">
         <v>2022</v>
       </c>
       <c r="C338">
-        <v>517355.29</v>
+        <v>577288.25</v>
       </c>
       <c r="D338">
-        <v>517355.29</v>
+        <v>109459.85</v>
       </c>
       <c r="E338">
-        <v>1</v>
+        <v>0.1896103896103896</v>
       </c>
       <c r="F338">
         <v>1</v>
@@ -7805,20 +7805,20 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Administração do Autódromo de Interlagos</t>
+          <t>Ampliação, Reforma e Requalificação de Mercado Municipal</t>
         </is>
       </c>
       <c r="B339">
         <v>2022</v>
       </c>
       <c r="C339">
-        <v>513389.41</v>
+        <v>570655.54</v>
       </c>
       <c r="D339">
-        <v>513389.41</v>
+        <v>109830.58</v>
       </c>
       <c r="E339">
-        <v>1</v>
+        <v>0.1924638811006724</v>
       </c>
       <c r="F339">
         <v>1</v>
@@ -7827,14 +7827,14 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Espaços Lúdicos e Educativos</t>
+          <t>Pesquisa de Satisfação do Cidadão em Relação aos Serviços, Políticas e Programas</t>
         </is>
       </c>
       <c r="B340">
         <v>2022</v>
       </c>
       <c r="C340">
-        <v>470715.01</v>
+        <v>558000</v>
       </c>
       <c r="D340">
         <v>0</v>
@@ -7849,146 +7849,146 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Território Hip Hop (Vocacional Hip Hop)</t>
+          <t>Reforma e Acessibilidade em Passeios Públicos</t>
         </is>
       </c>
       <c r="B341">
         <v>2022</v>
       </c>
       <c r="C341">
-        <v>426000</v>
+        <v>517355.29</v>
       </c>
       <c r="D341">
-        <v>426000</v>
+        <v>517355.29</v>
       </c>
       <c r="E341">
         <v>1</v>
       </c>
       <c r="F341">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Gestão do Patrimônio Imobiliário Municipal</t>
+          <t>Manutenção e Operação de Crematório</t>
         </is>
       </c>
       <c r="B342">
         <v>2022</v>
       </c>
       <c r="C342">
-        <v>389355.92</v>
+        <v>516830.14</v>
       </c>
       <c r="D342">
-        <v>389355.92</v>
+        <v>0</v>
       </c>
       <c r="E342">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F342">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Fomento e Apoio ao Cooperativismo</t>
+          <t>Administração do Autódromo de Interlagos</t>
         </is>
       </c>
       <c r="B343">
         <v>2022</v>
       </c>
       <c r="C343">
-        <v>386520</v>
+        <v>513389.41</v>
       </c>
       <c r="D343">
-        <v>0</v>
+        <v>513389.41</v>
       </c>
       <c r="E343">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F343">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Revitalização e Manutenção - Subprefeitura de Capela do Socorro</t>
+          <t>Manutenção e Operação de Espaços Lúdicos e Educativos</t>
         </is>
       </c>
       <c r="B344">
         <v>2022</v>
       </c>
       <c r="C344">
-        <v>385808.63</v>
+        <v>470715.01</v>
       </c>
       <c r="D344">
-        <v>385808.63</v>
+        <v>0</v>
       </c>
       <c r="E344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F344">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos da Assistência Social</t>
+          <t>Território Hip Hop (Vocacional Hip Hop)</t>
         </is>
       </c>
       <c r="B345">
         <v>2022</v>
       </c>
       <c r="C345">
-        <v>355634.76</v>
+        <v>426000</v>
       </c>
       <c r="D345">
-        <v>0</v>
+        <v>426000</v>
       </c>
       <c r="E345">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F345">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Implantação de Pontos e Pontões de Cultura - Cultura Viva</t>
+          <t>Gestão do Patrimônio Imobiliário Municipal</t>
         </is>
       </c>
       <c r="B346">
         <v>2022</v>
       </c>
       <c r="C346">
-        <v>327249.27</v>
+        <v>387457.99</v>
       </c>
       <c r="D346">
-        <v>0</v>
+        <v>387457.99</v>
       </c>
       <c r="E346">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F346">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos de Saúde Animal</t>
+          <t>Fomento e Apoio ao Cooperativismo</t>
         </is>
       </c>
       <c r="B347">
         <v>2022</v>
       </c>
       <c r="C347">
-        <v>316555.85</v>
+        <v>386520</v>
       </c>
       <c r="D347">
         <v>0</v>
@@ -8003,80 +8003,80 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Acordos Judiciais ou Administrativos</t>
+          <t>Revitalização e Manutenção - Subprefeitura de Capela do Socorro</t>
         </is>
       </c>
       <c r="B348">
         <v>2022</v>
       </c>
       <c r="C348">
-        <v>301660.14</v>
+        <v>385808.63</v>
       </c>
       <c r="D348">
-        <v>0</v>
+        <v>385808.63</v>
       </c>
       <c r="E348">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F348">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Serviço de Moto Verificação</t>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos da Assistência Social</t>
         </is>
       </c>
       <c r="B349">
         <v>2022</v>
       </c>
       <c r="C349">
-        <v>293908.42</v>
+        <v>355634.76</v>
       </c>
       <c r="D349">
-        <v>293908.42</v>
+        <v>0</v>
       </c>
       <c r="E349">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F349">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Projetos Sociais Diversos</t>
+          <t>Construção de Escolas Municipais de Ensino Fundamental (EMEF)</t>
         </is>
       </c>
       <c r="B350">
         <v>2022</v>
       </c>
       <c r="C350">
-        <v>276542.6</v>
+        <v>328154.12</v>
       </c>
       <c r="D350">
-        <v>276542.6</v>
+        <v>328154.12</v>
       </c>
       <c r="E350">
         <v>1</v>
       </c>
       <c r="F350">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Expansão e Aperfeiçoamento das Atividades do TCM</t>
+          <t>Implantação de Pontos e Pontões de Cultura - Cultura Viva</t>
         </is>
       </c>
       <c r="B351">
         <v>2022</v>
       </c>
       <c r="C351">
-        <v>250927.24</v>
+        <v>327249.27</v>
       </c>
       <c r="D351">
         <v>0</v>
@@ -8091,14 +8091,14 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Central de Interpretação de Libras, Intérpretes e Guias-Intérpretes</t>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos de Saúde Animal</t>
         </is>
       </c>
       <c r="B352">
         <v>2022</v>
       </c>
       <c r="C352">
-        <v>238469.87</v>
+        <v>316555.85</v>
       </c>
       <c r="D352">
         <v>0</v>
@@ -8113,146 +8113,146 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Construção de Terminais de Ônibus</t>
+          <t>Acordos Judiciais ou Administrativos</t>
         </is>
       </c>
       <c r="B353">
         <v>2022</v>
       </c>
       <c r="C353">
-        <v>233901.36</v>
+        <v>301660.14</v>
       </c>
       <c r="D353">
-        <v>233901.36</v>
+        <v>0</v>
       </c>
       <c r="E353">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F353">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Escola do Parlamento</t>
+          <t>Manutenção e Operação do Serviço de Moto Verificação</t>
         </is>
       </c>
       <c r="B354">
         <v>2022</v>
       </c>
       <c r="C354">
-        <v>230978.68</v>
+        <v>293908.42</v>
       </c>
       <c r="D354">
-        <v>0</v>
+        <v>293908.42</v>
       </c>
       <c r="E354">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F354">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Ações de Audiovisual</t>
+          <t>Projetos Sociais Diversos</t>
         </is>
       </c>
       <c r="B355">
         <v>2022</v>
       </c>
       <c r="C355">
-        <v>218500</v>
+        <v>276542.6</v>
       </c>
       <c r="D355">
-        <v>0</v>
+        <v>276542.6</v>
       </c>
       <c r="E355">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F355">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Implantação da Casa de Cultura Cidade Ademar</t>
+          <t>Expansão e Aperfeiçoamento das Atividades do TCM</t>
         </is>
       </c>
       <c r="B356">
         <v>2022</v>
       </c>
       <c r="C356">
-        <v>216731.53</v>
+        <v>250927.24</v>
       </c>
       <c r="D356">
-        <v>216731.53</v>
+        <v>0</v>
       </c>
       <c r="E356">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F356">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Expansão e Aperfeiçoamento das Atividades da CMSP</t>
+          <t>Construção de Terminais de Ônibus</t>
         </is>
       </c>
       <c r="B357">
         <v>2022</v>
       </c>
       <c r="C357">
-        <v>209505.91</v>
+        <v>233901.36</v>
       </c>
       <c r="D357">
-        <v>0</v>
+        <v>233901.36</v>
       </c>
       <c r="E357">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F357">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação das Instalações para a Guarda Civil Metropolitana</t>
+          <t>Escola do Parlamento</t>
         </is>
       </c>
       <c r="B358">
         <v>2022</v>
       </c>
       <c r="C358">
-        <v>204856.51</v>
+        <v>230978.68</v>
       </c>
       <c r="D358">
-        <v>204856.51</v>
+        <v>0</v>
       </c>
       <c r="E358">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F358">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>PMLLLB - Festas Literárias</t>
+          <t>Ações de Audiovisual</t>
         </is>
       </c>
       <c r="B359">
         <v>2022</v>
       </c>
       <c r="C359">
-        <v>200000</v>
+        <v>218500</v>
       </c>
       <c r="D359">
         <v>0</v>
@@ -8267,17 +8267,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Reforma da Escadaria na Viela Inominada, Localizada na Rua Rua José Ferreira Dantas, Nº 11, Jardim Boa Vista.</t>
+          <t>Implantação da Casa de Cultura Cidade Ademar</t>
         </is>
       </c>
       <c r="B360">
         <v>2022</v>
       </c>
       <c r="C360">
-        <v>196871.4</v>
+        <v>216731.53</v>
       </c>
       <c r="D360">
-        <v>196871.4</v>
+        <v>216731.53</v>
       </c>
       <c r="E360">
         <v>1</v>
@@ -8289,14 +8289,14 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Unidades Habitacionais</t>
+          <t>Expansão e Aperfeiçoamento das Atividades da CMSP</t>
         </is>
       </c>
       <c r="B361">
         <v>2022</v>
       </c>
       <c r="C361">
-        <v>189455.55</v>
+        <v>209505.91</v>
       </c>
       <c r="D361">
         <v>0</v>
@@ -8311,14 +8311,14 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Unidade de Vigilância em Saúde</t>
+          <t>PMLLLB - Festas Literárias</t>
         </is>
       </c>
       <c r="B362">
         <v>2022</v>
       </c>
       <c r="C362">
-        <v>169996.21</v>
+        <v>200000</v>
       </c>
       <c r="D362">
         <v>0</v>
@@ -8333,36 +8333,36 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Construção de Escolas Municipais de Ensino Fundamental (EMEF)</t>
+          <t>Reforma da Escadaria na Viela Inominada, Localizada na Rua Rua José Ferreira Dantas, Nº 11, Jardim Boa Vista.</t>
         </is>
       </c>
       <c r="B363">
         <v>2022</v>
       </c>
       <c r="C363">
-        <v>169554.61</v>
+        <v>196871.4</v>
       </c>
       <c r="D363">
-        <v>169554.61</v>
+        <v>196871.4</v>
       </c>
       <c r="E363">
         <v>1</v>
       </c>
       <c r="F363">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Execução de Projetos Visando o Combate das Desigualdades Raciais na Saúde</t>
+          <t>Ampliação, Reforma e Requalificação de Unidades Habitacionais</t>
         </is>
       </c>
       <c r="B364">
         <v>2022</v>
       </c>
       <c r="C364">
-        <v>150000</v>
+        <v>189455.55</v>
       </c>
       <c r="D364">
         <v>0</v>
@@ -8377,58 +8377,58 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Manutenção e Operação no Serviço de Guinchamento</t>
+          <t>Ampliação, Reforma e Requalificação de Unidade de Vigilância em Saúde</t>
         </is>
       </c>
       <c r="B365">
         <v>2022</v>
       </c>
       <c r="C365">
-        <v>147832.78</v>
+        <v>169996.21</v>
       </c>
       <c r="D365">
-        <v>147832.78</v>
+        <v>0</v>
       </c>
       <c r="E365">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F365">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Reforma da Quadra da Praça Gilberto Reis Possani, Parque São Rafael</t>
+          <t>Manutenção e Operação de Velório</t>
         </is>
       </c>
       <c r="B366">
         <v>2022</v>
       </c>
       <c r="C366">
-        <v>133159.64</v>
+        <v>168821.77</v>
       </c>
       <c r="D366">
-        <v>133159.64</v>
+        <v>0</v>
       </c>
       <c r="E366">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F366">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Ações do Programa Agentes de Governo Aberto</t>
+          <t>Execução de Projetos Visando o Combate das Desigualdades Raciais na Saúde</t>
         </is>
       </c>
       <c r="B367">
         <v>2022</v>
       </c>
       <c r="C367">
-        <v>132388.19</v>
+        <v>150000</v>
       </c>
       <c r="D367">
         <v>0</v>
@@ -8443,124 +8443,124 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos do Patrimônio Histórico</t>
+          <t>Manutenção e Operação no Serviço de Guinchamento</t>
         </is>
       </c>
       <c r="B368">
         <v>2022</v>
       </c>
       <c r="C368">
-        <v>111693.86</v>
+        <v>147832.78</v>
       </c>
       <c r="D368">
-        <v>109472.2</v>
+        <v>147832.78</v>
       </c>
       <c r="E368">
-        <v>0.9801093811244413</v>
+        <v>1</v>
       </c>
       <c r="F368">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Promoção da Transparência, do Acesso à Informação e do Controle Social</t>
+          <t>Reforma da Quadra da Praça Gilberto Reis Possani, Parque São Rafael</t>
         </is>
       </c>
       <c r="B369">
         <v>2022</v>
       </c>
       <c r="C369">
-        <v>103413.52</v>
+        <v>133159.64</v>
       </c>
       <c r="D369">
-        <v>0</v>
+        <v>133159.64</v>
       </c>
       <c r="E369">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F369">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Incentivo à Economia Popular e Solidária</t>
+          <t>Ações do Programa Agentes de Governo Aberto</t>
         </is>
       </c>
       <c r="B370">
         <v>2022</v>
       </c>
       <c r="C370">
-        <v>99983.39999999999</v>
+        <v>132388.19</v>
       </c>
       <c r="D370">
-        <v>99983.39999999999</v>
+        <v>0</v>
       </c>
       <c r="E370">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F370">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Manutenção e Operação das Praças Digitais</t>
+          <t>Transportes Fúnebres</t>
         </is>
       </c>
       <c r="B371">
         <v>2022</v>
       </c>
       <c r="C371">
-        <v>98814.97</v>
+        <v>125469.51</v>
       </c>
       <c r="D371">
-        <v>66883.29000000001</v>
+        <v>0</v>
       </c>
       <c r="E371">
-        <v>0.6768538208330176</v>
+        <v>0</v>
       </c>
       <c r="F371">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Edificação do Tribunal de Contas do Município</t>
+          <t>Manutenção e Operação de Equipamentos do Patrimônio Histórico</t>
         </is>
       </c>
       <c r="B372">
         <v>2022</v>
       </c>
       <c r="C372">
-        <v>94500</v>
+        <v>111693.86</v>
       </c>
       <c r="D372">
-        <v>94500</v>
+        <v>109472.2</v>
       </c>
       <c r="E372">
-        <v>1</v>
+        <v>0.9801093811244413</v>
       </c>
       <c r="F372">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Restituição de Receitas Descontinuadas</t>
+          <t>Promoção da Transparência, do Acesso à Informação e do Controle Social</t>
         </is>
       </c>
       <c r="B373">
         <v>2022</v>
       </c>
       <c r="C373">
-        <v>92905.70000000001</v>
+        <v>103413.52</v>
       </c>
       <c r="D373">
         <v>0</v>
@@ -8575,17 +8575,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Conservação e Valorização de Acervos da Biblioteca Mário de Andrade</t>
+          <t>Incentivo à Economia Popular e Solidária</t>
         </is>
       </c>
       <c r="B374">
         <v>2022</v>
       </c>
       <c r="C374">
-        <v>76969.92</v>
+        <v>99983.39999999999</v>
       </c>
       <c r="D374">
-        <v>76969.92</v>
+        <v>99983.39999999999</v>
       </c>
       <c r="E374">
         <v>1</v>
@@ -8597,58 +8597,58 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Manutenção, Programas e Suporte da Coordenadoria de Defesa do Consumidor</t>
+          <t>Manutenção e Operação das Praças Digitais</t>
         </is>
       </c>
       <c r="B375">
         <v>2022</v>
       </c>
       <c r="C375">
-        <v>68994.77</v>
+        <v>98814.97</v>
       </c>
       <c r="D375">
-        <v>0</v>
+        <v>66883.29000000001</v>
       </c>
       <c r="E375">
-        <v>0</v>
+        <v>0.6768538208330176</v>
       </c>
       <c r="F375">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Povos Indígenas</t>
+          <t>Ampliação, Reforma e Requalificação de Edificação do Tribunal de Contas do Município</t>
         </is>
       </c>
       <c r="B376">
         <v>2022</v>
       </c>
       <c r="C376">
-        <v>67975</v>
+        <v>94500</v>
       </c>
       <c r="D376">
-        <v>67975</v>
+        <v>94500</v>
       </c>
       <c r="E376">
         <v>1</v>
       </c>
       <c r="F376">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Implementação do Selo Municipal de Direitos Humanos e Diversidade</t>
+          <t>Restituição de Receitas Descontinuadas</t>
         </is>
       </c>
       <c r="B377">
         <v>2022</v>
       </c>
       <c r="C377">
-        <v>48075</v>
+        <v>92905.70000000001</v>
       </c>
       <c r="D377">
         <v>0</v>
@@ -8663,14 +8663,14 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Programa de Promoção da Imagem de São Paulo no Exterior</t>
+          <t>Comercialização de Artigos do Serviço Funerário</t>
         </is>
       </c>
       <c r="B378">
         <v>2022</v>
       </c>
       <c r="C378">
-        <v>43125.23</v>
+        <v>91555.8</v>
       </c>
       <c r="D378">
         <v>0</v>
@@ -8685,17 +8685,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Programa de Gestão Cultural Comunitária de Espaços</t>
+          <t>Conservação e Valorização de Acervos da Biblioteca Mário de Andrade</t>
         </is>
       </c>
       <c r="B379">
         <v>2022</v>
       </c>
       <c r="C379">
-        <v>40000</v>
+        <v>76969.92</v>
       </c>
       <c r="D379">
-        <v>40000</v>
+        <v>76969.92</v>
       </c>
       <c r="E379">
         <v>1</v>
@@ -8707,14 +8707,14 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Outras Dívidas</t>
+          <t>Manutenção, Programas e Suporte da Coordenadoria de Defesa do Consumidor</t>
         </is>
       </c>
       <c r="B380">
         <v>2022</v>
       </c>
       <c r="C380">
-        <v>39434.21</v>
+        <v>68994.77</v>
       </c>
       <c r="D380">
         <v>0</v>
@@ -8729,105 +8729,105 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Benefícios Eventuais</t>
+          <t>Políticas, Programas e Ações para Povos Indígenas</t>
         </is>
       </c>
       <c r="B381">
         <v>2022</v>
       </c>
       <c r="C381">
-        <v>38725.02</v>
+        <v>67975</v>
       </c>
       <c r="D381">
-        <v>38725.02</v>
+        <v>67975</v>
       </c>
       <c r="E381">
         <v>1</v>
       </c>
       <c r="F381">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Supervisão Geral das Juntas do Serviço Militar</t>
+          <t>Implementação do Selo Municipal de Direitos Humanos e Diversidade</t>
         </is>
       </c>
       <c r="B382">
         <v>2022</v>
       </c>
       <c r="C382">
-        <v>36542.4</v>
+        <v>48075</v>
       </c>
       <c r="D382">
-        <v>32462.82</v>
+        <v>0</v>
       </c>
       <c r="E382">
-        <v>0.8883603704190201</v>
+        <v>0</v>
       </c>
       <c r="F382">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Pessoas Desaparecidas</t>
+          <t>Manutenção e Operação da Supervisão Geral das Juntas do Serviço Militar</t>
         </is>
       </c>
       <c r="B383">
         <v>2022</v>
       </c>
       <c r="C383">
-        <v>29652.01</v>
+        <v>47307.04</v>
       </c>
       <c r="D383">
-        <v>0</v>
+        <v>42581.86</v>
       </c>
       <c r="E383">
-        <v>0</v>
+        <v>0.9001167690897591</v>
       </c>
       <c r="F383">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Conservação e Valorização de Acervos do Departamento dos Museus Municipais</t>
+          <t>Programa de Promoção da Imagem de São Paulo no Exterior</t>
         </is>
       </c>
       <c r="B384">
         <v>2022</v>
       </c>
       <c r="C384">
-        <v>29085</v>
+        <v>43125.23</v>
       </c>
       <c r="D384">
-        <v>29085</v>
+        <v>0</v>
       </c>
       <c r="E384">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F384">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Construção e Implantação de Unidades de Conservação</t>
+          <t>Programa de Gestão Cultural Comunitária de Espaços</t>
         </is>
       </c>
       <c r="B385">
         <v>2022</v>
       </c>
       <c r="C385">
-        <v>23245.36</v>
+        <v>40000</v>
       </c>
       <c r="D385">
-        <v>23245.36</v>
+        <v>40000</v>
       </c>
       <c r="E385">
         <v>1</v>
@@ -8839,14 +8839,14 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Promoção da Igualdade Racial</t>
+          <t>Outras Dívidas</t>
         </is>
       </c>
       <c r="B386">
         <v>2022</v>
       </c>
       <c r="C386">
-        <v>18650</v>
+        <v>39434.21</v>
       </c>
       <c r="D386">
         <v>0</v>
@@ -8861,36 +8861,36 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Ações e Atividades Culturais do Arquivo Histórico Municipal</t>
+          <t>Benefícios Eventuais</t>
         </is>
       </c>
       <c r="B387">
         <v>2022</v>
       </c>
       <c r="C387">
-        <v>17360</v>
+        <v>38725.02</v>
       </c>
       <c r="D387">
-        <v>17360</v>
+        <v>38725.02</v>
       </c>
       <c r="E387">
         <v>1</v>
       </c>
       <c r="F387">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Pessoa Idosa</t>
+          <t>Políticas, Programas e Ações para Pessoas Desaparecidas</t>
         </is>
       </c>
       <c r="B388">
         <v>2022</v>
       </c>
       <c r="C388">
-        <v>14500</v>
+        <v>29652.01</v>
       </c>
       <c r="D388">
         <v>0</v>
@@ -8905,17 +8905,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Implantação de Transporte Público Hidroviário</t>
+          <t>Conservação e Valorização de Acervos do Departamento dos Museus Municipais</t>
         </is>
       </c>
       <c r="B389">
         <v>2022</v>
       </c>
       <c r="C389">
-        <v>9500</v>
+        <v>29085</v>
       </c>
       <c r="D389">
-        <v>9500</v>
+        <v>29085</v>
       </c>
       <c r="E389">
         <v>1</v>
@@ -8927,123 +8927,129 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Herbário Municipal</t>
+          <t>Construção e Implantação de Unidades de Conservação</t>
         </is>
       </c>
       <c r="B390">
         <v>2022</v>
       </c>
       <c r="C390">
-        <v>9284</v>
+        <v>23245.36</v>
       </c>
       <c r="D390">
-        <v>0</v>
+        <v>23245.36</v>
       </c>
       <c r="E390">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F390">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Comunicação e Orientação na Valorização e Cuidado na Primeira Infância</t>
+          <t>Políticas, Programas e Ações para Promoção da Igualdade Racial</t>
         </is>
       </c>
       <c r="B391">
         <v>2022</v>
       </c>
       <c r="C391">
-        <v>9000</v>
+        <v>18650</v>
       </c>
       <c r="D391">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="E391">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F391">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para a Promoção do Direito à Memória e à Verdade</t>
+          <t>Ações e Atividades Culturais do Arquivo Histórico Municipal</t>
         </is>
       </c>
       <c r="B392">
         <v>2022</v>
       </c>
       <c r="C392">
-        <v>8640</v>
+        <v>17360</v>
       </c>
       <c r="D392">
-        <v>0</v>
+        <v>17360</v>
       </c>
       <c r="E392">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F392">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da UniCEU</t>
+          <t>Políticas, Programas e Ações para Pessoa Idosa</t>
         </is>
       </c>
       <c r="B393">
         <v>2022</v>
       </c>
       <c r="C393">
-        <v>4786.95</v>
+        <v>14500</v>
       </c>
       <c r="D393">
-        <v>4786.95</v>
+        <v>0</v>
       </c>
       <c r="E393">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F393">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Edificação da Câmara Municipal de São Paulo</t>
+          <t>Implantação de Transporte Público Hidroviário</t>
         </is>
       </c>
       <c r="B394">
         <v>2022</v>
       </c>
       <c r="C394">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="D394">
-        <v>0</v>
+        <v>9500</v>
+      </c>
+      <c r="E394">
+        <v>1</v>
       </c>
       <c r="F394">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Apoio e Suporte Técnico para o Desenvolvimento de Ações Pertinentes à Fiscalização e Escrituração de Certificados de Potencial Adicional de Construção - CEPACs</t>
+          <t>Manutenção e Operação do Herbário Municipal</t>
         </is>
       </c>
       <c r="B395">
         <v>2022</v>
       </c>
       <c r="C395">
-        <v>0</v>
+        <v>9284</v>
       </c>
       <c r="D395">
+        <v>0</v>
+      </c>
+      <c r="E395">
         <v>0</v>
       </c>
       <c r="F395">
@@ -9053,35 +9059,41 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Apoio às Ações Municipais de Turismo</t>
+          <t>Comunicação e Orientação na Valorização e Cuidado na Primeira Infância</t>
         </is>
       </c>
       <c r="B396">
         <v>2022</v>
       </c>
       <c r="C396">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="D396">
-        <v>0</v>
+        <v>9000</v>
+      </c>
+      <c r="E396">
+        <v>1</v>
       </c>
       <c r="F396">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Aquisição e Construção de Prédios Administrativos</t>
+          <t>Políticas, Programas e Ações para a Promoção do Direito à Memória e à Verdade</t>
         </is>
       </c>
       <c r="B397">
         <v>2022</v>
       </c>
       <c r="C397">
-        <v>0</v>
+        <v>8640</v>
       </c>
       <c r="D397">
+        <v>0</v>
+      </c>
+      <c r="E397">
         <v>0</v>
       </c>
       <c r="F397">
@@ -9091,26 +9103,29 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Ações Socioculturais em Espaços Cemiteriais</t>
+          <t>Manutenção e Operação da UniCEU</t>
         </is>
       </c>
       <c r="B398">
         <v>2022</v>
       </c>
       <c r="C398">
-        <v>0</v>
+        <v>4786.95</v>
       </c>
       <c r="D398">
-        <v>0</v>
+        <v>4786.95</v>
+      </c>
+      <c r="E398">
+        <v>1</v>
       </c>
       <c r="F398">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Ações de Pronto Atendimento Socioassistencial</t>
+          <t>Ampliação, Reforma e Requalificação de Edificação da Câmara Municipal de São Paulo</t>
         </is>
       </c>
       <c r="B399">
@@ -9129,7 +9144,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Ações de Vigilância Socioassistencial</t>
+          <t>Apoio e Suporte Técnico para o Desenvolvimento de Ações Pertinentes à Fiscalização e Escrituração de Certificados de Potencial Adicional de Construção - CEPACs</t>
         </is>
       </c>
       <c r="B400">
@@ -9148,7 +9163,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Comercialização de Artigos do Serviço Funerário</t>
+          <t>Apoio às Ações Municipais de Turismo</t>
         </is>
       </c>
       <c r="B401">
@@ -9167,7 +9182,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Educação Permanente dos Trabalhadores do SUAS</t>
+          <t>Aquisição e Construção de Prédios Administrativos</t>
         </is>
       </c>
       <c r="B402">
@@ -9186,7 +9201,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Cemitério</t>
+          <t>Ações Socioculturais em Espaços Cemiteriais</t>
         </is>
       </c>
       <c r="B403">
@@ -9205,7 +9220,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Crematório</t>
+          <t>Ações de Pronto Atendimento Socioassistencial</t>
         </is>
       </c>
       <c r="B404">
@@ -9224,7 +9239,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Velório</t>
+          <t>Ações de Vigilância Socioassistencial</t>
         </is>
       </c>
       <c r="B405">
@@ -9243,7 +9258,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Transportes Fúnebres</t>
+          <t>Educação Permanente dos Trabalhadores do SUAS</t>
         </is>
       </c>
       <c r="B406">
